--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13T20:47:43Z</t>
+          <t>2026-09-13T23:08:24Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13T20:47:43Z · 561 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-09-13T23:08:24Z · 561 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -780,17 +780,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - english.nepalnews.com</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood english.nepalnews.com</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>theclimatewatch.com</t>
+          <t>The Climate Watch</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - theclimatewatch.com</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - The Climate Watch</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood theclimatewatch.com</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood The Climate Watch</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -1389,42 +1389,42 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>b053f134835909ae</t>
+          <t>70ed83c991b2efeb</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-10T20:50:24Z</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Family cremates four after hope of return fades - Khabarhub</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Family cremates four after hope of return fades Khabarhub</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>70ed83c991b2efeb</t>
+          <t>6607210a4b69eff4</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1451,32 +1451,32 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T20:50:24Z</t>
+          <t>2026-09-11T04:36:53Z</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims The Rising Nepal</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>6607210a4b69eff4</t>
+          <t>8a39d2b6e977257c</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1503,32 +1503,32 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T04:36:53Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - ReliefWeb</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 ReliefWeb</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>8a39d2b6e977257c</t>
+          <t>f0d257c13960eb9d</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - Khabarhub</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims Khabarhub</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>f0d257c13960eb9d</t>
+          <t>cbec98d65b37335f</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1617,22 +1617,22 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
+          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
+          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1649,42 +1649,42 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>cbec98d65b37335f</t>
+          <t>c47a04aef0c20457</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood - myRepublica</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood myRepublica</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>c47a04aef0c20457</t>
+          <t>61acaf3888b70b31</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1721,22 +1721,22 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far - The Rising Nepal</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far The Rising Nepal</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1753,7 +1753,7 @@
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>61acaf3888b70b31</t>
+          <t>43b44149e2b39c71</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1763,32 +1763,32 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far - The Rising Nepal</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far The Rising Nepal</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>43b44149e2b39c71</t>
+          <t>d8002ad908db19e7</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-10T23:08:55Z</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - english.nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing english.nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>d8002ad908db19e7</t>
+          <t>879325423fb38443</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1867,32 +1867,32 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T23:08:55Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - Khabarhub</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far Khabarhub</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>879325423fb38443</t>
+          <t>6331e8a91369eb2f</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 - Khabarhub</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 Khabarhub</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1961,7 +1961,7 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>6331e8a91369eb2f</t>
+          <t>8759263a9a2778c7</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1981,22 +1981,22 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 - Khabarhub</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood - Khabarhub</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 Khabarhub</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood Khabarhub</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>8759263a9a2778c7</t>
+          <t>f67225d3b28943ab</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2023,32 +2023,32 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood - Khabarhub</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood Khabarhub</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>f67225d3b28943ab</t>
+          <t>ae8d167a621c7582</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - english.nepalnews.com</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 - Khabarhub</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing english.nepalnews.com</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 Khabarhub</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>ae8d167a621c7582</t>
+          <t>d160ec5375994c91</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 - Khabarhub</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - Khabarhub</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 Khabarhub</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage Khabarhub</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>d160ec5375994c91</t>
+          <t>c3994b48332f5978</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2179,32 +2179,32 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-10T04:39:43Z</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - Khabarhub</t>
+          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage Khabarhub</t>
+          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>c3994b48332f5978</t>
+          <t>423e61ff0037981d</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -2231,32 +2231,32 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T04:39:43Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - The Rising Nepal</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk The Rising Nepal</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>423e61ff0037981d</t>
+          <t>9496e16a0b0d46ea</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2283,32 +2283,32 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-10T16:22:37Z</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>OCHA</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - The Rising Nepal</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - OCHA</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk The Rising Nepal</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) OCHA</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2325,42 +2325,42 @@
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>9496e16a0b0d46ea</t>
+          <t>d33843b64ba6980a</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T16:22:37Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>OCHA</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - OCHA</t>
+          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions - Ekantipur</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) OCHA</t>
+          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions Ekantipur</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPeFNRbzlyLVdZS1hfQk1idWFiOGc1TV94VjBWMjB5RzZvWUhJM0g1V19CMzdmT29IbDhpSHl5cGVxazl5My14UTNxN3Nwd2l3dXV5SE1ZNExmVDJqNXlIclhyTFhaWFlPaDJYYVhFc0dNYXlvbUZzcGlDRnBVaGJEMTdCeFpWaXF6eF81N25LcHM1TE1aRnZuY3dHcjg1Y2dkSnY3czcwVWk2M0FLQUc3ak84U21lTVprN0VaSDJNUG9IWERaSTF2U2pqS3EzZ21iaWhkYkZDMVYtZ2tM?oc=5</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPeFNRbzlyLVdZS1hfQk1idWFiOGc1TV94VjBWMjB5RzZvWUhJM0g1V19CMzdmT29IbDhpSHl5cGVxazl5My14UTNxN3Nwd2l3dXV5SE1ZNExmVDJqNXlIclhyTFhaWFlPaDJYYVhFc0dNYXlvbUZzcGlDRnBVaGJEMTdCeFpWaXF6eF81N25LcHM1TE1aRnZuY3dHcjg1Y2dkSnY3czcwVWk2M0FLQUc3ak84U21lTVprN0VaSDJNUG9IWERaSTF2U2pqS3EzZ21iaWhkYkZDMVYtZ2tM?oc=5</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>d33843b64ba6980a</t>
+          <t>078323d2f25a50d5</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -2387,32 +2387,32 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions - ekantipur.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions ekantipur.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPeFNRbzlyLVdZS1hfQk1idWFiOGc1TV94VjBWMjB5RzZvWUhJM0g1V19CMzdmT29IbDhpSHl5cGVxazl5My14UTNxN3Nwd2l3dXV5SE1ZNExmVDJqNXlIclhyTFhaWFlPaDJYYVhFc0dNYXlvbUZzcGlDRnBVaGJEMTdCeFpWaXF6eF81N25LcHM1TE1aRnZuY3dHcjg1Y2dkSnY3czcwVWk2M0FLQUc3ak84U21lTVprN0VaSDJNUG9IWERaSTF2U2pqS3EzZ21iaWhkYkZDMVYtZ2tM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPeFNRbzlyLVdZS1hfQk1idWFiOGc1TV94VjBWMjB5RzZvWUhJM0g1V19CMzdmT29IbDhpSHl5cGVxazl5My14UTNxN3Nwd2l3dXV5SE1ZNExmVDJqNXlIclhyTFhaWFlPaDJYYVhFc0dNYXlvbUZzcGlDRnBVaGJEMTdCeFpWaXF6eF81N25LcHM1TE1aRnZuY3dHcjg1Y2dkSnY3czcwVWk2M0FLQUc3ak84U21lTVprN0VaSDJNUG9IWERaSTF2U2pqS3EzZ21iaWhkYkZDMVYtZ2tM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2429,7 +2429,7 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>078323d2f25a50d5</t>
+          <t>4aa35d4139dfe46a</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -2444,27 +2444,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>4aa35d4139dfe46a</t>
+          <t>2224bc266e8af095</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -2496,27 +2496,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning - Nepalnews.com</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning Nepalnews.com</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQalJQY29weG5BcnFRb2ZqNzhWcTVBYmpjM2xOckFxTXhWWEtGTUhZSndrZzA4ZmNNNVE0R1YxemRYTXE0cVZLdzN2SnBtMlRvQ25UU2hFWDZsZ0p3aEk1ZmxNeFRITENfV1BidXZYeUs4MnBZY3AxUFZsNnZTekVPX1hxeTU3VWFQbzh2aWZKSEd4Q2tyVXF2ckxRTVRpSFBLTWppZnBvU2NlSk9NdEZvODB3?oc=5</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQalJQY29weG5BcnFRb2ZqNzhWcTVBYmpjM2xOckFxTXhWWEtGTUhZSndrZzA4ZmNNNVE0R1YxemRYTXE0cVZLdzN2SnBtMlRvQ25UU2hFWDZsZ0p3aEk1ZmxNeFRITENfV1BidXZYeUs4MnBZY3AxUFZsNnZTekVPX1hxeTU3VWFQbzh2aWZKSEd4Q2tyVXF2ckxRTVRpSFBLTWppZnBvU2NlSk9NdEZvODB3?oc=5</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2224bc266e8af095</t>
+          <t>7b6d21a31b902d56</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -2543,32 +2543,32 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Everest Chronicle</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning - english.nepalnews.com</t>
+          <t>Rasuwa flood death toll rises to 1,357, more than 5,300 missing - Everest Chronicle</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning english.nepalnews.com</t>
+          <t>Rasuwa flood death toll rises to 1,357, more than 5,300 missing Everest Chronicle</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQalJQY29weG5BcnFRb2ZqNzhWcTVBYmpjM2xOckFxTXhWWEtGTUhZSndrZzA4ZmNNNVE0R1YxemRYTXE0cVZLdzN2SnBtMlRvQ25UU2hFWDZsZ0p3aEk1ZmxNeFRITENfV1BidXZYeUs4MnBZY3AxUFZsNnZTekVPX1hxeTU3VWFQbzh2aWZKSEd4Q2tyVXF2ckxRTVRpSFBLTWppZnBvU2NlSk9NdEZvODB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDN4MnNNS25TaXdHR09xbnp1VWNGQjlfbmRhZHRLTnBGb29KZmh4c1g2dXB1bG51X29NemM3dS1vdE1zOVdabDJoVEQtQnYteGVoUHI5VzAwbkJOQklPWklFRUxQMmR4SWZYQ0pGbVJGeTVVZkU2bk9ZMV9HcWxRNnZ3aUJSSmdkNnhuSDQteTd4M2s?oc=5</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQalJQY29weG5BcnFRb2ZqNzhWcTVBYmpjM2xOckFxTXhWWEtGTUhZSndrZzA4ZmNNNVE0R1YxemRYTXE0cVZLdzN2SnBtMlRvQ25UU2hFWDZsZ0p3aEk1ZmxNeFRITENfV1BidXZYeUs4MnBZY3AxUFZsNnZTekVPX1hxeTU3VWFQbzh2aWZKSEd4Q2tyVXF2ckxRTVRpSFBLTWppZnBvU2NlSk9NdEZvODB3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDN4MnNNS25TaXdHR09xbnp1VWNGQjlfbmRhZHRLTnBGb29KZmh4c1g2dXB1bG51X29NemM3dS1vdE1zOVdabDJoVEQtQnYteGVoUHI5VzAwbkJOQklPWklFRUxQMmR4SWZYQ0pGbVJGeTVVZkU2bk9ZMV9HcWxRNnZ3aUJSSmdkNnhuSDQteTd4M2s?oc=5</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -2585,7 +2585,7 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>7b6d21a31b902d56</t>
+          <t>e4d9c4185afc34a4</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -2595,32 +2595,32 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Everest Chronicle</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll rises to 1,357, more than 5,300 missing - Everest Chronicle</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll rises to 1,357, more than 5,300 missing Everest Chronicle</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDN4MnNNS25TaXdHR09xbnp1VWNGQjlfbmRhZHRLTnBGb29KZmh4c1g2dXB1bG51X29NemM3dS1vdE1zOVdabDJoVEQtQnYteGVoUHI5VzAwbkJOQklPWklFRUxQMmR4SWZYQ0pGbVJGeTVVZkU2bk9ZMV9HcWxRNnZ3aUJSSmdkNnhuSDQteTd4M2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxNeDN4MnNNS25TaXdHR09xbnp1VWNGQjlfbmRhZHRLTnBGb29KZmh4c1g2dXB1bG51X29NemM3dS1vdE1zOVdabDJoVEQtQnYteGVoUHI5VzAwbkJOQklPWklFRUxQMmR4SWZYQ0pGbVJGeTVVZkU2bk9ZMV9HcWxRNnZ3aUJSSmdkNnhuSDQteTd4M2s?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>e4d9c4185afc34a4</t>
+          <t>3cce15282f424799</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -2647,32 +2647,32 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSXQxbnBuVjd5ckN3Wk0tdFU5WVc1LXlwQUdtN2lNY3pLNFU2VVRnNFhTLXFEdl9pczBxU1ZoU2JMMTB3b01zTFVTblY0NGJ0MFVRUkhCbDdERTl4NGdmNUJlZlJWX0Qxb3JibVdSYUtjdndLbnNzRmRaNjAzbUhIQ0dYSWxxczFvb0xEa0NqQ2JjNzFPTjhQMHhsd0Y1WU55d0pSYk4wUmdodw?oc=5</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSXQxbnBuVjd5ckN3Wk0tdFU5WVc1LXlwQUdtN2lNY3pLNFU2VVRnNFhTLXFEdl9pczBxU1ZoU2JMMTB3b01zTFVTblY0NGJ0MFVRUkhCbDdERTl4NGdmNUJlZlJWX0Qxb3JibVdSYUtjdndLbnNzRmRaNjAzbUhIQ0dYSWxxczFvb0xEa0NqQ2JjNzFPTjhQMHhsd0Y1WU55d0pSYk4wUmdodw?oc=5</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2689,7 +2689,7 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>3cce15282f424799</t>
+          <t>ae9fa86dafccec71</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -2704,27 +2704,27 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing - english.nepalnews.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing english.nepalnews.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSXQxbnBuVjd5ckN3Wk0tdFU5WVc1LXlwQUdtN2lNY3pLNFU2VVRnNFhTLXFEdl9pczBxU1ZoU2JMMTB3b01zTFVTblY0NGJ0MFVRUkhCbDdERTl4NGdmNUJlZlJWX0Qxb3JibVdSYUtjdndLbnNzRmRaNjAzbUhIQ0dYSWxxczFvb0xEa0NqQ2JjNzFPTjhQMHhsd0Y1WU55d0pSYk4wUmdodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSXQxbnBuVjd5ckN3Wk0tdFU5WVc1LXlwQUdtN2lNY3pLNFU2VVRnNFhTLXFEdl9pczBxU1ZoU2JMMTB3b01zTFVTblY0NGJ0MFVRUkhCbDdERTl4NGdmNUJlZlJWX0Qxb3JibVdSYUtjdndLbnNzRmRaNjAzbUhIQ0dYSWxxczFvb0xEa0NqQ2JjNzFPTjhQMHhsd0Y1WU55d0pSYk4wUmdodw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2741,42 +2741,42 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>ae9fa86dafccec71</t>
+          <t>5ed1f2577c7b1fdc</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - english.nepalnews.com</t>
+          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims english.nepalnews.com</t>
+          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1qWGNJZXhMY01wa2ZJUlgxSjBCNXBlSExTNUtydExaLXpnRE5JWXFJRkJOV1JSeG5BempKaU02RlM5Qmlnd0kzWEZUQjJBWFdrQXNDMkYyenA?oc=5</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1qWGNJZXhMY01wa2ZJUlgxSjBCNXBlSExTNUtydExaLXpnRE5JWXFJRkJOV1JSeG5BempKaU02RlM5Qmlnd0kzWEZUQjJBWFdrQXNDMkYyenA?oc=5</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>3362db09970c68c5</t>
+          <t>58dd4f75cb9b6184</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,293 - Khabarhub</t>
+          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board - Khabarhub</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,293 Khabarhub</t>
+          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board Khabarhub</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1vWU1zUG5BMEFBVnhOZE9mWjVRMUM4Q1ZMVG9jMS1sOC0wd0owOWZ6NnFXVUJPNmpRcnE3RmZ4eVhJQXZtWTFnX1JYazA1ZUlHT3pIeXplbEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE41OHotamQtMmF6bXNOVEFiam5aeThWTnNWRVo0V2xTY2V6UXZjZVRxNVdJN1FEakRJX0g2NVhXVjRBSnlMUlh6UXViZDZndjdoYVVnVDNTdV8?oc=5</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1vWU1zUG5BMEFBVnhOZE9mWjVRMUM4Q1ZMVG9jMS1sOC0wd0owOWZ6NnFXVUJPNmpRcnE3RmZ4eVhJQXZtWTFnX1JYazA1ZUlHT3pIeXplbEE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE41OHotamQtMmF6bXNOVEFiam5aeThWTnNWRVo0V2xTY2V6UXZjZVRxNVdJN1FEakRJX0g2NVhXVjRBSnlMUlh6UXViZDZndjdoYVVnVDNTdV8?oc=5</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>5ed1f2577c7b1fdc</t>
+          <t>c4d67c4602739f5e</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2860,27 +2860,27 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood - Khabarhub</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - Nepalnews.com</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood Khabarhub</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact Nepalnews.com</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1qWGNJZXhMY01wa2ZJUlgxSjBCNXBlSExTNUtydExaLXpnRE5JWXFJRkJOV1JSeG5BempKaU02RlM5Qmlnd0kzWEZUQjJBWFdrQXNDMkYyenA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1qWGNJZXhMY01wa2ZJUlgxSjBCNXBlSExTNUtydExaLXpnRE5JWXFJRkJOV1JSeG5BempKaU02RlM5Qmlnd0kzWEZUQjJBWFdrQXNDMkYyenA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -2897,7 +2897,7 @@
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>58dd4f75cb9b6184</t>
+          <t>76ee47ba59686ba1</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -2912,27 +2912,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board - Khabarhub</t>
+          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them - Ratopati</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board Khabarhub</t>
+          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them Ratopati</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE41OHotamQtMmF6bXNOVEFiam5aeThWTnNWRVo0V2xTY2V6UXZjZVRxNVdJN1FEakRJX0g2NVhXVjRBSnlMUlh6UXViZDZndjdoYVVnVDNTdV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE41OHotamQtMmF6bXNOVEFiam5aeThWTnNWRVo0V2xTY2V6UXZjZVRxNVdJN1FEakRJX0g2NVhXVjRBSnlMUlh6UXViZDZndjdoYVVnVDNTdV8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>c4d67c4602739f5e</t>
+          <t>193f6bc71c9aab53</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2959,32 +2959,32 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - english.nepalnews.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact english.nepalnews.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>76ee47ba59686ba1</t>
+          <t>66743f8886e880aa</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -3011,32 +3011,32 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-13T11:48:33Z</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them - Ratopati</t>
+          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas - myRepublica</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them Ratopati</t>
+          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas myRepublica</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3053,7 +3053,7 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>193f6bc71c9aab53</t>
+          <t>a392404b268ef048</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - Khabarhub</t>
+          <t>1,355 bodies recovered, 4,996 still unaccounted for in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood Khabarhub</t>
+          <t>1,355 bodies recovered, 4,996 still unaccounted for in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdUZFMV9KQ0R1azJlb0x1RXFCLVpOc3NOUHR6bVdzZzZoVzZmUlFRa3h2MGJicmxONEFKY1o0Y0xaQ2p4QXVEUkJjVFlYVkZ5dG1WS3RyNXZVZ3Q4Rjhjb19EMWhtbU12QmZYQjhudng4SHctRVZJcnFULWFKLVpBZjVob0taMDlZTnJ0RTRhU3VuWFJrT05Qb042VzB3emZJckd5OTRFa2JFYjE3Y1c5SEZnQV9oQ2JOdVFwX215d2U?oc=5</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdUZFMV9KQ0R1azJlb0x1RXFCLVpOc3NOUHR6bVdzZzZoVzZmUlFRa3h2MGJicmxONEFKY1o0Y0xaQ2p4QXVEUkJjVFlYVkZ5dG1WS3RyNXZVZ3Q4Rjhjb19EMWhtbU12QmZYQjhudng4SHctRVZJcnFULWFKLVpBZjVob0taMDlZTnJ0RTRhU3VuWFJrT05Qb042VzB3emZJckd5OTRFa2JFYjE3Y1c5SEZnQV9oQ2JOdVFwX215d2U?oc=5</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>66743f8886e880aa</t>
+          <t>4a5b39507a06f462</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -3115,32 +3115,32 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T11:48:33Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas - myRepublica</t>
+          <t>Rasuwa flood death toll reaches 1,355 - Khabarhub</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas myRepublica</t>
+          <t>Rasuwa flood death toll reaches 1,355 Khabarhub</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9LNDFPbWlROTdsS2tMMDdKTG9hNGVsTjJpSmdWZXhUV1dKaUpweVp5NzkzYVNKcGZ3ekZmdV9aRHpfRWRja2tOS3JFaVg3NW5UX0k5Z1JtS2o?oc=5</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9LNDFPbWlROTdsS2tMMDdKTG9hNGVsTjJpSmdWZXhUV1dKaUpweVp5NzkzYVNKcGZ3ekZmdV9aRHpfRWRja2tOS3JFaVg3NW5UX0k5Z1JtS2o?oc=5</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>a392404b268ef048</t>
+          <t>87b5592d2c58bbd9</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -3172,27 +3172,27 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>himalmag.com</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1,355 bodies recovered, 4,996 still unaccounted for in Bhotekoshi flood - myRepublica</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - himalmag.com</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>1,355 bodies recovered, 4,996 still unaccounted for in Bhotekoshi flood myRepublica</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world himalmag.com</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdUZFMV9KQ0R1azJlb0x1RXFCLVpOc3NOUHR6bVdzZzZoVzZmUlFRa3h2MGJicmxONEFKY1o0Y0xaQ2p4QXVEUkJjVFlYVkZ5dG1WS3RyNXZVZ3Q4Rjhjb19EMWhtbU12QmZYQjhudng4SHctRVZJcnFULWFKLVpBZjVob0taMDlZTnJ0RTRhU3VuWFJrT05Qb042VzB3emZJckd5OTRFa2JFYjE3Y1c5SEZnQV9oQ2JOdVFwX215d2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdUZFMV9KQ0R1azJlb0x1RXFCLVpOc3NOUHR6bVdzZzZoVzZmUlFRa3h2MGJicmxONEFKY1o0Y0xaQ2p4QXVEUkJjVFlYVkZ5dG1WS3RyNXZVZ3Q4Rjhjb19EMWhtbU12QmZYQjhudng4SHctRVZJcnFULWFKLVpBZjVob0taMDlZTnJ0RTRhU3VuWFJrT05Qb042VzB3emZJckd5OTRFa2JFYjE3Y1c5SEZnQV9oQ2JOdVFwX215d2U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>4a5b39507a06f462</t>
+          <t>30a8b09171137a8d</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -3219,32 +3219,32 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,355 - Khabarhub</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,355 Khabarhub</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9LNDFPbWlROTdsS2tMMDdKTG9hNGVsTjJpSmdWZXhUV1dKaUpweVp5NzkzYVNKcGZ3ekZmdV9aRHpfRWRja2tOS3JFaVg3NW5UX0k5Z1JtS2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9LNDFPbWlROTdsS2tMMDdKTG9hNGVsTjJpSmdWZXhUV1dKaUpweVp5NzkzYVNKcGZ3ekZmdV9aRHpfRWRja2tOS3JFaVg3NW5UX0k5Z1JtS2o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3261,42 +3261,42 @@
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>87b5592d2c58bbd9</t>
+          <t>40bcbff45ef246f3</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Himal Southasian</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Himal Southasian</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Himal Southasian</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3313,42 +3313,42 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>30a8b09171137a8d</t>
+          <t>ad88346da6844b20</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - Khabarhub</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world Khabarhub</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>40bcbff45ef246f3</t>
+          <t>bce011217f19bc6a</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - Khabarhub</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - Nepalnews.com</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital Khabarhub</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear Nepalnews.com</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>ad88346da6844b20</t>
+          <t>e7206a6f81806ce7</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - Khabarhub</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world Khabarhub</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>bce011217f19bc6a</t>
+          <t>9e0a27039da6e2ed</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -3479,32 +3479,32 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - english.nepalnews.com</t>
+          <t>Bhotekoshi flood: 3,071 people remain unaccounted for in Rasuwa - The Rising Nepal</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear english.nepalnews.com</t>
+          <t>Bhotekoshi flood: 3,071 people remain unaccounted for in Rasuwa The Rising Nepal</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BeTRIRGx0YUNJZlhzSkdsZWVJdS1Tbmhnd1JKN3lxOXY2azZlaVlFd19OLWdoRktQMmhZYUdnNkx2ZlhVYlEwME9LMzFoTHNQ?oc=5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BeTRIRGx0YUNJZlhzSkdsZWVJdS1Tbmhnd1JKN3lxOXY2azZlaVlFd19OLWdoRktQMmhZYUdnNkx2ZlhVYlEwME9LMzFoTHNQ?oc=5</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>e7206a6f81806ce7</t>
+          <t>423212fdf3d9e939</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - english.nepalnews.com</t>
+          <t>Roads washed away by Bhotekoshi Flood being rebuilt - myRepublica</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ english.nepalnews.com</t>
+          <t>Roads washed away by Bhotekoshi Flood being rebuilt myRepublica</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>9e0a27039da6e2ed</t>
+          <t>c5cc47b406fd1b88</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 3,071 people remain unaccounted for in Rasuwa - The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - Khabarhub</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 3,071 people remain unaccounted for in Rasuwa The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification Khabarhub</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BeTRIRGx0YUNJZlhzSkdsZWVJdS1Tbmhnd1JKN3lxOXY2azZlaVlFd19OLWdoRktQMmhZYUdnNkx2ZlhVYlEwME9LMzFoTHNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BeTRIRGx0YUNJZlhzSkdsZWVJdS1Tbmhnd1JKN3lxOXY2azZlaVlFd19OLWdoRktQMmhZYUdnNkx2ZlhVYlEwME9LMzFoTHNQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>423212fdf3d9e939</t>
+          <t>1c2c3ae0634abfb3</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3635,32 +3635,32 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Roads washed away by Bhotekoshi Flood being rebuilt - myRepublica</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Roads washed away by Bhotekoshi Flood being rebuilt myRepublica</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>c5cc47b406fd1b88</t>
+          <t>d1cfb76c84a4a44d</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - Khabarhub</t>
+          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged - Nepalnews.com</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification Khabarhub</t>
+          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged Nepalnews.com</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>1c2c3ae0634abfb3</t>
+          <t>47075b2c0944a15a</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-06T04:35:51Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - Khabarhub</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - Khabarhub</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital Khabarhub</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts Khabarhub</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,42 +3781,42 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>d1cfb76c84a4a44d</t>
+          <t>62c63745290773df</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged - english.nepalnews.com</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged english.nepalnews.com</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,42 +3833,42 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>47075b2c0944a15a</t>
+          <t>d74bb8f9671ee40d</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T04:35:51Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - Khabarhub</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts Khabarhub</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>62c63745290773df</t>
+          <t>c54270a94bbf8787</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -3895,32 +3895,32 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood update: Death toll reaches 1,344 - Khabarhub</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood update: Death toll reaches 1,344 Khabarhub</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE92R1NmanViZkRtbVowQUhsVWMyRUtQekpseUY1eVkzMTF0MDJ0Y3dCMzI0bzhfRW0xM3lFUHJ0c0JoWXcwcEJlY3pRZ283MVZHMnlCZ3FEN00?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE92R1NmanViZkRtbVowQUhsVWMyRUtQekpseUY1eVkzMTF0MDJ0Y3dCMzI0bzhfRW0xM3lFUHJ0c0JoWXcwcEJlY3pRZ283MVZHMnlCZ3FEN00?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>d74bb8f9671ee40d</t>
+          <t>d8f9de0510371c12</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>d8f9de0510371c12</t>
+          <t>d14614d3e2803615</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -3999,32 +3999,32 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
+          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing - The Rising Nepal</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
+          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing The Rising Nepal</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>c54270a94bbf8787</t>
+          <t>f7c2e6ce3f764d01</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -4051,32 +4051,32 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood update: Death toll reaches 1,344 - Khabarhub</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood update: Death toll reaches 1,344 Khabarhub</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE92R1NmanViZkRtbVowQUhsVWMyRUtQekpseUY1eVkzMTF0MDJ0Y3dCMzI0bzhfRW0xM3lFUHJ0c0JoWXcwcEJlY3pRZ283MVZHMnlCZ3FEN00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE92R1NmanViZkRtbVowQUhsVWMyRUtQekpseUY1eVkzMTF0MDJ0Y3dCMzI0bzhfRW0xM3lFUHJ0c0JoWXcwcEJlY3pRZ283MVZHMnlCZ3FEN00?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>d14614d3e2803615</t>
+          <t>848a39f095c7463c</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
@@ -4108,27 +4108,27 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>PAMIR TIMES</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing - The Rising Nepal</t>
+          <t>Nepal’s Rasuwa Flood: A Warning for Pakistan’s Mountain Communities - PAMIR TIMES</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing The Rising Nepal</t>
+          <t>Nepal’s Rasuwa Flood: A Warning for Pakistan’s Mountain Communities PAMIR TIMES</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRkUwb2RxaU1jaV9nUlp2Y1FZRngxZnljaG8wTERkaVJ3a2c3MDA4REYwOWpMMnJad2t0Ym92bmZKMThNRnBvOUo4Z0pJamFHMi1NeU12bkhCeENlNmZ5QTBfZFpPeUpLZFZGOWlpamZzMnZ4WkhtZkpDcy02U0ZNQmxfdjh4WTQtWU5wcThjWVYxSDZDQjFuRXpqYUJfLUE1?oc=5</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxNRkUwb2RxaU1jaV9nUlp2Y1FZRngxZnljaG8wTERkaVJ3a2c3MDA4REYwOWpMMnJad2t0Ym92bmZKMThNRnBvOUo4Z0pJamFHMi1NeU12bkhCeENlNmZ5QTBfZFpPeUpLZFZGOWlpamZzMnZ4WkhtZkpDcy02U0ZNQmxfdjh4WTQtWU5wcThjWVYxSDZDQjFuRXpqYUJfLUE1?oc=5</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4145,17 +4145,17 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>f7c2e6ce3f764d01</t>
+          <t>69c5156e1e556a67</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -4165,22 +4165,22 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4197,42 +4197,42 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>848a39f095c7463c</t>
+          <t>2c151d9781807ab6</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>PAMIR TIMES</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa Flood: A Warning for Pakistan’s Mountain Communities - PAMIR TIMES</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa Flood: A Warning for Pakistan’s Mountain Communities PAMIR TIMES</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRkUwb2RxaU1jaV9nUlp2Y1FZRngxZnljaG8wTERkaVJ3a2c3MDA4REYwOWpMMnJad2t0Ym92bmZKMThNRnBvOUo4Z0pJamFHMi1NeU12bkhCeENlNmZ5QTBfZFpPeUpLZFZGOWlpamZzMnZ4WkhtZkpDcy02U0ZNQmxfdjh4WTQtWU5wcThjWVYxSDZDQjFuRXpqYUJfLUE1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxNRkUwb2RxaU1jaV9nUlp2Y1FZRngxZnljaG8wTERkaVJ3a2c3MDA4REYwOWpMMnJad2t0Ym92bmZKMThNRnBvOUo4Z0pJamFHMi1NeU12bkhCeENlNmZ5QTBfZFpPeUpLZFZGOWlpamZzMnZ4WkhtZkpDcy02U0ZNQmxfdjh4WTQtWU5wcThjWVYxSDZDQjFuRXpqYUJfLUE1?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2c151d9781807ab6</t>
+          <t>258c222aa846d3dc</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -4259,32 +4259,32 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>258c222aa846d3dc</t>
+          <t>6c94171fc3f8e00c</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>6c94171fc3f8e00c</t>
+          <t>65516a3eea842847</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>65516a3eea842847</t>
+          <t>0370f1426397bded</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>0370f1426397bded</t>
+          <t>a28e8c7c678ad549</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
+          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
+          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQcGVldmo1RExQTEswak82T0RsWEU4Y2VkdG1MR0NTdjk0aGs3bjk0YU1wbEU0OWJnWEkyRGRDSGlPRDlNbldQMXB0QW5xNDA1NUpmZm1YM29ucjl1UVBkQ1VQTVdvLTFHaGJFWk93eWYybXdKSnBhTkZkN2RKWGRSamNIbHh1eFJySTR6TkZnQnFlbktyZGVsTHZreTZrRFNHc29WbVZucm1zRXItSGtPQWZadVQ1UQ?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQcGVldmo1RExQTEswak82T0RsWEU4Y2VkdG1MR0NTdjk0aGs3bjk0YU1wbEU0OWJnWEkyRGRDSGlPRDlNbldQMXB0QW5xNDA1NUpmZm1YM29ucjl1UVBkQ1VQTVdvLTFHaGJFWk93eWYybXdKSnBhTkZkN2RKWGRSamNIbHh1eFJySTR6TkZnQnFlbktyZGVsTHZreTZrRFNHc29WbVZucm1zRXItSGtPQWZadVQ1UQ?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>a28e8c7c678ad549</t>
+          <t>7ac8c48d235b6902</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -4519,32 +4519,32 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-05T22:53:38Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing - english.nepalnews.com</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing english.nepalnews.com</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQcGVldmo1RExQTEswak82T0RsWEU4Y2VkdG1MR0NTdjk0aGs3bjk0YU1wbEU0OWJnWEkyRGRDSGlPRDlNbldQMXB0QW5xNDA1NUpmZm1YM29ucjl1UVBkQ1VQTVdvLTFHaGJFWk93eWYybXdKSnBhTkZkN2RKWGRSamNIbHh1eFJySTR6TkZnQnFlbktyZGVsTHZreTZrRFNHc29WbVZucm1zRXItSGtPQWZadVQ1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQcGVldmo1RExQTEswak82T0RsWEU4Y2VkdG1MR0NTdjk0aGs3bjk0YU1wbEU0OWJnWEkyRGRDSGlPRDlNbldQMXB0QW5xNDA1NUpmZm1YM29ucjl1UVBkQ1VQTVdvLTFHaGJFWk93eWYybXdKSnBhTkZkN2RKWGRSamNIbHh1eFJySTR6TkZnQnFlbktyZGVsTHZreTZrRFNHc29WbVZucm1zRXItSGtPQWZadVQ1UQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>7ac8c48d235b6902</t>
+          <t>b80549513c064b0f</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T22:53:38Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>b80549513c064b0f</t>
+          <t>8810e59b1c1927f1</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - ekantipur.com</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood ekantipur.com</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4665,42 +4665,42 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>8810e59b1c1927f1</t>
+          <t>c52a95edc1229710</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-03T23:16:04Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>nepyork</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - ReliefWeb</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 ReliefWeb</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>c52a95edc1229710</t>
+          <t>5f76706cec031b28</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T23:16:04Z</t>
+          <t>2026-09-08T23:22:50Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>nepyork</t>
+          <t>FM Bharat</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - FM Bharat</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims FM Bharat</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>5f76706cec031b28</t>
+          <t>06e9d4415d0f0371</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T23:22:50Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>FM Bharat</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - FM Bharat</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims FM Bharat</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>06e9d4415d0f0371</t>
+          <t>af5a4a18108fca1c</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - ekantipur.com</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? ekantipur.com</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors The Kathmandu Post</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4873,42 +4873,42 @@
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>af5a4a18108fca1c</t>
+          <t>b9c42cfdd4afcb95</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-02T16:32:47Z</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - The Kathmandu Post</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - The Times of India</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors The Kathmandu Post</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September The Times of India</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQVW5ROHlXVElaLVdLXzE0OW9aSmhhMnAyd3lZMnlPcUt4dVdiUEQ3dTRvcjdYaHFIeHUzLURQX1JfM0M1TjE4M2xCOHJQMk0yMWZLNGtFNVhWa08zRWVkdkNnaDFYa29jMm1yelF3RWxaSERMNGxIRmNXdTZTdzA4VlAzanNjd2NFVmJBUVJyb3Y1UG91aGJ6N2M2YkJwcldyOWNRcmw1dGtNQ0h2N1hnNzNMa2lSaTVtZnN0dmVBRzNILTJWWm1hbHhkSlRtanNDME1IcHFZcWR2VXBGS2hUZlEtbG5XenhiZWZGMkE1T2ZKNkk3LXlMNlR1VGLSAYICQVVfeXFMTUdNb0trcmlWZlZrZXdmZWdUUkhzVDBCcGRId3hJaldZTnJWTzJ0YWIxTXNpNGVUQmkyUWtHVjdBTXM4MktFS08teE1mdlU1a2FheThjNl9tSENKS1BiYmZfUFI0cWx3dnFIWmdSb254Nnh5SEdocWRqdFlQUndIUDBTcFQ0MmN4X1gzelplTzBoaU9pbUtsSzZLSWJFSzltbS1BdjlKS1JRdXNjakhxN2tHNDFvMFk2Smk3VVhBLXEyWXRhWmtPUzFqTXdpX2h4QUp2blRILXhHTHY5NVRfSG5HcUtuMzd4RmVZWTI2cm1lc2pxX2xVaExnTmFVTWdsQ2dB?oc=5</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi_AFBVV95cUxQVW5ROHlXVElaLVdLXzE0OW9aSmhhMnAyd3lZMnlPcUt4dVdiUEQ3dTRvcjdYaHFIeHUzLURQX1JfM0M1TjE4M2xCOHJQMk0yMWZLNGtFNVhWa08zRWVkdkNnaDFYa29jMm1yelF3RWxaSERMNGxIRmNXdTZTdzA4VlAzanNjd2NFVmJBUVJyb3Y1UG91aGJ6N2M2YkJwcldyOWNRcmw1dGtNQ0h2N1hnNzNMa2lSaTVtZnN0dmVBRzNILTJWWm1hbHhkSlRtanNDME1IcHFZcWR2VXBGS2hUZlEtbG5XenhiZWZGMkE1T2ZKNkk3LXlMNlR1VGLSAYICQVVfeXFMTUdNb0trcmlWZlZrZXdmZWdUUkhzVDBCcGRId3hJaldZTnJWTzJ0YWIxTXNpNGVUQmkyUWtHVjdBTXM4MktFS08teE1mdlU1a2FheThjNl9tSENKS1BiYmZfUFI0cWx3dnFIWmdSb254Nnh5SEdocWRqdFlQUndIUDBTcFQ0MmN4X1gzelplTzBoaU9pbUtsSzZLSWJFSzltbS1BdjlKS1JRdXNjakhxN2tHNDFvMFk2Smk3VVhBLXEyWXRhWmtPUzFqTXdpX2h4QUp2blRILXhHTHY5NVRfSG5HcUtuMzd4RmVZWTI2cm1lc2pxX2xVaExnTmFVTWdsQ2dB?oc=5</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>b9c42cfdd4afcb95</t>
+          <t>30695ff7c38a1107</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -4935,32 +4935,32 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T16:32:47Z</t>
+          <t>2026-09-03T21:00:27Z</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - The Times of India</t>
+          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel - Ekantipur</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September The Times of India</t>
+          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel Ekantipur</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQVW5ROHlXVElaLVdLXzE0OW9aSmhhMnAyd3lZMnlPcUt4dVdiUEQ3dTRvcjdYaHFIeHUzLURQX1JfM0M1TjE4M2xCOHJQMk0yMWZLNGtFNVhWa08zRWVkdkNnaDFYa29jMm1yelF3RWxaSERMNGxIRmNXdTZTdzA4VlAzanNjd2NFVmJBUVJyb3Y1UG91aGJ6N2M2YkJwcldyOWNRcmw1dGtNQ0h2N1hnNzNMa2lSaTVtZnN0dmVBRzNILTJWWm1hbHhkSlRtanNDME1IcHFZcWR2VXBGS2hUZlEtbG5XenhiZWZGMkE1T2ZKNkk3LXlMNlR1VGLSAYICQVVfeXFMTUdNb0trcmlWZlZrZXdmZWdUUkhzVDBCcGRId3hJaldZTnJWTzJ0YWIxTXNpNGVUQmkyUWtHVjdBTXM4MktFS08teE1mdlU1a2FheThjNl9tSENKS1BiYmZfUFI0cWx3dnFIWmdSb254Nnh5SEdocWRqdFlQUndIUDBTcFQ0MmN4X1gzelplTzBoaU9pbUtsSzZLSWJFSzltbS1BdjlKS1JRdXNjakhxN2tHNDFvMFk2Smk3VVhBLXEyWXRhWmtPUzFqTXdpX2h4QUp2blRILXhHTHY5NVRfSG5HcUtuMzd4RmVZWTI2cm1lc2pxX2xVaExnTmFVTWdsQ2dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQeThSNEJvM0UyY3ByX2tWOFl1YXo0WFdPR1JlcUN4WUVVb2tRNmp6bXAwYWdObFdGdE9aSE1Qd1ZfTU5GYm92bVdZdlJJOXgyaXc2bFBXZ2haVDU4NE4wYWoyN1Q0X2JhV0tsLS0tOHVWamRVeXU5dWN0enYxTkdZQzB3eHVXOVpEbldlVk5CcWx0M3dwZlJ5ZmI2VXBHUXpGNlRWZHhucUhFa1I1aFdiNEc4YjU4Tzd5RmJMazI0eXNRUE1oZDRPcnoxMFU?oc=5</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi_AFBVV95cUxQVW5ROHlXVElaLVdLXzE0OW9aSmhhMnAyd3lZMnlPcUt4dVdiUEQ3dTRvcjdYaHFIeHUzLURQX1JfM0M1TjE4M2xCOHJQMk0yMWZLNGtFNVhWa08zRWVkdkNnaDFYa29jMm1yelF3RWxaSERMNGxIRmNXdTZTdzA4VlAzanNjd2NFVmJBUVJyb3Y1UG91aGJ6N2M2YkJwcldyOWNRcmw1dGtNQ0h2N1hnNzNMa2lSaTVtZnN0dmVBRzNILTJWWm1hbHhkSlRtanNDME1IcHFZcWR2VXBGS2hUZlEtbG5XenhiZWZGMkE1T2ZKNkk3LXlMNlR1VGLSAYICQVVfeXFMTUdNb0trcmlWZlZrZXdmZWdUUkhzVDBCcGRId3hJaldZTnJWTzJ0YWIxTXNpNGVUQmkyUWtHVjdBTXM4MktFS08teE1mdlU1a2FheThjNl9tSENKS1BiYmZfUFI0cWx3dnFIWmdSb254Nnh5SEdocWRqdFlQUndIUDBTcFQ0MmN4X1gzelplTzBoaU9pbUtsSzZLSWJFSzltbS1BdjlKS1JRdXNjakhxN2tHNDFvMFk2Smk3VVhBLXEyWXRhWmtPUzFqTXdpX2h4QUp2blRILXhHTHY5NVRfSG5HcUtuMzd4RmVZWTI2cm1lc2pxX2xVaExnTmFVTWdsQ2dB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxQeThSNEJvM0UyY3ByX2tWOFl1YXo0WFdPR1JlcUN4WUVVb2tRNmp6bXAwYWdObFdGdE9aSE1Qd1ZfTU5GYm92bVdZdlJJOXgyaXc2bFBXZ2haVDU4NE4wYWoyN1Q0X2JhV0tsLS0tOHVWamRVeXU5dWN0enYxTkdZQzB3eHVXOVpEbldlVk5CcWx0M3dwZlJ5ZmI2VXBHUXpGNlRWZHhucUhFa1I1aFdiNEc4YjU4Tzd5RmJMazI0eXNRUE1oZDRPcnoxMFU?oc=5</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -4977,42 +4977,42 @@
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>30695ff7c38a1107</t>
+          <t>771cf7d139729ca2</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T21:00:27Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>South Asia Network on Dams, Rivers and People</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel - ekantipur.com</t>
+          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? - South Asia Network on Dams, Rivers and People</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel ekantipur.com</t>
+          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? South Asia Network on Dams, Rivers and People</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQeThSNEJvM0UyY3ByX2tWOFl1YXo0WFdPR1JlcUN4WUVVb2tRNmp6bXAwYWdObFdGdE9aSE1Qd1ZfTU5GYm92bVdZdlJJOXgyaXc2bFBXZ2haVDU4NE4wYWoyN1Q0X2JhV0tsLS0tOHVWamRVeXU5dWN0enYxTkdZQzB3eHVXOVpEbldlVk5CcWx0M3dwZlJ5ZmI2VXBHUXpGNlRWZHhucUhFa1I1aFdiNEc4YjU4Tzd5RmJMazI0eXNRUE1oZDRPcnoxMFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPcmxMdWc1aGFYeWlwQ3d1dkQ3SXljVWYtc3RpNi1TQ1BCZnJyam01VVdLWFpXcGJmN1d0TFBIVGs1V2J5dHBUUnFDQmVtYjcxV1djMzhXSlBFUUZXZDliMDdBOWZVQzd6aUtQeHFvVGxyMkZQNTBiVXllVXU5UEdrVi1aQVZPX1NNdjVxRFg2d1B2SmZrN25TTXptWDBBR1lsYnEw?oc=5</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxQeThSNEJvM0UyY3ByX2tWOFl1YXo0WFdPR1JlcUN4WUVVb2tRNmp6bXAwYWdObFdGdE9aSE1Qd1ZfTU5GYm92bVdZdlJJOXgyaXc2bFBXZ2haVDU4NE4wYWoyN1Q0X2JhV0tsLS0tOHVWamRVeXU5dWN0enYxTkdZQzB3eHVXOVpEbldlVk5CcWx0M3dwZlJ5ZmI2VXBHUXpGNlRWZHhucUhFa1I1aFdiNEc4YjU4Tzd5RmJMazI0eXNRUE1oZDRPcnoxMFU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxPcmxMdWc1aGFYeWlwQ3d1dkQ3SXljVWYtc3RpNi1TQ1BCZnJyam01VVdLWFpXcGJmN1d0TFBIVGs1V2J5dHBUUnFDQmVtYjcxV1djMzhXSlBFUUZXZDliMDdBOWZVQzd6aUtQeHFvVGxyMkZQNTBiVXllVXU5UEdrVi1aQVZPX1NNdjVxRFg2d1B2SmZrN25TTXptWDBBR1lsYnEw?oc=5</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>771cf7d139729ca2</t>
+          <t>e3f339dc5e983047</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -5044,27 +5044,27 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>South Asia Network on Dams, Rivers and People</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? - South Asia Network on Dams, Rivers and People</t>
+          <t>Death toll from Bhotekoshi flood reaches 903 - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? South Asia Network on Dams, Rivers and People</t>
+          <t>Death toll from Bhotekoshi flood reaches 903 The Kathmandu Post</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPcmxMdWc1aGFYeWlwQ3d1dkQ3SXljVWYtc3RpNi1TQ1BCZnJyam01VVdLWFpXcGJmN1d0TFBIVGs1V2J5dHBUUnFDQmVtYjcxV1djMzhXSlBFUUZXZDliMDdBOWZVQzd6aUtQeHFvVGxyMkZQNTBiVXllVXU5UEdrVi1aQVZPX1NNdjVxRFg2d1B2SmZrN25TTXptWDBBR1lsYnEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOeTJ1OWMzQTJWOXVzN3dER3RGTXFXcnJ0WUtkNGFheTRQV0ZCMHhlcHo3amlYUnhoM3dTRTRhOUNLZUgycTA4blhHNU4tQWlDdmQzX1hkVEdQNkdVSnV4ZkVjcHIxQTFXTXRaNXZnZWdGUEtuZlJESGtqV3NYc0ZVaG9MX1FiVTBhWjlzOUl5S1BNMmFa?oc=5</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxPcmxMdWc1aGFYeWlwQ3d1dkQ3SXljVWYtc3RpNi1TQ1BCZnJyam01VVdLWFpXcGJmN1d0TFBIVGs1V2J5dHBUUnFDQmVtYjcxV1djMzhXSlBFUUZXZDliMDdBOWZVQzd6aUtQeHFvVGxyMkZQNTBiVXllVXU5UEdrVi1aQVZPX1NNdjVxRFg2d1B2SmZrN25TTXptWDBBR1lsYnEw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilAFBVV95cUxOeTJ1OWMzQTJWOXVzN3dER3RGTXFXcnJ0WUtkNGFheTRQV0ZCMHhlcHo3amlYUnhoM3dTRTRhOUNLZUgycTA4blhHNU4tQWlDdmQzX1hkVEdQNkdVSnV4ZkVjcHIxQTFXTXRaNXZnZWdGUEtuZlJESGtqV3NYc0ZVaG9MX1FiVTBhWjlzOUl5S1BNMmFa?oc=5</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5081,12 +5081,12 @@
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>e3f339dc5e983047</t>
+          <t>19a94ee940668d75</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -5096,27 +5096,27 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 903 - The Kathmandu Post</t>
+          <t>The Bhotekoshi flood | A Himalayan tragedy - The Hindu</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 903 The Kathmandu Post</t>
+          <t>The Bhotekoshi flood | A Himalayan tragedy The Hindu</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOeTJ1OWMzQTJWOXVzN3dER3RGTXFXcnJ0WUtkNGFheTRQV0ZCMHhlcHo3amlYUnhoM3dTRTRhOUNLZUgycTA4blhHNU4tQWlDdmQzX1hkVEdQNkdVSnV4ZkVjcHIxQTFXTXRaNXZnZWdGUEtuZlJESGtqV3NYc0ZVaG9MX1FiVTBhWjlzOUl5S1BNMmFa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNlJSejItQ3FMeVZwNndSYU9ORlA4bVg2b0xKVl9iUmt0RTZqWm94Z1lGakpMc3dSYWhfUGhDdE41aURjUEQ4UDRnU0xFQ2M4VFBMazZGTkxxbnVsc0lVeXBSbUdlSmJ1cVBiUDFkMFZCQU0yRjhKQ2F6bnhfZGk0VVgtd1BTTmw2QjRxRXpMMmlvQTk3OW9fenRMVi11djhF0gGnAUFVX3lxTFA4S0liWXZKSE0tWmZUWDhpSGkxWTAyUzVySmdzTzBkSnp0S2YzNzIzX2l5U204aW12VGVGTmotc2dWaFg5YnVXX0pEck92TlNKOEI1dF9wb1E2OG5KcUFjRkpWMFoyUlFsMUR0TmhNaUZiRktYRE5JWE4tb2x5MF9sYnhDWGljY0JvUTVWeDZJdFJVSjg2WjhhalE5R3JULWtPUmV1LTBB?oc=5</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilAFBVV95cUxOeTJ1OWMzQTJWOXVzN3dER3RGTXFXcnJ0WUtkNGFheTRQV0ZCMHhlcHo3amlYUnhoM3dTRTRhOUNLZUgycTA4blhHNU4tQWlDdmQzX1hkVEdQNkdVSnV4ZkVjcHIxQTFXTXRaNXZnZWdGUEtuZlJESGtqV3NYc0ZVaG9MX1FiVTBhWjlzOUl5S1BNMmFa?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxNNlJSejItQ3FMeVZwNndSYU9ORlA4bVg2b0xKVl9iUmt0RTZqWm94Z1lGakpMc3dSYWhfUGhDdE41aURjUEQ4UDRnU0xFQ2M4VFBMazZGTkxxbnVsc0lVeXBSbUdlSmJ1cVBiUDFkMFZCQU0yRjhKQ2F6bnhfZGk0VVgtd1BTTmw2QjRxRXpMMmlvQTk3OW9fenRMVi11djhF0gGnAUFVX3lxTFA4S0liWXZKSE0tWmZUWDhpSGkxWTAyUzVySmdzTzBkSnp0S2YzNzIzX2l5U204aW12VGVGTmotc2dWaFg5YnVXX0pEck92TlNKOEI1dF9wb1E2OG5KcUFjRkpWMFoyUlFsMUR0TmhNaUZiRktYRE5JWE4tb2x5MF9sYnhDWGljY0JvUTVWeDZJdFJVSjg2WjhhalE5R3JULWtPUmV1LTBB?oc=5</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>19a94ee940668d75</t>
+          <t>7fa4d874c1427604</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -5143,32 +5143,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-05T04:24:20Z</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>The Bhotekoshi flood | A Himalayan tragedy - The Hindu</t>
+          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 - The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>The Bhotekoshi flood | A Himalayan tragedy The Hindu</t>
+          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNlJSejItQ3FMeVZwNndSYU9ORlA4bVg2b0xKVl9iUmt0RTZqWm94Z1lGakpMc3dSYWhfUGhDdE41aURjUEQ4UDRnU0xFQ2M4VFBMazZGTkxxbnVsc0lVeXBSbUdlSmJ1cVBiUDFkMFZCQU0yRjhKQ2F6bnhfZGk0VVgtd1BTTmw2QjRxRXpMMmlvQTk3OW9fenRMVi11djhF0gGnAUFVX3lxTFA4S0liWXZKSE0tWmZUWDhpSGkxWTAyUzVySmdzTzBkSnp0S2YzNzIzX2l5U204aW12VGVGTmotc2dWaFg5YnVXX0pEck92TlNKOEI1dF9wb1E2OG5KcUFjRkpWMFoyUlFsMUR0TmhNaUZiRktYRE5JWE4tb2x5MF9sYnhDWGljY0JvUTVWeDZJdFJVSjg2WjhhalE5R3JULWtPUmV1LTBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPS2dzV29DaENoQTYwSWJqazRSR0dpQ1BqQ0xlU2tHSmFMRmFKNG90cjM5bHJGRjF0WHZodTJpZmlvS2dmekR5Vzg3QnJzUUFmV2E2cTBQZThvZEhtc2FXcDREdWs4enBpZ0RKYW9odVRNYTZmcjZWcENScjVLVzNXcWY3WGIyZF9obU4waEdEVEthVDBVSFA5VnhWSkc0QlRYZV9uSUhEM3ZPNkhIVzhSYUNWT3RsZw?oc=5</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxNNlJSejItQ3FMeVZwNndSYU9ORlA4bVg2b0xKVl9iUmt0RTZqWm94Z1lGakpMc3dSYWhfUGhDdE41aURjUEQ4UDRnU0xFQ2M4VFBMazZGTkxxbnVsc0lVeXBSbUdlSmJ1cVBiUDFkMFZCQU0yRjhKQ2F6bnhfZGk0VVgtd1BTTmw2QjRxRXpMMmlvQTk3OW9fenRMVi11djhF0gGnAUFVX3lxTFA4S0liWXZKSE0tWmZUWDhpSGkxWTAyUzVySmdzTzBkSnp0S2YzNzIzX2l5U204aW12VGVGTmotc2dWaFg5YnVXX0pEck92TlNKOEI1dF9wb1E2OG5KcUFjRkpWMFoyUlFsMUR0TmhNaUZiRktYRE5JWE4tb2x5MF9sYnhDWGljY0JvUTVWeDZJdFJVSjg2WjhhalE5R3JULWtPUmV1LTBB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxPS2dzV29DaENoQTYwSWJqazRSR0dpQ1BqQ0xlU2tHSmFMRmFKNG90cjM5bHJGRjF0WHZodTJpZmlvS2dmekR5Vzg3QnJzUUFmV2E2cTBQZThvZEhtc2FXcDREdWs4enBpZ0RKYW9odVRNYTZmcjZWcENScjVLVzNXcWY3WGIyZF9obU4waEdEVEthVDBVSFA5VnhWSkc0QlRYZV9uSUhEM3ZPNkhIVzhSYUNWT3RsZw?oc=5</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>7fa4d874c1427604</t>
+          <t>a58c8e2afb9e532d</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -5195,32 +5195,32 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T04:24:20Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>The Watchers - Watching the world evolve and transform</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 - The Watchers - Watching the world evolve and transform</t>
+          <t>Death toll from Bhotekoshi flood reaches 734 - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 The Watchers - Watching the world evolve and transform</t>
+          <t>Death toll from Bhotekoshi flood reaches 734 The Kathmandu Post</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPS2dzV29DaENoQTYwSWJqazRSR0dpQ1BqQ0xlU2tHSmFMRmFKNG90cjM5bHJGRjF0WHZodTJpZmlvS2dmekR5Vzg3QnJzUUFmV2E2cTBQZThvZEhtc2FXcDREdWs4enBpZ0RKYW9odVRNYTZmcjZWcENScjVLVzNXcWY3WGIyZF9obU4waEdEVEthVDBVSFA5VnhWSkc0QlRYZV9uSUhEM3ZPNkhIVzhSYUNWT3RsZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdnVnakg4QVpKWjR4N1paNEp1dXlDZHgxYUFBN2JZZDljUG1EUVdYaGNxb3lpVndyWUtZOVBiakk4Xzd1Ynk5a3l3d2dQei1VX255MWJ0ZjBSbVJYSzN6eUpiNjRRVG4tZFVNa0NyZGJDb2lvVVhwUENwQ18xSUVHVnNCTHByOE56TktxY2VvcDROQ0pt?oc=5</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxPS2dzV29DaENoQTYwSWJqazRSR0dpQ1BqQ0xlU2tHSmFMRmFKNG90cjM5bHJGRjF0WHZodTJpZmlvS2dmekR5Vzg3QnJzUUFmV2E2cTBQZThvZEhtc2FXcDREdWs4enBpZ0RKYW9odVRNYTZmcjZWcENScjVLVzNXcWY3WGIyZF9obU4waEdEVEthVDBVSFA5VnhWSkc0QlRYZV9uSUhEM3ZPNkhIVzhSYUNWT3RsZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilAFBVV95cUxPdnVnakg4QVpKWjR4N1paNEp1dXlDZHgxYUFBN2JZZDljUG1EUVdYaGNxb3lpVndyWUtZOVBiakk4Xzd1Ynk5a3l3d2dQei1VX255MWJ0ZjBSbVJYSzN6eUpiNjRRVG4tZFVNa0NyZGJDb2lvVVhwUENwQ18xSUVHVnNCTHByOE56TktxY2VvcDROQ0pt?oc=5</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -5237,12 +5237,12 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>a58c8e2afb9e532d</t>
+          <t>c0a613234873e701</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -5257,22 +5257,22 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 734 - The Kathmandu Post</t>
+          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 734 The Kathmandu Post</t>
+          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for The Kathmandu Post</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdnVnakg4QVpKWjR4N1paNEp1dXlDZHgxYUFBN2JZZDljUG1EUVdYaGNxb3lpVndyWUtZOVBiakk4Xzd1Ynk5a3l3d2dQei1VX255MWJ0ZjBSbVJYSzN6eUpiNjRRVG4tZFVNa0NyZGJDb2lvVVhwUENwQ18xSUVHVnNCTHByOE56TktxY2VvcDROQ0pt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ3hjNkpxZFJaWEFXUnRlYXlwUmQzMGZxNG03ejB4bmFOTEhya1lWSno0U21ROG1FcFdHcEU0bzNGai14cTQtbjdvRndrclJfZzN1X2k4UjFiZ0l0X1ZCYlJGdlh0WEJqWXNmalZtWUlMRG9rbmsxWVFKU1E5ZExFdU03VWxkX2cweW4wV1VWLTIxdlZhQ0VRYW0zU2FUdW5GcHZ0OW5jU0hKTFplb19XM2dqdll0WlU?oc=5</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilAFBVV95cUxPdnVnakg4QVpKWjR4N1paNEp1dXlDZHgxYUFBN2JZZDljUG1EUVdYaGNxb3lpVndyWUtZOVBiakk4Xzd1Ynk5a3l3d2dQei1VX255MWJ0ZjBSbVJYSzN6eUpiNjRRVG4tZFVNa0NyZGJDb2lvVVhwUENwQ18xSUVHVnNCTHByOE56TktxY2VvcDROQ0pt?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ3hjNkpxZFJaWEFXUnRlYXlwUmQzMGZxNG03ejB4bmFOTEhya1lWSno0U21ROG1FcFdHcEU0bzNGai14cTQtbjdvRndrclJfZzN1X2k4UjFiZ0l0X1ZCYlJGdlh0WEJqWXNmalZtWUlMRG9rbmsxWVFKU1E5ZExFdU03VWxkX2cweW4wV1VWLTIxdlZhQ0VRYW0zU2FUdW5GcHZ0OW5jU0hKTFplb19XM2dqdll0WlU?oc=5</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -5289,12 +5289,12 @@
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>c0a613234873e701</t>
+          <t>5c7deb8a11483ad8</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -5309,22 +5309,22 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for - The Kathmandu Post</t>
+          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for The Kathmandu Post</t>
+          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events The Kathmandu Post</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ3hjNkpxZFJaWEFXUnRlYXlwUmQzMGZxNG03ejB4bmFOTEhya1lWSno0U21ROG1FcFdHcEU0bzNGai14cTQtbjdvRndrclJfZzN1X2k4UjFiZ0l0X1ZCYlJGdlh0WEJqWXNmalZtWUlMRG9rbmsxWVFKU1E5ZExFdU03VWxkX2cweW4wV1VWLTIxdlZhQ0VRYW0zU2FUdW5GcHZ0OW5jU0hKTFplb19XM2dqdll0WlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNanBjaGZzOFJjZmdCSnZQRHhpczEyOG9CWXltSnFyNE1qTDk1cE0wZUlrR2lhNGRmWHJvRkFHTVVjcjhDVVRWaDFISVR2ZTVibGFEb05yUUJ6UkFpcnJZRU9KLTdqQVRYd29vRzdmcE85OW41dUo5RkNIMEJ0S2hyeWFwSmhlSHFrQlpoVDdFZm00V3VPRzhuVFpFUUg4cjN5bXh2LVZudnpWOG1aa3JlMUNDX1hmWE1SRWcyX3dTZGVEWDFfYjNZYw?oc=5</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ3hjNkpxZFJaWEFXUnRlYXlwUmQzMGZxNG03ejB4bmFOTEhya1lWSno0U21ROG1FcFdHcEU0bzNGai14cTQtbjdvRndrclJfZzN1X2k4UjFiZ0l0X1ZCYlJGdlh0WEJqWXNmalZtWUlMRG9rbmsxWVFKU1E5ZExFdU03VWxkX2cweW4wV1VWLTIxdlZhQ0VRYW0zU2FUdW5GcHZ0OW5jU0hKTFplb19XM2dqdll0WlU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxNanBjaGZzOFJjZmdCSnZQRHhpczEyOG9CWXltSnFyNE1qTDk1cE0wZUlrR2lhNGRmWHJvRkFHTVVjcjhDVVRWaDFISVR2ZTVibGFEb05yUUJ6UkFpcnJZRU9KLTdqQVRYd29vRzdmcE85OW41dUo5RkNIMEJ0S2hyeWFwSmhlSHFrQlpoVDdFZm00V3VPRzhuVFpFUUg4cjN5bXh2LVZudnpWOG1aa3JlMUNDX1hmWE1SRWcyX3dTZGVEWDFfYjNZYw?oc=5</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>5c7deb8a11483ad8</t>
+          <t>ae89500f49c1d81d</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -5356,27 +5356,27 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Straits Times</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events - The Kathmandu Post</t>
+          <t>Nepal-Tibet floods: Nepal tourism faces another setback as Rasuwa disaster exposes mountain risks - The Straits Times</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events The Kathmandu Post</t>
+          <t>Nepal-Tibet floods: Nepal tourism faces another setback as Rasuwa disaster exposes mountain risks The Straits Times</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNanBjaGZzOFJjZmdCSnZQRHhpczEyOG9CWXltSnFyNE1qTDk1cE0wZUlrR2lhNGRmWHJvRkFHTVVjcjhDVVRWaDFISVR2ZTVibGFEb05yUUJ6UkFpcnJZRU9KLTdqQVRYd29vRzdmcE85OW41dUo5RkNIMEJ0S2hyeWFwSmhlSHFrQlpoVDdFZm00V3VPRzhuVFpFUUg4cjN5bXh2LVZudnpWOG1aa3JlMUNDX1hmWE1SRWcyX3dTZGVEWDFfYjNZYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNajI0QXFiNHdiRl9iYkdmdGtCSllHeGdfYk9KZ3B2VmhoVFRZa3JVOExob0RSWHNUY0VqMUtrbHdRWkRqX1BxM1l2SVdlUnhhdUxwaXNjZ1gyRk80alhvQUYtY0czaTZUVjhQLU1CbHpBNUVBNVZmWE1vMUZTLVhBcmctT2tSWURIYjVOcVBlUEVYMXZQNXd6bElUX0xlbFB3cU5jNjhDb2VneXNXU0dTMXdETmFvM2x0SWxmeE1oQmxIQjZBdnZfZHJR?oc=5</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxNanBjaGZzOFJjZmdCSnZQRHhpczEyOG9CWXltSnFyNE1qTDk1cE0wZUlrR2lhNGRmWHJvRkFHTVVjcjhDVVRWaDFISVR2ZTVibGFEb05yUUJ6UkFpcnJZRU9KLTdqQVRYd29vRzdmcE85OW41dUo5RkNIMEJ0S2hyeWFwSmhlSHFrQlpoVDdFZm00V3VPRzhuVFpFUUg4cjN5bXh2LVZudnpWOG1aa3JlMUNDX1hmWE1SRWcyX3dTZGVEWDFfYjNZYw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNajI0QXFiNHdiRl9iYkdmdGtCSllHeGdfYk9KZ3B2VmhoVFRZa3JVOExob0RSWHNUY0VqMUtrbHdRWkRqX1BxM1l2SVdlUnhhdUxwaXNjZ1gyRk80alhvQUYtY0czaTZUVjhQLU1CbHpBNUVBNVZmWE1vMUZTLVhBcmctT2tSWURIYjVOcVBlUEVYMXZQNXd6bElUX0xlbFB3cU5jNjhDb2VneXNXU0dTMXdETmFvM2x0SWxmeE1oQmxIQjZBdnZfZHJR?oc=5</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>ae89500f49c1d81d</t>
+          <t>9520dc392cc0533f</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -5403,32 +5403,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>The Straits Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Nepal-Tibet floods: Nepal tourism faces another setback as Rasuwa disaster exposes mountain risks - The Straits Times</t>
+          <t>Xtreme Energy Drinks Donates Rs 10 Million to Bhotekoshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Nepal-Tibet floods: Nepal tourism faces another setback as Rasuwa disaster exposes mountain risks The Straits Times</t>
+          <t>Xtreme Energy Drinks Donates Rs 10 Million to Bhotekoshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNajI0QXFiNHdiRl9iYkdmdGtCSllHeGdfYk9KZ3B2VmhoVFRZa3JVOExob0RSWHNUY0VqMUtrbHdRWkRqX1BxM1l2SVdlUnhhdUxwaXNjZ1gyRk80alhvQUYtY0czaTZUVjhQLU1CbHpBNUVBNVZmWE1vMUZTLVhBcmctT2tSWURIYjVOcVBlUEVYMXZQNXd6bElUX0xlbFB3cU5jNjhDb2VneXNXU0dTMXdETmFvM2x0SWxmeE1oQmxIQjZBdnZfZHJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBFd1dRQ1o5OV9JMmI3TlRmVlZaSFhvWHdFTGt1aXFndE9adWxLVDdFOXNDT2NJV3VSTHpubTlIRC1acjFOYm93VWZpSGo5TEw4Xzh0d2Zvc2kzR3ViU0laS081cUJHLTkzY1JzV3pUR2ZKdDNP?oc=5</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNajI0QXFiNHdiRl9iYkdmdGtCSllHeGdfYk9KZ3B2VmhoVFRZa3JVOExob0RSWHNUY0VqMUtrbHdRWkRqX1BxM1l2SVdlUnhhdUxwaXNjZ1gyRk80alhvQUYtY0czaTZUVjhQLU1CbHpBNUVBNVZmWE1vMUZTLVhBcmctT2tSWURIYjVOcVBlUEVYMXZQNXd6bElUX0xlbFB3cU5jNjhDb2VneXNXU0dTMXdETmFvM2x0SWxmeE1oQmxIQjZBdnZfZHJR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBFd1dRQ1o5OV9JMmI3TlRmVlZaSFhvWHdFTGt1aXFndE9adWxLVDdFOXNDT2NJV3VSTHpubTlIRC1acjFOYm93VWZpSGo5TEw4Xzh0d2Zvc2kzR3ViU0laS081cUJHLTkzY1JzV3pUR2ZKdDNP?oc=5</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>9520dc392cc0533f</t>
+          <t>361818007042640d</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Xtreme Energy Drinks Donates Rs 10 Million to Bhotekoshi Flood Victims - ekantipur.com</t>
+          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Xtreme Energy Drinks Donates Rs 10 Million to Bhotekoshi Flood Victims ekantipur.com</t>
+          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) ReliefWeb</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBFd1dRQ1o5OV9JMmI3TlRmVlZaSFhvWHdFTGt1aXFndE9adWxLVDdFOXNDT2NJV3VSTHpubTlIRC1acjFOYm93VWZpSGo5TEw4Xzh0d2Zvc2kzR3ViU0laS081cUJHLTkzY1JzV3pUR2ZKdDNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOUV9PeUMybEQ1TV9Gbks2RnVxSkJSNVJGUmxnUFNNWG1TYkZtcnNfWXozYk9Bc2lZVWpzZXZnelhQX1ZwTWlLME80QTV0RllRN0tOTDk1TWhXUnVkUjRmY1dtNnRpZTlwRkJtNGdOYnowSl94STlUR2ZCeHZ3VEZsTVFsTU9za2dUcFV2RDd3ck9hVmlFbWNwdVpzUlFLYjB4MVpBU1RuWWlvY3cxVXBzc1E5bjZ1OVFMTWI2ODdGbzYzUV9yT0VRMmp1MXBFR2lERnBsUlFYWnZFNTVneDREUk5PbnZSVWQxSlVOZGhOQjktak5mUEEtb0NtVTlfUjIxMzdfR2NhQjhPd2ZBcDhqNDUzdWcwd25sd0g2RGFB?oc=5</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBFd1dRQ1o5OV9JMmI3TlRmVlZaSFhvWHdFTGt1aXFndE9adWxLVDdFOXNDT2NJV3VSTHpubTlIRC1acjFOYm93VWZpSGo5TEw4Xzh0d2Zvc2kzR3ViU0laS081cUJHLTkzY1JzV3pUR2ZKdDNP?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingJBVV95cUxOUV9PeUMybEQ1TV9Gbks2RnVxSkJSNVJGUmxnUFNNWG1TYkZtcnNfWXozYk9Bc2lZVWpzZXZnelhQX1ZwTWlLME80QTV0RllRN0tOTDk1TWhXUnVkUjRmY1dtNnRpZTlwRkJtNGdOYnowSl94STlUR2ZCeHZ3VEZsTVFsTU9za2dUcFV2RDd3ck9hVmlFbWNwdVpzUlFLYjB4MVpBU1RuWWlvY3cxVXBzc1E5bjZ1OVFMTWI2ODdGbzYzUV9yT0VRMmp1MXBFR2lERnBsUlFYWnZFNTVneDREUk5PbnZSVWQxSlVOZGhOQjktak5mUEEtb0NtVTlfUjIxMzdfR2NhQjhPd2ZBcDhqNDUzdWcwd25sd0g2RGFB?oc=5</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="99" ht="48" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>361818007042640d</t>
+          <t>cdc58d4e00999f5c</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -5512,27 +5512,27 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026</t>
+          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) ReliefWeb</t>
+          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? The Kathmandu Post</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOUV9PeUMybEQ1TV9Gbks2RnVxSkJSNVJGUmxnUFNNWG1TYkZtcnNfWXozYk9Bc2lZVWpzZXZnelhQX1ZwTWlLME80QTV0RllRN0tOTDk1TWhXUnVkUjRmY1dtNnRpZTlwRkJtNGdOYnowSl94STlUR2ZCeHZ3VEZsTVFsTU9za2dUcFV2RDd3ck9hVmlFbWNwdVpzUlFLYjB4MVpBU1RuWWlvY3cxVXBzc1E5bjZ1OVFMTWI2ODdGbzYzUV9yT0VRMmp1MXBFR2lERnBsUlFYWnZFNTVneDREUk5PbnZSVWQxSlVOZGhOQjktak5mUEEtb0NtVTlfUjIxMzdfR2NhQjhPd2ZBcDhqNDUzdWcwd25sd0g2RGFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR2hvZlB2RGV1b09EcUdkQUdmNU1oanV5ZDZGOWZZNl8wSXVhVlVQNmJGeENoSk93OUZvZFpEbWpwQTBWZ2UyaUFucTRlcnBEN29Faml4bGRXYzF4SmViWWdjM1dEbTM4al9xUWZOTFlWNlM4Qk10MUI5X2JjUmNmRElyWmVjNWF4MEdfWUhQcl9GTnV3dW1FUlNzdlkxdzJNLVRRaU9hb2xaSlZfY1RrbThaUDJoZWFC?oc=5</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingJBVV95cUxOUV9PeUMybEQ1TV9Gbks2RnVxSkJSNVJGUmxnUFNNWG1TYkZtcnNfWXozYk9Bc2lZVWpzZXZnelhQX1ZwTWlLME80QTV0RllRN0tOTDk1TWhXUnVkUjRmY1dtNnRpZTlwRkJtNGdOYnowSl94STlUR2ZCeHZ3VEZsTVFsTU9za2dUcFV2RDd3ck9hVmlFbWNwdVpzUlFLYjB4MVpBU1RuWWlvY3cxVXBzc1E5bjZ1OVFMTWI2ODdGbzYzUV9yT0VRMmp1MXBFR2lERnBsUlFYWnZFNTVneDREUk5PbnZSVWQxSlVOZGhOQjktak5mUEEtb0NtVTlfUjIxMzdfR2NhQjhPd2ZBcDhqNDUzdWcwd25sd0g2RGFB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR2hvZlB2RGV1b09EcUdkQUdmNU1oanV5ZDZGOWZZNl8wSXVhVlVQNmJGeENoSk93OUZvZFpEbWpwQTBWZ2UyaUFucTRlcnBEN29Faml4bGRXYzF4SmViWWdjM1dEbTM4al9xUWZOTFlWNlM4Qk10MUI5X2JjUmNmRElyWmVjNWF4MEdfWUhQcl9GTnV3dW1FUlNzdlkxdzJNLVRRaU9hb2xaSlZfY1RrbThaUDJoZWFC?oc=5</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>cdc58d4e00999f5c</t>
+          <t>a5bce12e457a5d23</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
@@ -5569,22 +5569,22 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? - The Kathmandu Post</t>
+          <t>How the Bhotekoshi flood unfolded over 10 hours - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? The Kathmandu Post</t>
+          <t>How the Bhotekoshi flood unfolded over 10 hours The Kathmandu Post</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR2hvZlB2RGV1b09EcUdkQUdmNU1oanV5ZDZGOWZZNl8wSXVhVlVQNmJGeENoSk93OUZvZFpEbWpwQTBWZ2UyaUFucTRlcnBEN29Faml4bGRXYzF4SmViWWdjM1dEbTM4al9xUWZOTFlWNlM4Qk10MUI5X2JjUmNmRElyWmVjNWF4MEdfWUhQcl9GTnV3dW1FUlNzdlkxdzJNLVRRaU9hb2xaSlZfY1RrbThaUDJoZWFC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ29aRHQxeDJnNTYzQ1VBYnkwTHYzZnhYXzYySzZtblFZSEpVb0dhcXp1WmRnd0wtbUV0MF8zWUw1aXp5TnY2a0JoSzZmZmdVd1d6S0QxeDRFZHFobGRNTFJtdnFpNE4xaW56X2w5a0pORVlQcEVUY2Q0UmxnV1dZbUhaWjQtMEd3czN4SFhmUTRCZ2xCOFRNTg?oc=5</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR2hvZlB2RGV1b09EcUdkQUdmNU1oanV5ZDZGOWZZNl8wSXVhVlVQNmJGeENoSk93OUZvZFpEbWpwQTBWZ2UyaUFucTRlcnBEN29Faml4bGRXYzF4SmViWWdjM1dEbTM4al9xUWZOTFlWNlM4Qk10MUI5X2JjUmNmRElyWmVjNWF4MEdfWUhQcl9GTnV3dW1FUlNzdlkxdzJNLVRRaU9hb2xaSlZfY1RrbThaUDJoZWFC?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ29aRHQxeDJnNTYzQ1VBYnkwTHYzZnhYXzYySzZtblFZSEpVb0dhcXp1WmRnd0wtbUV0MF8zWUw1aXp5TnY2a0JoSzZmZmdVd1d6S0QxeDRFZHFobGRNTFJtdnFpNE4xaW56X2w5a0pORVlQcEVUY2Q0UmxnV1dZbUhaWjQtMEd3czN4SFhmUTRCZ2xCOFRNTg?oc=5</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="101" ht="48" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>a5bce12e457a5d23</t>
+          <t>b91ed876613616f1</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -5611,32 +5611,32 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>How the Bhotekoshi flood unfolded over 10 hours - The Kathmandu Post</t>
+          <t>Technical report details Bhotekoshi flood’s journey from Tibet to Devghat - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>How the Bhotekoshi flood unfolded over 10 hours The Kathmandu Post</t>
+          <t>Technical report details Bhotekoshi flood’s journey from Tibet to Devghat Onlinekhabar English</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ29aRHQxeDJnNTYzQ1VBYnkwTHYzZnhYXzYySzZtblFZSEpVb0dhcXp1WmRnd0wtbUV0MF8zWUw1aXp5TnY2a0JoSzZmZmdVd1d6S0QxeDRFZHFobGRNTFJtdnFpNE4xaW56X2w5a0pORVlQcEVUY2Q0UmxnV1dZbUhaWjQtMEd3czN4SFhmUTRCZ2xCOFRNTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1McldQQXlGN1dJRzhwRlVWd0pMSWNBNFRrblM5TWxFczRvTnJMdDdxcjlETVRsUk16U25HY3diSDQ5YzMyd2FpdDBoSFduXzZUTHZwRjVjbTJRWVRrMkdGVGxEN25tU1BlN3NlWjN4MXRldjl1cWc?oc=5</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ29aRHQxeDJnNTYzQ1VBYnkwTHYzZnhYXzYySzZtblFZSEpVb0dhcXp1WmRnd0wtbUV0MF8zWUw1aXp5TnY2a0JoSzZmZmdVd1d6S0QxeDRFZHFobGRNTFJtdnFpNE4xaW56X2w5a0pORVlQcEVUY2Q0UmxnV1dZbUhaWjQtMEd3czN4SFhmUTRCZ2xCOFRNTg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidkFVX3lxTE1McldQQXlGN1dJRzhwRlVWd0pMSWNBNFRrblM5TWxFczRvTnJMdDdxcjlETVRsUk16U25HY3diSDQ5YzMyd2FpdDBoSFduXzZUTHZwRjVjbTJRWVRrMkdGVGxEN25tU1BlN3NlWjN4MXRldjl1cWc?oc=5</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="102" ht="48" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>b91ed876613616f1</t>
+          <t>86fd34bb8c83f384</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -5663,32 +5663,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Technical report details Bhotekoshi flood’s journey from Tibet to Devghat - Onlinekhabar English</t>
+          <t>826 out of contact after Bhotekoshi flood, including 590 tourists - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Technical report details Bhotekoshi flood’s journey from Tibet to Devghat Onlinekhabar English</t>
+          <t>826 out of contact after Bhotekoshi flood, including 590 tourists The Kathmandu Post</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1McldQQXlGN1dJRzhwRlVWd0pMSWNBNFRrblM5TWxFczRvTnJMdDdxcjlETVRsUk16U25HY3diSDQ5YzMyd2FpdDBoSFduXzZUTHZwRjVjbTJRWVRrMkdGVGxEN25tU1BlN3NlWjN4MXRldjl1cWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTGV0c3YtMDUxMmVTQzFFcjM3b2RRa2xWLUNUZE82Yms5bGU1RnowbGV6MHVHOVpQdEFHejJWQnNUVlpvbnFIVDJuLXVIaDNBRFRiWXFQTExDVXdhUEtXdGQwZnBJa002TUVIRTNCaFZUdFFUcXVZOEVtSXhSTFQxMDh1Q0JCcng3NVFabmE5NnUzajA1OGozZTZuSWJNZTEzV2V0cldn?oc=5</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidkFVX3lxTE1McldQQXlGN1dJRzhwRlVWd0pMSWNBNFRrblM5TWxFczRvTnJMdDdxcjlETVRsUk16U25HY3diSDQ5YzMyd2FpdDBoSFduXzZUTHZwRjVjbTJRWVRrMkdGVGxEN25tU1BlN3NlWjN4MXRldjl1cWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxQTGV0c3YtMDUxMmVTQzFFcjM3b2RRa2xWLUNUZE82Yms5bGU1RnowbGV6MHVHOVpQdEFHejJWQnNUVlpvbnFIVDJuLXVIaDNBRFRiWXFQTExDVXdhUEtXdGQwZnBJa002TUVIRTNCaFZUdFFUcXVZOEVtSXhSTFQxMDh1Q0JCcng3NVFabmE5NnUzajA1OGozZTZuSWJNZTEzV2V0cldn?oc=5</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="103" ht="48" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>86fd34bb8c83f384</t>
+          <t>368b5e7643172009</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -5720,27 +5720,27 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>malaysiasun.com</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>826 out of contact after Bhotekoshi flood, including 590 tourists - The Kathmandu Post</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood in Nepal: Report - malaysiasun.com</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>826 out of contact after Bhotekoshi flood, including 590 tourists The Kathmandu Post</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood in Nepal: Report malaysiasun.com</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTGV0c3YtMDUxMmVTQzFFcjM3b2RRa2xWLUNUZE82Yms5bGU1RnowbGV6MHVHOVpQdEFHejJWQnNUVlpvbnFIVDJuLXVIaDNBRFRiWXFQTExDVXdhUEtXdGQwZnBJa002TUVIRTNCaFZUdFFUcXVZOEVtSXhSTFQxMDh1Q0JCcng3NVFabmE5NnUzajA1OGozZTZuSWJNZTEzV2V0cldn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmlKUHFCY21XeDVYd2pzYjhYYWppb2pvaWtNNjRaZU9vbmdfc3gxMWtqOTF0ZUY4UUZhTmlJMXZGeDNUaUctREJlN0N5dGR2LTRuSlJBYzhXMndlWTg0WHRacWNHRG8zSzA1WGwxZTZQMk5lek9jWFRGMmpGb2VDUmJ3bnNQQ2o0QXVOeS1ENTc1dGdKYS1raG00cnI1UENEUmR6NW1CX3pXLVNuVmJBbTItQlpDZmluX0FGQg?oc=5</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxQTGV0c3YtMDUxMmVTQzFFcjM3b2RRa2xWLUNUZE82Yms5bGU1RnowbGV6MHVHOVpQdEFHejJWQnNUVlpvbnFIVDJuLXVIaDNBRFRiWXFQTExDVXdhUEtXdGQwZnBJa002TUVIRTNCaFZUdFFUcXVZOEVtSXhSTFQxMDh1Q0JCcng3NVFabmE5NnUzajA1OGozZTZuSWJNZTEzV2V0cldn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmlKUHFCY21XeDVYd2pzYjhYYWppb2pvaWtNNjRaZU9vbmdfc3gxMWtqOTF0ZUY4UUZhTmlJMXZGeDNUaUctREJlN0N5dGR2LTRuSlJBYzhXMndlWTg0WHRacWNHRG8zSzA1WGwxZTZQMk5lek9jWFRGMmpGb2VDUmJ3bnNQQ2o0QXVOeS1ENTc1dGdKYS1raG00cnI1UENEUmR6NW1CX3pXLVNuVmJBbTItQlpDZmluX0FGQg?oc=5</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="104" ht="48" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>368b5e7643172009</t>
+          <t>4f3e4792ababfb65</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -5772,27 +5772,27 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>malaysiasun.com</t>
+          <t>Public TV English</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood in Nepal: Report - malaysiasun.com</t>
+          <t>Ice avalanche, debris lake may have triggered Bhote Koshi flood in Nepal: Report - Public TV English</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood in Nepal: Report malaysiasun.com</t>
+          <t>Ice avalanche, debris lake may have triggered Bhote Koshi flood in Nepal: Report Public TV English</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmlKUHFCY21XeDVYd2pzYjhYYWppb2pvaWtNNjRaZU9vbmdfc3gxMWtqOTF0ZUY4UUZhTmlJMXZGeDNUaUctREJlN0N5dGR2LTRuSlJBYzhXMndlWTg0WHRacWNHRG8zSzA1WGwxZTZQMk5lek9jWFRGMmpGb2VDUmJ3bnNQQ2o0QXVOeS1ENTc1dGdKYS1raG00cnI1UENEUmR6NW1CX3pXLVNuVmJBbTItQlpDZmluX0FGQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbWtKamZESkVkVjNWdENFNWZNbjJETFhUVWo1VVNTYUpGVmdrUkZRdzZSaWV4SXlHelRuYzhiQVhVTFBCbEQ1N1U3NGdTbVFMVWRnMlgxcDgwQXZVdzF2Z1JDdEhFUnE3dEZUc01mZHMtNy1GNURjR01BWmFGVmZZOUpTWDhrSVJ0dXFVOEFfaWh5d1I1NXdLdlh5MXlrOWozWkdScnlxNDlNQ0k?oc=5</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmlKUHFCY21XeDVYd2pzYjhYYWppb2pvaWtNNjRaZU9vbmdfc3gxMWtqOTF0ZUY4UUZhTmlJMXZGeDNUaUctREJlN0N5dGR2LTRuSlJBYzhXMndlWTg0WHRacWNHRG8zSzA1WGwxZTZQMk5lek9jWFRGMmpGb2VDUmJ3bnNQQ2o0QXVOeS1ENTc1dGdKYS1raG00cnI1UENEUmR6NW1CX3pXLVNuVmJBbTItQlpDZmluX0FGQg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbWtKamZESkVkVjNWdENFNWZNbjJETFhUVWo1VVNTYUpGVmdrUkZRdzZSaWV4SXlHelRuYzhiQVhVTFBCbEQ1N1U3NGdTbVFMVWRnMlgxcDgwQXZVdzF2Z1JDdEhFUnE3dEZUc01mZHMtNy1GNURjR01BWmFGVmZZOUpTWDhrSVJ0dXFVOEFfaWh5d1I1NXdLdlh5MXlrOWozWkdScnlxNDlNQ0k?oc=5</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -5809,12 +5809,12 @@
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>4f3e4792ababfb65</t>
+          <t>18743ea168b8bdf1</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -5824,27 +5824,27 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Public TV English</t>
+          <t>Stimson Center</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhote Koshi flood in Nepal: Report - Public TV English</t>
+          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later - Stimson Center</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhote Koshi flood in Nepal: Report Public TV English</t>
+          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later Stimson Center</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbWtKamZESkVkVjNWdENFNWZNbjJETFhUVWo1VVNTYUpGVmdrUkZRdzZSaWV4SXlHelRuYzhiQVhVTFBCbEQ1N1U3NGdTbVFMVWRnMlgxcDgwQXZVdzF2Z1JDdEhFUnE3dEZUc01mZHMtNy1GNURjR01BWmFGVmZZOUpTWDhrSVJ0dXFVOEFfaWh5d1I1NXdLdlh5MXlrOWozWkdScnlxNDlNQ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQS2hEOVJzWDRUV2hEaEdsS3YwSFRaQjFLeHdYdXRzaVFxT3ZNaXc5LUpHRkE1Z2wxNEhpcUtLYXE3cTJMX001czZzRG5vTFk3aHNWT19TTHhjQUtjZ3VkQzFRZjVDeG1vZE5LRHNiQnB2UFhLM0hvaWdWT0FOZmktZFpqdGlFUzNLMVB6UUV6Y05iZXV1d1NIa2NiRDdvbGdKc2lNSjNxaEdDMlpsYUsxaTl4Qkw3YzB4M29VVmF0QWFRZw?oc=5</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbWtKamZESkVkVjNWdENFNWZNbjJETFhUVWo1VVNTYUpGVmdrUkZRdzZSaWV4SXlHelRuYzhiQVhVTFBCbEQ1N1U3NGdTbVFMVWRnMlgxcDgwQXZVdzF2Z1JDdEhFUnE3dEZUc01mZHMtNy1GNURjR01BWmFGVmZZOUpTWDhrSVJ0dXFVOEFfaWh5d1I1NXdLdlh5MXlrOWozWkdScnlxNDlNQ0k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxQS2hEOVJzWDRUV2hEaEdsS3YwSFRaQjFLeHdYdXRzaVFxT3ZNaXc5LUpHRkE1Z2wxNEhpcUtLYXE3cTJMX001czZzRG5vTFk3aHNWT19TTHhjQUtjZ3VkQzFRZjVDeG1vZE5LRHNiQnB2UFhLM0hvaWdWT0FOZmktZFpqdGlFUzNLMVB6UUV6Y05iZXV1d1NIa2NiRDdvbGdKc2lNSjNxaEdDMlpsYUsxaTl4Qkw3YzB4M29VVmF0QWFRZw?oc=5</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="106" ht="48" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>18743ea168b8bdf1</t>
+          <t>9160337bb9adfe1c</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -5876,27 +5876,27 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Stimson Center</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later - Stimson Center</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later Stimson Center</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood The Kathmandu Post</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQS2hEOVJzWDRUV2hEaEdsS3YwSFRaQjFLeHdYdXRzaVFxT3ZNaXc5LUpHRkE1Z2wxNEhpcUtLYXE3cTJMX001czZzRG5vTFk3aHNWT19TTHhjQUtjZ3VkQzFRZjVDeG1vZE5LRHNiQnB2UFhLM0hvaWdWT0FOZmktZFpqdGlFUzNLMVB6UUV6Y05iZXV1d1NIa2NiRDdvbGdKc2lNSjNxaEdDMlpsYUsxaTl4Qkw3YzB4M29VVmF0QWFRZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQTUzeFNEcDVoYk8wcDJ1Q3REREhhM3VuUi14MktPSV9xYXZJUC1XalhTT01QdlJLU3R1d3YtNzB4OWRDNm9nM0E4dFFHOXFqaWhlZ1B6Q2dHZ0Q3djdyODdMZzdIQWFFQURkZlVuSjhnaHV0NHhOR201MXVQNnpnU0hTanFnaDMzMjBXSmdDYW96WlZDQ09mUmlybTFwaG1pbXBiV1Q4QXZIeTA?oc=5</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxQS2hEOVJzWDRUV2hEaEdsS3YwSFRaQjFLeHdYdXRzaVFxT3ZNaXc5LUpHRkE1Z2wxNEhpcUtLYXE3cTJMX001czZzRG5vTFk3aHNWT19TTHhjQUtjZ3VkQzFRZjVDeG1vZE5LRHNiQnB2UFhLM0hvaWdWT0FOZmktZFpqdGlFUzNLMVB6UUV6Y05iZXV1d1NIa2NiRDdvbGdKc2lNSjNxaEdDMlpsYUsxaTl4Qkw3YzB4M29VVmF0QWFRZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQTUzeFNEcDVoYk8wcDJ1Q3REREhhM3VuUi14MktPSV9xYXZJUC1XalhTT01QdlJLU3R1d3YtNzB4OWRDNm9nM0E4dFFHOXFqaWhlZ1B6Q2dHZ0Q3djdyODdMZzdIQWFFQURkZlVuSjhnaHV0NHhOR201MXVQNnpnU0hTanFnaDMzMjBXSmdDYW96WlZDQ09mUmlybTFwaG1pbXBiV1Q4QXZIeTA?oc=5</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="107" ht="48" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>9160337bb9adfe1c</t>
+          <t>5279e1ad5e883f58</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -5933,22 +5933,22 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood - The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What we know, what remains unclear - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What we know, what remains unclear The Kathmandu Post</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQTUzeFNEcDVoYk8wcDJ1Q3REREhhM3VuUi14MktPSV9xYXZJUC1XalhTT01QdlJLU3R1d3YtNzB4OWRDNm9nM0E4dFFHOXFqaWhlZ1B6Q2dHZ0Q3djdyODdMZzdIQWFFQURkZlVuSjhnaHV0NHhOR201MXVQNnpnU0hTanFnaDMzMjBXSmdDYW96WlZDQ09mUmlybTFwaG1pbXBiV1Q4QXZIeTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNLTVhQVlLblMtNlpMQnNyZjBad2pKQ2F0SmRjVXJXa3ZMcXhTM25BR0VNYU1jaGpidUZRMi1rS21lV0pZbFcxN0JZV0xKdTVGWWhMVmxUMk5ZTUlmYjVvb2dvcGM4Z2k5dzctNXVjQXkzRmVCd3VCcWFwSVRIU2NadS1IOXJnRTNmU1ZZdy1PdjVFOVdrOFFmNVBqTFQ?oc=5</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQTUzeFNEcDVoYk8wcDJ1Q3REREhhM3VuUi14MktPSV9xYXZJUC1XalhTT01QdlJLU3R1d3YtNzB4OWRDNm9nM0E4dFFHOXFqaWhlZ1B6Q2dHZ0Q3djdyODdMZzdIQWFFQURkZlVuSjhnaHV0NHhOR201MXVQNnpnU0hTanFnaDMzMjBXSmdDYW96WlZDQ09mUmlybTFwaG1pbXBiV1Q4QXZIeTA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNLTVhQVlLblMtNlpMQnNyZjBad2pKQ2F0SmRjVXJXa3ZMcXhTM25BR0VNYU1jaGpidUZRMi1rS21lV0pZbFcxN0JZV0xKdTVGWWhMVmxUMk5ZTUlmYjVvb2dvcGM4Z2k5dzctNXVjQXkzRmVCd3VCcWFwSVRIU2NadS1IOXJnRTNmU1ZZdy1PdjVFOVdrOFFmNVBqTFQ?oc=5</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="108" ht="48" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>5279e1ad5e883f58</t>
+          <t>6af1b1f739c5791b</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -5985,22 +5985,22 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What we know, what remains unclear - The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What we know, what remains unclear The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing The Kathmandu Post</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNLTVhQVlLblMtNlpMQnNyZjBad2pKQ2F0SmRjVXJXa3ZMcXhTM25BR0VNYU1jaGpidUZRMi1rS21lV0pZbFcxN0JZV0xKdTVGWWhMVmxUMk5ZTUlmYjVvb2dvcGM4Z2k5dzctNXVjQXkzRmVCd3VCcWFwSVRIU2NadS1IOXJnRTNmU1ZZdy1PdjVFOVdrOFFmNVBqTFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNM0FpenU5ZFpHLU03bDJ3N2t1MHN3dGVaa1V6NXFKdGplYmhXekpaNGNlQTVvaEF2QWlSWUxTWFVuYjRQRzJ6UjNwTzhJSlhHLWJkNXdpYWJ1UGV3Y05EMGRpN3RHaUtyRUlHS1B1cFdzU2Q2WGhSaGFlbnVBNG13ZFBqNjFCSEI3V3lPTHN0V25UVl80Q1VwQi13RHhHMkd1SzhJQjhpUk1CYlFHMU9tYUxyLW0?oc=5</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNLTVhQVlLblMtNlpMQnNyZjBad2pKQ2F0SmRjVXJXa3ZMcXhTM25BR0VNYU1jaGpidUZRMi1rS21lV0pZbFcxN0JZV0xKdTVGWWhMVmxUMk5ZTUlmYjVvb2dvcGM4Z2k5dzctNXVjQXkzRmVCd3VCcWFwSVRIU2NadS1IOXJnRTNmU1ZZdy1PdjVFOVdrOFFmNVBqTFQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNM0FpenU5ZFpHLU03bDJ3N2t1MHN3dGVaa1V6NXFKdGplYmhXekpaNGNlQTVvaEF2QWlSWUxTWFVuYjRQRzJ6UjNwTzhJSlhHLWJkNXdpYWJ1UGV3Y05EMGRpN3RHaUtyRUlHS1B1cFdzU2Q2WGhSaGFlbnVBNG13ZFBqNjFCSEI3V3lPTHN0V25UVl80Q1VwQi13RHhHMkd1SzhJQjhpUk1CYlFHMU9tYUxyLW0?oc=5</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>6af1b1f739c5791b</t>
+          <t>caeca886c62dcd16</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -6037,22 +6037,22 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing - The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing The Kathmandu Post</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNM0FpenU5ZFpHLU03bDJ3N2t1MHN3dGVaa1V6NXFKdGplYmhXekpaNGNlQTVvaEF2QWlSWUxTWFVuYjRQRzJ6UjNwTzhJSlhHLWJkNXdpYWJ1UGV3Y05EMGRpN3RHaUtyRUlHS1B1cFdzU2Q2WGhSaGFlbnVBNG13ZFBqNjFCSEI3V3lPTHN0V25UVl80Q1VwQi13RHhHMkd1SzhJQjhpUk1CYlFHMU9tYUxyLW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOb0hYSEg3RTlESG8xY2JjUkZ1WVkycTVwUzFkN2d1VElaUWNHYjdFMkxDN1B3dG9UU1dGallPT1hPRTJBSFZvMjdJX2VORGVjV2xHd0pBTDYyQk9aS19melNzZEtWWkFhQWtoc3QxdUpwWDU1UkpiRXZIUEVSNUhtRGVXWEQtaU1RMzVlSG9raXphN0pjSDdYN1JGNWtjMk9OWm9adk9wSm93SXV6N3lteHdBYy0?oc=5</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNM0FpenU5ZFpHLU03bDJ3N2t1MHN3dGVaa1V6NXFKdGplYmhXekpaNGNlQTVvaEF2QWlSWUxTWFVuYjRQRzJ6UjNwTzhJSlhHLWJkNXdpYWJ1UGV3Y05EMGRpN3RHaUtyRUlHS1B1cFdzU2Q2WGhSaGFlbnVBNG13ZFBqNjFCSEI3V3lPTHN0V25UVl80Q1VwQi13RHhHMkd1SzhJQjhpUk1CYlFHMU9tYUxyLW0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOb0hYSEg3RTlESG8xY2JjUkZ1WVkycTVwUzFkN2d1VElaUWNHYjdFMkxDN1B3dG9UU1dGallPT1hPRTJBSFZvMjdJX2VORGVjV2xHd0pBTDYyQk9aS19melNzZEtWWkFhQWtoc3QxdUpwWDU1UkpiRXZIUEVSNUhtRGVXWEQtaU1RMzVlSG9raXphN0pjSDdYN1JGNWtjMk9OWm9adk9wSm93SXV6N3lteHdBYy0?oc=5</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>caeca886c62dcd16</t>
+          <t>36d6bf1476d37aa9</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing - The Kathmandu Post</t>
+          <t>Before And After Satellite Images Show Bhote Koshi Flash Flood Impact In Nepal - News18</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing The Kathmandu Post</t>
+          <t>Before And After Satellite Images Show Bhote Koshi Flash Flood Impact In Nepal News18</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOb0hYSEg3RTlESG8xY2JjUkZ1WVkycTVwUzFkN2d1VElaUWNHYjdFMkxDN1B3dG9UU1dGallPT1hPRTJBSFZvMjdJX2VORGVjV2xHd0pBTDYyQk9aS19melNzZEtWWkFhQWtoc3QxdUpwWDU1UkpiRXZIUEVSNUhtRGVXWEQtaU1RMzVlSG9raXphN0pjSDdYN1JGNWtjMk9OWm9adk9wSm93SXV6N3lteHdBYy0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQTURQOTNzd2UwOXlUZ1JYazZfM0pmLTJLd0EzbmhiSmMyNERtNXhPNzBhWGU4ZktPLWswWXNhbTFGRmllM1dRNG9CRUprZ3JKR1pULXl0YmsydUpBa2pNdkI4TkZUZ2swcDIySFhRNVlmQmVCU0hsOXpWclRVR1NmdG56WEZPTTF2OXlwcDVralZJd3R4M2ZkWDJ2Nm1uS0VTY0JPbksyMzVDanJ1THBET3FfVXlFdUtNQTVfVzJDblJNeE9o0gHKAUFVX3lxTFA3bGFMUjJ2Yl95alEzaXRILUIzS0VNbkJQM0VFejFyZmo0RE0wRS1RT2pELWNjTTZNM1VlWnpieHNyU2NhSGo3aFlwOHRRS3RyaTFJdlZRc3lFYVNGMTUwNUUtRmZPVXQyVG9HU09DeGt1N0syZTd5Y3R4eU5Bc1hOMlo2RFJwRVQ4WjdRV18tRFZQZE9sd3RxbmhoczBCVGo3U3RjaHYyd3VjTHdCVTkyeEdzbk5fOGZSenNLcmg1V3k5QnJsZHVSZXc?oc=5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOb0hYSEg3RTlESG8xY2JjUkZ1WVkycTVwUzFkN2d1VElaUWNHYjdFMkxDN1B3dG9UU1dGallPT1hPRTJBSFZvMjdJX2VORGVjV2xHd0pBTDYyQk9aS19melNzZEtWWkFhQWtoc3QxdUpwWDU1UkpiRXZIUEVSNUhtRGVXWEQtaU1RMzVlSG9raXphN0pjSDdYN1JGNWtjMk9OWm9adk9wSm93SXV6N3lteHdBYy0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxQTURQOTNzd2UwOXlUZ1JYazZfM0pmLTJLd0EzbmhiSmMyNERtNXhPNzBhWGU4ZktPLWswWXNhbTFGRmllM1dRNG9CRUprZ3JKR1pULXl0YmsydUpBa2pNdkI4TkZUZ2swcDIySFhRNVlmQmVCU0hsOXpWclRVR1NmdG56WEZPTTF2OXlwcDVralZJd3R4M2ZkWDJ2Nm1uS0VTY0JPbksyMzVDanJ1THBET3FfVXlFdUtNQTVfVzJDblJNeE9o0gHKAUFVX3lxTFA3bGFMUjJ2Yl95alEzaXRILUIzS0VNbkJQM0VFejFyZmo0RE0wRS1RT2pELWNjTTZNM1VlWnpieHNyU2NhSGo3aFlwOHRRS3RyaTFJdlZRc3lFYVNGMTUwNUUtRmZPVXQyVG9HU09DeGt1N0syZTd5Y3R4eU5Bc1hOMlo2RFJwRVQ4WjdRV18tRFZQZE9sd3RxbmhoczBCVGo3U3RjaHYyd3VjTHdCVTkyeEdzbk5fOGZSenNLcmg1V3k5QnJsZHVSZXc?oc=5</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>36d6bf1476d37aa9</t>
+          <t>e9550e970e5822af</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -6136,27 +6136,27 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>News18</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Before And After Satellite Images Show Bhote Koshi Flash Flood Impact In Nepal - News18</t>
+          <t>In Photos: Bhotekoshi flood leaves a trail of destruction - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Before And After Satellite Images Show Bhote Koshi Flash Flood Impact In Nepal News18</t>
+          <t>In Photos: Bhotekoshi flood leaves a trail of destruction The Kathmandu Post</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQTURQOTNzd2UwOXlUZ1JYazZfM0pmLTJLd0EzbmhiSmMyNERtNXhPNzBhWGU4ZktPLWswWXNhbTFGRmllM1dRNG9CRUprZ3JKR1pULXl0YmsydUpBa2pNdkI4TkZUZ2swcDIySFhRNVlmQmVCU0hsOXpWclRVR1NmdG56WEZPTTF2OXlwcDVralZJd3R4M2ZkWDJ2Nm1uS0VTY0JPbksyMzVDanJ1THBET3FfVXlFdUtNQTVfVzJDblJNeE9o0gHKAUFVX3lxTFA3bGFMUjJ2Yl95alEzaXRILUIzS0VNbkJQM0VFejFyZmo0RE0wRS1RT2pELWNjTTZNM1VlWnpieHNyU2NhSGo3aFlwOHRRS3RyaTFJdlZRc3lFYVNGMTUwNUUtRmZPVXQyVG9HU09DeGt1N0syZTd5Y3R4eU5Bc1hOMlo2RFJwRVQ4WjdRV18tRFZQZE9sd3RxbmhoczBCVGo3U3RjaHYyd3VjTHdCVTkyeEdzbk5fOGZSenNLcmg1V3k5QnJsZHVSZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOclZ4Q0xZRjNpcUF6a1FWcVVJbWFWMU9UM2FTUmFvZWlqeDB6SmhnbVByd1FJOHZEbVdyUUZQOFNfV2c0Z3RrckYyMlk1NVY2YVpDS0p2X05LbWJIOXdMc0h3U3dtNnRVekVzWW1rZzFqSEl0aTJXMDhGZ2FzdVpGeTI0RW5vZVViREhXY19vbWQ0YTZ5N0FyZWZISk5JaERZcDVBdQ?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxQTURQOTNzd2UwOXlUZ1JYazZfM0pmLTJLd0EzbmhiSmMyNERtNXhPNzBhWGU4ZktPLWswWXNhbTFGRmllM1dRNG9CRUprZ3JKR1pULXl0YmsydUpBa2pNdkI4TkZUZ2swcDIySFhRNVlmQmVCU0hsOXpWclRVR1NmdG56WEZPTTF2OXlwcDVralZJd3R4M2ZkWDJ2Nm1uS0VTY0JPbksyMzVDanJ1THBET3FfVXlFdUtNQTVfVzJDblJNeE9o0gHKAUFVX3lxTFA3bGFMUjJ2Yl95alEzaXRILUIzS0VNbkJQM0VFejFyZmo0RE0wRS1RT2pELWNjTTZNM1VlWnpieHNyU2NhSGo3aFlwOHRRS3RyaTFJdlZRc3lFYVNGMTUwNUUtRmZPVXQyVG9HU09DeGt1N0syZTd5Y3R4eU5Bc1hOMlo2RFJwRVQ4WjdRV18tRFZQZE9sd3RxbmhoczBCVGo3U3RjaHYyd3VjTHdCVTkyeEdzbk5fOGZSenNLcmg1V3k5QnJsZHVSZXc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxOclZ4Q0xZRjNpcUF6a1FWcVVJbWFWMU9UM2FTUmFvZWlqeDB6SmhnbVByd1FJOHZEbVdyUUZQOFNfV2c0Z3RrckYyMlk1NVY2YVpDS0p2X05LbWJIOXdMc0h3U3dtNnRVekVzWW1rZzFqSEl0aTJXMDhGZ2FzdVpGeTI0RW5vZVViREhXY19vbWQ0YTZ5N0FyZWZISk5JaERZcDVBdQ?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>e9550e970e5822af</t>
+          <t>aa483da402e56a6d</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -6183,32 +6183,32 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-06T04:35:51Z</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>In Photos: Bhotekoshi flood leaves a trail of destruction - The Kathmandu Post</t>
+          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem - The Tourism Times</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>In Photos: Bhotekoshi flood leaves a trail of destruction The Kathmandu Post</t>
+          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem The Tourism Times</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOclZ4Q0xZRjNpcUF6a1FWcVVJbWFWMU9UM2FTUmFvZWlqeDB6SmhnbVByd1FJOHZEbVdyUUZQOFNfV2c0Z3RrckYyMlk1NVY2YVpDS0p2X05LbWJIOXdMc0h3U3dtNnRVekVzWW1rZzFqSEl0aTJXMDhGZ2FzdVpGeTI0RW5vZVViREhXY19vbWQ0YTZ5N0FyZWZISk5JaERZcDVBdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMDZBSXgwLTR4eERuWXRsNlJOSXlMVEhESHhlWDl3LXFzLS1wWnh5S1h3OHRTb29kYUJSamVKZk9nQmgxSzdlRzhrMlFlVkhVSmY4WDhrcHN0VFdJVFE1YW5xemVpdGhqdWhhTXdxaTN0M3JYQmtWc3BPM0Y2Z2haT0ZMRnF1NU4zUnNMdEFvSmhfa3hhcVpwSWNkRDNvTGpVc2MzLUpsWDZaYVBTT1M5TWJfN1R0VjNJMGwxOGZTQVhKazlaNHFkVFZQZkxYWk5XWUF0MTNR?oc=5</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxOclZ4Q0xZRjNpcUF6a1FWcVVJbWFWMU9UM2FTUmFvZWlqeDB6SmhnbVByd1FJOHZEbVdyUUZQOFNfV2c0Z3RrckYyMlk1NVY2YVpDS0p2X05LbWJIOXdMc0h3U3dtNnRVekVzWW1rZzFqSEl0aTJXMDhGZ2FzdVpGeTI0RW5vZVViREhXY19vbWQ0YTZ5N0FyZWZISk5JaERZcDVBdQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMDZBSXgwLTR4eERuWXRsNlJOSXlMVEhESHhlWDl3LXFzLS1wWnh5S1h3OHRTb29kYUJSamVKZk9nQmgxSzdlRzhrMlFlVkhVSmY4WDhrcHN0VFdJVFE1YW5xemVpdGhqdWhhTXdxaTN0M3JYQmtWc3BPM0Y2Z2haT0ZMRnF1NU4zUnNMdEFvSmhfa3hhcVpwSWNkRDNvTGpVc2MzLUpsWDZaYVBTT1M5TWJfN1R0VjNJMGwxOGZTQVhKazlaNHFkVFZQZkxYWk5XWUF0MTNR?oc=5</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6225,7 +6225,7 @@
     <row r="113" ht="48" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>aa483da402e56a6d</t>
+          <t>2aa7dbd2d902a8d2</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T04:35:51Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>thetourismtimes.com</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem - thetourismtimes.com</t>
+          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem thetourismtimes.com</t>
+          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood The Kathmandu Post</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMDZBSXgwLTR4eERuWXRsNlJOSXlMVEhESHhlWDl3LXFzLS1wWnh5S1h3OHRTb29kYUJSamVKZk9nQmgxSzdlRzhrMlFlVkhVSmY4WDhrcHN0VFdJVFE1YW5xemVpdGhqdWhhTXdxaTN0M3JYQmtWc3BPM0Y2Z2haT0ZMRnF1NU4zUnNMdEFvSmhfa3hhcVpwSWNkRDNvTGpVc2MzLUpsWDZaYVBTT1M5TWJfN1R0VjNJMGwxOGZTQVhKazlaNHFkVFZQZkxYWk5XWUF0MTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxONXRqclNtY1ZodkZDTVNjRkxHTWJZNllvRWtiV0o1clFIVUtaYlNmbGJVSnBlWlpGV2FpOHZYQTRSSUVhNmhrLVRadlRFbDBEZVg5YkFiN1RSVjkxcXQ3WVRNZlRnWWFlTjF5ZGZJTW9PSm40dzZ1VjFmLVBuOWFzR016eDZrQlE1NUo3OUoyY3lYd2p1UGNIeEFBSXNhcUhHV3hhZDN3d0w?oc=5</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMDZBSXgwLTR4eERuWXRsNlJOSXlMVEhESHhlWDl3LXFzLS1wWnh5S1h3OHRTb29kYUJSamVKZk9nQmgxSzdlRzhrMlFlVkhVSmY4WDhrcHN0VFdJVFE1YW5xemVpdGhqdWhhTXdxaTN0M3JYQmtWc3BPM0Y2Z2haT0ZMRnF1NU4zUnNMdEFvSmhfa3hhcVpwSWNkRDNvTGpVc2MzLUpsWDZaYVBTT1M5TWJfN1R0VjNJMGwxOGZTQVhKazlaNHFkVFZQZkxYWk5XWUF0MTNR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxONXRqclNtY1ZodkZDTVNjRkxHTWJZNllvRWtiV0o1clFIVUtaYlNmbGJVSnBlWlpGV2FpOHZYQTRSSUVhNmhrLVRadlRFbDBEZVg5YkFiN1RSVjkxcXQ3WVRNZlRnWWFlTjF5ZGZJTW9PSm40dzZ1VjFmLVBuOWFzR016eDZrQlE1NUo3OUoyY3lYd2p1UGNIeEFBSXNhcUhHV3hhZDN3d0w?oc=5</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="114" ht="48" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>2aa7dbd2d902a8d2</t>
+          <t>28762909049f8568</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood - The Kathmandu Post</t>
+          <t>What we know about the Bhotekoshi flood so far - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood The Kathmandu Post</t>
+          <t>What we know about the Bhotekoshi flood so far The Kathmandu Post</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxONXRqclNtY1ZodkZDTVNjRkxHTWJZNllvRWtiV0o1clFIVUtaYlNmbGJVSnBlWlpGV2FpOHZYQTRSSUVhNmhrLVRadlRFbDBEZVg5YkFiN1RSVjkxcXQ3WVRNZlRnWWFlTjF5ZGZJTW9PSm40dzZ1VjFmLVBuOWFzR016eDZrQlE1NUo3OUoyY3lYd2p1UGNIeEFBSXNhcUhHV3hhZDN3d0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTlnUUNMdVFFMHVGS0gyTnZreWIyN1pPeTR4UlJoNFM5ZVNJRTQ0MU1JbkhjaXdfQlpDUnV5MkJudkJLbF9qcUx2OThWSWVINlVmeENFclZnS0NKOVZHZ09JTG9CT1g5Wk9GaW9ZRUNlRjZKMkh3TTc3b2JxS190QTQza01LajFFZUVXaUs3bFJ2Z1BmQ19J?oc=5</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxONXRqclNtY1ZodkZDTVNjRkxHTWJZNllvRWtiV0o1clFIVUtaYlNmbGJVSnBlWlpGV2FpOHZYQTRSSUVhNmhrLVRadlRFbDBEZVg5YkFiN1RSVjkxcXQ3WVRNZlRnWWFlTjF5ZGZJTW9PSm40dzZ1VjFmLVBuOWFzR016eDZrQlE1NUo3OUoyY3lYd2p1UGNIeEFBSXNhcUhHV3hhZDN3d0w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTlnUUNMdVFFMHVGS0gyTnZreWIyN1pPeTR4UlJoNFM5ZVNJRTQ0MU1JbkhjaXdfQlpDUnV5MkJudkJLbF9qcUx2OThWSWVINlVmeENFclZnS0NKOVZHZ09JTG9CT1g5Wk9GaW9ZRUNlRjZKMkh3TTc3b2JxS190QTQza01LajFFZUVXaUs3bFJ2Z1BmQ19J?oc=5</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -6329,42 +6329,42 @@
     <row r="115" ht="48" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>28762909049f8568</t>
+          <t>74b200acb9b39a43</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-13T11:48:33Z</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>What we know about the Bhotekoshi flood so far - The Kathmandu Post</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>What we know about the Bhotekoshi flood so far The Kathmandu Post</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTlnUUNMdVFFMHVGS0gyTnZreWIyN1pPeTR4UlJoNFM5ZVNJRTQ0MU1JbkhjaXdfQlpDUnV5MkJudkJLbF9qcUx2OThWSWVINlVmeENFclZnS0NKOVZHZ09JTG9CT1g5Wk9GaW9ZRUNlRjZKMkh3TTc3b2JxS190QTQza01LajFFZUVXaUs3bFJ2Z1BmQ19J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTlnUUNMdVFFMHVGS0gyTnZreWIyN1pPeTR4UlJoNFM5ZVNJRTQ0MU1JbkhjaXdfQlpDUnV5MkJudkJLbF9qcUx2OThWSWVINlVmeENFclZnS0NKOVZHZ09JTG9CT1g5Wk9GaW9ZRUNlRjZKMkh3TTc3b2JxS190QTQza01LajFFZUVXaUs3bFJ2Z1BmQ19J?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -6381,7 +6381,7 @@
     <row r="116" ht="48" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>74b200acb9b39a43</t>
+          <t>ae42ae903bc8d76f</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T11:48:33Z</t>
+          <t>2026-09-13T04:44:23Z</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -6433,42 +6433,42 @@
     <row r="117" ht="48" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>ae42ae903bc8d76f</t>
+          <t>b053f134835909ae</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T04:44:23Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood: Family cremates four after hope of return fades - Khabarhub</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood: Family cremates four after hope of return fades Khabarhub</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -7161,7 +7161,7 @@
     <row r="131" ht="48" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>a6b93b3275da5c95</t>
+          <t>3362db09970c68c5</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -7171,32 +7171,32 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>National Mourning Day Observed Today in Memory of Bhotekoshi Flood Victims - radionepalonline.com</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,293 - Khabarhub</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>National Mourning Day Observed Today in Memory of Bhotekoshi Flood Victims radionepalonline.com</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,293 Khabarhub</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wYmZ4YlBCUkxyWTVZQjlsQy00M25TTVFrbVh0Q2dtZTBENkFPVHZrNGM2N1RYY3FiUjZBckFMT3hhaU02Ykp0X3lfQXRKeG5lQVBEbHRJamUxbkh1MmIxcERoaVY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1vWU1zUG5BMEFBVnhOZE9mWjVRMUM4Q1ZMVG9jMS1sOC0wd0owOWZ6NnFXVUJPNmpRcnE3RmZ4eVhJQXZtWTFnX1JYazA1ZUlHT3pIeXplbEE?oc=5</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wYmZ4YlBCUkxyWTVZQjlsQy00M25TTVFrbVh0Q2dtZTBENkFPVHZrNGM2N1RYY3FiUjZBckFMT3hhaU02Ykp0X3lfQXRKeG5lQVBEbHRJamUxbkh1MmIxcERoaVY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1vWU1zUG5BMEFBVnhOZE9mWjVRMUM4Q1ZMVG9jMS1sOC0wd0owOWZ6NnFXVUJPNmpRcnE3RmZ4eVhJQXZtWTFnX1JYazA1ZUlHT3pIeXplbEE?oc=5</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -7213,7 +7213,7 @@
     <row r="132" ht="48" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>7c4f8e2a99a4ce1f</t>
+          <t>a6b93b3275da5c95</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
@@ -7228,27 +7228,27 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - Nepalnews.com</t>
+          <t>National Mourning Day Observed Today in Memory of Bhotekoshi Flood Victims - radionepalonline.com</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund Nepalnews.com</t>
+          <t>National Mourning Day Observed Today in Memory of Bhotekoshi Flood Victims radionepalonline.com</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wYmZ4YlBCUkxyWTVZQjlsQy00M25TTVFrbVh0Q2dtZTBENkFPVHZrNGM2N1RYY3FiUjZBckFMT3hhaU02Ykp0X3lfQXRKeG5lQVBEbHRJamUxbkh1MmIxcERoaVY?oc=5</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wYmZ4YlBCUkxyWTVZQjlsQy00M25TTVFrbVh0Q2dtZTBENkFPVHZrNGM2N1RYY3FiUjZBckFMT3hhaU02Ykp0X3lfQXRKeG5lQVBEbHRJamUxbkh1MmIxcERoaVY?oc=5</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -7265,7 +7265,7 @@
     <row r="133" ht="48" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>32607a2038a98f33</t>
+          <t>7c4f8e2a99a4ce1f</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
@@ -7280,27 +7280,27 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>boldnewsonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Death Toll Climbs to 1,341 - boldnewsonline.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - Nepalnews.com</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Death Toll Climbs to 1,341 boldnewsonline.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund Nepalnews.com</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5uRTlwNzFEN1lYazN3Y04td1NCMlBIX3RRNjJmS0VUMFVsV2hLMUdVODZVeFRNcmZ6R0VYbGV2UXM2XzV0MzBKNUpTbjRFUlMzX0t4UHphUkhFM2UzMTBiclhUN2ZaZl90MWZyYjZLTnp6NWFSRS04UGZBYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMie0FVX3lxTE5uRTlwNzFEN1lYazN3Y04td1NCMlBIX3RRNjJmS0VUMFVsV2hLMUdVODZVeFRNcmZ6R0VYbGV2UXM2XzV0MzBKNUpTbjRFUlMzX0t4UHphUkhFM2UzMTBiclhUN2ZaZl90MWZyYjZLTnp6NWFSRS04UGZBYw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="134" ht="48" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>89e9a4d07a132f8a</t>
+          <t>32607a2038a98f33</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T23:08:55Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>boldnewsonline.com</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
+          <t>Bhote Koshi Flood Death Toll Climbs to 1,341 - boldnewsonline.com</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
+          <t>Bhote Koshi Flood Death Toll Climbs to 1,341 boldnewsonline.com</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdzRoc3R0cDZUTlRoQzF1WU1YSnRJOHNWSmNZMDB2VU5nWjViV2p4R0NmMlZ2cFBxXzE4dW9uNmhCRmkwYXV1WW05UDdNUi1TakpOVUoyZmNfdUo0RGp4MFpNUnhobFBuQlFNR2RHZXozekxPUHp4UEU2X2VwX1lNVGtKTkJFbXlqRU9DdWxDZjlOenlUcFRBa3NGdUFyeGZfUnkxcnpVZEcwUnlQTmdoaVNPWUVtX2VZNnpHR1VqOXBCZVVNQlBN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5uRTlwNzFEN1lYazN3Y04td1NCMlBIX3RRNjJmS0VUMFVsV2hLMUdVODZVeFRNcmZ6R0VYbGV2UXM2XzV0MzBKNUpTbjRFUlMzX0t4UHphUkhFM2UzMTBiclhUN2ZaZl90MWZyYjZLTnp6NWFSRS04UGZBYw?oc=5</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOdzRoc3R0cDZUTlRoQzF1WU1YSnRJOHNWSmNZMDB2VU5nWjViV2p4R0NmMlZ2cFBxXzE4dW9uNmhCRmkwYXV1WW05UDdNUi1TakpOVUoyZmNfdUo0RGp4MFpNUnhobFBuQlFNR2RHZXozekxPUHp4UEU2X2VwX1lNVGtKTkJFbXlqRU9DdWxDZjlOenlUcFRBa3NGdUFyeGZfUnkxcnpVZEcwUnlQTmdoaVNPWUVtX2VZNnpHR1VqOXBCZVVNQlBN?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMie0FVX3lxTE5uRTlwNzFEN1lYazN3Y04td1NCMlBIX3RRNjJmS0VUMFVsV2hLMUdVODZVeFRNcmZ6R0VYbGV2UXM2XzV0MzBKNUpTbjRFUlMzX0t4UHphUkhFM2UzMTBiclhUN2ZaZl90MWZyYjZLTnp6NWFSRS04UGZBYw?oc=5</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -7369,7 +7369,7 @@
     <row r="135" ht="48" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>f32b02490f2f13bb</t>
+          <t>89e9a4d07a132f8a</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-10T23:08:55Z</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -7389,22 +7389,22 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood exposes Nepal’s warning system, raises questions over state accountability - myRepublica</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood exposes Nepal’s warning system, raises questions over state accountability myRepublica</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdUJaZy1aSktUZUZVTmJ4cE5XZ2E2RmxNX0QyZFZsdGdSNlhKSW1JRjk4RU04b0t4NURXVU12ZHFLTFNCNzNqcVNPbERLRXhKOWZsQVZTbGo0NjBtWURFZFRzeDVPTkxZVEhoUk8za2ZHajVBRzk1bGhRckxJdkRaUUw4WHNQcHlib2JDWnZlYl9paXFUeHdlWFN0UExMQ18wWVloeXZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdzRoc3R0cDZUTlRoQzF1WU1YSnRJOHNWSmNZMDB2VU5nWjViV2p4R0NmMlZ2cFBxXzE4dW9uNmhCRmkwYXV1WW05UDdNUi1TakpOVUoyZmNfdUo0RGp4MFpNUnhobFBuQlFNR2RHZXozekxPUHp4UEU2X2VwX1lNVGtKTkJFbXlqRU9DdWxDZjlOenlUcFRBa3NGdUFyeGZfUnkxcnpVZEcwUnlQTmdoaVNPWUVtX2VZNnpHR1VqOXBCZVVNQlBN?oc=5</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxPdUJaZy1aSktUZUZVTmJ4cE5XZ2E2RmxNX0QyZFZsdGdSNlhKSW1JRjk4RU04b0t4NURXVU12ZHFLTFNCNzNqcVNPbERLRXhKOWZsQVZTbGo0NjBtWURFZFRzeDVPTkxZVEhoUk8za2ZHajVBRzk1bGhRckxJdkRaUUw4WHNQcHlib2JDWnZlYl9paXFUeHdlWFN0UExMQ18wWVloeXZR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOdzRoc3R0cDZUTlRoQzF1WU1YSnRJOHNWSmNZMDB2VU5nWjViV2p4R0NmMlZ2cFBxXzE4dW9uNmhCRmkwYXV1WW05UDdNUi1TakpOVUoyZmNfdUo0RGp4MFpNUnhobFBuQlFNR2RHZXozekxPUHp4UEU2X2VwX1lNVGtKTkJFbXlqRU9DdWxDZjlOenlUcFRBa3NGdUFyeGZfUnkxcnpVZEcwUnlQTmdoaVNPWUVtX2VZNnpHR1VqOXBCZVVNQlBN?oc=5</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>9a5bbb90dc6eac43</t>
+          <t>f32b02490f2f13bb</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -7431,32 +7431,32 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>775 people remain missing in Bhote Koshi flood, including 587 foreign nationals - Nepalnews.com</t>
+          <t>Bhotekoshi flood exposes Nepal’s warning system, raises questions over state accountability - myRepublica</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>775 people remain missing in Bhote Koshi flood, including 587 foreign nationals Nepalnews.com</t>
+          <t>Bhotekoshi flood exposes Nepal’s warning system, raises questions over state accountability myRepublica</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTlNVcm1YM3g2TFpTVDlJc0hWVnpUZ1NkS0xJZUlwRzJ0bDV5dDczaDZ3Y1hJWERmcUJnaEpmcERZS1hfeC1qbC1keVVzZlczRy1jRXFTUmM0RGV2VFFBOWx1QzVtVHhRSWJydGxrN1RrS3hsYk51RTBGU3haTGhaZWVOQzBuQjBPcUZoRmRITDd4dXdsbUhvakg5NHp1MzJzbFNXMFpvS01rb2I3V3lla3ZtSFEybExzSWNObUotMmlFOXQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdUJaZy1aSktUZUZVTmJ4cE5XZ2E2RmxNX0QyZFZsdGdSNlhKSW1JRjk4RU04b0t4NURXVU12ZHFLTFNCNzNqcVNPbERLRXhKOWZsQVZTbGo0NjBtWURFZFRzeDVPTkxZVEhoUk8za2ZHajVBRzk1bGhRckxJdkRaUUw4WHNQcHlib2JDWnZlYl9paXFUeHdlWFN0UExMQ18wWVloeXZR?oc=5</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOTlNVcm1YM3g2TFpTVDlJc0hWVnpUZ1NkS0xJZUlwRzJ0bDV5dDczaDZ3Y1hJWERmcUJnaEpmcERZS1hfeC1qbC1keVVzZlczRy1jRXFTUmM0RGV2VFFBOWx1QzVtVHhRSWJydGxrN1RrS3hsYk51RTBGU3haTGhaZWVOQzBuQjBPcUZoRmRITDd4dXdsbUhvakg5NHp1MzJzbFNXMFpvS01rb2I3V3lla3ZtSFEybExzSWNObUotMmlFOXQw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxPdUJaZy1aSktUZUZVTmJ4cE5XZ2E2RmxNX0QyZFZsdGdSNlhKSW1JRjk4RU04b0t4NURXVU12ZHFLTFNCNzNqcVNPbERLRXhKOWZsQVZTbGo0NjBtWURFZFRzeDVPTkxZVEhoUk8za2ZHajVBRzk1bGhRckxJdkRaUUw4WHNQcHlib2JDWnZlYl9paXFUeHdlWFN0UExMQ18wWVloeXZR?oc=5</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="137" ht="48" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>fc7ba7db5d3cb268</t>
+          <t>9a5bbb90dc6eac43</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T21:07:58Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 587 foreign tourists from 34 countries missing – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>775 people remain missing in Bhote Koshi flood, including 587 foreign nationals - Nepalnews.com</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 587 foreign tourists from 34 countries missing – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>775 people remain missing in Bhote Koshi flood, including 587 foreign nationals Nepalnews.com</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9LSld2YjJIRnFKenpCV19Ub1NkdXhhcXJ0UWRQemZkb1FjRVBhcjNzTXQ0UWxUUjZvbzFUTzVGdXUxZDNlT0Q5ZUlnNDhYUXN6UzI5Nnp5ZF9iSW1zaXA5UU1qUk8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTlNVcm1YM3g2TFpTVDlJc0hWVnpUZ1NkS0xJZUlwRzJ0bDV5dDczaDZ3Y1hJWERmcUJnaEpmcERZS1hfeC1qbC1keVVzZlczRy1jRXFTUmM0RGV2VFFBOWx1QzVtVHhRSWJydGxrN1RrS3hsYk51RTBGU3haTGhaZWVOQzBuQjBPcUZoRmRITDd4dXdsbUhvakg5NHp1MzJzbFNXMFpvS01rb2I3V3lla3ZtSFEybExzSWNObUotMmlFOXQw?oc=5</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9LSld2YjJIRnFKenpCV19Ub1NkdXhhcXJ0UWRQemZkb1FjRVBhcjNzTXQ0UWxUUjZvbzFUTzVGdXUxZDNlT0Q5ZUlnNDhYUXN6UzI5Nnp5ZF9iSW1zaXA5UU1qUk8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOTlNVcm1YM3g2TFpTVDlJc0hWVnpUZ1NkS0xJZUlwRzJ0bDV5dDczaDZ3Y1hJWERmcUJnaEpmcERZS1hfeC1qbC1keVVzZlczRy1jRXFTUmM0RGV2VFFBOWx1QzVtVHhRSWJydGxrN1RrS3hsYk51RTBGU3haTGhaZWVOQzBuQjBPcUZoRmRITDd4dXdsbUhvakg5NHp1MzJzbFNXMFpvS01rb2I3V3lla3ZtSFEybExzSWNObUotMmlFOXQw?oc=5</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -7525,7 +7525,7 @@
     <row r="138" ht="48" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>8162ad1453d0b13b</t>
+          <t>fc7ba7db5d3cb268</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -7535,32 +7535,32 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-08T21:07:58Z</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh provides USD 1 million aid to Bhotekoshi flood victims - Khabarhub</t>
+          <t>Bhotekoshi flood: 587 foreign tourists from 34 countries missing – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh provides USD 1 million aid to Bhotekoshi flood victims Khabarhub</t>
+          <t>Bhotekoshi flood: 587 foreign tourists from 34 countries missing – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE44ZXJ1VDNVdTZ4QmdyYkJIZDZIblY3V1pmSGdnOWZrM0NMLVozS1FsQnBCRXNGdndJNF84ZUR0aVB6VU9hSE5jYXBJVWdTRmduQUlrd0xhaW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9LSld2YjJIRnFKenpCV19Ub1NkdXhhcXJ0UWRQemZkb1FjRVBhcjNzTXQ0UWxUUjZvbzFUTzVGdXUxZDNlT0Q5ZUlnNDhYUXN6UzI5Nnp5ZF9iSW1zaXA5UU1qUk8?oc=5</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE44ZXJ1VDNVdTZ4QmdyYkJIZDZIblY3V1pmSGdnOWZrM0NMLVozS1FsQnBCRXNGdndJNF84ZUR0aVB6VU9hSE5jYXBJVWdTRmduQUlrd0xhaW8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9LSld2YjJIRnFKenpCV19Ub1NkdXhhcXJ0UWRQemZkb1FjRVBhcjNzTXQ0UWxUUjZvbzFUTzVGdXUxZDNlT0Q5ZUlnNDhYUXN6UzI5Nnp5ZF9iSW1zaXA5UU1qUk8?oc=5</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -7577,7 +7577,7 @@
     <row r="139" ht="48" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>f43348b0ff3c84ce</t>
+          <t>8162ad1453d0b13b</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: National Day of Mourning observed - risingnepaldaily.com</t>
+          <t>Bangladesh provides USD 1 million aid to Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: National Day of Mourning observed risingnepaldaily.com</t>
+          <t>Bangladesh provides USD 1 million aid to Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1fYUF1QTVTS3lxUXVQZDZlajFqbEh6RXhmT3RrUDB1MkpaMkQxYVN3Znd6aXlGMWwxaFN3V2lJNXpwN3ZWaGtHb08xYVloaXR2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE44ZXJ1VDNVdTZ4QmdyYkJIZDZIblY3V1pmSGdnOWZrM0NMLVozS1FsQnBCRXNGdndJNF84ZUR0aVB6VU9hSE5jYXBJVWdTRmduQUlrd0xhaW8?oc=5</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1fYUF1QTVTS3lxUXVQZDZlajFqbEh6RXhmT3RrUDB1MkpaMkQxYVN3Znd6aXlGMWwxaFN3V2lJNXpwN3ZWaGtHb08xYVloaXR2?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE44ZXJ1VDNVdTZ4QmdyYkJIZDZIblY3V1pmSGdnOWZrM0NMLVozS1FsQnBCRXNGdndJNF84ZUR0aVB6VU9hSE5jYXBJVWdTRmduQUlrd0xhaW8?oc=5</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="140" ht="48" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>7f3783a8d8a09b8c</t>
+          <t>f43348b0ff3c84ce</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -7639,32 +7639,32 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>risingnepaldaily.com</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: More than 13,000 rescued – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhotekoshi flood: National Day of Mourning observed - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: More than 13,000 rescued – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhotekoshi flood: National Day of Mourning observed risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFB5Zlc5M3VxMTQ4QXVnOGRkcjhwSVJMMFhZRGIzc2dTNU10TllMZVNXZ3FZbjg1d1pfeC00by1KaGFJbkFvNUNSb1p3SWI1c0ZjNU4wUFJmSjZwSmwzN1kyenJkeG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1fYUF1QTVTS3lxUXVQZDZlajFqbEh6RXhmT3RrUDB1MkpaMkQxYVN3Znd6aXlGMWwxaFN3V2lJNXpwN3ZWaGtHb08xYVloaXR2?oc=5</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFB5Zlc5M3VxMTQ4QXVnOGRkcjhwSVJMMFhZRGIzc2dTNU10TllMZVNXZ3FZbjg1d1pfeC00by1KaGFJbkFvNUNSb1p3SWI1c0ZjNU4wUFJmSjZwSmwzN1kyenJkeG4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1fYUF1QTVTS3lxUXVQZDZlajFqbEh6RXhmT3RrUDB1MkpaMkQxYVN3Znd6aXlGMWwxaFN3V2lJNXpwN3ZWaGtHb08xYVloaXR2?oc=5</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -7681,7 +7681,7 @@
     <row r="141" ht="48" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>d66c2531c86c7532</t>
+          <t>7f3783a8d8a09b8c</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -7691,32 +7691,32 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>1,355 bodies recovered so far in Rasuwa flood disaster - Nepalnews.com</t>
+          <t>Bhotekoshi flood: More than 13,000 rescued – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>1,355 bodies recovered so far in Rasuwa flood disaster Nepalnews.com</t>
+          <t>Bhotekoshi flood: More than 13,000 rescued – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNbENiWlBCQmtTbjVocWxsalpJLUJPSGxpenI2NlNDUWtidGROMVFWdlRuQjJRaWUzMEVSWm5iV3g3QVVjYkgyU1ZZUnpBMkp3R0JHYjNfa2hmSUhOQUxHaUlpcWZNM21fU2FXeWVlUThsQkpOWWFHMjBNRnVSOThTSGNwNVlIVDZySXRHcEtwRUxzeWh5bzBNaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFB5Zlc5M3VxMTQ4QXVnOGRkcjhwSVJMMFhZRGIzc2dTNU10TllMZVNXZ3FZbjg1d1pfeC00by1KaGFJbkFvNUNSb1p3SWI1c0ZjNU4wUFJmSjZwSmwzN1kyenJkeG4?oc=5</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNbENiWlBCQmtTbjVocWxsalpJLUJPSGxpenI2NlNDUWtidGROMVFWdlRuQjJRaWUzMEVSWm5iV3g3QVVjYkgyU1ZZUnpBMkp3R0JHYjNfa2hmSUhOQUxHaUlpcWZNM21fU2FXeWVlUThsQkpOWWFHMjBNRnVSOThTSGNwNVlIVDZySXRHcEtwRUxzeWh5bzBNaw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFB5Zlc5M3VxMTQ4QXVnOGRkcjhwSVJMMFhZRGIzc2dTNU10TllMZVNXZ3FZbjg1d1pfeC00by1KaGFJbkFvNUNSb1p3SWI1c0ZjNU4wUFJmSjZwSmwzN1kyenJkeG4?oc=5</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="142" ht="48" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>7065107f5e15019e</t>
+          <t>d66c2531c86c7532</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
@@ -7748,27 +7748,27 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
+          <t>1,355 bodies recovered so far in Rasuwa flood disaster - Nepalnews.com</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
+          <t>1,355 bodies recovered so far in Rasuwa flood disaster Nepalnews.com</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRWpqOGQwYzFlX2prZDViaVVRa1dabng0VlloRmswWGttellVZ1IxSEw5NV9kc2ZocW43YlBHWWhQaVNVMVBxMGNockNvdG14cWpIdm9EREZrN2pheVpqdm5KVHZaUmkzcDhkZzY5aWNZVEh4dFAta2t6amszaWg4QmR0SThHOEdoLXpiZkFCek9naHNhTlBDUXFaWkY0VUF2Sm5pM0pWV2NfMlByMER1d19EbVZwdTc0Q3RoZnVBcGJjVndVN3JZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNbENiWlBCQmtTbjVocWxsalpJLUJPSGxpenI2NlNDUWtidGROMVFWdlRuQjJRaWUzMEVSWm5iV3g3QVVjYkgyU1ZZUnpBMkp3R0JHYjNfa2hmSUhOQUxHaUlpcWZNM21fU2FXeWVlUThsQkpOWWFHMjBNRnVSOThTSGNwNVlIVDZySXRHcEtwRUxzeWh5bzBNaw?oc=5</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxQRWpqOGQwYzFlX2prZDViaVVRa1dabng0VlloRmswWGttellVZ1IxSEw5NV9kc2ZocW43YlBHWWhQaVNVMVBxMGNockNvdG14cWpIdm9EREZrN2pheVpqdm5KVHZaUmkzcDhkZzY5aWNZVEh4dFAta2t6amszaWg4QmR0SThHOEdoLXpiZkFCek9naHNhTlBDUXFaWkY0VUF2Sm5pM0pWV2NfMlByMER1d19EbVZwdTc0Q3RoZnVBcGJjVndVN3JZ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNbENiWlBCQmtTbjVocWxsalpJLUJPSGxpenI2NlNDUWtidGROMVFWdlRuQjJRaWUzMEVSWm5iV3g3QVVjYkgyU1ZZUnpBMkp3R0JHYjNfa2hmSUhOQUxHaUlpcWZNM21fU2FXeWVlUThsQkpOWWFHMjBNRnVSOThTSGNwNVlIVDZySXRHcEtwRUxzeWh5bzBNaw?oc=5</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -7785,42 +7785,42 @@
     <row r="143" ht="48" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>2ee38bc59050fb64</t>
+          <t>7065107f5e15019e</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss - The Himalayan Times</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myRepublica</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss The Himalayan Times</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myRepublica</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRWpqOGQwYzFlX2prZDViaVVRa1dabng0VlloRmswWGttellVZ1IxSEw5NV9kc2ZocW43YlBHWWhQaVNVMVBxMGNockNvdG14cWpIdm9EREZrN2pheVpqdm5KVHZaUmkzcDhkZzY5aWNZVEh4dFAta2t6amszaWg4QmR0SThHOEdoLXpiZkFCek9naHNhTlBDUXFaWkY0VUF2Sm5pM0pWV2NfMlByMER1d19EbVZwdTc0Q3RoZnVBcGJjVndVN3JZ?oc=5</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxQRWpqOGQwYzFlX2prZDViaVVRa1dabng0VlloRmswWGttellVZ1IxSEw5NV9kc2ZocW43YlBHWWhQaVNVMVBxMGNockNvdG14cWpIdm9EREZrN2pheVpqdm5KVHZaUmkzcDhkZzY5aWNZVEh4dFAta2t6amszaWg4QmR0SThHOEdoLXpiZkFCek9naHNhTlBDUXFaWkY0VUF2Sm5pM0pWV2NfMlByMER1d19EbVZwdTc0Q3RoZnVBcGJjVndVN3JZ?oc=5</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -7837,7 +7837,7 @@
     <row r="144" ht="48" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>4255cd2b59ff3527</t>
+          <t>2ee38bc59050fb64</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -7847,32 +7847,32 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing - Khabarhub</t>
+          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss - The Himalayan Times</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing Khabarhub</t>
+          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss The Himalayan Times</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="145" ht="48" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>9d37d48a2c995a2b</t>
+          <t>4255cd2b59ff3527</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing - Khabarhub</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing Khabarhub</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7941,7 +7941,7 @@
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>ce567896a53480b0</t>
+          <t>9d37d48a2c995a2b</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
@@ -7951,32 +7951,32 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment - myRepublica</t>
+          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment myRepublica</t>
+          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts english.khabarhub.com</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -7993,7 +7993,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>7ac6592e31db85a5</t>
+          <t>ce567896a53480b0</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
+          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment - myRepublica</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
+          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment myRepublica</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>8b22056f7cc30e08</t>
+          <t>7ac6592e31db85a5</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T04:36:55Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>2d236097b3cf1832</t>
+          <t>8b22056f7cc30e08</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-07T04:36:55Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -8117,22 +8117,22 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>54ae0dd183a5ffe8</t>
+          <t>2d236097b3cf1832</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing - Ratopati</t>
+          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing Ratopati</t>
+          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="151" ht="48" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>007a8e4ea9da5310</t>
+          <t>54ae0dd183a5ffe8</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -8211,32 +8211,32 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing - Ratopati</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing Ratopati</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -8253,42 +8253,42 @@
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>8c46e92e2eedb44d</t>
+          <t>007a8e4ea9da5310</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T20:18:30Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Chinese worker pulled alive from Trishuli 1 tunnel 10 days after Rasuwa flood disaster - myRepublica</t>
+          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Chinese worker pulled alive from Trishuli 1 tunnel 10 days after Rasuwa flood disaster myRepublica</t>
+          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQMmpmVkxSWEFtbmx6TDNENkx0amoweU02emd0UC1xaEQ3Ym1TRUw3RTc4a3pIaWdwNGxJMTVBOUktOHN2ZDJ0NWhFOXNxWHFmb180UmhTQmt1WmY3NlpvdjNBYXJvMjR0VzVNZ3ZlV1hyMm1KbEVFdXplV3NzOWV5Uzdta0NkWDhjeWdMUnkycHZrUkxqQ0xSa0lQSHRfbkllLWtRTUszUThVU0FFTVVCRDlvQ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQMmpmVkxSWEFtbmx6TDNENkx0amoweU02emd0UC1xaEQ3Ym1TRUw3RTc4a3pIaWdwNGxJMTVBOUktOHN2ZDJ0NWhFOXNxWHFmb180UmhTQmt1WmY3NlpvdjNBYXJvMjR0VzVNZ3ZlV1hyMm1KbEVFdXplV3NzOWV5Uzdta0NkWDhjeWdMUnkycHZrUkxqQ0xSa0lQSHRfbkllLWtRTUszUThVU0FFTVVCRDlvQ2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8305,7 +8305,7 @@
     <row r="153" ht="48" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>b42da176f0e827b6</t>
+          <t>8c46e92e2eedb44d</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-05T20:18:30Z</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
+          <t>Chinese worker pulled alive from Trishuli 1 tunnel 10 days after Rasuwa flood disaster - myRepublica</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
+          <t>Chinese worker pulled alive from Trishuli 1 tunnel 10 days after Rasuwa flood disaster myRepublica</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQMmpmVkxSWEFtbmx6TDNENkx0amoweU02emd0UC1xaEQ3Ym1TRUw3RTc4a3pIaWdwNGxJMTVBOUktOHN2ZDJ0NWhFOXNxWHFmb180UmhTQmt1WmY3NlpvdjNBYXJvMjR0VzVNZ3ZlV1hyMm1KbEVFdXplV3NzOWV5Uzdta0NkWDhjeWdMUnkycHZrUkxqQ0xSa0lQSHRfbkllLWtRTUszUThVU0FFTVVCRDlvQ2c?oc=5</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQMmpmVkxSWEFtbmx6TDNENkx0amoweU02emd0UC1xaEQ3Ym1TRUw3RTc4a3pIaWdwNGxJMTVBOUktOHN2ZDJ0NWhFOXNxWHFmb180UmhTQmt1WmY3NlpvdjNBYXJvMjR0VzVNZ3ZlV1hyMm1KbEVFdXplV3NzOWV5Uzdta0NkWDhjeWdMUnkycHZrUkxqQ0xSa0lQSHRfbkllLWtRTUszUThVU0FFTVVCRDlvQ2c?oc=5</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>f805b0f8b9633407</t>
+          <t>b42da176f0e827b6</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -8367,32 +8367,32 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T17:19:49Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="155" ht="48" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>c5ff5f7f2df9bf7b</t>
+          <t>f805b0f8b9633407</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -8419,32 +8419,32 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-05T17:19:49Z</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myRepublica</t>
+          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myRepublica</t>
+          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONmZ6RWs4VkhQZ3RHeUpwNWdEbnNvRGMwTE1tX1lBUWJ3eHhnMnFhZElYb0s3X2M3TTNsMkZXMXFKRXE3WlNzU1BSdDlfQXlxOHpIeC1ZbzRmT25xTFBRVjRFdEc1Yi1wVE1rZ3UzQUdhNXVGUXV5dEVManh1MF9sTzBQR3lCdFI2QzhNSWJlQkpGNy1fbUdoUHN2UW16VlA4VmUtYUtzV28wMXdVN1gwVDFwRlQzWnJPNlJaeTBRSXA4eGxiTG9Jc0VlSGItdGticmVBUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi1AFBVV95cUxONmZ6RWs4VkhQZ3RHeUpwNWdEbnNvRGMwTE1tX1lBUWJ3eHhnMnFhZElYb0s3X2M3TTNsMkZXMXFKRXE3WlNzU1BSdDlfQXlxOHpIeC1ZbzRmT25xTFBRVjRFdEc1Yi1wVE1rZ3UzQUdhNXVGUXV5dEVManh1MF9sTzBQR3lCdFI2QzhNSWJlQkpGNy1fbUdoUHN2UW16VlA4VmUtYUtzV28wMXdVN1gwVDFwRlQzWnJPNlJaeTBRSXA4eGxiTG9Jc0VlSGItdGticmVBUw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>c961382bdeb2fc5d</t>
+          <t>c5ff5f7f2df9bf7b</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -8471,32 +8471,32 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No-6 (As of 5 September 2026) - consultaelectoral.onpe.gob.pe</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No-6 (As of 5 September 2026) consultaelectoral.onpe.gob.pe</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQ2t4eHFrZFFjNUtodWcxOG1lT2JQcVowdy14OTFCNExXMEE4QXlHcXo0dklVem1ER2F6emZHN3VaZko0WVpNbTZ1NmlpcEZGUU1vbjZyemJCMkpJN0pnQTN0eU5XRTVtUXNWdEJYVG55WGdzbGRvdlMxR0FTd2VscDdmOUthRUs2eW02azQtMkZvMl9pNkdr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONmZ6RWs4VkhQZ3RHeUpwNWdEbnNvRGMwTE1tX1lBUWJ3eHhnMnFhZElYb0s3X2M3TTNsMkZXMXFKRXE3WlNzU1BSdDlfQXlxOHpIeC1ZbzRmT25xTFBRVjRFdEc1Yi1wVE1rZ3UzQUdhNXVGUXV5dEVManh1MF9sTzBQR3lCdFI2QzhNSWJlQkpGNy1fbUdoUHN2UW16VlA4VmUtYUtzV28wMXdVN1gwVDFwRlQzWnJPNlJaeTBRSXA4eGxiTG9Jc0VlSGItdGticmVBUw?oc=5</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxNQ2t4eHFrZFFjNUtodWcxOG1lT2JQcVowdy14OTFCNExXMEE4QXlHcXo0dklVem1ER2F6emZHN3VaZko0WVpNbTZ1NmlpcEZGUU1vbjZyemJCMkpJN0pnQTN0eU5XRTVtUXNWdEJYVG55WGdzbGRvdlMxR0FTd2VscDdmOUthRUs2eW02azQtMkZvMl9pNkdr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi1AFBVV95cUxONmZ6RWs4VkhQZ3RHeUpwNWdEbnNvRGMwTE1tX1lBUWJ3eHhnMnFhZElYb0s3X2M3TTNsMkZXMXFKRXE3WlNzU1BSdDlfQXlxOHpIeC1ZbzRmT25xTFBRVjRFdEc1Yi1wVE1rZ3UzQUdhNXVGUXV5dEVManh1MF9sTzBQR3lCdFI2QzhNSWJlQkpGNy1fbUdoUHN2UW16VlA4VmUtYUtzV28wMXdVN1gwVDFwRlQzWnJPNlJaeTBRSXA4eGxiTG9Jc0VlSGItdGticmVBUw?oc=5</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="157" ht="48" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>c5f3eda4abaa3020</t>
+          <t>c961382bdeb2fc5d</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -8523,32 +8523,32 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>consultaelectoral.onpe.gob.pe</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Another warning from the Himalayas. Are we listening? - The Daily Star</t>
+          <t>Nepal: Rasuwa Flood Situation Report No-6 (As of 5 September 2026) - consultaelectoral.onpe.gob.pe</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Another warning from the Himalayas. Are we listening? The Daily Star</t>
+          <t>Nepal: Rasuwa Flood Situation Report No-6 (As of 5 September 2026) consultaelectoral.onpe.gob.pe</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOOGMyRWdaX2RhakZ6T3FDYWU4U1BDSE1iUU1OZ2ZnT1VSeHF0dzRNUlJWSFdTX1NoN1Nfdm9zdUxfYWVHZjBrRlVGNjVSM1NqUDk2OEFGdEhZSmVQV0RxVWNYNW1wVEdDRmJsTk5oR1o3Zld1dmZrQndVUXJrVTRidlRTV2ktX3FFUEMtbFlfQ084YWd6Y0FUVnhoVGRqNFhQNGUwcmRrY2NnVW5qZkM3NUdRTGxmcXF3dnNGaElPR09UTXJhTUdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQ2t4eHFrZFFjNUtodWcxOG1lT2JQcVowdy14OTFCNExXMEE4QXlHcXo0dklVem1ER2F6emZHN3VaZko0WVpNbTZ1NmlpcEZGUU1vbjZyemJCMkpJN0pnQTN0eU5XRTVtUXNWdEJYVG55WGdzbGRvdlMxR0FTd2VscDdmOUthRUs2eW02azQtMkZvMl9pNkdr?oc=5</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOOGMyRWdaX2RhakZ6T3FDYWU4U1BDSE1iUU1OZ2ZnT1VSeHF0dzRNUlJWSFdTX1NoN1Nfdm9zdUxfYWVHZjBrRlVGNjVSM1NqUDk2OEFGdEhZSmVQV0RxVWNYNW1wVEdDRmJsTk5oR1o3Zld1dmZrQndVUXJrVTRidlRTV2ktX3FFUEMtbFlfQ084YWd6Y0FUVnhoVGRqNFhQNGUwcmRrY2NnVW5qZkM3NUdRTGxmcXF3dnNGaElPR09UTXJhTUdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxNQ2t4eHFrZFFjNUtodWcxOG1lT2JQcVowdy14OTFCNExXMEE4QXlHcXo0dklVem1ER2F6emZHN3VaZko0WVpNbTZ1NmlpcEZGUU1vbjZyemJCMkpJN0pnQTN0eU5XRTVtUXNWdEJYVG55WGdzbGRvdlMxR0FTd2VscDdmOUthRUs2eW02azQtMkZvMl9pNkdr?oc=5</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>c3cfac049bb8c021</t>
+          <t>c5f3eda4abaa3020</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -8580,27 +8580,27 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood survivors fear loss of culture - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Another warning from the Himalayas. Are we listening? - The Daily Star</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood survivors fear loss of culture The Rising Nepal</t>
+          <t>Bhotekoshi flood: Another warning from the Himalayas. Are we listening? The Daily Star</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lVUNfOW01SlJPbHNIUnAyUl9mb21iWFdXeXhMNURUQXluMGpKSlpIYU01VTdUSEJjTGNzeWROWEU3ai1hdGdNMEw5WnVfWXhf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOOGMyRWdaX2RhakZ6T3FDYWU4U1BDSE1iUU1OZ2ZnT1VSeHF0dzRNUlJWSFdTX1NoN1Nfdm9zdUxfYWVHZjBrRlVGNjVSM1NqUDk2OEFGdEhZSmVQV0RxVWNYNW1wVEdDRmJsTk5oR1o3Zld1dmZrQndVUXJrVTRidlRTV2ktX3FFUEMtbFlfQ084YWd6Y0FUVnhoVGRqNFhQNGUwcmRrY2NnVW5qZkM3NUdRTGxmcXF3dnNGaElPR09UTXJhTUdn?oc=5</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lVUNfOW01SlJPbHNIUnAyUl9mb21iWFdXeXhMNURUQXluMGpKSlpIYU01VTdUSEJjTGNzeWROWEU3ai1hdGdNMEw5WnVfWXhf?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOOGMyRWdaX2RhakZ6T3FDYWU4U1BDSE1iUU1OZ2ZnT1VSeHF0dzRNUlJWSFdTX1NoN1Nfdm9zdUxfYWVHZjBrRlVGNjVSM1NqUDk2OEFGdEhZSmVQV0RxVWNYNW1wVEdDRmJsTk5oR1o3Zld1dmZrQndVUXJrVTRidlRTV2ktX3FFUEMtbFlfQ084YWd6Y0FUVnhoVGRqNFhQNGUwcmRrY2NnVW5qZkM3NUdRTGxmcXF3dnNGaElPR09UTXJhTUdn?oc=5</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8617,7 +8617,7 @@
     <row r="159" ht="48" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>cf4a53a2b3990724</t>
+          <t>c3cfac049bb8c021</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -8627,32 +8627,32 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T17:19:49Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Rs 2.5 million relief provided to families of deceased APF personnel - Nepalnews.com</t>
+          <t>Bhotekoshi flood survivors fear loss of culture - The Rising Nepal</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Rs 2.5 million relief provided to families of deceased APF personnel Nepalnews.com</t>
+          <t>Bhotekoshi flood survivors fear loss of culture The Rising Nepal</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQTVSZFpvNzBqOWVZYi1zWFBKZDJHM19uSWh3SHdpbi1OOWFna25lbVJ0bWx6N2NNOTQ4NW8yRUR1X2ZWTUlBZ3E2X3d3Y3NDVHBkelIyV1FkNnJKcmR6dTFsSlk5aXZvN2s4S2NSRWdTVVROTklRQV82OEt3b29LTnpqYmFZMzZodnVYZ0dMWjEtWS1FS0Zjc0ZPSFU2UERDcGFoUEc5Ml92QkZGT0RDdVQ3ZUtDQUJCYUFKZUJuM2Q2ejc2Y2U4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lVUNfOW01SlJPbHNIUnAyUl9mb21iWFdXeXhMNURUQXluMGpKSlpIYU01VTdUSEJjTGNzeWROWEU3ai1hdGdNMEw5WnVfWXhf?oc=5</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOQTVSZFpvNzBqOWVZYi1zWFBKZDJHM19uSWh3SHdpbi1OOWFna25lbVJ0bWx6N2NNOTQ4NW8yRUR1X2ZWTUlBZ3E2X3d3Y3NDVHBkelIyV1FkNnJKcmR6dTFsSlk5aXZvN2s4S2NSRWdTVVROTklRQV82OEt3b29LTnpqYmFZMzZodnVYZ0dMWjEtWS1FS0Zjc0ZPSFU2UERDcGFoUEc5Ml92QkZGT0RDdVQ3ZUtDQUJCYUFKZUJuM2Q2ejc2Y2U4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lVUNfOW01SlJPbHNIUnAyUl9mb21iWFdXeXhMNURUQXluMGpKSlpIYU01VTdUSEJjTGNzeWROWEU3ai1hdGdNMEw5WnVfWXhf?oc=5</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>27c2e8ea5c47889d</t>
+          <t>cf4a53a2b3990724</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -8679,32 +8679,32 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-05T17:19:49Z</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>NepalNews</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhote Koshi flood - NepalNews</t>
+          <t>Bhote Koshi flood: Rs 2.5 million relief provided to families of deceased APF personnel - Nepalnews.com</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhote Koshi flood NepalNews</t>
+          <t>Bhote Koshi flood: Rs 2.5 million relief provided to families of deceased APF personnel Nepalnews.com</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQjhMUG9TU2xWekhONDVyWk1pY0VzR1JtU0pWVUd2MG9OWUFFc3pWS0oyWndHSVNqWUdEUndWQTkxeEVSWG1xcnhlSGVSWkFFbzNXU1o2ZWNnSVBpd2RlUUJ6ZnhsX0V4emVpZ1lvUEZBQ2FyMEV3RW9ZYWpHVF81dGRjcHVTa0Uxanc2NVVndlBBYWFTMFI2Wm8xS09QRUNKOVhpVzlkMVNmaEN6UlNxOHYwblRnN0kxbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQTVSZFpvNzBqOWVZYi1zWFBKZDJHM19uSWh3SHdpbi1OOWFna25lbVJ0bWx6N2NNOTQ4NW8yRUR1X2ZWTUlBZ3E2X3d3Y3NDVHBkelIyV1FkNnJKcmR6dTFsSlk5aXZvN2s4S2NSRWdTVVROTklRQV82OEt3b29LTnpqYmFZMzZodnVYZ0dMWjEtWS1FS0Zjc0ZPSFU2UERDcGFoUEc5Ml92QkZGT0RDdVQ3ZUtDQUJCYUFKZUJuM2Q2ejc2Y2U4?oc=5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPQjhMUG9TU2xWekhONDVyWk1pY0VzR1JtU0pWVUd2MG9OWUFFc3pWS0oyWndHSVNqWUdEUndWQTkxeEVSWG1xcnhlSGVSWkFFbzNXU1o2ZWNnSVBpd2RlUUJ6ZnhsX0V4emVpZ1lvUEZBQ2FyMEV3RW9ZYWpHVF81dGRjcHVTa0Uxanc2NVVndlBBYWFTMFI2Wm8xS09QRUNKOVhpVzlkMVNmaEN6UlNxOHYwblRnN0kxbmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxOQTVSZFpvNzBqOWVZYi1zWFBKZDJHM19uSWh3SHdpbi1OOWFna25lbVJ0bWx6N2NNOTQ4NW8yRUR1X2ZWTUlBZ3E2X3d3Y3NDVHBkelIyV1FkNnJKcmR6dTFsSlk5aXZvN2s4S2NSRWdTVVROTklRQV82OEt3b29LTnpqYmFZMzZodnVYZ0dMWjEtWS1FS0Zjc0ZPSFU2UERDcGFoUEc5Ml92QkZGT0RDdVQ3ZUtDQUJCYUFKZUJuM2Q2ejc2Y2U4?oc=5</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>4828d8ce17685c25</t>
+          <t>27c2e8ea5c47889d</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T17:19:49Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>NepalNews</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myRepublica</t>
+          <t>Four Australian nationals of Indian origin missing in Bhote Koshi flood - NepalNews</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myRepublica</t>
+          <t>Four Australian nationals of Indian origin missing in Bhote Koshi flood NepalNews</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMWkyWDc1UFlWZlhBd2M3SWd5M2EzM1VUUzZJUnpqWHBfT0U2OW0xUTVLMUJXTmJFN04zRHBrWTFMaXlidWpLVmhNU0tUaXlkYTNQUGIwdVhqOS03MWVwXzN6T1JybFdFdFlIcVNSanRQdlE5M2ZzWkt4VkJOck0tVGlHWnRXbE9RbndnVW9Nd2VXRnN0ZWZRUExTMjdHNGdGWFlVZ3EwVVIxVHp6aVU2MlZZS05hdFhLZjU4SExLOGlxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQjhMUG9TU2xWekhONDVyWk1pY0VzR1JtU0pWVUd2MG9OWUFFc3pWS0oyWndHSVNqWUdEUndWQTkxeEVSWG1xcnhlSGVSWkFFbzNXU1o2ZWNnSVBpd2RlUUJ6ZnhsX0V4emVpZ1lvUEZBQ2FyMEV3RW9ZYWpHVF81dGRjcHVTa0Uxanc2NVVndlBBYWFTMFI2Wm8xS09QRUNKOVhpVzlkMVNmaEN6UlNxOHYwblRnN0kxbmc?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMWkyWDc1UFlWZlhBd2M3SWd5M2EzM1VUUzZJUnpqWHBfT0U2OW0xUTVLMUJXTmJFN04zRHBrWTFMaXlidWpLVmhNU0tUaXlkYTNQUGIwdVhqOS03MWVwXzN6T1JybFdFdFlIcVNSanRQdlE5M2ZzWkt4VkJOck0tVGlHWnRXbE9RbndnVW9Nd2VXRnN0ZWZRUExTMjdHNGdGWFlVZ3EwVVIxVHp6aVU2MlZZS05hdFhLZjU4SExLOGlxUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPQjhMUG9TU2xWekhONDVyWk1pY0VzR1JtU0pWVUd2MG9OWUFFc3pWS0oyWndHSVNqWUdEUndWQTkxeEVSWG1xcnhlSGVSWkFFbzNXU1o2ZWNnSVBpd2RlUUJ6ZnhsX0V4emVpZ1lvUEZBQ2FyMEV3RW9ZYWpHVF81dGRjcHVTa0Uxanc2NVVndlBBYWFTMFI2Wm8xS09QRUNKOVhpVzlkMVNmaEN6UlNxOHYwblRnN0kxbmc?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>821ba43b4203c3a5</t>
+          <t>4828d8ce17685c25</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,32 +8783,32 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T22:53:38Z</t>
+          <t>2026-09-05T17:19:49Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin, missing in Bhotekoshi flood - The Rising Nepal</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin, missing in Bhotekoshi flood The Rising Nepal</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1mczFFTi1lYkZBVmZyRWhBanJtanZCNXByTWRuTjN6S21kQTF4dXBHWGotTnBuTWxJNXRvY0NRZDR1Q1JRSWJKWnpFb2ZYbzhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMWkyWDc1UFlWZlhBd2M3SWd5M2EzM1VUUzZJUnpqWHBfT0U2OW0xUTVLMUJXTmJFN04zRHBrWTFMaXlidWpLVmhNU0tUaXlkYTNQUGIwdVhqOS03MWVwXzN6T1JybFdFdFlIcVNSanRQdlE5M2ZzWkt4VkJOck0tVGlHWnRXbE9RbndnVW9Nd2VXRnN0ZWZRUExTMjdHNGdGWFlVZ3EwVVIxVHp6aVU2MlZZS05hdFhLZjU4SExLOGlxUQ?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1mczFFTi1lYkZBVmZyRWhBanJtanZCNXByTWRuTjN6S21kQTF4dXBHWGotTnBuTWxJNXRvY0NRZDR1Q1JRSWJKWnpFb2ZYbzhJ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMWkyWDc1UFlWZlhBd2M3SWd5M2EzM1VUUzZJUnpqWHBfT0U2OW0xUTVLMUJXTmJFN04zRHBrWTFMaXlidWpLVmhNU0tUaXlkYTNQUGIwdVhqOS03MWVwXzN6T1JybFdFdFlIcVNSanRQdlE5M2ZzWkt4VkJOck0tVGlHWnRXbE9RbndnVW9Nd2VXRnN0ZWZRUExTMjdHNGdGWFlVZ3EwVVIxVHp6aVU2MlZZS05hdFhLZjU4SExLOGlxUQ?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>8007d1be9ab6c893</t>
+          <t>821ba43b4203c3a5</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8835,32 +8835,32 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-05T22:53:38Z</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,030 recovered bodies managed so far - Khabarhub</t>
+          <t>Four Australian nationals of Indian origin, missing in Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,030 recovered bodies managed so far Khabarhub</t>
+          <t>Four Australian nationals of Indian origin, missing in Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBTRW1HOFB6REU3WFNzVEM2TkhXLTVkejFmSHlyWWFEbGw0VTM5Q0xzV3U4bFFwNGw0UjhZSkk3NVZxVGZhWC13b3hBZFB4aVNfSWpJaTk4d0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1mczFFTi1lYkZBVmZyRWhBanJtanZCNXByTWRuTjN6S21kQTF4dXBHWGotTnBuTWxJNXRvY0NRZDR1Q1JRSWJKWnpFb2ZYbzhJ?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBTRW1HOFB6REU3WFNzVEM2TkhXLTVkejFmSHlyWWFEbGw0VTM5Q0xzV3U4bFFwNGw0UjhZSkk3NVZxVGZhWC13b3hBZFB4aVNfSWpJaTk4d0k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1mczFFTi1lYkZBVmZyRWhBanJtanZCNXByTWRuTjN6S21kQTF4dXBHWGotTnBuTWxJNXRvY0NRZDR1Q1JRSWJKWnpFb2ZYbzhJ?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,42 +8877,42 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>95216a0448be4ecd</t>
+          <t>8007d1be9ab6c893</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
+          <t>Bhotekoshi flood: 1,030 recovered bodies managed so far - Khabarhub</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
+          <t>Bhotekoshi flood: 1,030 recovered bodies managed so far Khabarhub</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBTRW1HOFB6REU3WFNzVEM2TkhXLTVkejFmSHlyWWFEbGw0VTM5Q0xzV3U4bFFwNGw0UjhZSkk3NVZxVGZhWC13b3hBZFB4aVNfSWpJaTk4d0k?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBTRW1HOFB6REU3WFNzVEM2TkhXLTVkejFmSHlyWWFEbGw0VTM5Q0xzV3U4bFFwNGw0UjhZSkk3NVZxVGZhWC13b3hBZFB4aVNfSWpJaTk4d0k?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>69c5156e1e556a67</t>
+          <t>95216a0448be4ecd</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22T21:16:33Z</t>
+          <t>2026-09-22T23:36:39Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-09-22T21:16:33Z · 650 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-09-22T23:36:39Z · 650 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -988,17 +988,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myrepublica.nagariknetwork.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myrepublica.nagariknetwork.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors english.khabarhub.com</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds - myrepublica.nagariknetwork.com</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds - myRepublica</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds myrepublica.nagariknetwork.com</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds myRepublica</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 english.khabarhub.com</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief english.khabarhub.com</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing english.khabarhub.com</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
+          <t>Government forms expert panel to study Bhotekoshi flood - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
+          <t>Government forms expert panel to study Bhotekoshi flood english.khabarhub.com</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>3a44f3c3227b20ff</t>
+          <t>97b6fb8c1bbdde22</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1961,7 +1961,7 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>355ca1951767eb7e</t>
+          <t>3a44f3c3227b20ff</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>38b94bc7bc5df2f9</t>
+          <t>355ca1951767eb7e</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2028,27 +2028,27 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myrepublica.nagariknetwork.com</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myrepublica.nagariknetwork.com</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>976a3738cc5bbc8c</t>
+          <t>38b94bc7bc5df2f9</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myRepublica</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myRepublica</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2117,42 +2117,42 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>4f53e036a604bfe8</t>
+          <t>976a3738cc5bbc8c</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myrepublica.nagariknetwork.com</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myrepublica.nagariknetwork.com</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myRepublica</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myRepublica</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -2548,17 +2548,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report - myrepublica.nagariknetwork.com</t>
+          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report - myRepublica</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report myrepublica.nagariknetwork.com</t>
+          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report myRepublica</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 english.khabarhub.com</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -2741,42 +2741,42 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>113175714853bb7e</t>
+          <t>6331e8a91369eb2f</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 english.khabarhub.com</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lQlBZcGdXUGdGMDc2TUdQbkFuWWxvWVZvX3RlUUVHWEthYlZiQm5nLWhCbTVybVdkc21JZjVFQ3diYmpMd0hVS0VXTWdEN09s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lQlBZcGdXUGdGMDc2TUdQbkFuWWxvWVZvX3RlUUVHWEthYlZiQm5nLWhCbTVybVdkc21JZjVFQ3diYmpMd0hVS0VXTWdEN09s?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>aa0c38e5dbcd204a</t>
+          <t>113175714853bb7e</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2803,32 +2803,32 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims - myrepublica.nagariknetwork.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts - The Rising Nepal</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims myrepublica.nagariknetwork.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts The Rising Nepal</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lQlBZcGdXUGdGMDc2TUdQbkFuWWxvWVZvX3RlUUVHWEthYlZiQm5nLWhCbTVybVdkc21JZjVFQ3diYmpMd0hVS0VXTWdEN09s?oc=5</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9lQlBZcGdXUGdGMDc2TUdQbkFuWWxvWVZvX3RlUUVHWEthYlZiQm5nLWhCbTVybVdkc21JZjVFQ3diYmpMd0hVS0VXTWdEN09s?oc=5</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>198a51a993ffe8e0</t>
+          <t>aa0c38e5dbcd204a</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - ReliefWeb</t>
+          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims - myRepublica</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) ReliefWeb</t>
+          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims myRepublica</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>8b20128d66cc3dfc</t>
+          <t>8759263a9a2778c7</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2959,32 +2959,32 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T21:16:13Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: How Is DNA Matching Conducted? How Do Relatives Receive the Bodies? - Ekantipur</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: How Is DNA Matching Conducted? How Do Relatives Receive the Bodies? Ekantipur</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood english.khabarhub.com</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSUZTSy1yb01CbXlYM2J0eFE2VDlpV3NrQTM0Y3pTOW5DenMzb19hS002a1ZwaEFibTBJZWNQRExxS3NaQWZtbWNMQnlBaEJUcUh3Z0p4Mks0U2xOTVlIdXNhWDFkdXIxLW1LZnNqWU5jQjdpY0ppSVV3QmR0ckt2eWU5N3dXeW94clBMaHRPT2xDRmd0Wk1nU3I0N0dtWlV0RHY0d2lMcExYZVVMaVF1QXAtRXh2VGszeVk2VmJIeGZhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSUZTSy1yb01CbXlYM2J0eFE2VDlpV3NrQTM0Y3pTOW5DenMzb19hS002a1ZwaEFibTBJZWNQRExxS3NaQWZtbWNMQnlBaEJUcUh3Z0p4Mks0U2xOTVlIdXNhWDFkdXIxLW1LZnNqWU5jQjdpY0ppSVV3QmR0ckt2eWU5N3dXeW94clBMaHRPT2xDRmd0Wk1nU3I0N0dtWlV0RHY0d2lMcExYZVVMaVF1QXAtRXh2VGszeVk2VmJIeGZhZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>8759263a9a2778c7</t>
+          <t>cbec98d65b37335f</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -3016,27 +3016,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood - Khabarhub</t>
+          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood Khabarhub</t>
+          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1TTjJXZnVsZVdEbDdOdHJteFhYWVBMZHJBc0UzSmxhcTFhbHZ0VEFsbkM4MTBRcTBzeDJSTThxUnZBY2JmYkdDNThLLTNLX1J3TEFnZmZtNEM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3053,7 +3053,7 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>cbec98d65b37335f</t>
+          <t>9496e16a0b0d46ea</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-10T16:22:37Z</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>OCHA</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood - myrepublica.nagariknetwork.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - OCHA</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 12 billion collected in PM's Relief Fund after Bhotekoshi flood myrepublica.nagariknetwork.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) OCHA</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQdkp1UV94WmdmblJIRmdidC1MOTg1VVNDcTE3UjlVX3UwbkN3cS12UGx2MThIM19BbURLdkZsdVdhTEF4QkRVTkFsa0F5UXFxMkxlaDVWOXJBVzdtTXpVU0FiT0Y0eGFSYWFMeUQtdDZTd0dmZjE2dEtOZHJTcEVEOV8taDl0MHh1OFJRUHl0blh6bkt6WjVybmF5SHNZVDdiTG9jeGxvSnJtOWNIWXMtZ1dFVl9vWlpQeTBtQU95RmlxVm5RYkE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>6331e8a91369eb2f</t>
+          <t>078323d2f25a50d5</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -3323,32 +3323,32 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBkaTlKOGhhNjBvZnN6M29aMkdkZHlGcEdFSDdBR3dUWnJzbXUyUVJzeTdZdDR3dmtROWFxNDh4eXFzeTduN05zLXhLUGhoT21STVpKX3JQdlA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3365,42 +3365,42 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>078323d2f25a50d5</t>
+          <t>193f6bc71c9aab53</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - Nepalnews.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM Nepalnews.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood english.khabarhub.com</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQQU8xY0J2NkhqMlVfZkFNSlBOaV9ORGMwXzhsbnNzZ3UxLWhoZ0VBbFI3bEQ1S0FiOEc3Z2JSVWdQUVpEUkx5ZDR2RGVjNDFNTXFINGV3XzNreFNoZS1wODdSOVozVjA5cHVhT25LM1dGQTVxbTZQLS1CdEZzYzcwN3Yyb00wQllyaDFDZU1GUDc3VzR3SmJjVkRLZXpDdFhkTDJSMGhBV1daMW55YktyU2p3ZHpCUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>193f6bc71c9aab53</t>
+          <t>c4d67c4602739f5e</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - Khabarhub</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - Nepalnews.com</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood Khabarhub</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact Nepalnews.com</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5sZEVYa0JvVWhmTWxvY0Q5ZWMxVWFNZWI5TFdlWmltNk1BOTVDS1hNcGNmTkNjQ250c2hfY0xLcWlqMnc3QzNZSXVQQVJpTzd4VFNObXNOZm4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>c4d67c4602739f5e</t>
+          <t>87b5592d2c58bbd9</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -3479,32 +3479,32 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Himal Southasian</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - Nepalnews.com</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Himal Southasian</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact Nepalnews.com</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Himal Southasian</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOQXJWOWI5Q09IeXBuUHk2ZVotbERjWVJzNmVDX2xXRE9lejNrZWd4M1V5MWpYb1pmTUhHVTBhUkZEcmZGVjJHb3BabmZxWUpaQWdiV1lfN3ZxZzJUWUpVczZHeG53SFBaVFE2S1hZb3VKUzdsU0lKeElfVjhfUF9tOWRuVllxN0xxXzgtOWVZeDN2S2N4TGNOenE2dFpBQUZQdmhsQnpMdHRyTXI4bXQ4d1Q4dFJMbVNMZG5rVXB6LVNuZXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>87b5592d2c58bbd9</t>
+          <t>66743f8886e880aa</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-13T11:48:33Z</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>himalmag.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - himalmag.com</t>
+          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas - myRepublica</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world himalmag.com</t>
+          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas myRepublica</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE9PblpNSG9XN1cyUUJvNEZ6MUNUSW85RFp2MTNVTGE1bzVvWTk0YU5Za3A5WnlaTTN5cDUzM1czLTZTclM0NHotMGo2S0N1cDZWYzZjMW92REZtaHRNbURtNmRFV1h4Um84SGxMUmdLSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>66743f8886e880aa</t>
+          <t>7c4f8e2a99a4ce1f</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -3583,32 +3583,32 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T11:48:33Z</t>
+          <t>2026-09-07T12:28:25Z</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas - myrepublica.nagariknetwork.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - Nepalnews.com</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Up to 20 helicopters a day become lifeline in Bhotekoshi flood-hit areas myrepublica.nagariknetwork.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund Nepalnews.com</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNbFRRNFlfdnlld3ZUN25vZURSNlp1Sl9ua2RuMFh6NVctWDhhM3BBeGwtVWwtUzM2dFBoV1Nnb2ZQLVF1aF9UdktKdndLZTY0NlVWT21DMzhkTmYtYTlLVlN2SFJzcnRHSlVLTjVkR1JnZndMbndTQ1QxbHR2WDF2VnBYWEt1dmlOSVhBaEw2SnRaR2EyM1VrZXFJTHJBYVdKR0ZOcFBzVmt2SnVVRk5WeFhFZUQ0dGNSUXo0RTVtT2pIWlU2Mmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>47075b2c0944a15a</t>
+          <t>423212fdf3d9e939</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T04:35:51Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - Khabarhub</t>
+          <t>Roads washed away by Bhotekoshi Flood being rebuilt - myRepublica</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts Khabarhub</t>
+          <t>Roads washed away by Bhotekoshi Flood being rebuilt myRepublica</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,42 +3729,42 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>423212fdf3d9e939</t>
+          <t>d8f9de0510371c12</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Roads washed away by Bhotekoshi Flood being rebuilt - myrepublica.nagariknetwork.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Roads washed away by Bhotekoshi Flood being rebuilt myrepublica.nagariknetwork.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZjl4ejBCUURjT1ZVMHpvYWluY0JUa1Jtc3ZnOXlpYzhjYzB0dl9BN1NQZU1MT0VOaFM4TDctMDNFbGk5WjVuWjNsVy1sdlppNU9LQUJ6X1gxRTVZaGlpQWJpOVNHaFl4U2JyQkUxZEZtOS1UVGZIZ3BCa3otd09QUGpDdzhPdERyQ3FpVFVOVmRoSmFIbDY2enFmanZMYjZJOGJ6ZGhWdnJxUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>d8f9de0510371c12</t>
+          <t>ce567896a53480b0</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -3791,32 +3791,32 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
+          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment - myRepublica</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
+          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment myRepublica</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>ce567896a53480b0</t>
+          <t>b02b6baeae823858</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -3843,32 +3843,32 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-19T10:55:34Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment - myrepublica.nagariknetwork.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,342; nearly 4,900 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 38 injured discharged from Trauma Center, 12 still receiving treatment myrepublica.nagariknetwork.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,342; nearly 4,900 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSGRxNWxTai1wcFZib2M3ek02bEhGbjY1RFAtdTJvaDR1WWRXNWZaUkFBalRhUy1NOFd6NVhLRmZIUm9vOUdTTExfcW1zTzJlTnhBamNfV0pXcmtNY1U1cHdHenhOa0JjRzhIQ3FlOXEzRU42Y1lEQmhJN3V3VDVNSlZiTm9FSmg2LXpkcU5qYWtqc0NzdG0wcnBiSDhIUnpKLVM2X1pROFBTZ00?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNdWk5OW1pQ3o4Y2VJbkFlLVoweUVOUnRmQlFHMXQxTWZaZ1F2NWxYNlp5NlRCYnVhNFJKTElxMFlwcVQybFpYdkJ5a0haUTgyWE5ETTZEWGhmU0hYXzk0UDZFMU1SXzFSVkZ2VW00M3NpR3JFUW0tX0loT3BrcHpnajBHWHdldlZ5c2FsbG1PcUhyVzBKcVFVQllxQ1QxbjlmTUhMT1FsaVVtOEJUVmRtTzVyRjM4MHJCaDc5VXpRcGtXcEJOTlg3bUp3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSGRxNWxTai1wcFZib2M3ek02bEhGbjY1RFAtdTJvaDR1WWRXNWZaUkFBalRhUy1NOFd6NVhLRmZIUm9vOUdTTExfcW1zTzJlTnhBamNfV0pXcmtNY1U1cHdHenhOa0JjRzhIQ3FlOXEzRU42Y1lEQmhJN3V3VDVNSlZiTm9FSmg2LXpkcU5qYWtqc0NzdG0wcnBiSDhIUnpKLVM2X1pROFBTZ00?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood update: Death toll reaches 1,344 - Khabarhub</t>
+          <t>Bhotekoshi flood update: Death toll reaches 1,344 - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood update: Death toll reaches 1,344 Khabarhub</t>
+          <t>Bhotekoshi flood update: Death toll reaches 1,344 english.khabarhub.com</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myrepublica.nagariknetwork.com</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myrepublica.nagariknetwork.com</t>
+          <t>1,294 bodies recovered, 5,053 remain unaccounted for in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -4249,42 +4249,42 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>eb73716a3ee4f27a</t>
+          <t>5f76706cec031b28</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-09-08T23:22:50Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>FM Bharat</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing - Ratopati</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - FM Bharat</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing Ratopati</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims FM Bharat</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbDNtYTQ5Y21CUG1kUjVqb1E0U3lKeUx0Q3hYQVJNWVlRUGZVa3JSNGRvVUNJeGJveUdXa05qdDRGSmZsRHhraUh0UXhPUVBfR3IzQndBSHNFSzhabm9jNGxiNGVkYXpfZ0xDUzZuMnkxX1hDTURjOW5OZEhMdGtia1RpbjdIZTNsNGwtY2I3RTFzQ3hhTDRmM2JHVDZ0M1BnWEd4eHpScTdEQmoxUW5jOWI4RzgtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQbDNtYTQ5Y21CUG1kUjVqb1E0U3lKeUx0Q3hYQVJNWVlRUGZVa3JSNGRvVUNJeGJveUdXa05qdDRGSmZsRHhraUh0UXhPUVBfR3IzQndBSHNFSzhabm9jNGxiNGVkYXpfZ0xDUzZuMnkxX1hDTURjOW5OZEhMdGtia1RpbjdIZTNsNGwtY2I3RTFzQ3hhTDRmM2JHVDZ0M1BnWEd4eHpScTdEQmoxUW5jOWI4RzgtQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>5f76706cec031b28</t>
+          <t>c52a95edc1229710</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T23:22:50Z</t>
+          <t>2026-09-03T23:16:04Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>fmbharat.com</t>
+          <t>nepyork</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - fmbharat.com</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims fmbharat.com</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>c52a95edc1229710</t>
+          <t>06e9d4415d0f0371</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T23:16:04Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>nepyork</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>06e9d4415d0f0371</t>
+          <t>af5a4a18108fca1c</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors The Kathmandu Post</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>af5a4a18108fca1c</t>
+          <t>e73fa902d1fda14b</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - The Kathmandu Post</t>
+          <t>MP Malla Presents 7 Demands to the Government Regarding the Bhotekoshi Flood - Ekantipur</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors The Kathmandu Post</t>
+          <t>MP Malla Presents 7 Demands to the Government Regarding the Bhotekoshi Flood Ekantipur</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSlNDcTNaN2l6RFc2SVFvSTVrcGdNRHlIUVJUOXNqSWM2Rl9iYWQ3ZUhtS0RCUzBlQmZEcmp5UWZKUWpRcnhKOHdEVXBzNnQ2dnZTcDVmUGdwUFFVcG81b2xKWVc5Yzg5STIyYWUtVUlMd2V2X3lScXZJVUxXdldoalR3eWlDTGdCOFI0aW9fVnB4U2NZZ1JCNzFFY3dGWkhIeGg0YVJ5X1lSZThqX1ByT2xlVjBzcXFydWZWclU5dE1yazE5Q0I2clVFNmlKMEtLVUE?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSlNDcTNaN2l6RFc2SVFvSTVrcGdNRHlIUVJUOXNqSWM2Rl9iYWQ3ZUhtS0RCUzBlQmZEcmp5UWZKUWpRcnhKOHdEVXBzNnQ2dnZTcDVmUGdwUFFVcG81b2xKWVc5Yzg5STIyYWUtVUlMd2V2X3lScXZJVUxXdldoalR3eWlDTGdCOFI0aW9fVnB4U2NZZ1JCNzFFY3dGWkhIeGg0YVJ5X1lSZThqX1ByT2xlVjBzcXFydWZWclU5dE1yazE5Q0I2clVFNmlKMEtLVUE?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>e73fa902d1fda14b</t>
+          <t>df79e0b20e3c0e4a</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -4519,32 +4519,32 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>MP Malla Presents 7 Demands to the Government Regarding the Bhotekoshi Flood - Ekantipur</t>
+          <t>Rasuwa flood lessons: Build fewer, taller and longer bridges - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>MP Malla Presents 7 Demands to the Government Regarding the Bhotekoshi Flood Ekantipur</t>
+          <t>Rasuwa flood lessons: Build fewer, taller and longer bridges Onlinekhabar English</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSlNDcTNaN2l6RFc2SVFvSTVrcGdNRHlIUVJUOXNqSWM2Rl9iYWQ3ZUhtS0RCUzBlQmZEcmp5UWZKUWpRcnhKOHdEVXBzNnQ2dnZTcDVmUGdwUFFVcG81b2xKWVc5Yzg5STIyYWUtVUlMd2V2X3lScXZJVUxXdldoalR3eWlDTGdCOFI0aW9fVnB4U2NZZ1JCNzFFY3dGWkhIeGg0YVJ5X1lSZThqX1ByT2xlVjBzcXFydWZWclU5dE1yazE5Q0I2clVFNmlKMEtLVUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNLWE1WExJYXJubmJOVzNiaVAwZGhvZkpaRTdfMTZySjE1b0lOVFcwOFp3UERGRmRFdjRCN0dYelNfUHRnd2FlSVBqbEd6ZGdJSWs4NmFQMWVaX1UwREFBZVBnUkdlZkJwaFJDYzAyNTRDa1NnamdFaENWWHM2dWRuM01TNXgzRHliRG5OTFRMUWY2QUxGdVBnTE1WdDY?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSlNDcTNaN2l6RFc2SVFvSTVrcGdNRHlIUVJUOXNqSWM2Rl9iYWQ3ZUhtS0RCUzBlQmZEcmp5UWZKUWpRcnhKOHdEVXBzNnQ2dnZTcDVmUGdwUFFVcG81b2xKWVc5Yzg5STIyYWUtVUlMd2V2X3lScXZJVUxXdldoalR3eWlDTGdCOFI0aW9fVnB4U2NZZ1JCNzFFY3dGWkhIeGg0YVJ5X1lSZThqX1ByT2xlVjBzcXFydWZWclU5dE1yazE5Q0I2clVFNmlKMEtLVUE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNLWE1WExJYXJubmJOVzNiaVAwZGhvZkpaRTdfMTZySjE1b0lOVFcwOFp3UERGRmRFdjRCN0dYelNfUHRnd2FlSVBqbEd6ZGdJSWs4NmFQMWVaX1UwREFBZVBnUkdlZkJwaFJDYzAyNTRDa1NnamdFaENWWHM2dWRuM01TNXgzRHliRG5OTFRMUWY2QUxGdVBnTE1WdDY?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>df79e0b20e3c0e4a</t>
+          <t>e18cb5fbf60ca971</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-22T11:34:48Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood lessons: Build fewer, taller and longer bridges - Onlinekhabar English</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,259 - Nepalnews.com</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood lessons: Build fewer, taller and longer bridges Onlinekhabar English</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,259 Nepalnews.com</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNLWE1WExJYXJubmJOVzNiaVAwZGhvZkpaRTdfMTZySjE1b0lOVFcwOFp3UERGRmRFdjRCN0dYelNfUHRnd2FlSVBqbEd6ZGdJSWs4NmFQMWVaX1UwREFBZVBnUkdlZkJwaFJDYzAyNTRDa1NnamdFaENWWHM2dWRuM01TNXgzRHliRG5OTFRMUWY2QUxGdVBnTE1WdDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQRWdwYTI5Y0Q4eXp4TDlRUUJBc2dxOEhibUlPV2NtbGJaTTBtMFBYZGQwQ2VMNFBfblY0eGRGakYyOTlwTnZfUTBMWU5oUkRkUVRCU3IzTGhFcmpmQzBYYkcxWllha2paRFpwclpzYXZyQ3A4TkwtZlZMVlFqMTZzcjVBdjR5Y19S?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNLWE1WExJYXJubmJOVzNiaVAwZGhvZkpaRTdfMTZySjE1b0lOVFcwOFp3UERGRmRFdjRCN0dYelNfUHRnd2FlSVBqbEd6ZGdJSWs4NmFQMWVaX1UwREFBZVBnUkdlZkJwaFJDYzAyNTRDa1NnamdFaENWWHM2dWRuM01TNXgzRHliRG5OTFRMUWY2QUxGdVBnTE1WdDY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiAFBVV95cUxQRWdwYTI5Y0Q4eXp4TDlRUUJBc2dxOEhibUlPV2NtbGJaTTBtMFBYZGQwQ2VMNFBfblY0eGRGakYyOTlwTnZfUTBMWU5oUkRkUVRCU3IzTGhFcmpmQzBYYkcxWllha2paRFpwclpzYXZyQ3A4TkwtZlZMVlFqMTZzcjVBdjR5Y19S?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>e18cb5fbf60ca971</t>
+          <t>5c4263c295568c39</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T11:34:48Z</t>
+          <t>2026-09-03T11:11:13Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,259 - Nepalnews.com</t>
+          <t>Nepal briefs diplomats on Bhotekoshi flood devastation - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,259 Nepalnews.com</t>
+          <t>Nepal briefs diplomats on Bhotekoshi flood devastation The Kathmandu Post</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQRWdwYTI5Y0Q4eXp4TDlRUUJBc2dxOEhibUlPV2NtbGJaTTBtMFBYZGQwQ2VMNFBfblY0eGRGakYyOTlwTnZfUTBMWU5oUkRkUVRCU3IzTGhFcmpmQzBYYkcxWllha2paRFpwclpzYXZyQ3A4TkwtZlZMVlFqMTZzcjVBdjR5Y19S?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbkxPNmlNNndjclg4cWgzNVZIYXNGOEVBZDdEY2pOQXRXelNSMFB1QWJ2VnpreEdXZEQ1QnJGOFJTZHBVRDdFU0lYM0dKODBxa3k4TUc3ZmNYT0x5Vk11b3E2dEJRcnlMVHZfXzBOYVV4ZENabUYwc25DeUo4dVYxYjNzcVV2a09FT01RbFZsX1phS2k1dXBLY0tyOWRyOHZqNXc?oc=5</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiAFBVV95cUxQRWdwYTI5Y0Q4eXp4TDlRUUJBc2dxOEhibUlPV2NtbGJaTTBtMFBYZGQwQ2VMNFBfblY0eGRGakYyOTlwTnZfUTBMWU5oUkRkUVRCU3IzTGhFcmpmQzBYYkcxWllha2paRFpwclpzYXZyQ3A4TkwtZlZMVlFqMTZzcjVBdjR5Y19S?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxQbkxPNmlNNndjclg4cWgzNVZIYXNGOEVBZDdEY2pOQXRXelNSMFB1QWJ2VnpreEdXZEQ1QnJGOFJTZHBVRDdFU0lYM0dKODBxa3k4TUc3ZmNYT0x5Vk11b3E2dEJRcnlMVHZfXzBOYVV4ZENabUYwc25DeUo4dVYxYjNzcVV2a09FT01RbFZsX1phS2k1dXBLY0tyOWRyOHZqNXc?oc=5</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4665,7 +4665,7 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>5c4263c295568c39</t>
+          <t>4ae7f5a5316a4917</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T11:11:13Z</t>
+          <t>2026-09-03T04:20:55Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -4685,22 +4685,22 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Nepal briefs diplomats on Bhotekoshi flood devastation - The Kathmandu Post</t>
+          <t>School students cut snack money to help Bhotekoshi flood victims - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Nepal briefs diplomats on Bhotekoshi flood devastation The Kathmandu Post</t>
+          <t>School students cut snack money to help Bhotekoshi flood victims The Kathmandu Post</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbkxPNmlNNndjclg4cWgzNVZIYXNGOEVBZDdEY2pOQXRXelNSMFB1QWJ2VnpreEdXZEQ1QnJGOFJTZHBVRDdFU0lYM0dKODBxa3k4TUc3ZmNYT0x5Vk11b3E2dEJRcnlMVHZfXzBOYVV4ZENabUYwc25DeUo4dVYxYjNzcVV2a09FT01RbFZsX1phS2k1dXBLY0tyOWRyOHZqNXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNVJQY2IzaG1nZU1BRVhwYlg4UUtTc1dsWFRMNWdpQjdWLWNjSmpseUpGZ0I2clRFcGlkeVRVOE1XZTdlb2hLcFZNQXFPMU9DWXVfOTZxYk1aR2xudlcwTWo3cDN1QVUxQWhHeGdVMDkwTmR2bkpTS3l5Z3o0TFg2SFFzdTJGR01HaTExVUI3VUYtOHdwWHFYTXhyNjB1TE5Da0M0WlVHUkkyQzh0VU13?oc=5</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxQbkxPNmlNNndjclg4cWgzNVZIYXNGOEVBZDdEY2pOQXRXelNSMFB1QWJ2VnpreEdXZEQ1QnJGOFJTZHBVRDdFU0lYM0dKODBxa3k4TUc3ZmNYT0x5Vk11b3E2dEJRcnlMVHZfXzBOYVV4ZENabUYwc25DeUo4dVYxYjNzcVV2a09FT01RbFZsX1phS2k1dXBLY0tyOWRyOHZqNXc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNNVJQY2IzaG1nZU1BRVhwYlg4UUtTc1dsWFRMNWdpQjdWLWNjSmpseUpGZ0I2clRFcGlkeVRVOE1XZTdlb2hLcFZNQXFPMU9DWXVfOTZxYk1aR2xudlcwTWo3cDN1QVUxQWhHeGdVMDkwTmR2bkpTS3l5Z3o0TFg2SFFzdTJGR01HaTExVUI3VUYtOHdwWHFYTXhyNjB1TE5Da0M0WlVHUkkyQzh0VU13?oc=5</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>4ae7f5a5316a4917</t>
+          <t>a82013ca21037b39</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -4732,27 +4732,27 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>School students cut snack money to help Bhotekoshi flood victims - The Kathmandu Post</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,204 as over 4,200 remain missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>School students cut snack money to help Bhotekoshi flood victims The Kathmandu Post</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,204 as over 4,200 remain missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNVJQY2IzaG1nZU1BRVhwYlg4UUtTc1dsWFRMNWdpQjdWLWNjSmpseUpGZ0I2clRFcGlkeVRVOE1XZTdlb2hLcFZNQXFPMU9DWXVfOTZxYk1aR2xudlcwTWo3cDN1QVUxQWhHeGdVMDkwTmR2bkpTS3l5Z3o0TFg2SFFzdTJGR01HaTExVUI3VUYtOHdwWHFYTXhyNjB1TE5Da0M0WlVHUkkyQzh0VU13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNN3RuYkxxVzhmUzRfSWZpcWxLYnJUS0FkUXN1WjRvc1dxdFJJaVVVaFVQNU1CMFNwdGtFTUkyZ3Znenkxak1kN0VLWVRacGFfbE5JTEM1UG1WM2ExRE1hYUVNTnNKak9TVGJTWHBrUFdFR3JtTVJzRVhoVWgzc2ZfaWhGbmNidHd1emU1d2V5UFVpTUNCTjkyWWZMWWZ3UzVlazRoRWszWWNyVDVRdEE?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNNVJQY2IzaG1nZU1BRVhwYlg4UUtTc1dsWFRMNWdpQjdWLWNjSmpseUpGZ0I2clRFcGlkeVRVOE1XZTdlb2hLcFZNQXFPMU9DWXVfOTZxYk1aR2xudlcwTWo3cDN1QVUxQWhHeGdVMDkwTmR2bkpTS3l5Z3o0TFg2SFFzdTJGR01HaTExVUI3VUYtOHdwWHFYTXhyNjB1TE5Da0M0WlVHUkkyQzh0VU13?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNN3RuYkxxVzhmUzRfSWZpcWxLYnJUS0FkUXN1WjRvc1dxdFJJaVVVaFVQNU1CMFNwdGtFTUkyZ3Znenkxak1kN0VLWVRacGFfbE5JTEM1UG1WM2ExRE1hYUVNTnNKak9TVGJTWHBrUFdFR3JtTVJzRVhoVWgzc2ZfaWhGbmNidHd1emU1d2V5UFVpTUNCTjkyWWZMWWZ3UzVlazRoRWszWWNyVDVRdEE?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4784,17 +4784,17 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>timesofindia.indiatimes.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - timesofindia.indiatimes.com</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - The Times of India</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September timesofindia.indiatimes.com</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September The Times of India</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>stimson.org</t>
+          <t>Stimson Center</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later - stimson.org</t>
+          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later - Stimson Center</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later stimson.org</t>
+          <t>A Cascading Disaster on the China–Nepal Border: What to Know About the August 2026 Rasuwa Flood, 72 Hours Later Stimson Center</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -7005,7 +7005,7 @@
     <row r="128" ht="48" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>97b6fb8c1bbdde22</t>
+          <t>b933797459c3a582</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -7025,22 +7025,22 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - Khabarhub</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing Khabarhub</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -7057,7 +7057,7 @@
     <row r="129" ht="48" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>b933797459c3a582</t>
+          <t>62d5c38304aa356a</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -7077,22 +7077,22 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -7109,7 +7109,7 @@
     <row r="130" ht="48" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>62d5c38304aa356a</t>
+          <t>71f08f0e90525437</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
@@ -7119,32 +7119,32 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -7161,7 +7161,7 @@
     <row r="131" ht="48" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>71f08f0e90525437</t>
+          <t>2ff03089e15253df</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -7171,32 +7171,32 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? Onlinekhabar English</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -7213,7 +7213,7 @@
     <row r="132" ht="48" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>2ff03089e15253df</t>
+          <t>038d44da2885beeb</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
@@ -7223,32 +7223,32 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? - Onlinekhabar English</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? Onlinekhabar English</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -7265,42 +7265,42 @@
     <row r="133" ht="48" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>038d44da2885beeb</t>
+          <t>4f53e036a604bfe8</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>048136aff52fd1c4</t>
+          <t>198a51a993ffe8e0</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -8991,32 +8991,32 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>ANI News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - ANI News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing ANI News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>f67225d3b28943ab</t>
+          <t>8b20128d66cc3dfc</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-16T21:16:13Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - english.nepalnews.com</t>
+          <t>Bhotekoshi Flood: How Is DNA Matching Conducted? How Do Relatives Receive the Bodies? - Ekantipur</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing english.nepalnews.com</t>
+          <t>Bhotekoshi Flood: How Is DNA Matching Conducted? How Do Relatives Receive the Bodies? Ekantipur</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSUZTSy1yb01CbXlYM2J0eFE2VDlpV3NrQTM0Y3pTOW5DenMzb19hS002a1ZwaEFibTBJZWNQRExxS3NaQWZtbWNMQnlBaEJUcUh3Z0p4Mks0U2xOTVlIdXNhWDFkdXIxLW1LZnNqWU5jQjdpY0ppSVV3QmR0ckt2eWU5N3dXeW94clBMaHRPT2xDRmd0Wk1nU3I0N0dtWlV0RHY0d2lMcExYZVVMaVF1QXAtRXh2VGszeVk2VmJIeGZhZw?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxOSUZTSy1yb01CbXlYM2J0eFE2VDlpV3NrQTM0Y3pTOW5DenMzb19hS002a1ZwaEFibTBJZWNQRExxS3NaQWZtbWNMQnlBaEJUcUh3Z0p4Mks0U2xOTVlIdXNhWDFkdXIxLW1LZnNqWU5jQjdpY0ppSVV3QmR0ckt2eWU5N3dXeW94clBMaHRPT2xDRmd0Wk1nU3I0N0dtWlV0RHY0d2lMcExYZVVMaVF1QXAtRXh2VGszeVk2VmJIeGZhZw?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>9496e16a0b0d46ea</t>
+          <t>048136aff52fd1c4</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T16:22:37Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>OCHA</t>
+          <t>ANI News</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - OCHA</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - ANI News</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) OCHA</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing ANI News</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeTNnNkVBem1Fc0sySFFTQ3dnMzdtWmFZUTF2MVQ1bTU1b1pzcmtSanVqUkJsdTRKMUlfOHRoYTRIT1ppalNZbUZLTnJoRHVsUWk4Uk1XUzFDMEphSUJzSEw5R04xdnk1Yld0M0kyNHVHQTJ4T3c1dVdqeENQVXdCLTZnalpwWkJJb0NlZGZzSS1SWkVONXNvR3Fja1ZQaFlsWVE3cTdCbFRGZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>423e61ff0037981d</t>
+          <t>f67225d3b28943ab</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>english.nepalnews.com</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - risingnepaldaily.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - english.nepalnews.com</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk risingnepaldaily.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing english.nepalnews.com</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>c47a04aef0c20457</t>
+          <t>423e61ff0037981d</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -9199,32 +9199,32 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>risingnepaldaily.com</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9HWDMyY3NpWm9nbTlxUm5zTnVlcmxQYVlhRF9wZElfVDdYam54T3BGSW50cFdSZ2RWVjJNdGFJb0dIWW5mRDdWX1I0VzA3WERp?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>879325423fb38443</t>
+          <t>c47a04aef0c20457</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,32 +9251,32 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - Khabarhub</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far Khabarhub</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>d160ec5375994c91</t>
+          <t>879325423fb38443</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -9313,22 +9313,22 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - Khabarhub</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far Khabarhub</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpNWFvcTJheVY3aHU2d2xSRkQ2YXJJZmhnVXVxckc2eURqV242Si1CYWhUZWhUUFU2MFdFM1RsYkdfQ2dJX0VSbExXVFB4VzlEWVR3aGdWUlM?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>d8002ad908db19e7</t>
+          <t>d160ec5375994c91</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -9355,32 +9355,32 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T23:08:55Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - Khabarhub</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage Khabarhub</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5rRkYzS2hDYlFPYklDSVl5Z1NNbjExY183N21HQkhoRW9lMFZOMm04NXNzX0Q1QmNkT3hhbGg2N2dpMzBwdGNNRnctcXdlbGxOejZHQXpQU04?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>ae8d167a621c7582</t>
+          <t>d8002ad908db19e7</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-10T23:08:55Z</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 - Khabarhub</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 Khabarhub</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5sMkhOR05CX0xJeF93QlZCUW1CRkNmVnZUSE4xcjY5WHlZSGs0NXdYZGMxMUszQjVFTnk0bVowcU9hWFJiUEdaT0JWczl3NEFOWHY2cVhsOEhPSWo0WV9teGVHUHo?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>c3994b48332f5978</t>
+          <t>ae8d167a621c7582</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
@@ -9459,32 +9459,32 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T04:39:43Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 - Khabarhub</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 Khabarhub</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1mN2lKUnpKTUVweHZ2bTNKelo1QzNFeXJDU3ItdE5Qd0NYUV90VjVGR0VreUdJN0RUQ1pQdEJSUnRDYnRpWkhob21JeXhNZUEwZ2ZtRVJxS0Y?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>36a51c1501835742</t>
+          <t>c3994b48332f5978</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
@@ -9511,32 +9511,32 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-10T04:39:43Z</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts - The Annapurna Express</t>
+          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts The Annapurna Express</t>
+          <t>Security personnel put grief aside to lead rescue efforts after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA4dEZyMjZ2Vk4yajRCTGdZSl9Md3djR3hWQTlBR3hHVnNlVkpqYVhBUjE3LXJMUTJGa1FIOGRsUkN1WkFUMllJMGlfWXZMYmN6MWp1eDVLWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTFA4dEZyMjZ2Vk4yajRCTGdZSl9Md3djR3hWQTlBR3hHVnNlVkpqYVhBUjE3LXJMUTJGa1FIOGRsUkN1WkFUMllJMGlfWXZMYmN6MWp1eDVLWQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNSTRVb01SZTNPRTRWd21OR2Zvb0ptRGVMSkVucWQ3OVZwMlBnMENtN0wtalZITncwazFGdmk0OFpwZXZYQ05qcTRJTGRqQV9za2YtR3hiN0RkRWVZYldhd0RJZHY0VXhDWFVlUW8wdnBhdjY0RkdKaDdUcWFnYTVjQ2ZzcHh1NDBScElQa1piVWJPQS15djBCVTJSdkpQbGhiQThweUlsNllpQWJWWWRXNUFzTzdpcjh4azJYOXptZUx3TmROMVhLcHdR?oc=5</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>cacf216fc326da0d</t>
+          <t>36a51c1501835742</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T04:36:53Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>tribuneindia.com</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - tribuneindia.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts - The Annapurna Express</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing tribuneindia.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts The Annapurna Express</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSFRndEhBQzU4SzI3ZGplTUVLVGNYV1ZDMHAxWXdTTUtVZDNIbzlpdlpSUHp4ZzEwdG1oTUMwd3hDLUYybDdILTdoTlJPT2hYUU5VUVkyVzNXY2NtYnBDSEllbW1TckxmTEhZSVUxaUI4cXQ5cmYycGhDM3NHZHdrenZIT2JqNm1ETGFsMmt0aW1rdk9Nb0M3cDJmSlAwUThQN280NVlKV185UDVUeTlpYkRiRnpoZWRpdUx3MHBsUdIBwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA4dEZyMjZ2Vk4yajRCTGdZSl9Md3djR3hWQTlBR3hHVnNlVkpqYVhBUjE3LXJMUTJGa1FIOGRsUkN1WkFUMllJMGlfWXZMYmN6MWp1eDVLWQ?oc=5</t>
         </is>
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxQSFRndEhBQzU4SzI3ZGplTUVLVGNYV1ZDMHAxWXdTTUtVZDNIbzlpdlpSUHp4ZzEwdG1oTUMwd3hDLUYybDdILTdoTlJPT2hYUU5VUVkyVzNXY2NtYnBDSEllbW1TckxmTEhZSVUxaUI4cXQ5cmYycGhDM3NHZHdrenZIT2JqNm1ETGFsMmt0aW1rdk9Nb0M3cDJmSlAwUThQN280NVlKV185UDVUeTlpYkRiRnpoZWRpdUx3MHBsUdIBwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTFA4dEZyMjZ2Vk4yajRCTGdZSl9Md3djR3hWQTlBR3hHVnNlVkpqYVhBUjE3LXJMUTJGa1FIOGRsUkN1WkFUMllJMGlfWXZMYmN6MWp1eDVLWQ?oc=5</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>61acaf3888b70b31</t>
+          <t>cacf216fc326da0d</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-11T04:36:53Z</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>tribuneindia.com</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far - The Rising Nepal</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - tribuneindia.com</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far The Rising Nepal</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing tribuneindia.com</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSFRndEhBQzU4SzI3ZGplTUVLVGNYV1ZDMHAxWXdTTUtVZDNIbzlpdlpSUHp4ZzEwdG1oTUMwd3hDLUYybDdILTdoTlJPT2hYUU5VUVkyVzNXY2NtYnBDSEllbW1TckxmTEhZSVUxaUI4cXQ5cmYycGhDM3NHZHdrenZIT2JqNm1ETGFsMmt0aW1rdk9Nb0M3cDJmSlAwUThQN280NVlKV185UDVUeTlpYkRiRnpoZWRpdUx3MHBsUdIBwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzg?oc=5</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxQSFRndEhBQzU4SzI3ZGplTUVLVGNYV1ZDMHAxWXdTTUtVZDNIbzlpdlpSUHp4ZzEwdG1oTUMwd3hDLUYybDdILTdoTlJPT2hYUU5VUVkyVzNXY2NtYnBDSEllbW1TckxmTEhZSVUxaUI4cXQ5cmYycGhDM3NHZHdrenZIT2JqNm1ETGFsMmt0aW1rdk9Nb0M3cDJmSlAwUThQN280NVlKV185UDVUeTlpYkRiRnpoZWRpdUx3MHBsUdIBwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzg?oc=5</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -9657,7 +9657,7 @@
     <row r="179" ht="48" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>bcb3af284d3724c7</t>
+          <t>61acaf3888b70b31</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T20:54:48Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - The Tribune</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far - The Rising Nepal</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing The Tribune</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far The Rising Nepal</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
         </is>
       </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1hcjdLNGp2aTlTX2pfa2RoVHZqTlRoZ2dfN3FXUlppeWxPR2gzVlI3OGtIRTVQaV9mSEdzbDJVM0dJbHVhM0ZJWTJWWWZKdlND?oc=5</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>eee4a696ede15285</t>
+          <t>bcb3af284d3724c7</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -9719,32 +9719,32 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-09T20:54:48Z</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Mshale</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>बेत्रावतीमा खोजिरहेछन् आफन्तको सास र लास | Rasuwa Flood | Betrawati | Onlinekhabar Nathalie Caldonazzo (MlmsBBbdF9) - Mshale</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - The Tribune</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>बेत्रावतीमा खोजिरहेछन् आफन्तको सास र लास | Rasuwa Flood | Betrawati | Onlinekhabar Nathalie Caldonazzo (MlmsBBbdF9) Mshale</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing The Tribune</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFZllia0xxWGlBb3M1NnlqQ1M1aGVxNUhiSXc2X3l3TzBzSFpyellfaG9qQnljVzFrdldUcW5sUnk5MnZndFlkSUJQUmZMM25PbF9Ha2ljNUFnTV9PUkhhdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFZllia0xxWGlBb3M1NnlqQ1M1aGVxNUhiSXc2X3l3TzBzSFpyellfaG9qQnljVzFrdldUcW5sUnk5MnZndFlkSUJQUmZMM25PbF9Ha2ljNUFnTV9PUkhhdg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="181" ht="48" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>a4a0f705a84ebf28</t>
+          <t>eee4a696ede15285</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
@@ -9776,27 +9776,27 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Mshale</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing - Nepalnews.com</t>
+          <t>बेत्रावतीमा खोजिरहेछन् आफन्तको सास र लास | Rasuwa Flood | Betrawati | Onlinekhabar Nathalie Caldonazzo (MlmsBBbdF9) - Mshale</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing Nepalnews.com</t>
+          <t>बेत्रावतीमा खोजिरहेछन् आफन्तको सास र लास | Rasuwa Flood | Betrawati | Onlinekhabar Nathalie Caldonazzo (MlmsBBbdF9) Mshale</t>
         </is>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFZllia0xxWGlBb3M1NnlqQ1M1aGVxNUhiSXc2X3l3TzBzSFpyellfaG9qQnljVzFrdldUcW5sUnk5MnZndFlkSUJQUmZMM25PbF9Ha2ljNUFnTV9PUkhhdg?oc=5</t>
         </is>
       </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFZllia0xxWGlBb3M1NnlqQ1M1aGVxNUhiSXc2X3l3TzBzSFpyellfaG9qQnljVzFrdldUcW5sUnk5MnZndFlkSUJQUmZMM25PbF9Ha2ljNUFnTV9PUkhhdg?oc=5</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -9813,17 +9813,17 @@
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>4aa35d4139dfe46a</t>
+          <t>a4a0f705a84ebf28</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -9833,22 +9833,22 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing - Nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing Nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="183" ht="48" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>38a90ce021ea7d8a</t>
+          <t>4aa35d4139dfe46a</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -9875,32 +9875,32 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T00:04:58Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Germany to Provide Assistance Worth 8 Million Euros for Bhote Koshi Flood Victims - Ekantipur</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Germany to Provide Assistance Worth 8 Million Euros for Bhote Koshi Flood Victims Ekantipur</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQdXdFdzctTzdDdlE1XzVWeGtMeUtPR2tKYlhKNEQyZUZURmVtbE0zbFJCS2MtTU9nVUZTMlZJOEdXcVJLSnZjZkNQWTVrbXpDQ1BMOVRiX2lNN1JQQnJOazdvN1BSSmU0LS13MzlaVzc4VmZMYll0YnBGSHVyVXA2WVhPZTRlYzhCRmhHV2NrVVdEYjhKSHhsZ1o0NEhMQThVWVNuTmpNM2h0VHJaVDhKVjREOGY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQdXdFdzctTzdDdlE1XzVWeGtMeUtPR2tKYlhKNEQyZUZURmVtbE0zbFJCS2MtTU9nVUZTMlZJOEdXcVJLSnZjZkNQWTVrbXpDQ1BMOVRiX2lNN1JQQnJOazdvN1BSSmU0LS13MzlaVzc4VmZMYll0YnBGSHVyVXA2WVhPZTRlYzhCRmhHV2NrVVdEYjhKSHhsZ1o0NEhMQThVWVNuTmpNM2h0VHJaVDhKVjREOGY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxPWm0yRGRLeC1seDlEU1pLdW1SUzZacDk1bU9nQ2ZFVlhfYzZyUHgyNjlRZkpSYVRGcXAxWlpndkVwQ19pSjZnSGtqMjM5alZEb0I1YlFzdW55U0lWbFp0ckVKSnJ1Z014aXdVOWs4bHBDNkZPMVlrNUNLZlV3MERMR3BRWGlMOUJzMXFpWEZrSmNxNEFicWZuZw?oc=5</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>e4d9c4185afc34a4</t>
+          <t>38a90ce021ea7d8a</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
@@ -9927,32 +9927,32 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:36:36Z</t>
+          <t>2026-09-22T00:04:58Z</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - Khabarhub</t>
+          <t>Germany to Provide Assistance Worth 8 Million Euros for Bhote Koshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims Khabarhub</t>
+          <t>Germany to Provide Assistance Worth 8 Million Euros for Bhote Koshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQdXdFdzctTzdDdlE1XzVWeGtMeUtPR2tKYlhKNEQyZUZURmVtbE0zbFJCS2MtTU9nVUZTMlZJOEdXcVJLSnZjZkNQWTVrbXpDQ1BMOVRiX2lNN1JQQnJOazdvN1BSSmU0LS13MzlaVzc4VmZMYll0YnBGSHVyVXA2WVhPZTRlYzhCRmhHV2NrVVdEYjhKSHhsZ1o0NEhMQThVWVNuTmpNM2h0VHJaVDhKVjREOGY?oc=5</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQdXdFdzctTzdDdlE1XzVWeGtMeUtPR2tKYlhKNEQyZUZURmVtbE0zbFJCS2MtTU9nVUZTMlZJOEdXcVJLSnZjZkNQWTVrbXpDQ1BMOVRiX2lNN1JQQnJOazdvN1BSSmU0LS13MzlaVzc4VmZMYll0YnBGSHVyVXA2WVhPZTRlYzhCRmhHV2NrVVdEYjhKSHhsZ1o0NEhMQThVWVNuTmpNM2h0VHJaVDhKVjREOGY?oc=5</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="185" ht="48" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>4bf585263842ae12</t>
+          <t>e4d9c4185afc34a4</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-08T16:36:36Z</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -9989,22 +9989,22 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 13,396 people rescued so far - Khabarhub</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 13,396 people rescued so far Khabarhub</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9sZTlnQ2NkWW9hUVlmcmZzVXIxUW1nTlJYakV1WnVSUVhjWEVydjhzWG9SQVo5YWtmWmpxZUlqNG12cElTc0IyZzJQRHpJMUUtcmVXN3F4ZzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
         </is>
       </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9sZTlnQ2NkWW9hUVlmcmZzVXIxUW1nTlJYakV1WnVSUVhjWEVydjhzWG9SQVo5YWtmWmpxZUlqNG12cElTc0IyZzJQRHpJMUUtcmVXN3F4ZzU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBCX3QxaWd5bFBrZlFjMFRFTmRaRlVpSWtBNXUxMDQySzZHNHdxMHIwV2tzMnZINTZQdlhoN3NwNkJWd2d2N3NOX2x0cnNnZmt1dHF4UzkwNV8?oc=5</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>ae9fa86dafccec71</t>
+          <t>4bf585263842ae12</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -10031,32 +10031,32 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 13,396 people rescued so far - Khabarhub</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims Nepalnews.com</t>
+          <t>Bhotekoshi flood: 13,396 people rescued so far Khabarhub</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9sZTlnQ2NkWW9hUVlmcmZzVXIxUW1nTlJYakV1WnVSUVhjWEVydjhzWG9SQVo5YWtmWmpxZUlqNG12cElTc0IyZzJQRHpJMUUtcmVXN3F4ZzU?oc=5</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9sZTlnQ2NkWW9hUVlmcmZzVXIxUW1nTlJYakV1WnVSUVhjWEVydjhzWG9SQVo5YWtmWmpxZUlqNG12cElTc0IyZzJQRHpJMUUtcmVXN3F4ZzU?oc=5</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="187" ht="48" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>1de436c02fc58f80</t>
+          <t>ae9fa86dafccec71</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -10083,32 +10083,32 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T16:22:37Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,357 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,357 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE4xbS1FYXlfTnladzdyeDl0Mnl1eThodFlvMjFYaERhVXVRUHVqa21vOXZHNHV5SDBwWkNzb3R6S2dnYmhHaHkyQkJQSk5JZXEzUDhocFZ3Y2w4dldTTVh1OVdtbUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
         </is>
       </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE4xbS1FYXlfTnladzdyeDl0Mnl1eThodFlvMjFYaERhVXVRUHVqa21vOXZHNHV5SDBwWkNzb3R6S2dnYmhHaHkyQkJQSk5JZXEzUDhocFZ3Y2w4dldTTVh1OVdtbUw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxNYlJFdEI5QktWNjJ2OEpYWWhVemtpdnBJMlc1VjdVVEgwWkQxbFgtemtfZl9ESFY3VTR0aHA4d0pwV0YwRWpWbWFfQ0dQSnVmM2xMamdJR2o2bzNCc3NTdWdtWGlwRFpEYVAyamtzWUZpSndBbnRITG5jckphRnhVRGlTTVJmV1VSbmdCNko5b1hEVkF5VkZvUXFrT3U?oc=5</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>deb603fb6091d44c</t>
+          <t>1de436c02fc58f80</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
@@ -10135,32 +10135,32 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T23:22:50Z</t>
+          <t>2026-09-10T16:22:37Z</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Mshale</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>बेत्रावतीमा बाँचेकाहरू रातभर खुला आकाशमुनि छन् | Rasuwa Flood | Betrawati Nuwakot | Onlinekhabar Tassi Bce (4BlThk57wu) - Mshale</t>
+          <t>Bhotekoshi flood: 1,357 bodies recovered so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>बेत्रावतीमा बाँचेकाहरू रातभर खुला आकाशमुनि छन् | Rasuwa Flood | Betrawati Nuwakot | Onlinekhabar Tassi Bce (4BlThk57wu) Mshale</t>
+          <t>Bhotekoshi flood: 1,357 bodies recovered so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdF8wcWtIaXZfMWktRzFSSlVTV2Yxc1Atak8wbVlTX2F6bFlqQzlnclV3Tk5ZRnJac0hpM3U5WDZQM2JLNDQ5UUZMVUVNQ0I5U3AtbjBjWHlaQm94N0licFVoSUM1MXZSSWVzX1ByZU5Ya01YMVFlRDJQX2hGTzBnTG44ZngtemxYMGFsRFNoMUxvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE4xbS1FYXlfTnladzdyeDl0Mnl1eThodFlvMjFYaERhVXVRUHVqa21vOXZHNHV5SDBwWkNzb3R6S2dnYmhHaHkyQkJQSk5JZXEzUDhocFZ3Y2w4dldTTVh1OVdtbUw?oc=5</t>
         </is>
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxNdF8wcWtIaXZfMWktRzFSSlVTV2Yxc1Atak8wbVlTX2F6bFlqQzlnclV3Tk5ZRnJac0hpM3U5WDZQM2JLNDQ5UUZMVUVNQ0I5U3AtbjBjWHlaQm94N0licFVoSUM1MXZSSWVzX1ByZU5Ya01YMVFlRDJQX2hGTzBnTG44ZngtemxYMGFsRFNoMUxvQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE4xbS1FYXlfTnladzdyeDl0Mnl1eThodFlvMjFYaERhVXVRUHVqa21vOXZHNHV5SDBwWkNzb3R6S2dnYmhHaHkyQkJQSk5JZXEzUDhocFZ3Y2w4dldTTVh1OVdtbUw?oc=5</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
     <row r="189" ht="48" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>dc502f64e1b6333f</t>
+          <t>deb603fb6091d44c</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-08T23:22:50Z</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>Mshale</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises - thehimalayantimes.com</t>
+          <t>बेत्रावतीमा बाँचेकाहरू रातभर खुला आकाशमुनि छन् | Rasuwa Flood | Betrawati Nuwakot | Onlinekhabar Tassi Bce (4BlThk57wu) - Mshale</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises thehimalayantimes.com</t>
+          <t>बेत्रावतीमा बाँचेकाहरू रातभर खुला आकाशमुनि छन् | Rasuwa Flood | Betrawati Nuwakot | Onlinekhabar Tassi Bce (4BlThk57wu) Mshale</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQTU1QaDBvMW1kSTVzR1FkTzdLckE2Mk1pSGxlWHFDMGZIVXg5TTZFQlhtMWVsYmt1b0pIMk5VLXBTMzFTOFFzVEZlNnF0Q2RVekZlMU5jLUFfLWIx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdF8wcWtIaXZfMWktRzFSSlVTV2Yxc1Atak8wbVlTX2F6bFlqQzlnclV3Tk5ZRnJac0hpM3U5WDZQM2JLNDQ5UUZMVUVNQ0I5U3AtbjBjWHlaQm94N0licFVoSUM1MXZSSWVzX1ByZU5Ya01YMVFlRDJQX2hGTzBnTG44ZngtemxYMGFsRFNoMUxvQQ?oc=5</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQTU1QaDBvMW1kSTVzR1FkTzdLckE2Mk1pSGxlWHFDMGZIVXg5TTZFQlhtMWVsYmt1b0pIMk5VLXBTMzFTOFFzVEZlNnF0Q2RVekZlMU5jLUFfLWIx?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxNdF8wcWtIaXZfMWktRzFSSlVTV2Yxc1Atak8wbVlTX2F6bFlqQzlnclV3Tk5ZRnJac0hpM3U5WDZQM2JLNDQ5UUZMVUVNQ0I5U3AtbjBjWHlaQm94N0licFVoSUM1MXZSSWVzX1ByZU5Ya01YMVFlRDJQX2hGTzBnTG44ZngtemxYMGFsRFNoMUxvQQ?oc=5</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -10229,42 +10229,42 @@
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>76ee47ba59686ba1</t>
+          <t>dc502f64e1b6333f</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>thehimalayantimes.com</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them - Ratopati</t>
+          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises - thehimalayantimes.com</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them Ratopati</t>
+          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises thehimalayantimes.com</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQTU1QaDBvMW1kSTVzR1FkTzdLckE2Mk1pSGxlWHFDMGZIVXg5TTZFQlhtMWVsYmt1b0pIMk5VLXBTMzFTOFFzVEZlNnF0Q2RVekZlMU5jLUFfLWIx?oc=5</t>
         </is>
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBQTU1QaDBvMW1kSTVzR1FkTzdLckE2Mk1pSGxlWHFDMGZIVXg5TTZFQlhtMWVsYmt1b0pIMk5VLXBTMzFTOFFzVEZlNnF0Q2RVekZlMU5jLUFfLWIx?oc=5</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -10281,7 +10281,7 @@
     <row r="191" ht="48" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>7c4f8e2a99a4ce1f</t>
+          <t>76ee47ba59686ba1</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -10291,32 +10291,32 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T12:28:25Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - Nepalnews.com</t>
+          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them - Ratopati</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund Nepalnews.com</t>
+          <t>21 Injured in Bhote Koshi Flood Treated at Teaching Hospital, One Indian National Among Them Ratopati</t>
         </is>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
         </is>
       </c>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPcEYzb3c4VHM0M0xxVnpsYWJxN3FmNDNGVDcxOUF1ZkswSkhxRWxRRnd4T051Q0cwVGZ0ZWQ5Yi1SX1hRcmlCMERvVERwcEhsQ3pMX2NobWx6Y2xQUldZTDhPOGRrc1lTczR4Qi1PTXF6Y19iZEp2bUdWQmRRc0ZySnhvUi1ONkxuajR2UXZvMDJ3Nkg1dC1YaE5Pc2s3SUlmRndsdGlDRU4taV9DSURHdlJB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOWWFGMmFad2tBUnNwSndWX0ZKMEJwQTY2WWdNbmw2eHZFZndnd3JRX2hteUFNSDhaUjI0Y3lXOHVpRkx4T2RjOC1mOEVaZVl3TG1rMTNPZ21ZbC1wcnc1czdjRlFLN2N1dE9sR0ktMzAxSUNtQ1M2NF9kaGZXdW9WZ3p4T2sxYzFKd3VvajRpT25fR0ZrclZaVmdtem4zZWZGelRIMy1TclBrMHIzb3UyNg?oc=5</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -11217,7 +11217,7 @@
     <row r="209" ht="48" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>ad88346da6844b20</t>
+          <t>47075b2c0944a15a</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-06T04:35:51Z</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -11237,22 +11237,22 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - Khabarhub</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - Khabarhub</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world Khabarhub</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts Khabarhub</t>
         </is>
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
         </is>
       </c>
       <c r="H209" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE84NTJkWEJQNWllOTNQMXlHYjVkV1BzZ25tNTJQLWQybF8zZncyT0lraGwzUHlPb1NfUkxnOC02T2x2c3ZkNHRIa240ckRDZkRpc0ctYW9HVV8?oc=5</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -11269,7 +11269,7 @@
     <row r="210" ht="48" customHeight="1">
       <c r="A210" s="8" t="inlineStr">
         <is>
-          <t>bce011217f19bc6a</t>
+          <t>ad88346da6844b20</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
@@ -11279,32 +11279,32 @@
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - english.nepalnews.com</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - Khabarhub</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear english.nepalnews.com</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world Khabarhub</t>
         </is>
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
         </is>
       </c>
       <c r="H210" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9EMnROUW9KQjNzY3lLbkFIMlVBZEktcE9vZnl2R3hiZHdYemM3bElPLXEwY0FxbTJWX001QnBYLWZERjFsQzFxejBSX0hodkw0em5lN25RZXI?oc=5</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -11321,7 +11321,7 @@
     <row r="211" ht="48" customHeight="1">
       <c r="A211" s="8" t="inlineStr">
         <is>
-          <t>c5cc47b406fd1b88</t>
+          <t>bce011217f19bc6a</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
@@ -11331,32 +11331,32 @@
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.nepalnews.com</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - Khabarhub</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - english.nepalnews.com</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification Khabarhub</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear english.nepalnews.com</t>
         </is>
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
         </is>
       </c>
       <c r="H211" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPVU81VERrZ001OWZvd2VLOHZSVWNHRVhjQkdwRU8zXzNQdEJsQTVwbEc5WHJrUHdQanVvdkNsZ0hYSDVOdEhURmFCemtGOUpYN0lQSFJIcXhabzB5VzIwZi10aHo4VGR3ZU94T1ZkR2ZlZ3V0MzFlQjktdFZuVzBRM3ZLTW8xaHZiaWNsaURlUFRkVWFlM2RVN1hZUF9aeHJYQU9RU2tVU2dLd2YtSGpLcEpuQTMtbWc2UzNpdmxGdWpwMERRTlJfMkVkVDlTY2M?oc=5</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -11373,7 +11373,7 @@
     <row r="212" ht="48" customHeight="1">
       <c r="A212" s="8" t="inlineStr">
         <is>
-          <t>40bcbff45ef246f3</t>
+          <t>c5cc47b406fd1b88</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -11393,22 +11393,22 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - Khabarhub</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - Khabarhub</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital Khabarhub</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification Khabarhub</t>
         </is>
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
         </is>
       </c>
       <c r="H212" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE00SXRYNnlENW9XRG9Wa3BnUzJteFMwWmozaFJHcmd3TUM5OU1ERzVxUTRsZXpzM05uQ2NJNF9VOGNnV3kydVJLOWY3SmFBdThWVUFncGRJYXM?oc=5</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -11425,7 +11425,7 @@
     <row r="213" ht="48" customHeight="1">
       <c r="A213" s="8" t="inlineStr">
         <is>
-          <t>9d37d48a2c995a2b</t>
+          <t>40bcbff45ef246f3</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -11445,22 +11445,22 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts - Khabarhub</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts Khabarhub</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
         </is>
       </c>
       <c r="H213" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1GclZJdHkxdTRwQ1JEaUdac3IzNmgzcC1uS29ZakFSNnozQWpJS1BySjFxa0pxR25mb1RqMDg5ekxQS183WXJkYXhDNXVEM1ZXS0lRbDlRdlk?oc=5</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
@@ -11477,7 +11477,7 @@
     <row r="214" ht="48" customHeight="1">
       <c r="A214" s="8" t="inlineStr">
         <is>
-          <t>e7206a6f81806ce7</t>
+          <t>9d37d48a2c995a2b</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
@@ -11487,32 +11487,32 @@
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
+          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts - Khabarhub</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
+          <t>Nepal, South Korea discuss Bhotekoshi flood, climate change impacts Khabarhub</t>
         </is>
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
         </is>
       </c>
       <c r="H214" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5IQWdSaHdOSk80Qm9ic0NPeGFteGU3U1pmNFRzeWZrWFVQQ0tDVGdVYU9Od2NWazlIc2gzbWJyMmMwY1Q4ZzJ2VVhlQlFBQ002ZC1nMnE1ZUY?oc=5</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -11529,7 +11529,7 @@
     <row r="215" ht="48" customHeight="1">
       <c r="A215" s="8" t="inlineStr">
         <is>
-          <t>d1cfb76c84a4a44d</t>
+          <t>e7206a6f81806ce7</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -11549,22 +11549,22 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged - Nepalnews.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged Nepalnews.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
         </is>
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
         </is>
       </c>
       <c r="H215" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNZlJmdm1DNEdSSzNNVW5BSmpjcTFZWFU3Ykw3WFNRczh4OTFhbnMxdXpPbFROQVptQ1JTQjVuNWE3eFZsaFo2UG9OUzVKMGZQd203T2lnR20ydGNUZXdYQWFNTXdYUml2bU1EUk8tWkR3S25JaWo2cUtoenl3RDR3NWY0ejRVZXY0eDItMGx1TFRCZ1dRcXotSWVDNkFoWjBIUkE?oc=5</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -11581,7 +11581,7 @@
     <row r="216" ht="48" customHeight="1">
       <c r="A216" s="8" t="inlineStr">
         <is>
-          <t>1c2c3ae0634abfb3</t>
+          <t>d1cfb76c84a4a44d</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
@@ -11591,32 +11591,32 @@
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - Khabarhub</t>
+          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged - Nepalnews.com</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital Khabarhub</t>
+          <t>Bhote Koshi flood: 38 treated at National Trauma Center discharged Nepalnews.com</t>
         </is>
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
         </is>
       </c>
       <c r="H216" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTWwzZUVuZHBlaU1rUDMyVngySkxnTXlHbkRUZkVLWWtEVXdUR25DTk1PeXJfQWkzY3p4cVVjWTZvTFgzRVJTMk9tUXQzS0M3RVpPMFkwdG5ySVY5ZE1BekNaMDJxLTB3eDkwcmt1d1NYYWo1R1NRa09ZdDNrTDg5REx1S0JORXJYbzlWNUtwT05JTjZuc2VQTVpFbVNiWEktVTl4LWNNRUg?oc=5</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="217" ht="48" customHeight="1">
       <c r="A217" s="8" t="inlineStr">
         <is>
-          <t>30a8b09171137a8d</t>
+          <t>1c2c3ae0634abfb3</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
@@ -11643,32 +11643,32 @@
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
         </is>
       </c>
       <c r="H217" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBMalZNdTV6TnV2N3JBQVAwT3BuS3dSaGZXQzhTUWtEa1AwemNBWjdYLTZTOTNZdEJFVzhNcVd4U1puLWRnQU1uU1FFS3NmZUFWZGJVWWw2Q2w?oc=5</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -11685,7 +11685,7 @@
     <row r="218" ht="48" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>2a2d86f779d94eae</t>
+          <t>30a8b09171137a8d</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
@@ -11695,32 +11695,32 @@
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Pakistani player dedicates his award for Bhotekoshi flood victims - risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Pakistani player dedicates his award for Bhotekoshi flood victims risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,353 bodies recovered, 3,992 still missing myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9rZHBNLVZKN0p0VHNXVjZzdUlrVVNONTZ3eW1fYzRPaU9uZk9xeDV5blQ3NWVjZDFqbVU4SmlJX3VKWEdOX0pKM1JBYkhvc0pu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
         </is>
       </c>
       <c r="H218" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9rZHBNLVZKN0p0VHNXVjZzdUlrVVNONTZ3eW1fYzRPaU9uZk9xeDV5blQ3NWVjZDFqbVU4SmlJX3VKWEdOX0pKM1JBYkhvc0pu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaHFWQ29DZ0w4OEl2eDBQcWk5d2s2SHBSVXpqOXZtb01vekFEMWdMdlU2NWRoN1plN2toemk1WkswcHV0VDVmal96Mzd5dTRJLWVpd3VHeG56ODBPbmJNNTNfOEpzbjJhcEl2dWROV2M1VUxlNmxqNk4zdldBTWlQREE2T29uMlVkY3ZrUDZQalBYUE1ZeTRudHhENHh6dTYxMnE5MFV3M2lHbmhOME1IbUQtZzVCci1wakFTeHFCcVVwQQ?oc=5</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr">
@@ -11737,7 +11737,7 @@
     <row r="219" ht="48" customHeight="1">
       <c r="A219" s="8" t="inlineStr">
         <is>
-          <t>2ee38bc59050fb64</t>
+          <t>2a2d86f779d94eae</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
@@ -11747,32 +11747,32 @@
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>risingnepaldaily.com</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss - The Himalayan Times</t>
+          <t>Pakistani player dedicates his award for Bhotekoshi flood victims - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss The Himalayan Times</t>
+          <t>Pakistani player dedicates his award for Bhotekoshi flood victims risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9rZHBNLVZKN0p0VHNXVjZzdUlrVVNONTZ3eW1fYzRPaU9uZk9xeDV5blQ3NWVjZDFqbVU4SmlJX3VKWEdOX0pKM1JBYkhvc0pu?oc=5</t>
         </is>
       </c>
       <c r="H219" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9rZHBNLVZKN0p0VHNXVjZzdUlrVVNONTZ3eW1fYzRPaU9uZk9xeDV5blQ3NWVjZDFqbVU4SmlJX3VKWEdOX0pKM1JBYkhvc0pu?oc=5</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
     <row r="220" ht="48" customHeight="1">
       <c r="A220" s="8" t="inlineStr">
         <is>
-          <t>4255cd2b59ff3527</t>
+          <t>2ee38bc59050fb64</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing - Khabarhub</t>
+          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss - The Himalayan Times</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing Khabarhub</t>
+          <t>Bhotekoshi flood damages 55 drinking water projects, Rs 640m loss The Himalayan Times</t>
         </is>
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
         </is>
       </c>
       <c r="H220" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNWnVHRmplWWZSb3NpT3lpVFo1bmFEQ1huQU1RamlSWFY0U3F4R3FybzVESTVaZDhGbTh5STVUVWM4XzRJYlljejc3NEVNYlgzQlN1NDZpT3oxWHQ0dTFkR2RoMV9oRmk2T3R0R0pOa2NnSzkxaGtidi1oUnJmZkI0WFFJMWM1UUZHMFlKVE9ZeUVHSkFPUnJ2Y3NBdlp5MkZKSmfSAVxBVV95cUxPM2poekJ0UGRhMGwyaGcxak0xMjB2cFRjSlhjdXlDUlZWSU81Q2ZpdnllOTZ3T09tVWpwRkFGOTFKdVVMcjJIaHgyUmMydExuLU83aS0xX0hJOXE0Ug?oc=5</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="221" ht="48" customHeight="1">
       <c r="A221" s="8" t="inlineStr">
         <is>
-          <t>7ac6592e31db85a5</t>
+          <t>4255cd2b59ff3527</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
@@ -11851,32 +11851,32 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing - Khabarhub</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,341 bodies recovered, 4,044 people missing Khabarhub</t>
         </is>
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
         </is>
       </c>
       <c r="H221" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE91SFdxRDhLd1lVcUlyTHQ3NWdHa1ZpTTJPZGFyajBTdkpjMkQ2QzUwUk5SVUgzSWJRZXNTbXJOSmhkYTctbDhtanFaTWJjdUMtU0JXVm5WSzg?oc=5</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
@@ -11893,7 +11893,7 @@
     <row r="222" ht="48" customHeight="1">
       <c r="A222" s="8" t="inlineStr">
         <is>
-          <t>8b22056f7cc30e08</t>
+          <t>7ac6592e31db85a5</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
@@ -11903,32 +11903,32 @@
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T04:36:55Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ - Nepalnews.com</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhote Koshi flood exposes Nepal’s hydropower ‘cascade risk’ Nepalnews.com</t>
         </is>
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
         </is>
       </c>
       <c r="H222" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxNcmtJUVV0ZWFuYmFpcGxDTFBrTnd2S21GcnBxNjU2M1J3U2k0bEh5cGRyM19hdVowUURZZHBFREpMYUtJWGdxMUFjcjFaSUhPX09hOHJaLVlLZ3VPeFBCc1dYNXQ4OFlpSklITUZvLWtFYXZSNWxBVkZ1REo2czNuUURCTHk3akp3NTJoQ0xaZlBjYmdQelY3NjZxS2xYZU0?oc=5</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
@@ -11945,7 +11945,7 @@
     <row r="223" ht="48" customHeight="1">
       <c r="A223" s="8" t="inlineStr">
         <is>
-          <t>2d236097b3cf1832</t>
+          <t>8b22056f7cc30e08</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T10:53:40Z</t>
+          <t>2026-09-07T04:36:55Z</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -11965,22 +11965,22 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhotekoshi flood: An overview on search, rescue and relief operations – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
         </is>
       </c>
       <c r="H223" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBrZmlQUjJYMlkzRTNQNmlBWlNnNDY0SG1ZX2Q3MkpJUDdtTVNRWU1YdFdSTWhFTDBKSk9nS1BtcVlNU0V5VE5QbmV3U1RVWUFHeFFpcnk5dVJKRGxvekZFTHdPMHY?oc=5</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="224" ht="48" customHeight="1">
       <c r="A224" s="8" t="inlineStr">
         <is>
-          <t>54ae0dd183a5ffe8</t>
+          <t>2d236097b3cf1832</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
@@ -12007,32 +12007,32 @@
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T20:22:52Z</t>
+          <t>2026-09-06T10:53:40Z</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing - Ratopati</t>
+          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing Ratopati</t>
+          <t>Bhotekoshi Flood Damages 55 Drinking Water Projects in Four Districts – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
         </is>
       </c>
       <c r="H224" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9NbnVUVlJ5U0ZYOG5DXzB2UGpHbDVzd3p2aGMxd1ltS0ZVQmMtcEVwZnhTZjM1emlSSDB2blNQM1RVWVpmc1dkbnhTNEFjcm5PWXVCellVTENYUGNuV1B0M0Z3OTQ?oc=5</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr">
@@ -12049,7 +12049,7 @@
     <row r="225" ht="48" customHeight="1">
       <c r="A225" s="8" t="inlineStr">
         <is>
-          <t>007a8e4ea9da5310</t>
+          <t>54ae0dd183a5ffe8</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
@@ -12059,32 +12059,32 @@
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T15:26:41Z</t>
+          <t>2026-09-06T20:22:52Z</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing - Ratopati</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>1,353 Bodies Recovered from Bhote Koshi Flood; 3,992 Still Missing Ratopati</t>
         </is>
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
         </is>
       </c>
       <c r="H225" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnE3OTN2YXZpXzNqQXRRZ0VrYjBqaDY5UTlSeDNlV3Q1YnQtYlREd3otRDUtX29yV2loWXMwUkdwRWhGNzRFNWFubnZydWRHNlJWU3VOV0tXZ1BmMTJuRTh6QjB1OFlWXzFialR0NWJXY0FObmdlTVVqNzdfSzdCdw?oc=5</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -12101,42 +12101,42 @@
     <row r="226" ht="48" customHeight="1">
       <c r="A226" s="8" t="inlineStr">
         <is>
-          <t>62c63745290773df</t>
+          <t>007a8e4ea9da5310</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-06T15:26:41Z</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood brings to fore demand of climate justice again – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
         </is>
       </c>
       <c r="H226" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBlMWs0UEhkWGpHTGtYRUpSU0RrY1pEeGRtcEpJNTRoMFpCVG41V2ctUmlYbmZtejJYUTU2SE5hZWhxaV9sWUQzMTRBc1l2T2p1Y0JyaFdSbHVkM0JZeHlLUGFEQWE?oc=5</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
     <row r="227" ht="48" customHeight="1">
       <c r="A227" s="8" t="inlineStr">
         <is>
-          <t>b02b6baeae823858</t>
+          <t>62c63745290773df</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
@@ -12163,32 +12163,32 @@
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T10:55:34Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,342; nearly 4,900 still missing - Nepalnews.com</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,342; nearly 4,900 still missing Nepalnews.com</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSGRxNWxTai1wcFZib2M3ek02bEhGbjY1RFAtdTJvaDR1WWRXNWZaUkFBalRhUy1NOFd6NVhLRmZIUm9vOUdTTExfcW1zTzJlTnhBamNfV0pXcmtNY1U1cHdHenhOa0JjRzhIQ3FlOXEzRU42Y1lEQmhJN3V3VDVNSlZiTm9FSmg2LXpkcU5qYWtqc0NzdG0wcnBiSDhIUnpKLVM2X1pROFBTZ00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="H227" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSGRxNWxTai1wcFZib2M3ek02bEhGbjY1RFAtdTJvaDR1WWRXNWZaUkFBalRhUy1NOFd6NVhLRmZIUm9vOUdTTExfcW1zTzJlTnhBamNfV0pXcmtNY1U1cHdHenhOa0JjRzhIQ3FlOXEzRU42Y1lEQmhJN3V3VDVNSlZiTm9FSmg2LXpkcU5qYWtqc0NzdG0wcnBiSDhIUnpKLVM2X1pROFBTZ00?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -12829,7 +12829,7 @@
     <row r="240" ht="48" customHeight="1">
       <c r="A240" s="8" t="inlineStr">
         <is>
-          <t>f7c2e6ce3f764d01</t>
+          <t>eb73716a3ee4f27a</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
@@ -12839,32 +12839,32 @@
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
+          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing - Ratopati</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
+          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing Ratopati</t>
         </is>
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbDNtYTQ5Y21CUG1kUjVqb1E0U3lKeUx0Q3hYQVJNWVlRUGZVa3JSNGRvVUNJeGJveUdXa05qdDRGSmZsRHhraUh0UXhPUVBfR3IzQndBSHNFSzhabm9jNGxiNGVkYXpfZ0xDUzZuMnkxX1hDTURjOW5OZEhMdGtia1RpbjdIZTNsNGwtY2I3RTFzQ3hhTDRmM2JHVDZ0M1BnWEd4eHpScTdEQmoxUW5jOWI4RzgtQQ?oc=5</t>
         </is>
       </c>
       <c r="H240" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQbDNtYTQ5Y21CUG1kUjVqb1E0U3lKeUx0Q3hYQVJNWVlRUGZVa3JSNGRvVUNJeGJveUdXa05qdDRGSmZsRHhraUh0UXhPUVBfR3IzQndBSHNFSzhabm9jNGxiNGVkYXpfZ0xDUzZuMnkxX1hDTURjOW5OZEhMdGtia1RpbjdIZTNsNGwtY2I3RTFzQ3hhTDRmM2JHVDZ0M1BnWEd4eHpScTdEQmoxUW5jOWI4RzgtQQ?oc=5</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
@@ -12881,7 +12881,7 @@
     <row r="241" ht="48" customHeight="1">
       <c r="A241" s="8" t="inlineStr">
         <is>
-          <t>b80549513c064b0f</t>
+          <t>f7c2e6ce3f764d01</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
@@ -12891,32 +12891,32 @@
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
         </is>
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="H241" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="242" ht="48" customHeight="1">
       <c r="A242" s="8" t="inlineStr">
         <is>
-          <t>2c151d9781807ab6</t>
+          <t>b80549513c064b0f</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
@@ -12943,32 +12943,32 @@
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="H242" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="243" ht="48" customHeight="1">
       <c r="A243" s="8" t="inlineStr">
         <is>
-          <t>7ac8c48d235b6902</t>
+          <t>2c151d9781807ab6</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
@@ -12995,32 +12995,32 @@
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T22:53:38Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myrepublica.nagariknetwork.com</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myrepublica.nagariknetwork.com</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
         </is>
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="H243" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="244" ht="48" customHeight="1">
       <c r="A244" s="8" t="inlineStr">
         <is>
-          <t>02f3fec961d30051</t>
+          <t>7ac8c48d235b6902</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
@@ -13047,32 +13047,32 @@
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-05T22:53:38Z</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area - The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="H244" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr">
@@ -13089,7 +13089,7 @@
     <row r="245" ht="48" customHeight="1">
       <c r="A245" s="8" t="inlineStr">
         <is>
-          <t>90760ad09deb442c</t>
+          <t>02f3fec961d30051</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
@@ -13099,32 +13099,32 @@
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,294 - Onlinekhabar English</t>
+          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area - The Rising Nepal</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,294 Onlinekhabar English</t>
+          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area The Rising Nepal</t>
         </is>
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBuVzh0dGR1T2xfZnpyWkFhdmRjdlF0RGFPRU9YTmVQOTBpRkxVcXMtaFQ1aEE1VmJQOTZlS3pnV25Ra1BSbzlZTzdfbEZpZ2JRVjlLTlRqTGJINGVrWGtuSWJKU2ZwLWMxNnRoZGZYVnA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
         </is>
       </c>
       <c r="H245" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFBuVzh0dGR1T2xfZnpyWkFhdmRjdlF0RGFPRU9YTmVQOTBpRkxVcXMtaFQ1aEE1VmJQOTZlS3pnV25Ra1BSbzlZTzdfbEZpZ2JRVjlLTlRqTGJINGVrWGtuSWJKU2ZwLWMxNnRoZGZYVnA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="246" ht="48" customHeight="1">
       <c r="A246" s="8" t="inlineStr">
         <is>
-          <t>3f458a24f691b6af</t>
+          <t>90760ad09deb442c</t>
         </is>
       </c>
       <c r="B246" s="8" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' - The Rising Nepal</t>
+          <t>Rasuwa flood death toll reaches 1,294 - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' The Rising Nepal</t>
+          <t>Rasuwa flood death toll reaches 1,294 Onlinekhabar English</t>
         </is>
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBuVzh0dGR1T2xfZnpyWkFhdmRjdlF0RGFPRU9YTmVQOTBpRkxVcXMtaFQ1aEE1VmJQOTZlS3pnV25Ra1BSbzlZTzdfbEZpZ2JRVjlLTlRqTGJINGVrWGtuSWJKU2ZwLWMxNnRoZGZYVnA?oc=5</t>
         </is>
       </c>
       <c r="H246" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFBuVzh0dGR1T2xfZnpyWkFhdmRjdlF0RGFPRU9YTmVQOTBpRkxVcXMtaFQ1aEE1VmJQOTZlS3pnV25Ra1BSbzlZTzdfbEZpZ2JRVjlLTlRqTGJINGVrWGtuSWJKU2ZwLWMxNnRoZGZYVnA?oc=5</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr">
@@ -13193,7 +13193,7 @@
     <row r="247" ht="48" customHeight="1">
       <c r="A247" s="8" t="inlineStr">
         <is>
-          <t>6c94171fc3f8e00c</t>
+          <t>3f458a24f691b6af</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -13213,22 +13213,22 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
+          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' The Rising Nepal</t>
         </is>
       </c>
       <c r="G247" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
         </is>
       </c>
       <c r="H247" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
@@ -13245,7 +13245,7 @@
     <row r="248" ht="48" customHeight="1">
       <c r="A248" s="8" t="inlineStr">
         <is>
-          <t>69c5156e1e556a67</t>
+          <t>6c94171fc3f8e00c</t>
         </is>
       </c>
       <c r="B248" s="8" t="inlineStr">
@@ -13255,32 +13255,32 @@
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
         </is>
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="H248" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
@@ -13297,7 +13297,7 @@
     <row r="249" ht="48" customHeight="1">
       <c r="A249" s="8" t="inlineStr">
         <is>
-          <t>95216a0448be4ecd</t>
+          <t>69c5156e1e556a67</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
@@ -13312,27 +13312,27 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myrepublica.nagariknetwork.com</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myrepublica.nagariknetwork.com</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="H249" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -13349,7 +13349,7 @@
     <row r="250" ht="48" customHeight="1">
       <c r="A250" s="8" t="inlineStr">
         <is>
-          <t>258c222aa846d3dc</t>
+          <t>95216a0448be4ecd</t>
         </is>
       </c>
       <c r="B250" s="8" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="H250" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr">
@@ -13401,7 +13401,7 @@
     <row r="251" ht="48" customHeight="1">
       <c r="A251" s="8" t="inlineStr">
         <is>
-          <t>40652f6cba568b14</t>
+          <t>258c222aa846d3dc</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="C251" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T04:29:29Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
         </is>
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="H251" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -13453,7 +13453,7 @@
     <row r="252" ht="48" customHeight="1">
       <c r="A252" s="8" t="inlineStr">
         <is>
-          <t>b49f667ad8e744b7</t>
+          <t>40652f6cba568b14</t>
         </is>
       </c>
       <c r="B252" s="8" t="inlineStr">
@@ -13463,32 +13463,32 @@
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T15:29:59Z</t>
+          <t>2026-09-04T04:29:29Z</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
         </is>
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="H252" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr">
@@ -13505,7 +13505,7 @@
     <row r="253" ht="48" customHeight="1">
       <c r="A253" s="8" t="inlineStr">
         <is>
-          <t>44d5da90c9532a74</t>
+          <t>b49f667ad8e744b7</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
@@ -13515,32 +13515,32 @@
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-12T15:29:59Z</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
         </is>
       </c>
       <c r="G253" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
         </is>
       </c>
       <c r="H253" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
@@ -13557,7 +13557,7 @@
     <row r="254" ht="48" customHeight="1">
       <c r="A254" s="8" t="inlineStr">
         <is>
-          <t>e5d64e09de0bd232</t>
+          <t>44d5da90c9532a74</t>
         </is>
       </c>
       <c r="B254" s="8" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -13577,22 +13577,22 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims The Rising Nepal</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="H254" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
@@ -13609,7 +13609,7 @@
     <row r="255" ht="48" customHeight="1">
       <c r="A255" s="8" t="inlineStr">
         <is>
-          <t>5e55f5bee3be9088</t>
+          <t>e5d64e09de0bd232</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
@@ -13619,32 +13619,32 @@
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T21:07:58Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
+          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
+          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G255" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
         </is>
       </c>
       <c r="H255" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -13661,7 +13661,7 @@
     <row r="256" ht="48" customHeight="1">
       <c r="A256" s="8" t="inlineStr">
         <is>
-          <t>d85a94e8900b3070</t>
+          <t>5e55f5bee3be9088</t>
         </is>
       </c>
       <c r="B256" s="8" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-08T21:07:58Z</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -13681,22 +13681,22 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
         </is>
       </c>
       <c r="H256" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr">
@@ -13713,7 +13713,7 @@
     <row r="257" ht="48" customHeight="1">
       <c r="A257" s="8" t="inlineStr">
         <is>
-          <t>830f7a3c5e28048a</t>
+          <t>d85a94e8900b3070</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -13733,22 +13733,22 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued - myRepublica</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued myRepublica</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
         </is>
       </c>
       <c r="G257" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
         </is>
       </c>
       <c r="H257" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr">
@@ -13765,7 +13765,7 @@
     <row r="258" ht="48" customHeight="1">
       <c r="A258" s="8" t="inlineStr">
         <is>
-          <t>48d3e154be99628d</t>
+          <t>830f7a3c5e28048a</t>
         </is>
       </c>
       <c r="B258" s="8" t="inlineStr">
@@ -13775,32 +13775,32 @@
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T23:02:25Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors - The Annapurna Express</t>
+          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued - myRepublica</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors The Annapurna Express</t>
+          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued myRepublica</t>
         </is>
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
         </is>
       </c>
       <c r="H258" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
@@ -13817,7 +13817,7 @@
     <row r="259" ht="48" customHeight="1">
       <c r="A259" s="8" t="inlineStr">
         <is>
-          <t>c887d95a53da880f</t>
+          <t>48d3e154be99628d</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
@@ -13827,32 +13827,32 @@
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T23:02:25Z</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhote Koshi flood affected area - Nepalnews.com</t>
+          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors - The Annapurna Express</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhote Koshi flood affected area Nepalnews.com</t>
+          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors The Annapurna Express</t>
         </is>
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
         </is>
       </c>
       <c r="H259" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
@@ -13869,7 +13869,7 @@
     <row r="260" ht="48" customHeight="1">
       <c r="A260" s="8" t="inlineStr">
         <is>
-          <t>1cd5958711f2fd98</t>
+          <t>c887d95a53da880f</t>
         </is>
       </c>
       <c r="B260" s="8" t="inlineStr">
@@ -13889,22 +13889,22 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief - Nepalnews.com</t>
+          <t>Heavy rain forecast in Bhote Koshi flood affected area - Nepalnews.com</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief Nepalnews.com</t>
+          <t>Heavy rain forecast in Bhote Koshi flood affected area Nepalnews.com</t>
         </is>
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
         </is>
       </c>
       <c r="H260" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
@@ -13921,7 +13921,7 @@
     <row r="261" ht="48" customHeight="1">
       <c r="A261" s="8" t="inlineStr">
         <is>
-          <t>68b706a9a3354119</t>
+          <t>1cd5958711f2fd98</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified - myRepublica</t>
+          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief - Nepalnews.com</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified myRepublica</t>
+          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief Nepalnews.com</t>
         </is>
       </c>
       <c r="G261" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
         </is>
       </c>
       <c r="H261" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr">
@@ -13973,7 +13973,7 @@
     <row r="262" ht="48" customHeight="1">
       <c r="A262" s="8" t="inlineStr">
         <is>
-          <t>e6746450786fdf1d</t>
+          <t>68b706a9a3354119</t>
         </is>
       </c>
       <c r="B262" s="8" t="inlineStr">
@@ -13983,32 +13983,32 @@
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue - Nepalnews.com</t>
+          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified - myRepublica</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue Nepalnews.com</t>
+          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified myRepublica</t>
         </is>
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
         </is>
       </c>
       <c r="H262" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr">
@@ -14025,7 +14025,7 @@
     <row r="263" ht="48" customHeight="1">
       <c r="A263" s="8" t="inlineStr">
         <is>
-          <t>51205720cf66f904</t>
+          <t>e6746450786fdf1d</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
@@ -14035,32 +14035,32 @@
       </c>
       <c r="C263" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt continues search and rescue operations - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue - Nepalnews.com</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt continues search and rescue operations Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue Nepalnews.com</t>
         </is>
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
         </is>
       </c>
       <c r="H263" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
@@ -14077,7 +14077,7 @@
     <row r="264" ht="48" customHeight="1">
       <c r="A264" s="8" t="inlineStr">
         <is>
-          <t>8a2301952fd337c9</t>
+          <t>51205720cf66f904</t>
         </is>
       </c>
       <c r="B264" s="8" t="inlineStr">
@@ -14087,32 +14087,32 @@
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Nepal demands urgent climate funds after Bhotekoshi flood - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Govt continues search and rescue operations - Khabarhub</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Nepal demands urgent climate funds after Bhotekoshi flood The Rising Nepal</t>
+          <t>Bhotekoshi flood: Govt continues search and rescue operations Khabarhub</t>
         </is>
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
         </is>
       </c>
       <c r="H264" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
         </is>
       </c>
       <c r="I264" s="3" t="inlineStr">
@@ -14129,7 +14129,7 @@
     <row r="265" ht="48" customHeight="1">
       <c r="A265" s="8" t="inlineStr">
         <is>
-          <t>8d6e2ecb2368dfef</t>
+          <t>8a2301952fd337c9</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
@@ -14139,32 +14139,32 @@
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T04:35:51Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
+          <t>Nepal demands urgent climate funds after Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
+          <t>Nepal demands urgent climate funds after Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G265" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
         </is>
       </c>
       <c r="H265" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
@@ -14181,7 +14181,7 @@
     <row r="266" ht="48" customHeight="1">
       <c r="A266" s="8" t="inlineStr">
         <is>
-          <t>bcfd74891234047d</t>
+          <t>8d6e2ecb2368dfef</t>
         </is>
       </c>
       <c r="B266" s="8" t="inlineStr">
@@ -14191,32 +14191,32 @@
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-06T04:35:51Z</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims - radionepalonline.com</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims radionepalonline.com</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
         </is>
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
         </is>
       </c>
       <c r="H266" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
         </is>
       </c>
       <c r="I266" s="3" t="inlineStr">
@@ -14233,7 +14233,7 @@
     <row r="267" ht="48" customHeight="1">
       <c r="A267" s="8" t="inlineStr">
         <is>
-          <t>15b1509ca084c43e</t>
+          <t>bcfd74891234047d</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="C267" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -14253,22 +14253,22 @@
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims - radionepalonline.com</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims radionepalonline.com</t>
         </is>
       </c>
       <c r="G267" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
         </is>
       </c>
       <c r="H267" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
@@ -14285,7 +14285,7 @@
     <row r="268" ht="48" customHeight="1">
       <c r="A268" s="8" t="inlineStr">
         <is>
-          <t>2f51aada7d65b122</t>
+          <t>15b1509ca084c43e</t>
         </is>
       </c>
       <c r="B268" s="8" t="inlineStr">
@@ -14295,32 +14295,32 @@
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
         </is>
       </c>
       <c r="H268" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
@@ -14337,7 +14337,7 @@
     <row r="269" ht="48" customHeight="1">
       <c r="A269" s="8" t="inlineStr">
         <is>
-          <t>b81c16b925a58806</t>
+          <t>2f51aada7d65b122</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
@@ -14352,27 +14352,27 @@
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>english.ratopati.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood - english.ratopati.com</t>
+          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood english.ratopati.com</t>
+          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G269" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
         </is>
       </c>
       <c r="H269" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
@@ -14389,7 +14389,7 @@
     <row r="270" ht="48" customHeight="1">
       <c r="A270" s="8" t="inlineStr">
         <is>
-          <t>86d22dfe0810a933</t>
+          <t>b81c16b925a58806</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
@@ -14399,32 +14399,32 @@
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution - radionepalonline.com</t>
+          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood - english.ratopati.com</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution radionepalonline.com</t>
+          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood english.ratopati.com</t>
         </is>
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
         </is>
       </c>
       <c r="H270" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
         </is>
       </c>
       <c r="I270" s="3" t="inlineStr">
@@ -14441,7 +14441,7 @@
     <row r="271" ht="48" customHeight="1">
       <c r="A271" s="8" t="inlineStr">
         <is>
-          <t>ca7286e595d52280</t>
+          <t>86d22dfe0810a933</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
@@ -14456,27 +14456,27 @@
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,325 - Khabarhub</t>
+          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution - radionepalonline.com</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,325 Khabarhub</t>
+          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution radionepalonline.com</t>
         </is>
       </c>
       <c r="G271" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
         </is>
       </c>
       <c r="H271" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="272" ht="48" customHeight="1">
       <c r="A272" s="8" t="inlineStr">
         <is>
-          <t>856502028ad6525f</t>
+          <t>ca7286e595d52280</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
@@ -14503,32 +14503,32 @@
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA testing process begins to identify bodies - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,325 - Khabarhub</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA testing process begins to identify bodies The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,325 Khabarhub</t>
         </is>
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
         </is>
       </c>
       <c r="H272" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
         </is>
       </c>
       <c r="I272" s="3" t="inlineStr">
@@ -14545,7 +14545,7 @@
     <row r="273" ht="48" customHeight="1">
       <c r="A273" s="8" t="inlineStr">
         <is>
-          <t>d1d4dff918ddaa2a</t>
+          <t>856502028ad6525f</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh aids one million USD for Bhotekoshi flood affected - The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA testing process begins to identify bodies - The Rising Nepal</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh aids one million USD for Bhotekoshi flood affected The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA testing process begins to identify bodies The Rising Nepal</t>
         </is>
       </c>
       <c r="G273" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
         </is>
       </c>
       <c r="H273" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr">
@@ -14597,42 +14597,42 @@
     <row r="274" ht="48" customHeight="1">
       <c r="A274" s="8" t="inlineStr">
         <is>
-          <t>4549b91541db80ab</t>
+          <t>d1d4dff918ddaa2a</t>
         </is>
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa Flood: 1,252 bodies recovered, 4,216 still missing - Onlinekhabar English</t>
+          <t>Bangladesh aids one million USD for Bhotekoshi flood affected - The Rising Nepal</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa Flood: 1,252 bodies recovered, 4,216 still missing Onlinekhabar English</t>
+          <t>Bangladesh aids one million USD for Bhotekoshi flood affected The Rising Nepal</t>
         </is>
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOSFpnNVdIeXFqdm1aMUhLQU5NcVV1M1pIQ29YdVlDQWVOcXc2SVpJWjlveDNSN2dVLXBNd3I0TlpONFJoc0M5TXlIeEdseFdvWm42ZWplVTdCeXoxUWxfeks2OVVPdmd5bGFvajZpamkwdlRUU2hCd0lpYkZZNFRDb3VfTklDdHZ4cVVqdXgwNjBadzhkekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
         </is>
       </c>
       <c r="H274" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilgFBVV95cUxOSFpnNVdIeXFqdm1aMUhLQU5NcVV1M1pIQ29YdVlDQWVOcXc2SVpJWjlveDNSN2dVLXBNd3I0TlpONFJoc0M5TXlIeEdseFdvWm42ZWplVTdCeXoxUWxfeks2OVVPdmd5bGFvajZpamkwdlRUU2hCd0lpYkZZNFRDb3VfTklDdHZ4cVVqdXgwNjBadzhkekE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr">
@@ -14649,7 +14649,7 @@
     <row r="275" ht="48" customHeight="1">
       <c r="A275" s="8" t="inlineStr">
         <is>
-          <t>a82013ca21037b39</t>
+          <t>4549b91541db80ab</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
@@ -14659,32 +14659,32 @@
       </c>
       <c r="C275" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T04:20:55Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,204 as over 4,200 remain missing - Nepalnews.com</t>
+          <t>Rasuwa Flood: 1,252 bodies recovered, 4,216 still missing - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,204 as over 4,200 remain missing Nepalnews.com</t>
+          <t>Rasuwa Flood: 1,252 bodies recovered, 4,216 still missing Onlinekhabar English</t>
         </is>
       </c>
       <c r="G275" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNN3RuYkxxVzhmUzRfSWZpcWxLYnJUS0FkUXN1WjRvc1dxdFJJaVVVaFVQNU1CMFNwdGtFTUkyZ3Znenkxak1kN0VLWVRacGFfbE5JTEM1UG1WM2ExRE1hYUVNTnNKak9TVGJTWHBrUFdFR3JtTVJzRVhoVWgzc2ZfaWhGbmNidHd1emU1d2V5UFVpTUNCTjkyWWZMWWZ3UzVlazRoRWszWWNyVDVRdEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOSFpnNVdIeXFqdm1aMUhLQU5NcVV1M1pIQ29YdVlDQWVOcXc2SVpJWjlveDNSN2dVLXBNd3I0TlpONFJoc0M5TXlIeEdseFdvWm42ZWplVTdCeXoxUWxfeks2OVVPdmd5bGFvajZpamkwdlRUU2hCd0lpYkZZNFRDb3VfTklDdHZ4cVVqdXgwNjBadzhkekE?oc=5</t>
         </is>
       </c>
       <c r="H275" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNN3RuYkxxVzhmUzRfSWZpcWxLYnJUS0FkUXN1WjRvc1dxdFJJaVVVaFVQNU1CMFNwdGtFTUkyZ3Znenkxak1kN0VLWVRacGFfbE5JTEM1UG1WM2ExRE1hYUVNTnNKak9TVGJTWHBrUFdFR3JtTVJzRVhoVWgzc2ZfaWhGbmNidHd1emU1d2V5UFVpTUNCTjkyWWZMWWZ3UzVlazRoRWszWWNyVDVRdEE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilgFBVV95cUxOSFpnNVdIeXFqdm1aMUhLQU5NcVV1M1pIQ29YdVlDQWVOcXc2SVpJWjlveDNSN2dVLXBNd3I0TlpONFJoc0M5TXlIeEdseFdvWm42ZWplVTdCeXoxUWxfeks2OVVPdmd5bGFvajZpamkwdlRUU2hCd0lpYkZZNFRDb3VfTklDdHZ4cVVqdXgwNjBadzhkekE?oc=5</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03T16:15:23Z</t>
+          <t>2026-10-03T21:13:26Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-03T16:15:23Z · 766 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-03T21:13:26Z · 766 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - thehimalayantimes.com</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims thehimalayantimes.com</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims - Ratopati</t>
+          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims - english.ratopati.com</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims Ratopati</t>
+          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims english.ratopati.com</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims - ekantipur.com</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims ekantipur.com</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid - Ekantipur</t>
+          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid - ekantipur.com</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid Ekantipur</t>
+          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid ekantipur.com</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -884,17 +884,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood - thehimalayantimes.com</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood thehimalayantimes.com</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing - Ekantipur</t>
+          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing - ekantipur.com</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing Ekantipur</t>
+          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing ekantipur.com</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction - Ekantipur</t>
+          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction - ekantipur.com</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction Ekantipur</t>
+          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction ekantipur.com</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - ekantipur.com</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims ekantipur.com</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - thehimalayantimes.com</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood thehimalayantimes.com</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - ekantipur.com</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies ekantipur.com</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -2845,42 +2845,42 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>a098d8aae7af06f0</t>
+          <t>a0d887b6e71fa24a</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-29T09:46:47Z</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -2897,42 +2897,42 @@
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>5dee575dde9896b2</t>
+          <t>9740579eff616080</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2949,42 +2949,42 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>a0d887b6e71fa24a</t>
+          <t>976a3738cc5bbc8c</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T09:46:47Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>9740579eff616080</t>
+          <t>3a44f3c3227b20ff</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -3011,32 +3011,32 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - english.ratopati.com</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims english.ratopati.com</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3053,7 +3053,7 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>976a3738cc5bbc8c</t>
+          <t>3f5e5c359d3906bd</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>3a44f3c3227b20ff</t>
+          <t>a724087f81f68a0e</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -3115,32 +3115,32 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - english.ratopati.com</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing english.ratopati.com</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>3f5e5c359d3906bd</t>
+          <t>355ca1951767eb7e</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - ekantipur.com</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood ekantipur.com</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3209,42 +3209,42 @@
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>a724087f81f68a0e</t>
+          <t>2fdda12f5042e371</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years - UA.NEWS</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years UA.NEWS</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3261,42 +3261,42 @@
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>355ca1951767eb7e</t>
+          <t>0179379ee0bcea80</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-29T00:59:03Z</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3313,42 +3313,42 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2fdda12f5042e371</t>
+          <t>fbacf2163aebfd9e</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Nepal government expects to resettle Bhotekoshi flood victims within two years - UA.NEWS</t>
+          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance - ekantipur.com</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Nepal government expects to resettle Bhotekoshi flood victims within two years UA.NEWS</t>
+          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance ekantipur.com</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3365,17 +3365,17 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>0179379ee0bcea80</t>
+          <t>4553867da1cf7f24</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T00:59:03Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3385,22 +3385,22 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood damages 7,570 homes across 5 districts - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
+          <t>Bhotekoshi flood damages 7,570 homes across 5 districts OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>fbacf2163aebfd9e</t>
+          <t>7b8b40468e96ee9a</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance - Ekantipur</t>
+          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. - ekantipur.com</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance Ekantipur</t>
+          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. ekantipur.com</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>4553867da1cf7f24</t>
+          <t>ae42ae903bc8d76f</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -3479,32 +3479,32 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-13T04:44:23Z</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 7,570 homes across 5 districts - OnlineKhabar English News</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 7,570 homes across 5 districts OnlineKhabar English News</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3521,42 +3521,42 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>7b8b40468e96ee9a</t>
+          <t>9b19a739b91a113a</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. - Ekantipur</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - english.ratopati.com</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. Ekantipur</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage english.ratopati.com</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>9b19a739b91a113a</t>
+          <t>d8f4f558107297e7</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - Ratopati</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage Ratopati</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>d8f4f558107297e7</t>
+          <t>599e39e4bd45cec7</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myRepublica</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood - english.ratopati.com</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myRepublica</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood english.ratopati.com</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>599e39e4bd45cec7</t>
+          <t>895a2cd3bab3daaf</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-12T20:31:43Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood - Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,17 +3729,17 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>895a2cd3bab3daaf</t>
+          <t>c128671407c846d2</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T20:31:43Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify - Nepalnews.com</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify Nepalnews.com</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>c128671407c846d2</t>
+          <t>b2b4017fc46c3af9</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -3791,32 +3791,32 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify - Nepalnews.com</t>
+          <t>Relief for Rasuwa flood victims stuck at Nepal-India border - The Himalayan Times</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify Nepalnews.com</t>
+          <t>Relief for Rasuwa flood victims stuck at Nepal-India border The Himalayan Times</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVdIBXEFVX3lxTE5Nc1RRTy1mcTNhenk3QU1JNWRkSndKMWtpbnMwZWRMSlRhN1lDcFBSckdyUmt2aHlvTkdKakpISFowUG4taDJGLWpEYjZNSXB5bmFNSGl4aDU5RjZW?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVdIBXEFVX3lxTE5Nc1RRTy1mcTNhenk3QU1JNWRkSndKMWtpbnMwZWRMSlRhN1lDcFBSckdyUmt2aHlvTkdKakpISFowUG4taDJGLWpEYjZNSXB5bmFNSGl4aDU5RjZW?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>b2b4017fc46c3af9</t>
+          <t>7c43c3f1886e0cd8</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -3843,32 +3843,32 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-28T13:50:00Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Relief for Rasuwa flood victims stuck at Nepal-India border - thehimalayantimes.com</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - The Annapurna Express</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Relief for Rasuwa flood victims stuck at Nepal-India border thehimalayantimes.com</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone The Annapurna Express</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVdIBXEFVX3lxTE5Nc1RRTy1mcTNhenk3QU1JNWRkSndKMWtpbnMwZWRMSlRhN1lDcFBSckdyUmt2aHlvTkdKakpISFowUG4taDJGLWpEYjZNSXB5bmFNSGl4aDU5RjZW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBRYlRqQlFndDVDZE45YXNrYWRVTWwtMktHcjBFOVM2TG5yR1FfMUZlU3ZFenRxY29FMFRFZ0VTRDQwdVNyS2k2N2pzMGhPbUNjNE5zMGJnNA?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVdIBXEFVX3lxTE5Nc1RRTy1mcTNhenk3QU1JNWRkSndKMWtpbnMwZWRMSlRhN1lDcFBSckdyUmt2aHlvTkdKakpISFowUG4taDJGLWpEYjZNSXB5bmFNSGl4aDU5RjZW?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTFBRYlRqQlFndDVDZE45YXNrYWRVTWwtMktHcjBFOVM2TG5yR1FfMUZlU3ZFenRxY29FMFRFZ0VTRDQwdVNyS2k2N2pzMGhPbUNjNE5zMGJnNA?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3885,42 +3885,42 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>7c43c3f1886e0cd8</t>
+          <t>6607210a4b69eff4</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T13:50:00Z</t>
+          <t>2026-09-11T04:36:53Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - The Annapurna Express</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone The Annapurna Express</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBRYlRqQlFndDVDZE45YXNrYWRVTWwtMktHcjBFOVM2TG5yR1FfMUZlU3ZFenRxY29FMFRFZ0VTRDQwdVNyS2k2N2pzMGhPbUNjNE5zMGJnNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTFBRYlRqQlFndDVDZE45YXNrYWRVTWwtMktHcjBFOVM2TG5yR1FfMUZlU3ZFenRxY29FMFRFZ0VTRDQwdVNyS2k2N2pzMGhPbUNjNE5zMGJnNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>6607210a4b69eff4</t>
+          <t>8592d4acb296590f</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3947,32 +3947,32 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T04:36:53Z</t>
+          <t>2026-09-10T16:22:37Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - ReliefWeb</t>
+          <t>Bhote Koshi flood death toll reaches 1,377; more than 5,100 remain missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 ReliefWeb</t>
+          <t>Bhote Koshi flood death toll reaches 1,377; more than 5,100 remain missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFVsREZXWTVQVlJHTnRhZUpKRzkwSlF6THRlcXRaWDhGNkx6SGRtTnA0SXMwd0RibHUwVWtTdWZnS3FUeHJBRWJkZTdwRk5xZW9JXzlBRjl6QUJ1b0xKNHJFM05BMTRod3pSOFo1b2J2eWVNaEJXRXNRYkQ2OE1tN0NrbXg0WnA2MXR0NUt6aTFYWEZ5YUxkZHRMSG90VE4zaHEw?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNSmJlc0I5NmF4aXJlTFVodWlPalMzSktrMlJyVkFaWU5VTTVoTE9IazVScFNWbmlORWJhbTB3QXdqSXB3cHlqRGd2Wk9kdkdNVUdhNzdnUno0ZS05cmRZUGJYTGtXdTZkcV9lOGk0WVNzTjRVcUprRHFXbDd2ajF2bHM4bUdYMDZlRV9OVXJWTl9qNTZHdTRBMlJWb2czNWRsNlFr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFVsREZXWTVQVlJHTnRhZUpKRzkwSlF6THRlcXRaWDhGNkx6SGRtTnA0SXMwd0RibHUwVWtTdWZnS3FUeHJBRWJkZTdwRk5xZW9JXzlBRjl6QUJ1b0xKNHJFM05BMTRod3pSOFo1b2J2eWVNaEJXRXNRYkQ2OE1tN0NrbXg0WnA2MXR0NUt6aTFYWEZ5YUxkZHRMSG90VE4zaHEw?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>8592d4acb296590f</t>
+          <t>8a39d2b6e977257c</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -3999,32 +3999,32 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T16:22:37Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,377; more than 5,100 remain missing - Nepalnews.com</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,377; more than 5,100 remain missing Nepalnews.com</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFVsREZXWTVQVlJHTnRhZUpKRzkwSlF6THRlcXRaWDhGNkx6SGRtTnA0SXMwd0RibHUwVWtTdWZnS3FUeHJBRWJkZTdwRk5xZW9JXzlBRjl6QUJ1b0xKNHJFM05BMTRod3pSOFo1b2J2eWVNaEJXRXNRYkQ2OE1tN0NrbXg0WnA2MXR0NUt6aTFYWEZ5YUxkZHRMSG90VE4zaHEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFVsREZXWTVQVlJHTnRhZUpKRzkwSlF6THRlcXRaWDhGNkx6SGRtTnA0SXMwd0RibHUwVWtTdWZnS3FUeHJBRWJkZTdwRk5xZW9JXzlBRjl6QUJ1b0xKNHJFM05BMTRod3pSOFo1b2J2eWVNaEJXRXNRYkQ2OE1tN0NrbXg0WnA2MXR0NUt6aTFYWEZ5YUxkZHRMSG90VE4zaHEw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>8a39d2b6e977257c</t>
+          <t>d693f9bb64e76f66</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -4051,32 +4051,32 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - Khabarhub</t>
+          <t>1,377 Dead, 5,130 Missing in Rasuwa Flood - english.ratopati.com</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims Khabarhub</t>
+          <t>1,377 Dead, 5,130 Missing in Rasuwa Flood english.ratopati.com</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPWElvRnAwTng2WDVrUUlvM1EzNXZwSDlzaFBFcnd2bldHbUY3bVRHdkl0V1l2Y0FoSUVQOHhleUtTdHVxZ2t6cFdaeERLSVFEUjNScnhiRHNzRVM4Ti1ESFhGVmdqaUNQdHlxOUl1Sm9XNGIzeFFJSWhyNGVIWkJBanA5YkxRT012QlpYd1IzYVItY3EySE8wYnhlbjY?oc=5</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9VNHZ3YU1UalEtZVlSOVpmelNueFpBZUZYbEtsTEtDbWZSbm5HXzhhWFBOOEVlZGlXbFRvRWZtTlF3bjR2UmVQc3ZMODZkSEcyeDh3VUFJQnI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPWElvRnAwTng2WDVrUUlvM1EzNXZwSDlzaFBFcnd2bldHbUY3bVRHdkl0V1l2Y0FoSUVQOHhleUtTdHVxZ2t6cFdaeERLSVFEUjNScnhiRHNzRVM4Ti1ESFhGVmdqaUNQdHlxOUl1Sm9XNGIzeFFJSWhyNGVIWkJBanA5YkxRT012QlpYd1IzYVItY3EySE8wYnhlbjY?oc=5</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4093,42 +4093,42 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>d693f9bb64e76f66</t>
+          <t>f275af8b34c207e4</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1,377 Dead, 5,130 Missing in Rasuwa Flood - Ratopati</t>
+          <t>Ranjoo Darshana Draws Attention to Bhote Koshi Flood Devastation in Parliament - english.ratopati.com</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>1,377 Dead, 5,130 Missing in Rasuwa Flood Ratopati</t>
+          <t>Ranjoo Darshana Draws Attention to Bhote Koshi Flood Devastation in Parliament english.ratopati.com</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPWElvRnAwTng2WDVrUUlvM1EzNXZwSDlzaFBFcnd2bldHbUY3bVRHdkl0V1l2Y0FoSUVQOHhleUtTdHVxZ2t6cFdaeERLSVFEUjNScnhiRHNzRVM4Ti1ESFhGVmdqaUNQdHlxOUl1Sm9XNGIzeFFJSWhyNGVIWkJBanA5YkxRT012QlpYd1IzYVItY3EySE8wYnhlbjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNZTR5Y3lxRmNJQ1o0ZTBBaXY1aWJFQ1o1SjZQS19WejQwWHBIQjBpMVd3a1VjR01DalRFandaU0t3amFGcUpVZk9FdEVsaXk0QU1hcHltaU53V1VzSXFjaEFtcnhBUlNCRW96RDdJU3gxOWJ0MEkyOHd4Qk9hVmxtUEE5MXJiVEc4MkVXTnVSTElhS0F3ZDlUNzBnSkx5OExnOURnWGRpN3pLVjFmcmloczNfUWZ1TmlzbjBfWVpSY0Q3a2I2ZUlNbQ?oc=5</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPWElvRnAwTng2WDVrUUlvM1EzNXZwSDlzaFBFcnd2bldHbUY3bVRHdkl0V1l2Y0FoSUVQOHhleUtTdHVxZ2t6cFdaeERLSVFEUjNScnhiRHNzRVM4Ti1ESFhGVmdqaUNQdHlxOUl1Sm9XNGIzeFFJSWhyNGVIWkJBanA5YkxRT012QlpYd1IzYVItY3EySE8wYnhlbjY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxNZTR5Y3lxRmNJQ1o0ZTBBaXY1aWJFQ1o1SjZQS19WejQwWHBIQjBpMVd3a1VjR01DalRFandaU0t3amFGcUpVZk9FdEVsaXk0QU1hcHltaU53V1VzSXFjaEFtcnhBUlNCRW96RDdJU3gxOWJ0MEkyOHd4Qk9hVmxtUEE5MXJiVEc4MkVXTnVSTElhS0F3ZDlUNzBnSkx5OExnOURnWGRpN3pLVjFmcmloczNfUWZ1TmlzbjBfWVpSY0Q3a2I2ZUlNbQ?oc=5</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>f275af8b34c207e4</t>
+          <t>aa0c38e5dbcd204a</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -4155,32 +4155,32 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Ranjoo Darshana Draws Attention to Bhote Koshi Flood Devastation in Parliament - Ratopati</t>
+          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims - myRepublica</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Ranjoo Darshana Draws Attention to Bhote Koshi Flood Devastation in Parliament Ratopati</t>
+          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims myRepublica</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNZTR5Y3lxRmNJQ1o0ZTBBaXY1aWJFQ1o1SjZQS19WejQwWHBIQjBpMVd3a1VjR01DalRFandaU0t3amFGcUpVZk9FdEVsaXk0QU1hcHltaU53V1VzSXFjaEFtcnhBUlNCRW96RDdJU3gxOWJ0MEkyOHd4Qk9hVmxtUEE5MXJiVEc4MkVXTnVSTElhS0F3ZDlUNzBnSkx5OExnOURnWGRpN3pLVjFmcmloczNfUWZ1TmlzbjBfWVpSY0Q3a2I2ZUlNbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxNZTR5Y3lxRmNJQ1o0ZTBBaXY1aWJFQ1o1SjZQS19WejQwWHBIQjBpMVd3a1VjR01DalRFandaU0t3amFGcUpVZk9FdEVsaXk0QU1hcHltaU53V1VzSXFjaEFtcnhBUlNCRW96RDdJU3gxOWJ0MEkyOHd4Qk9hVmxtUEE5MXJiVEc4MkVXTnVSTElhS0F3ZDlUNzBnSkx5OExnOURnWGRpN3pLVjFmcmloczNfUWZ1TmlzbjBfWVpSY0Q3a2I2ZUlNbQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>aa0c38e5dbcd204a</t>
+          <t>43b44149e2b39c71</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -4207,32 +4207,32 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims - myRepublica</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA profiling stepped up to identify victims myRepublica</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNaXdXQjlPd2YtUXlYNEcwMUhNR09iQklJVTF2VjVxMnpXTG5tMjNEU2xjQl9uY0JxWldqUkxVc1VzTnBiM0Z4NlV4TWFCbGpweHk5NnFPSDZjMEpEWDg4RHBjNEtiX1NpY2c3NUx6bmFJRWFQM0dDMThnckoyY1NtdG03dFdtbWl3MkZQQ0d3ekpVZDFpU2pzNFpJbG5FQUNkU2taZFU3V1BnT2NfbzQ1S3RWOFFXdk0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>43b44149e2b39c71</t>
+          <t>f67225d3b28943ab</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -4269,22 +4269,22 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>f67225d3b28943ab</t>
+          <t>198a51a993ffe8e0</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - Nepalnews.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing Nepalnews.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa1dweTExd3pjSXk5TTBiamFLWm9MSkRZTUxNMWx6RUpnMFZ4WlVYZE04N1p2TXVlUUxDVmM4QV9tN3oxY3A4QVFJNGExZGNERkhpQ3JkZlVlOFF2UGFOM3RWajZKYVNVQmdhQnI2Q2J3MVVJOFFwMFIwdm1SUkhtZ3VBZ3BmUFdYbzFscEVkamt2a2w3b3R4ZlhoNGlEV0o3Y1hfejdWU2c0Zw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>198a51a993ffe8e0</t>
+          <t>048136aff52fd1c4</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>ANI News</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - ReliefWeb</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - ANI News</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) ReliefWeb</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing ANI News</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQV0FZeHhTbU1iNEYxd2NPZ0dQYm1HX2lYV1o1UVkxNVVEanJEcy1IT3NvN25MV0NmcEp4a2FTd3BvNHRPMklVYm1kZTRkQWdybGdJSTlEcEdfRWxQZVA1YzNaZmI2djhTS0JBc0RLMTd3bUZUblJVaHJZMV9yb1drTFV0Yk5zcGM2VS1FaGNMUkYyN0RKRUNR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>048136aff52fd1c4</t>
+          <t>eb267cf5ab869196</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4420,27 +4420,27 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ANI News</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - ANI News</t>
+          <t>Rasuwa flood toll mounts as 1,367 bodies are recovered - myRepublica</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing ANI News</t>
+          <t>Rasuwa flood toll mounts as 1,367 bodies are recovered myRepublica</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUldaV1NwbFhZazhSQkZualluZzNPMFZ3Rnp4TlNpaWRWZm5Oc29HZG0tY296OGhYdjVhdHBvTHpudWh5M3FCdkN2Tjk5M0otVm9YQXdYREZKVW03dnlHbkE2UjFDQy1oSmdQbzEzMmI0cEVCdEtOS0E2d1FCbVVSNTVyZVZOVGdITjBQZ0tLSjBvbG9UVkd2TnZOd3o?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNVllKZ0k2ODYta0lOMWxwd3JYQW1zVngyUm8tR2kzc19jalRBdWJBRjhnaUZzNFhhUmZkNDYyenVGNVFIRDNsMWtfdk5mWGNIYlFjSWNOOFEyaDdSZ3VaR2VEWUhmQjdVQ0JiY014SDB1eDF2REFwS1Nsbl9TT3RFNzllNEFYOHVjUWdNdE1hOHBjczZ1OFcxWmxBVkNSNWJ6dXhqVGhzN3lWY3Joc2ktZ0NOR1lfWHJRN1JyOXc3bFNSTUlKVUlyVXk0Z1lTVmM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQUldaV1NwbFhZazhSQkZualluZzNPMFZ3Rnp4TlNpaWRWZm5Oc29HZG0tY296OGhYdjVhdHBvTHpudWh5M3FCdkN2Tjk5M0otVm9YQXdYREZKVW03dnlHbkE2UjFDQy1oSmdQbzEzMmI0cEVCdEtOS0E2d1FCbVVSNTVyZVZOVGdITjBQZ0tLSjBvbG9UVkd2TnZOd3o?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>eb267cf5ab869196</t>
+          <t>a4a0f705a84ebf28</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-09T11:19:52Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood toll mounts as 1,367 bodies are recovered - myRepublica</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood toll mounts as 1,367 bodies are recovered myRepublica</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUldaV1NwbFhZazhSQkZualluZzNPMFZ3Rnp4TlNpaWRWZm5Oc29HZG0tY296OGhYdjVhdHBvTHpudWh5M3FCdkN2Tjk5M0otVm9YQXdYREZKVW03dnlHbkE2UjFDQy1oSmdQbzEzMmI0cEVCdEtOS0E2d1FCbVVSNTVyZVZOVGdITjBQZ0tLSjBvbG9UVkd2TnZOd3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQUldaV1NwbFhZazhSQkZualluZzNPMFZ3Rnp4TlNpaWRWZm5Oc29HZG0tY296OGhYdjVhdHBvTHpudWh5M3FCdkN2Tjk5M0otVm9YQXdYREZKVW03dnlHbkE2UjFDQy1oSmdQbzEzMmI0cEVCdEtOS0E2d1FCbVVSNTVyZVZOVGdITjBQZ0tLSjBvbG9UVkd2TnZOd3o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>thehimalayantimes.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises - thehimalayantimes.com</t>
+          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises - The Himalayan Times</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises thehimalayantimes.com</t>
+          <t>13,500 rescued, thousands in centres as Rasuwa flood toll rises The Himalayan Times</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>himalmag.com</t>
+          <t>Himal Southasian</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>The climate warning from Nepal’s Rasuwa flood disaster - himalmag.com</t>
+          <t>The climate warning from Nepal’s Rasuwa flood disaster - Himal Southasian</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>The climate warning from Nepal’s Rasuwa flood disaster himalmag.com</t>
+          <t>The climate warning from Nepal’s Rasuwa flood disaster Himal Southasian</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>4cb2bd46e4d614d5</t>
+          <t>45150033608b7edf</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -5257,22 +5257,22 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Nepali lawmakers seek Bhutan’s support for compensation over Rasuwa flood damage - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 244 bodies brought to TU Teaching Hospital - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Nepali lawmakers seek Bhutan’s support for compensation over Rasuwa flood damage OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 244 bodies brought to TU Teaching Hospital OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQZ3RnMzJQTHVNMTJPUnZ3T1B2S2d6Zjk0YWQ2RF9vajdfcEliOEUtNkkyU0RxRVE5ckdJRGhZLWJhbnNXYkxnR0pYOVZMdFoya0R0RkM2ei1CcUV2WUFfZGlmb1Fla0xMMFpEaDFoRFZrcS1td1ZmdnQ1NFR2MUFsVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQdFoyczM5RjVoRzI0U3JLTmJZeDZMT2ZXYzBKRGdnLU12ZndibGVNVjNnNWY0c1ZZaUJ2LUhCbWt5VE54ZmlULUxlMnUtMVNYeW5xdzN5OURvNjBUR0RMLTRrSm4wMWFkWEU5N0c5blpaN2pEM0dQRzVnTUlZY2VlRDllemp6MEJyNHlZY2puZzhVRmxjOF9haE4yeloyZw?oc=5</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQZ3RnMzJQTHVNMTJPUnZ3T1B2S2d6Zjk0YWQ2RF9vajdfcEliOEUtNkkyU0RxRVE5ckdJRGhZLWJhbnNXYkxnR0pYOVZMdFoya0R0RkM2ei1CcUV2WUFfZGlmb1Fla0xMMFpEaDFoRFZrcS1td1ZmdnQ1NFR2MUFsVA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxQdFoyczM5RjVoRzI0U3JLTmJZeDZMT2ZXYzBKRGdnLU12ZndibGVNVjNnNWY0c1ZZaUJ2LUhCbWt5VE54ZmlULUxlMnUtMVNYeW5xdzN5OURvNjBUR0RMLTRrSm4wMWFkWEU5N0c5blpaN2pEM0dQRzVnTUlZY2VlRDllemp6MEJyNHlZY2puZzhVRmxjOF9haE4yeloyZw?oc=5</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing - Ratopati</t>
+          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing - english.ratopati.com</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing Ratopati</t>
+          <t>1,290 Bodies Recovered After Bhote Koshi Flood, 4,798 Still Missing english.ratopati.com</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -7785,7 +7785,7 @@
     <row r="143" ht="48" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>63e3a3c4068798b8</t>
+          <t>a098d8aae7af06f0</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -7795,32 +7795,32 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T16:02:57Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -7837,7 +7837,7 @@
     <row r="144" ht="48" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>4199945559bb4c8e</t>
+          <t>5dee575dde9896b2</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -7847,32 +7847,32 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="145" ht="48" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>a3af223902597f26</t>
+          <t>63e3a3c4068798b8</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-20T16:02:57Z</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7941,7 +7941,7 @@
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>c16a9e76fde589cb</t>
+          <t>4199945559bb4c8e</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
@@ -7951,32 +7951,32 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T11:38:32Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
+          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
+          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -7993,7 +7993,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>035dc924f46d515d</t>
+          <t>a3af223902597f26</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,42 +8045,42 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>ddd57575c35c350d</t>
+          <t>c16a9e76fde589cb</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-17T11:38:32Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,42 +8097,42 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>2c0a3b5d2befbf82</t>
+          <t>035dc924f46d515d</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T05:20:23Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>cc1e404c3c7b5539</t>
+          <t>ddd57575c35c350d</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="151" ht="48" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>f391daeeca51bbbc</t>
+          <t>2c0a3b5d2befbf82</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -8221,22 +8221,22 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>751a0e165234bde9</t>
+          <t>cc1e404c3c7b5539</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -8263,32 +8263,32 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>hariyalinepal.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
+          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
+          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8305,7 +8305,7 @@
     <row r="153" ht="48" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>9ab27519f391ac8a</t>
+          <t>f391daeeca51bbbc</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T04:46:36Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -8357,42 +8357,42 @@
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>7c8af6b0d120695d</t>
+          <t>751a0e165234bde9</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>hariyalinepal.com</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8409,42 +8409,42 @@
     <row r="155" ht="48" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>2ff03089e15253df</t>
+          <t>9ab27519f391ac8a</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-16T04:46:36Z</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>509e249c7e4eed4b</t>
+          <t>7c8af6b0d120695d</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -8471,32 +8471,32 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="157" ht="48" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>b933797459c3a582</t>
+          <t>2ff03089e15253df</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -8523,32 +8523,32 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>97b6fb8c1bbdde22</t>
+          <t>509e249c7e4eed4b</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -8575,32 +8575,32 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
+          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
+          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8617,7 +8617,7 @@
     <row r="159" ht="48" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>38b94bc7bc5df2f9</t>
+          <t>b933797459c3a582</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -8627,32 +8627,32 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myRepublica</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myRepublica</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>f62c2f3efb4f90da</t>
+          <t>97b6fb8c1bbdde22</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -8679,32 +8679,32 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>c0bc6670e36c05ca</t>
+          <t>38b94bc7bc5df2f9</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Ministry Of Foreign Affairs</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood - Ministry Of Foreign Affairs</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myRepublica</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood Ministry Of Foreign Affairs</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myRepublica</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>62d5c38304aa356a</t>
+          <t>f62c2f3efb4f90da</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,32 +8783,32 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>71f08f0e90525437</t>
+          <t>c0bc6670e36c05ca</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8840,27 +8840,27 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
+          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood - Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
+          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>038d44da2885beeb</t>
+          <t>62d5c38304aa356a</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,42 +8929,42 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>167458bbff2621be</t>
+          <t>71f08f0e90525437</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing - Nepalnews.com</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing Nepalnews.com</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8981,42 +8981,42 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>1db4b46680067f6b</t>
+          <t>038d44da2885beeb</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - Khabarhub</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses Khabarhub</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>7ac46d8fe1e78a5e</t>
+          <t>167458bbff2621be</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood dampens Teej celebrations - The Rising Nepal</t>
+          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood dampens Teej celebrations The Rising Nepal</t>
+          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>7901378bf0efe6dd</t>
+          <t>1db4b46680067f6b</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post - UA.NEWS</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - Khabarhub</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post UA.NEWS</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses Khabarhub</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>4f53e036a604bfe8</t>
+          <t>7ac46d8fe1e78a5e</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood dampens Teej celebrations - The Rising Nepal</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood dampens Teej celebrations The Rising Nepal</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>0df7da2f9815834b</t>
+          <t>7901378bf0efe6dd</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -9199,32 +9199,32 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post - UA.NEWS</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post UA.NEWS</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>59b055075d559d93</t>
+          <t>4f53e036a604bfe8</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,32 +9251,32 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll rises to 1,392 - Khabarhub</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll rises to 1,392 Khabarhub</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>353f4e432ea55d9d</t>
+          <t>0df7da2f9815834b</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,32 +9303,32 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly - The Rising Nepal</t>
+          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly The Rising Nepal</t>
+          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,42 +9345,42 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>ae42ae903bc8d76f</t>
+          <t>59b055075d559d93</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T04:44:23Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood death toll rises to 1,392 - Khabarhub</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood death toll rises to 1,392 Khabarhub</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,42 +9397,42 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>d8670c3b0d995ad2</t>
+          <t>353f4e432ea55d9d</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T23:52:01Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing - myRepublica</t>
+          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly - The Rising Nepal</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing myRepublica</t>
+          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly The Rising Nepal</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>03019cd0bb2d589e</t>
+          <t>d8670c3b0d995ad2</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T17:08:24Z</t>
+          <t>2026-09-14T23:52:01Z</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -9469,22 +9469,22 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing - myRepublica</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing myRepublica</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>36ae5311c55c236f</t>
+          <t>03019cd0bb2d589e</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
@@ -9511,32 +9511,32 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T05:15:51Z</t>
+          <t>2026-09-25T17:08:24Z</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families - Nepalnews.com</t>
+          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families Nepalnews.com</t>
+          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>ee48897af3fcec08</t>
+          <t>36ae5311c55c236f</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-27T05:15:51Z</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: Over 3,000 DNA samples collected - OnlineKhabar English News</t>
+          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families - Nepalnews.com</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: Over 3,000 DNA samples collected OnlineKhabar English News</t>
+          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families Nepalnews.com</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
         </is>
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>67b5a6753c351977</t>
+          <t>ee48897af3fcec08</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims - myRepublica</t>
+          <t>Rasuwa flood: Over 3,000 DNA samples collected - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims myRepublica</t>
+          <t>Rasuwa flood: Over 3,000 DNA samples collected OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -9657,7 +9657,7 @@
     <row r="179" ht="48" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>115ca238296d3ef7</t>
+          <t>67b5a6753c351977</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million - Khabarhub</t>
+          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million Khabarhub</t>
+          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
         </is>
       </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>74b200acb9b39a43</t>
+          <t>115ca238296d3ef7</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T11:48:33Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -9729,22 +9729,22 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
+          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million - Khabarhub</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
+          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million Khabarhub</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -9761,42 +9761,42 @@
     <row r="181" ht="48" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>52872a4049999b34</t>
+          <t>74b200acb9b39a43</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-13T11:48:33Z</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked - Ekantipur</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked Ekantipur</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
         </is>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -9813,7 +9813,7 @@
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>ff75d7063b59861e</t>
+          <t>52872a4049999b34</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -9833,22 +9833,22 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,386 Bodies Found - Ekantipur</t>
+          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked - Ekantipur</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,386 Bodies Found Ekantipur</t>
+          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked Ekantipur</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="183" ht="48" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>8e86fdb64fbd8e65</t>
+          <t>ff75d7063b59861e</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -9875,32 +9875,32 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T04:32:06Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myRepublica</t>
+          <t>Bhotekoshi Flood: 1,386 Bodies Found - Ekantipur</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myRepublica</t>
+          <t>Bhotekoshi Flood: 1,386 Bodies Found Ekantipur</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNS1JWdzlmN0VMWEoxT1poRVNQbl8yUTBqWUNHYXZRZ2o3UU03aGxKeEZhOFQxaGZ6ejRsQW4wdWJDeVU5eWVRbXQyX2FfVEljNmpGM1NEaTdaNk1RNmlvSTdZZjJjSjZ6RzJQVXJHTUZHMy1oLXo1ZElFRVFHRXdVcHhDelFNXzIwU3R1T2NFbUFpN0FpdHFsMnduQWNJVkRkYnB1aEhicTZfU3B4T1VIWGtEWDNNMkM5R1NmTXlKNFdXc1E4V2E3dUJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNS1JWdzlmN0VMWEoxT1poRVNQbl8yUTBqWUNHYXZRZ2o3UU03aGxKeEZhOFQxaGZ6ejRsQW4wdWJDeVU5eWVRbXQyX2FfVEljNmpGM1NEaTdaNk1RNmlvSTdZZjJjSjZ6RzJQVXJHTUZHMy1oLXo1ZElFRVFHRXdVcHhDelFNXzIwU3R1T2NFbUFpN0FpdHFsMnduQWNJVkRkYnB1aEhicTZfU3B4T1VIWGtEWDNNMkM5R1NmTXlKNFdXc1E4V2E3dUJR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>b24ad7ca0530ad59</t>
+          <t>8e86fdb64fbd8e65</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
@@ -9927,32 +9927,32 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-12T04:32:06Z</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myRepublica</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myRepublica</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNS1JWdzlmN0VMWEoxT1poRVNQbl8yUTBqWUNHYXZRZ2o3UU03aGxKeEZhOFQxaGZ6ejRsQW4wdWJDeVU5eWVRbXQyX2FfVEljNmpGM1NEaTdaNk1RNmlvSTdZZjJjSjZ6RzJQVXJHTUZHMy1oLXo1ZElFRVFHRXdVcHhDelFNXzIwU3R1T2NFbUFpN0FpdHFsMnduQWNJVkRkYnB1aEhicTZfU3B4T1VIWGtEWDNNMkM5R1NmTXlKNFdXc1E4V2E3dUJR?oc=5</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNS1JWdzlmN0VMWEoxT1poRVNQbl8yUTBqWUNHYXZRZ2o3UU03aGxKeEZhOFQxaGZ6ejRsQW4wdWJDeVU5eWVRbXQyX2FfVEljNmpGM1NEaTdaNk1RNmlvSTdZZjJjSjZ6RzJQVXJHTUZHMy1oLXo1ZElFRVFHRXdVcHhDelFNXzIwU3R1T2NFbUFpN0FpdHFsMnduQWNJVkRkYnB1aEhicTZfU3B4T1VIWGtEWDNNMkM5R1NmTXlKNFdXc1E4V2E3dUJR?oc=5</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9969,42 +9969,42 @@
     <row r="185" ht="48" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>e7b1f598696acaa9</t>
+          <t>b24ad7ca0530ad59</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T16:14:56Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - The Himalayan Times</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill The Himalayan Times</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbzFVcDV0Z1Iwc2QtTXVfVVFPWE9sOUpZZlJjVG05cW9JN1hYZHY2UUJOV0phQzV3dkFxRzlyLVNCVW5paTlYaWtBbExYZVJJaklQdGE1S1JCYnpxY0FzNXdSUnZXS1JNUURvaERrMmxubDQ2Z0RwbHFnV0p3V3pXbGYwcjM0RXRaSnNoY3RLR0JHTlBBUDhkbS1wbkxfMWtOS3JR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNbzFVcDV0Z1Iwc2QtTXVfVVFPWE9sOUpZZlJjVG05cW9JN1hYZHY2UUJOV0phQzV3dkFxRzlyLVNCVW5paTlYaWtBbExYZVJJaklQdGE1S1JCYnpxY0FzNXdSUnZXS1JNUURvaERrMmxubDQ2Z0RwbHFnV0p3V3pXbGYwcjM0RXRaSnNoY3RLR0JHTlBBUDhkbS1wbkxfMWtOS3JR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>9d60f800df2c908d</t>
+          <t>e7b1f598696acaa9</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -10031,32 +10031,32 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T23:37:00Z</t>
+          <t>2026-09-13T16:14:56Z</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Recovery of the education sector after the Bhotekoshi flood will cost Rs 2.34 billion - Ekantipur</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - The Himalayan Times</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Recovery of the education sector after the Bhotekoshi flood will cost Rs 2.34 billion Ekantipur</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill The Himalayan Times</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNV1NUeFlaWmZjQkFQR0I5bURCcDMxUUJoWmoxQm11bElENk5LN3JDV1dFSVZBdjVseUpoMHl2b3dGN0lMcERtVWllNHZxS2lpdVJCNTNSY3ZMaHhZc3U0MW5KVmZDX0NDZHFCOTF1RkRhQU1JcThQeFhaYko1b0pWck96VnRaOV9nX0wyQzByNVJiYXFSNVpnRXdGVGo5UXQyNVJHRUFTaHRCY1RPcTVHUnVNYkcza3FZUVBlMXhjSFZ1eWE1bFFYZlNFSjJwemZUVkM0c2ZYQ1RpLVF1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbzFVcDV0Z1Iwc2QtTXVfVVFPWE9sOUpZZlJjVG05cW9JN1hYZHY2UUJOV0phQzV3dkFxRzlyLVNCVW5paTlYaWtBbExYZVJJaklQdGE1S1JCYnpxY0FzNXdSUnZXS1JNUURvaERrMmxubDQ2Z0RwbHFnV0p3V3pXbGYwcjM0RXRaSnNoY3RLR0JHTlBBUDhkbS1wbkxfMWtOS3JR?oc=5</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxNV1NUeFlaWmZjQkFQR0I5bURCcDMxUUJoWmoxQm11bElENk5LN3JDV1dFSVZBdjVseUpoMHl2b3dGN0lMcERtVWllNHZxS2lpdVJCNTNSY3ZMaHhZc3U0MW5KVmZDX0NDZHFCOTF1RkRhQU1JcThQeFhaYko1b0pWck96VnRaOV9nX0wyQzByNVJiYXFSNVpnRXdGVGo5UXQyNVJHRUFTaHRCY1RPcTVHUnVNYkcza3FZUVBlMXhjSFZ1eWE1bFFYZlNFSjJwemZUVkM0c2ZYQ1RpLVF1?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxNbzFVcDV0Z1Iwc2QtTXVfVVFPWE9sOUpZZlJjVG05cW9JN1hYZHY2UUJOV0phQzV3dkFxRzlyLVNCVW5paTlYaWtBbExYZVJJaklQdGE1S1JCYnpxY0FzNXdSUnZXS1JNUURvaERrMmxubDQ2Z0RwbHFnV0p3V3pXbGYwcjM0RXRaSnNoY3RLR0JHTlBBUDhkbS1wbkxfMWtOS3JR?oc=5</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="187" ht="48" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>e2ab49cc0755acf3</t>
+          <t>9d60f800df2c908d</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -10083,32 +10083,32 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-09-26T23:37:00Z</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications Authority Provides Rs 150 Million in Aid for Bhotekoshi Flood Victims - ekantipur.com</t>
+          <t>Recovery of the education sector after the Bhotekoshi flood will cost Rs 2.34 billion - Ekantipur</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications Authority Provides Rs 150 Million in Aid for Bhotekoshi Flood Victims ekantipur.com</t>
+          <t>Recovery of the education sector after the Bhotekoshi flood will cost Rs 2.34 billion Ekantipur</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9aak4waGJmcmw4OXF3ZzlZbHlPck1YODF3OWxnNjdfdnpoRjg5NlB1VWpIY2lwcDdpZEdvR3dWZmhCUTVCX21iSEUwUHpoS0RjMDZzMVM0aXZZTHdlV2tydVB6YUQ5UHFyLUxaeWtHQjlOVWtjN2xV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNV1NUeFlaWmZjQkFQR0I5bURCcDMxUUJoWmoxQm11bElENk5LN3JDV1dFSVZBdjVseUpoMHl2b3dGN0lMcERtVWllNHZxS2lpdVJCNTNSY3ZMaHhZc3U0MW5KVmZDX0NDZHFCOTF1RkRhQU1JcThQeFhaYko1b0pWck96VnRaOV9nX0wyQzByNVJiYXFSNVpnRXdGVGo5UXQyNVJHRUFTaHRCY1RPcTVHUnVNYkcza3FZUVBlMXhjSFZ1eWE1bFFYZlNFSjJwemZUVkM0c2ZYQ1RpLVF1?oc=5</t>
         </is>
       </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMid0FVX3lxTE9aak4waGJmcmw4OXF3ZzlZbHlPck1YODF3OWxnNjdfdnpoRjg5NlB1VWpIY2lwcDdpZEdvR3dWZmhCUTVCX21iSEUwUHpoS0RjMDZzMVM0aXZZTHdlV2tydVB6YUQ5UHFyLUxaeWtHQjlOVWtjN2xV?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxNV1NUeFlaWmZjQkFQR0I5bURCcDMxUUJoWmoxQm11bElENk5LN3JDV1dFSVZBdjVseUpoMHl2b3dGN0lMcERtVWllNHZxS2lpdVJCNTNSY3ZMaHhZc3U0MW5KVmZDX0NDZHFCOTF1RkRhQU1JcThQeFhaYko1b0pWck96VnRaOV9nX0wyQzByNVJiYXFSNVpnRXdGVGo5UXQyNVJHRUFTaHRCY1RPcTVHUnVNYkcza3FZUVBlMXhjSFZ1eWE1bFFYZlNFSjJwemZUVkM0c2ZYQ1RpLVF1?oc=5</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>a75b589881133382</t>
+          <t>e2ab49cc0755acf3</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
@@ -10135,32 +10135,32 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>The Climate Watch</t>
+          <t>ekantipur.com</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - The Climate Watch</t>
+          <t>Telecommunications Authority Provides Rs 150 Million in Aid for Bhotekoshi Flood Victims - ekantipur.com</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood The Climate Watch</t>
+          <t>Telecommunications Authority Provides Rs 150 Million in Aid for Bhotekoshi Flood Victims ekantipur.com</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9aak4waGJmcmw4OXF3ZzlZbHlPck1YODF3OWxnNjdfdnpoRjg5NlB1VWpIY2lwcDdpZEdvR3dWZmhCUTVCX21iSEUwUHpoS0RjMDZzMVM0aXZZTHdlV2tydVB6YUQ5UHFyLUxaeWtHQjlOVWtjN2xV?oc=5</t>
         </is>
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMid0FVX3lxTE9aak4waGJmcmw4OXF3ZzlZbHlPck1YODF3OWxnNjdfdnpoRjg5NlB1VWpIY2lwcDdpZEdvR3dWZmhCUTVCX21iSEUwUHpoS0RjMDZzMVM0aXZZTHdlV2tydVB6YUQ5UHFyLUxaeWtHQjlOVWtjN2xV?oc=5</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
     <row r="189" ht="48" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>4a168e8692066c34</t>
+          <t>a75b589881133382</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -10192,27 +10192,27 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Climate Watch</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA - The Rising Nepal</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - The Climate Watch</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA The Rising Nepal</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood The Climate Watch</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1wdjVhRU5DVV9OdmctRUt2NHBkUG5WZnFMNURZdnhqdVBIaV85SVZXdHF4cGRCc0V6QmVOVHdjeUNxYW1zdW0tUnRwa3RtU3Jw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1wdjVhRU5DVV9OdmctRUt2NHBkUG5WZnFMNURZdnhqdVBIaV85SVZXdHF4cGRCc0V6QmVOVHdjeUNxYW1zdW0tUnRwa3RtU3Jw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>74904a9e27c05cbb</t>
+          <t>4a168e8692066c34</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
@@ -10239,32 +10239,32 @@
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report - myRepublica</t>
+          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA - The Rising Nepal</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report myRepublica</t>
+          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA The Rising Nepal</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQjJISkJvQXl0dE5ic21GbTdqMmY0WnY1cktCbHo2bUx3Q0JDLTJxVFdzVE5DSUx6ZjRNTTRCYXRoS2lLdVpBYzFuS0RIaF9oLWhyVE8yejBmc1B5ZVEydl9IOFFqYmlhbEhNOE5Qa25mdFFaM05LV0dGZFkxcDN2YU1VQ291NFpJNTJOQk5WY2JWRncteGZpSFAwMnFDdlVsc0dDTEhIeGdyNGhXM0k3UWdZdWRWd0IwTDNfNlBEeW9GaC1XSms4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1wdjVhRU5DVV9OdmctRUt2NHBkUG5WZnFMNURZdnhqdVBIaV85SVZXdHF4cGRCc0V6QmVOVHdjeUNxYW1zdW0tUnRwa3RtU3Jw?oc=5</t>
         </is>
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxPQjJISkJvQXl0dE5ic21GbTdqMmY0WnY1cktCbHo2bUx3Q0JDLTJxVFdzVE5DSUx6ZjRNTTRCYXRoS2lLdVpBYzFuS0RIaF9oLWhyVE8yejBmc1B5ZVEydl9IOFFqYmlhbEhNOE5Qa25mdFFaM05LV0dGZFkxcDN2YU1VQ291NFpJNTJOQk5WY2JWRncteGZpSFAwMnFDdlVsc0dDTEhIeGdyNGhXM0k3UWdZdWRWd0IwTDNfNlBEeW9GaC1XSms4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1wdjVhRU5DVV9OdmctRUt2NHBkUG5WZnFMNURZdnhqdVBIaV85SVZXdHF4cGRCc0V6QmVOVHdjeUNxYW1zdW0tUnRwa3RtU3Jw?oc=5</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -10281,7 +10281,7 @@
     <row r="191" ht="48" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>d0d766933140860c</t>
+          <t>74904a9e27c05cbb</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -10291,32 +10291,32 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
+          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report - myRepublica</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
+          <t>Rs 95.42 billion required for removing Bhotekoshi flood debris: RDNA report myRepublica</t>
         </is>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQjJISkJvQXl0dE5ic21GbTdqMmY0WnY1cktCbHo2bUx3Q0JDLTJxVFdzVE5DSUx6ZjRNTTRCYXRoS2lLdVpBYzFuS0RIaF9oLWhyVE8yejBmc1B5ZVEydl9IOFFqYmlhbEhNOE5Qa25mdFFaM05LV0dGZFkxcDN2YU1VQ291NFpJNTJOQk5WY2JWRncteGZpSFAwMnFDdlVsc0dDTEhIeGdyNGhXM0k3UWdZdWRWd0IwTDNfNlBEeW9GaC1XSms4?oc=5</t>
         </is>
       </c>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxPQjJISkJvQXl0dE5ic21GbTdqMmY0WnY1cktCbHo2bUx3Q0JDLTJxVFdzVE5DSUx6ZjRNTTRCYXRoS2lLdVpBYzFuS0RIaF9oLWhyVE8yejBmc1B5ZVEydl9IOFFqYmlhbEhNOE5Qa25mdFFaM05LV0dGZFkxcDN2YU1VQ291NFpJNTJOQk5WY2JWRncteGZpSFAwMnFDdlVsc0dDTEhIeGdyNGhXM0k3UWdZdWRWd0IwTDNfNlBEeW9GaC1XSms4?oc=5</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>23eb19e5e1175351</t>
+          <t>d0d766933140860c</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
@@ -10343,32 +10343,32 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T00:04:58Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myRepublica</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myRepublica</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSUVRby1GYjJfcVpjSkVuUmNxT1FIckJJRUx1TlNERTE0MG9pRHpjN3JxY3RlQ2lRWmpmeUg0MjhYQXZBc1ZrTHdBQktOZ1JwcEt2R0tDaGNjUUI2WTRJSlp3YVZhYUZsVUtHdUFYMXlqd0l0Ri1obVFKZjM2My05Zm1OVTJoTTk3VzVDTW9OY0Z3bHlBeDNTc0k0NWJIcnI1R0NkXzI1WE01X2pzVG9jRkVORjAxaVVkYXptMTVZdHdaaDRIWkQ1c0tXc0JVVG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
         </is>
       </c>
       <c r="H192" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNSUVRby1GYjJfcVpjSkVuUmNxT1FIckJJRUx1TlNERTE0MG9pRHpjN3JxY3RlQ2lRWmpmeUg0MjhYQXZBc1ZrTHdBQktOZ1JwcEt2R0tDaGNjUUI2WTRJSlp3YVZhYUZsVUtHdUFYMXlqd0l0Ri1obVFKZjM2My05Zm1OVTJoTTk3VzVDTW9OY0Z3bHlBeDNTc0k0NWJIcnI1R0NkXzI1WE01X2pzVG9jRkVORjAxaVVkYXptMTVZdHdaaDRIWkQ1c0tXc0JVVG8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="193" ht="48" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>9b5c642e492710ec</t>
+          <t>23eb19e5e1175351</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -10395,32 +10395,32 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-22T00:04:58Z</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - Khabarhub</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively - myRepublica</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone Khabarhub</t>
+          <t>Bhotekoshi flood leaves children among hardest hit; media urged to report sensitively myRepublica</t>
         </is>
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSUVRby1GYjJfcVpjSkVuUmNxT1FIckJJRUx1TlNERTE0MG9pRHpjN3JxY3RlQ2lRWmpmeUg0MjhYQXZBc1ZrTHdBQktOZ1JwcEt2R0tDaGNjUUI2WTRJSlp3YVZhYUZsVUtHdUFYMXlqd0l0Ri1obVFKZjM2My05Zm1OVTJoTTk3VzVDTW9OY0Z3bHlBeDNTc0k0NWJIcnI1R0NkXzI1WE01X2pzVG9jRkVORjAxaVVkYXptMTVZdHdaaDRIWkQ1c0tXc0JVVG8?oc=5</t>
         </is>
       </c>
       <c r="H193" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNSUVRby1GYjJfcVpjSkVuUmNxT1FIckJJRUx1TlNERTE0MG9pRHpjN3JxY3RlQ2lRWmpmeUg0MjhYQXZBc1ZrTHdBQktOZ1JwcEt2R0tDaGNjUUI2WTRJSlp3YVZhYUZsVUtHdUFYMXlqd0l0Ri1obVFKZjM2My05Zm1OVTJoTTk3VzVDTW9OY0Z3bHlBeDNTc0k0NWJIcnI1R0NkXzI1WE01X2pzVG9jRkVORjAxaVVkYXptMTVZdHdaaDRIWkQ1c0tXc0JVVG8?oc=5</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -10437,7 +10437,7 @@
     <row r="194" ht="48" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>37438c875f11623f</t>
+          <t>9b5c642e492710ec</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - Khabarhub</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone Khabarhub</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMlloMG1iTW5LZUExV04xSU1VTFZOdnFYRlBXZ2k0dlpCd3AxMlJpMzBBQk1OS2hiTnRBNktMYWJCODJ4bmZ3Vm9Pcl9oUUFjNDI1UURNZjRpU1BCWUFRQ3cwa1hiZDF6bnhSVGtMTF90bUlCSFNtZjRQQTAzWTUwN1NDdFZCM0JlYVY5cTN3OTVwZnpzRG95bWFPYXNnYXFSZmVjQWMzeEcwcHQ1MDdpdThLemFfTHlENC1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
         </is>
       </c>
       <c r="H194" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMlloMG1iTW5LZUExV04xSU1VTFZOdnFYRlBXZ2k0dlpCd3AxMlJpMzBBQk1OS2hiTnRBNktMYWJCODJ4bmZ3Vm9Pcl9oUUFjNDI1UURNZjRpU1BCWUFRQ3cwa1hiZDF6bnhSVGtMTF90bUlCSFNtZjRQQTAzWTUwN1NDdFZCM0JlYVY5cTN3OTVwZnpzRG95bWFPYXNnYXFSZmVjQWMzeEcwcHQ1MDdpdThLemFfTHlENC1r?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="195" ht="48" customHeight="1">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>04bf12c411b86519</t>
+          <t>37438c875f11623f</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Relief for Rasuwa flood victims stuck at Nepal-India border - The Himalayan Times</t>
+          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Relief for Rasuwa flood victims stuck at Nepal-India border The Himalayan Times</t>
+          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMlloMG1iTW5LZUExV04xSU1VTFZOdnFYRlBXZ2k0dlpCd3AxMlJpMzBBQk1OS2hiTnRBNktMYWJCODJ4bmZ3Vm9Pcl9oUUFjNDI1UURNZjRpU1BCWUFRQ3cwa1hiZDF6bnhSVGtMTF90bUlCSFNtZjRQQTAzWTUwN1NDdFZCM0JlYVY5cTN3OTVwZnpzRG95bWFPYXNnYXFSZmVjQWMzeEcwcHQ1MDdpdThLemFfTHlENC1r?oc=5</t>
         </is>
       </c>
       <c r="H195" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMlloMG1iTW5LZUExV04xSU1VTFZOdnFYRlBXZ2k0dlpCd3AxMlJpMzBBQk1OS2hiTnRBNktMYWJCODJ4bmZ3Vm9Pcl9oUUFjNDI1UURNZjRpU1BCWUFRQ3cwa1hiZDF6bnhSVGtMTF90bUlCSFNtZjRQQTAzWTUwN1NDdFZCM0JlYVY5cTN3OTVwZnpzRG95bWFPYXNnYXFSZmVjQWMzeEcwcHQ1MDdpdThLemFfTHlENC1r?oc=5</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -10541,7 +10541,7 @@
     <row r="196" ht="48" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>b053f134835909ae</t>
+          <t>04bf12c411b86519</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
@@ -10551,32 +10551,32 @@
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Family cremates four after hope of return fades - Khabarhub</t>
+          <t>Relief for Rasuwa flood victims stuck at Nepal-India border - The Himalayan Times</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Family cremates four after hope of return fades Khabarhub</t>
+          <t>Relief for Rasuwa flood victims stuck at Nepal-India border The Himalayan Times</t>
         </is>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVQ?oc=5</t>
         </is>
       </c>
       <c r="H196" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNZEgtdW55NDdkTEptR1UyYWh1R0JlWVU1bTlqekRIQW9BU1hFN3VBQ2JDSGVQMm1ydWtNRG9mamttUVpMS19CZDR0QUI4SzZDTjUxdFZCLWFnNzBjcF9zRUNZWlJGaEJKMmkxWFpfX2hhM3J6VVVZWkQ4Mm9jYzNWVFBFLTdndmZDTjVwazN5U1NZa05uNHBaRGFDVQ?oc=5</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -10593,7 +10593,7 @@
     <row r="197" ht="48" customHeight="1">
       <c r="A197" s="8" t="inlineStr">
         <is>
-          <t>f10226ed7e1ac86c</t>
+          <t>b053f134835909ae</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
@@ -10603,32 +10603,32 @@
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T16:26:37Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - The Himalayan Times</t>
+          <t>Bhotekoshi flood: Family cremates four after hope of return fades - Khabarhub</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill The Himalayan Times</t>
+          <t>Bhotekoshi flood: Family cremates four after hope of return fades Khabarhub</t>
         </is>
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfQjE3UFdpTWR3RUxNaVFSMDk5WUg5VEVTVFl2N0pxSXYyWmtBVXg0N3VndmNNUEtFUGkwTV9DTnd4TTRIVHVQSlpoM2RSZDdGV2ZBUExfUmpLQlFG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
         </is>
       </c>
       <c r="H197" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfQjE3UFdpTWR3RUxNaVFSMDk5WUg5VEVTVFl2N0pxSXYyWmtBVXg0N3VndmNNUEtFUGkwTV9DTnd4TTRIVHVQSlpoM2RSZDdGV2ZBUExfUmpLQlFG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9ZZDZtbHQyR0EwQm5MVjZPNmhhalJmeW5uVGdJRHVQeURZUURmN3h0ckIyTVViV0xzeGptZHhoX0lqUEQ1dDhHOHFJQUxqaU5uVGpBS2FUMnM?oc=5</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -10645,42 +10645,42 @@
     <row r="198" ht="48" customHeight="1">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>437defac5b095a7a</t>
+          <t>f10226ed7e1ac86c</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T09:46:47Z</t>
+          <t>2026-09-11T16:26:37Z</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - The Himalayan Times</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill The Himalayan Times</t>
         </is>
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaWh2WlN1Sm1KSXd1WTExNm5YSkdUM19OemdzUG1tajlDbWFxdmdxSWFnMXh6TjdnaTJuSTJWTms0Wm9kd24zVW1yRUJ2d1VfcHBkVVNRSmlPWkJuM2NOTG54dkYzRmo3X1pNNE1RS3NDREl0cHJZUm90Wm1RZDFtcFMycWJRVzJDLTJ2ckhRZW96Q3dpVXlFa3k0Yk1aNTJxdThVZEtqdU5PQ01wQVBCU0d0WHZyQnhS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfQjE3UFdpTWR3RUxNaVFSMDk5WUg5VEVTVFl2N0pxSXYyWmtBVXg0N3VndmNNUEtFUGkwTV9DTnd4TTRIVHVQSlpoM2RSZDdGV2ZBUExfUmpLQlFG?oc=5</t>
         </is>
       </c>
       <c r="H198" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaWh2WlN1Sm1KSXd1WTExNm5YSkdUM19OemdzUG1tajlDbWFxdmdxSWFnMXh6TjdnaTJuSTJWTms0Wm9kd24zVW1yRUJ2d1VfcHBkVVNRSmlPWkJuM2NOTG54dkYzRmo3X1pNNE1RS3NDREl0cHJZUm90Wm1RZDFtcFMycWJRVzJDLTJ2ckhRZW96Q3dpVXlFa3k0Yk1aNTJxdThVZEtqdU5PQ01wQVBCU0d0WHZyQnhS?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBfQjE3UFdpTWR3RUxNaVFSMDk5WUg5VEVTVFl2N0pxSXYyWmtBVXg0N3VndmNNUEtFUGkwTV9DTnd4TTRIVHVQSlpoM2RSZDdGV2ZBUExfUmpLQlFG?oc=5</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="199" ht="48" customHeight="1">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>7179789cdd688fe0</t>
+          <t>437defac5b095a7a</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
@@ -10707,32 +10707,32 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T21:19:22Z</t>
+          <t>2026-09-29T09:46:47Z</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Unidentified remains and conflicting data prolong family grief - Nepalnews.com</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Unidentified remains and conflicting data prolong family grief Nepalnews.com</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
         </is>
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQQzRvcks0ZlByeEMxa2VSMkpHbVV1ZjhLckY3Y2ZidW9YdnJWTHZZUEN2emJHdHhMSFgtLXEzMHRGTG5JSElQV3B6MUJaSzJSUVlOemYxSzd1cklKSVgxR0JFUUdJR19hODE1WTRaOXZpY2htRlkwaTh1RnFQYUNhcHVxS3FXT0ZDRE4tZVVtMUZJVDR0S0FDcVMwd0d3QjdzS3E5a0lERHNJam1iVS1zZTNPNDkzcF9HdW9jOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaWh2WlN1Sm1KSXd1WTExNm5YSkdUM19OemdzUG1tajlDbWFxdmdxSWFnMXh6TjdnaTJuSTJWTms0Wm9kd24zVW1yRUJ2d1VfcHBkVVNRSmlPWkJuM2NOTG54dkYzRmo3X1pNNE1RS3NDREl0cHJZUm90Wm1RZDFtcFMycWJRVzJDLTJ2ckhRZW96Q3dpVXlFa3k0Yk1aNTJxdThVZEtqdU5PQ01wQVBCU0d0WHZyQnhS?oc=5</t>
         </is>
       </c>
       <c r="H199" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxQQzRvcks0ZlByeEMxa2VSMkpHbVV1ZjhLckY3Y2ZidW9YdnJWTHZZUEN2emJHdHhMSFgtLXEzMHRGTG5JSElQV3B6MUJaSzJSUVlOemYxSzd1cklKSVgxR0JFUUdJR19hODE1WTRaOXZpY2htRlkwaTh1RnFQYUNhcHVxS3FXT0ZDRE4tZVVtMUZJVDR0S0FDcVMwd0d3QjdzS3E5a0lERHNJam1iVS1zZTNPNDkzcF9HdW9jOQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaWh2WlN1Sm1KSXd1WTExNm5YSkdUM19OemdzUG1tajlDbWFxdmdxSWFnMXh6TjdnaTJuSTJWTms0Wm9kd24zVW1yRUJ2d1VfcHBkVVNRSmlPWkJuM2NOTG54dkYzRmo3X1pNNE1RS3NDREl0cHJZUm90Wm1RZDFtcFMycWJRVzJDLTJ2ckhRZW96Q3dpVXlFa3k0Yk1aNTJxdThVZEtqdU5PQ01wQVBCU0d0WHZyQnhS?oc=5</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -10749,7 +10749,7 @@
     <row r="200" ht="48" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>ea73b5345dff19f7</t>
+          <t>7179789cdd688fe0</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
@@ -10759,32 +10759,32 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-27T21:19:22Z</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
+          <t>Bhote Koshi flood: Unidentified remains and conflicting data prolong family grief - Nepalnews.com</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
+          <t>Bhote Koshi flood: Unidentified remains and conflicting data prolong family grief Nepalnews.com</t>
         </is>
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNX25lemRYZVF5VWdWXzlUX3lxYy1JVGpwbFQtcjNoM3YtcUFNNFZaUjhtbmpJSXpmRHl2NnRLUEIyUWNaUFpPeWp1V3NjQ1U5TDFOel9CQ1N2Q1p3LVRnLVZHTmc1WVV0SU1hNlFWX1JwdXU5cFRJWmtiWFFnaG9BUTk2LWdGeHpMcGNrMnJnX213Q1VHYTd1Y3dUckxTd1RRcVFmNHMyaXkzWmFJUXBLTlRzamFZejdsVnFSaWx1aVc1RllSaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQQzRvcks0ZlByeEMxa2VSMkpHbVV1ZjhLckY3Y2ZidW9YdnJWTHZZUEN2emJHdHhMSFgtLXEzMHRGTG5JSElQV3B6MUJaSzJSUVlOemYxSzd1cklKSVgxR0JFUUdJR19hODE1WTRaOXZpY2htRlkwaTh1RnFQYUNhcHVxS3FXT0ZDRE4tZVVtMUZJVDR0S0FDcVMwd0d3QjdzS3E5a0lERHNJam1iVS1zZTNPNDkzcF9HdW9jOQ?oc=5</t>
         </is>
       </c>
       <c r="H200" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNX25lemRYZVF5VWdWXzlUX3lxYy1JVGpwbFQtcjNoM3YtcUFNNFZaUjhtbmpJSXpmRHl2NnRLUEIyUWNaUFpPeWp1V3NjQ1U5TDFOel9CQ1N2Q1p3LVRnLVZHTmc1WVV0SU1hNlFWX1JwdXU5cFRJWmtiWFFnaG9BUTk2LWdGeHpMcGNrMnJnX213Q1VHYTd1Y3dUckxTd1RRcVFmNHMyaXkzWmFJUXBLTlRzamFZejdsVnFSaWx1aVc1RllSaFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxQQzRvcks0ZlByeEMxa2VSMkpHbVV1ZjhLckY3Y2ZidW9YdnJWTHZZUEN2emJHdHhMSFgtLXEzMHRGTG5JSElQV3B6MUJaSzJSUVlOemYxSzd1cklKSVgxR0JFUUdJR19hODE1WTRaOXZpY2htRlkwaTh1RnFQYUNhcHVxS3FXT0ZDRE4tZVVtMUZJVDR0S0FDcVMwd0d3QjdzS3E5a0lERHNJam1iVS1zZTNPNDkzcF9HdW9jOQ?oc=5</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="201" ht="48" customHeight="1">
       <c r="A201" s="8" t="inlineStr">
         <is>
-          <t>fa6c4a4cabc1acaa</t>
+          <t>ea73b5345dff19f7</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
@@ -10821,22 +10821,22 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
         </is>
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY0NhOFlVOWlJbXZyVEpLbmxkWTJuc25RRnAyX1RvV2xVZVpleHpGY3B3aHRsX0lORnJGY2pvYkUybk5WcThxRTNYUVRVWnhjR2VrLVBDeXRiVzl3NHVzYjNHaG5kNlk4MlRJeXFBZnpETWtZb29HOGIyY21IWFhkVUg1RE0xTjhyejU3V1VHel9YSkkzZVV4b1pvSHN1WWRUOUs5MnhhYkxkcUFVQTVMZ2J4QUdRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNX25lemRYZVF5VWdWXzlUX3lxYy1JVGpwbFQtcjNoM3YtcUFNNFZaUjhtbmpJSXpmRHl2NnRLUEIyUWNaUFpPeWp1V3NjQ1U5TDFOel9CQ1N2Q1p3LVRnLVZHTmc1WVV0SU1hNlFWX1JwdXU5cFRJWmtiWFFnaG9BUTk2LWdGeHpMcGNrMnJnX213Q1VHYTd1Y3dUckxTd1RRcVFmNHMyaXkzWmFJUXBLTlRzamFZejdsVnFSaWx1aVc1RllSaFE?oc=5</t>
         </is>
       </c>
       <c r="H201" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNY0NhOFlVOWlJbXZyVEpLbmxkWTJuc25RRnAyX1RvV2xVZVpleHpGY3B3aHRsX0lORnJGY2pvYkUybk5WcThxRTNYUVRVWnhjR2VrLVBDeXRiVzl3NHVzYjNHaG5kNlk4MlRJeXFBZnpETWtZb29HOGIyY21IWFhkVUg1RE0xTjhyejU3V1VHel9YSkkzZVV4b1pvSHN1WWRUOUs5MnhhYkxkcUFVQTVMZ2J4QUdRdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxNX25lemRYZVF5VWdWXzlUX3lxYy1JVGpwbFQtcjNoM3YtcUFNNFZaUjhtbmpJSXpmRHl2NnRLUEIyUWNaUFpPeWp1V3NjQ1U5TDFOel9CQ1N2Q1p3LVRnLVZHTmc1WVV0SU1hNlFWX1JwdXU5cFRJWmtiWFFnaG9BUTk2LWdGeHpMcGNrMnJnX213Q1VHYTd1Y3dUckxTd1RRcVFmNHMyaXkzWmFJUXBLTlRzamFZejdsVnFSaWx1aVc1RllSaFE?oc=5</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -10853,7 +10853,7 @@
     <row r="202" ht="48" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>86baaa8f62a4528b</t>
+          <t>fa6c4a4cabc1acaa</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11T11:17:35Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -10873,22 +10873,22 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
+          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
+          <t>Ramesh returns home after 11 days, surviving Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY0NhOFlVOWlJbXZyVEpLbmxkWTJuc25RRnAyX1RvV2xVZVpleHpGY3B3aHRsX0lORnJGY2pvYkUybk5WcThxRTNYUVRVWnhjR2VrLVBDeXRiVzl3NHVzYjNHaG5kNlk4MlRJeXFBZnpETWtZb29HOGIyY21IWFhkVUg1RE0xTjhyejU3V1VHel9YSkkzZVV4b1pvSHN1WWRUOUs5MnhhYkxkcUFVQTVMZ2J4QUdRdw?oc=5</t>
         </is>
       </c>
       <c r="H202" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNY0NhOFlVOWlJbXZyVEpLbmxkWTJuc25RRnAyX1RvV2xVZVpleHpGY3B3aHRsX0lORnJGY2pvYkUybk5WcThxRTNYUVRVWnhjR2VrLVBDeXRiVzl3NHVzYjNHaG5kNlk4MlRJeXFBZnpETWtZb29HOGIyY21IWFhkVUg1RE0xTjhyejU3V1VHel9YSkkzZVV4b1pvSHN1WWRUOUs5MnhhYkxkcUFVQTVMZ2J4QUdRdw?oc=5</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="203" ht="48" customHeight="1">
       <c r="A203" s="8" t="inlineStr">
         <is>
-          <t>70ed83c991b2efeb</t>
+          <t>86baaa8f62a4528b</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
@@ -10915,32 +10915,32 @@
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T20:50:24Z</t>
+          <t>2026-09-11T11:17:35Z</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - risingnepaldaily.com</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims risingnepaldaily.com</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
         </is>
       </c>
       <c r="H203" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="204" ht="48" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>0f5c1a8be0f179ae</t>
+          <t>70ed83c991b2efeb</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-10T20:50:24Z</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -10977,22 +10977,22 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>FM urges realistic assessment of Rasuwa flood damage and needs - risingnepaldaily.com</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>FM urges realistic assessment of Rasuwa flood damage and needs risingnepaldaily.com</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE45bUp2YkV0MUtlUnRRaXhfc2dSeC1BWURyTVI1c09PU090dXVWLVBYMkJTQkhGdTEzdENrTnlDUTFPcVZJNVl5T2pOYU9qVFhO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
         </is>
       </c>
       <c r="H204" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE45bUp2YkV0MUtlUnRRaXhfc2dSeC1BWURyTVI1c09PU090dXVWLVBYMkJTQkhGdTEzdENrTnlDUTFPcVZJNVl5T2pOYU9qVFhO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5ZQUtfdy1nZk4ybWZhaUdMN2wyQ0NtNDBtVFcwbG9taTJfRzc3cnpxNklKaUt3bTY3Vk50UlR5NWpDZU5DRVpsY2lySXNGcWYy?oc=5</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="205" ht="48" customHeight="1">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>bb76f8b3312005cd</t>
+          <t>0f5c1a8be0f179ae</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
@@ -11019,32 +11019,32 @@
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>risingnepaldaily.com</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster - The Himalayan Times</t>
+          <t>FM urges realistic assessment of Rasuwa flood damage and needs - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster The Himalayan Times</t>
+          <t>FM urges realistic assessment of Rasuwa flood damage and needs risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQaVlyU2ZXS2gzRGp0dTRRaEpXQlhYTHBsQzN5UHVzSmM0cmprdE1DTWZ1YmhUUDlSd0RDc0JLLTJHcGFHcEtjbXJjY3hVWHFvaTZscGRsV0Z6ZE1IZ2Y1WHhKRmIyNkVjWE92ZzZGcE5WM0M2VmFDeWFRYjNkbHk2LXg0bFRBQ21yd0tDYk1kZHFvRnFReVlLRnRlMnR1NXZ1S0VQZ1d3RXNlcnhxVWNuZUVoRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE45bUp2YkV0MUtlUnRRaXhfc2dSeC1BWURyTVI1c09PU090dXVWLVBYMkJTQkhGdTEzdENrTnlDUTFPcVZJNVl5T2pOYU9qVFhO?oc=5</t>
         </is>
       </c>
       <c r="H205" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQaVlyU2ZXS2gzRGp0dTRRaEpXQlhYTHBsQzN5UHVzSmM0cmprdE1DTWZ1YmhUUDlSd0RDc0JLLTJHcGFHcEtjbXJjY3hVWHFvaTZscGRsV0Z6ZE1IZ2Y1WHhKRmIyNkVjWE92ZzZGcE5WM0M2VmFDeWFRYjNkbHk2LXg0bFRBQ21yd0tDYk1kZHFvRnFReVlLRnRlMnR1NXZ1S0VQZ1d3RXNlcnhxVWNuZUVoRQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE45bUp2YkV0MUtlUnRRaXhfc2dSeC1BWURyTVI1c09PU090dXVWLVBYMkJTQkhGdTEzdENrTnlDUTFPcVZJNVl5T2pOYU9qVFhO?oc=5</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="206" ht="48" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>f0d257c13960eb9d</t>
+          <t>bb76f8b3312005cd</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
+          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster - The Himalayan Times</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
+          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster The Himalayan Times</t>
         </is>
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQaVlyU2ZXS2gzRGp0dTRRaEpXQlhYTHBsQzN5UHVzSmM0cmprdE1DTWZ1YmhUUDlSd0RDc0JLLTJHcGFHcEtjbXJjY3hVWHFvaTZscGRsV0Z6ZE1IZ2Y1WHhKRmIyNkVjWE92ZzZGcE5WM0M2VmFDeWFRYjNkbHk2LXg0bFRBQ21yd0tDYk1kZHFvRnFReVlLRnRlMnR1NXZ1S0VQZ1d3RXNlcnhxVWNuZUVoRQ?oc=5</t>
         </is>
       </c>
       <c r="H206" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQaVlyU2ZXS2gzRGp0dTRRaEpXQlhYTHBsQzN5UHVzSmM0cmprdE1DTWZ1YmhUUDlSd0RDc0JLLTJHcGFHcEtjbXJjY3hVWHFvaTZscGRsV0Z6ZE1IZ2Y1WHhKRmIyNkVjWE92ZzZGcE5WM0M2VmFDeWFRYjNkbHk2LXg0bFRBQ21yd0tDYk1kZHFvRnFReVlLRnRlMnR1NXZ1S0VQZ1d3RXNlcnhxVWNuZUVoRQ?oc=5</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="207" ht="48" customHeight="1">
       <c r="A207" s="8" t="inlineStr">
         <is>
-          <t>0be314eae73ad25d</t>
+          <t>f0d257c13960eb9d</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
@@ -11128,27 +11128,27 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Panel formed to study impacts of Rasuwa flood - myrepublica.nagariknetwork.com</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Panel formed to study impacts of Rasuwa flood myrepublica.nagariknetwork.com</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
         </is>
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPN0psMXp6WE1nNWpoLTh4MkFyMl9kRjYzWVFTRVozYnNtNzFjV2lHSlVHYkYtMHRleEZ6ek5xUWFwakpUNlRHckxtMlgtUi1MLVQyMHBoOHBuNzNYQ3lpZFYyQ0Y0ck0yZ1FfR2lSYjFpYjJ3U0JKM1dLZWJLVzdqejNVYWMxNEhQcHo2N1JwWlZFdW5MYlVEZVdWZjZ2cVo5bkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="H207" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxPN0psMXp6WE1nNWpoLTh4MkFyMl9kRjYzWVFTRVozYnNtNzFjV2lHSlVHYkYtMHRleEZ6ek5xUWFwakpUNlRHckxtMlgtUi1MLVQyMHBoOHBuNzNYQ3lpZFYyQ0Y0ck0yZ1FfR2lSYjFpYjJ3U0JKM1dLZWJLVzdqejNVYWMxNEhQcHo2N1JwWlZFdW5MYlVEZVdWZjZ2cVo5bkE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="208" ht="48" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>b9e8fd509d3b84b0</t>
+          <t>0be314eae73ad25d</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
@@ -11175,32 +11175,32 @@
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10T11:16:20Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster - The Himalayan Times</t>
+          <t>Panel formed to study impacts of Rasuwa flood - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster The Himalayan Times</t>
+          <t>Panel formed to study impacts of Rasuwa flood myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE95UDBWbEZYdWoxZWhIT0VYN0RiTnl1alN3aE0xbWMwOWRnNXd2ZlA5TzB0V0dZUTJNT2daVXFubTVNZWJfbFVQWW1HSVdpNE1HX1pyQTdOcHIteVct0gFcQVVfeXFMT3lQMFZsRlh1ajFlaEhPRVg3RGJOeXVqU3doTTFtYzA5ZGc1d3ZmUDlPMHRXR1lRMk1PZ1pVcW5tNU1lYl9sVVBZbUdJV2k0TUdfWnJBN05wci15Vy0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPN0psMXp6WE1nNWpoLTh4MkFyMl9kRjYzWVFTRVozYnNtNzFjV2lHSlVHYkYtMHRleEZ6ek5xUWFwakpUNlRHckxtMlgtUi1MLVQyMHBoOHBuNzNYQ3lpZFYyQ0Y0ck0yZ1FfR2lSYjFpYjJ3U0JKM1dLZWJLVzdqejNVYWMxNEhQcHo2N1JwWlZFdW5MYlVEZVdWZjZ2cVo5bkE?oc=5</t>
         </is>
       </c>
       <c r="H208" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE95UDBWbEZYdWoxZWhIT0VYN0RiTnl1alN3aE0xbWMwOWRnNXd2ZlA5TzB0V0dZUTJNT2daVXFubTVNZWJfbFVQWW1HSVdpNE1HX1pyQTdOcHIteVct0gFcQVVfeXFMT3lQMFZsRlh1ajFlaEhPRVg3RGJOeXVqU3doTTFtYzA5ZGc1d3ZmUDlPMHRXR1lRMk1PZ1pVcW5tNU1lYl9sVVBZbUdJV2k0TUdfWnJBN05wci15Vy0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxPN0psMXp6WE1nNWpoLTh4MkFyMl9kRjYzWVFTRVozYnNtNzFjV2lHSlVHYkYtMHRleEZ6ek5xUWFwakpUNlRHckxtMlgtUi1MLVQyMHBoOHBuNzNYQ3lpZFYyQ0Y0ck0yZ1FfR2lSYjFpYjJ3U0JKM1dLZWJLVzdqejNVYWMxNEhQcHo2N1JwWlZFdW5MYlVEZVdWZjZ2cVo5bkE?oc=5</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -11217,42 +11217,42 @@
     <row r="209" ht="48" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>a4a0f705a84ebf28</t>
+          <t>b9e8fd509d3b84b0</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T11:19:52Z</t>
+          <t>2026-09-10T11:16:20Z</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing - Nepalnews.com</t>
+          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster - The Himalayan Times</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,365; over 4,000 still missing Nepalnews.com</t>
+          <t>Rabi Lamichhane Calls Bhote Koshi Flood A Climate Crisis Burded, Not Disaster The Himalayan Times</t>
         </is>
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE95UDBWbEZYdWoxZWhIT0VYN0RiTnl1alN3aE0xbWMwOWRnNXd2ZlA5TzB0V0dZUTJNT2daVXFubTVNZWJfbFVQWW1HSVdpNE1HX1pyQTdOcHIteVct0gFcQVVfeXFMT3lQMFZsRlh1ajFlaEhPRVg3RGJOeXVqU3doTTFtYzA5ZGc1d3ZmUDlPMHRXR1lRMk1PZ1pVcW5tNU1lYl9sVVBZbUdJV2k0TUdfWnJBN05wci15Vy0?oc=5</t>
         </is>
       </c>
       <c r="H209" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd0k4QTVEX3NiZ2xfMUlGc09YZENXNnRUVzVzRkoxUnhKZXhFRjhrRlo3elA5ZFR4Z09oYnpvUXk4SXlneWdFTEdDZk5aWGh3RjFoaXM5TXFTSmFpTTlSRi15a3F4RWp4VW1GZnJ0MmJZak9hV3JnWVlJdGVaX0ZtUDlJUHYxRGhGVXpVNWE0OHNrV3JZdndlWmFiZHVKWjhNMHpTNnNYczg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE95UDBWbEZYdWoxZWhIT0VYN0RiTnl1alN3aE0xbWMwOWRnNXd2ZlA5TzB0V0dZUTJNT2daVXFubTVNZWJfbFVQWW1HSVdpNE1HX1pyQTdOcHIteVct0gFcQVVfeXFMT3lQMFZsRlh1ajFlaEhPRVg3RGJOeXVqU3doTTFtYzA5ZGc1d3ZmUDlPMHRXR1lRMk1PZ1pVcW5tNU1lYl9sVVBZbUdJV2k0TUdfWnJBN05wci15Vy0?oc=5</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -14389,7 +14389,7 @@
     <row r="270" ht="48" customHeight="1">
       <c r="A270" s="8" t="inlineStr">
         <is>
-          <t>45150033608b7edf</t>
+          <t>4cb2bd46e4d614d5</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
@@ -14409,22 +14409,22 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to TU Teaching Hospital - OnlineKhabar English News</t>
+          <t>Nepali lawmakers seek Bhutan’s support for compensation over Rasuwa flood damage - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to TU Teaching Hospital OnlineKhabar English News</t>
+          <t>Nepali lawmakers seek Bhutan’s support for compensation over Rasuwa flood damage OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQdFoyczM5RjVoRzI0U3JLTmJZeDZMT2ZXYzBKRGdnLU12ZndibGVNVjNnNWY0c1ZZaUJ2LUhCbWt5VE54ZmlULUxlMnUtMVNYeW5xdzN5OURvNjBUR0RMLTRrSm4wMWFkWEU5N0c5blpaN2pEM0dQRzVnTUlZY2VlRDllemp6MEJyNHlZY2puZzhVRmxjOF9haE4yeloyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQZ3RnMzJQTHVNMTJPUnZ3T1B2S2d6Zjk0YWQ2RF9vajdfcEliOEUtNkkyU0RxRVE5ckdJRGhZLWJhbnNXYkxnR0pYOVZMdFoya0R0RkM2ei1CcUV2WUFfZGlmb1Fla0xMMFpEaDFoRFZrcS1td1ZmdnQ1NFR2MUFsVA?oc=5</t>
         </is>
       </c>
       <c r="H270" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxQdFoyczM5RjVoRzI0U3JLTmJZeDZMT2ZXYzBKRGdnLU12ZndibGVNVjNnNWY0c1ZZaUJ2LUhCbWt5VE54ZmlULUxlMnUtMVNYeW5xdzN5OURvNjBUR0RMLTRrSm4wMWFkWEU5N0c5blpaN2pEM0dQRzVnTUlZY2VlRDllemp6MEJyNHlZY2puZzhVRmxjOF9haE4yeloyZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQZ3RnMzJQTHVNMTJPUnZ3T1B2S2d6Zjk0YWQ2RF9vajdfcEliOEUtNkkyU0RxRVE5ckdJRGhZLWJhbnNXYkxnR0pYOVZMdFoya0R0RkM2ei1CcUV2WUFfZGlmb1Fla0xMMFpEaDFoRFZrcS1td1ZmdnQ1NFR2MUFsVA?oc=5</t>
         </is>
       </c>
       <c r="I270" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-10T21:41:32Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10T17:19:50Z · 833 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-10T21:41:32Z · 833 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ea90ccbaf00b6f3a</t>
+          <t>11efb1b5283d4658</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -676,27 +676,27 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing - Ratopati</t>
+          <t>269 children lost their parents in the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing Ratopati</t>
+          <t>269 children lost their parents in the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -713,42 +713,42 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>356ab3a0efc73abe</t>
+          <t>ea90ccbaf00b6f3a</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing - Ratopati</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing Ratopati</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6c6838329cdfbfc3</t>
+          <t>356ab3a0efc73abe</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -775,32 +775,32 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T20:17:26Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood - The Rising Nepal</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood The Rising Nepal</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>8e369d28dac1be4d</t>
+          <t>6c6838329cdfbfc3</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-06T20:17:26Z</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -837,22 +837,22 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
+          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
+          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>a1c1bf932fb5fd38</t>
+          <t>8e369d28dac1be4d</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -879,32 +879,32 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ada55db68109e06e</t>
+          <t>a1c1bf932fb5fd38</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -973,42 +973,42 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>b514eaf62f9a2f3a</t>
+          <t>ada55db68109e06e</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T01:12:32Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>93bc198ad99eb753</t>
+          <t>b514eaf62f9a2f3a</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T18:49:52Z</t>
+          <t>2026-10-09T01:12:32Z</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction - The Kathmandu Post</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction The Kathmandu Post</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>162caaf3e8c44aad</t>
+          <t>93bc198ad99eb753</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T00:58:35Z</t>
+          <t>2026-10-08T18:49:52Z</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>The Climate Watch</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa - The Climate Watch</t>
+          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa The Climate Watch</t>
+          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction The Kathmandu Post</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>8f5026d4b74c2e76</t>
+          <t>162caaf3e8c44aad</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1139,32 +1139,32 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-08T00:58:35Z</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Climate Watch</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
+          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa - The Climate Watch</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
+          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa The Climate Watch</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>902d716c8ffa7987</t>
+          <t>8f5026d4b74c2e76</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1191,32 +1191,32 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T18:56:09Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Devdiscourse</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1233,42 +1233,42 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>6974acfd82237ba0</t>
+          <t>902d716c8ffa7987</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-10-07T18:56:09Z</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>cf90c325291d2551</t>
+          <t>6974acfd82237ba0</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1295,32 +1295,32 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T20:17:26Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood - The Kathmandu Post</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood The Kathmandu Post</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>10084f79d062af80</t>
+          <t>cf90c325291d2551</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1347,32 +1347,32 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-06T20:17:26Z</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
+          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
+          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood The Kathmandu Post</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>ab6e3de447176b06</t>
+          <t>10084f79d062af80</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1399,32 +1399,32 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>1f6c419cec878e51</t>
+          <t>3ab08920b47a6a0e</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-10-08T18:49:52Z</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>201 parents, 38 students missing in Rasuwa flood - myRepublica</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>201 parents, 38 students missing in Rasuwa flood myRepublica</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>3ab08920b47a6a0e</t>
+          <t>6e0819f293fe319a</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -3011,32 +3011,32 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T18:49:52Z</t>
+          <t>2026-09-27T11:59:03Z</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
+          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact - Nepalnews.com</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
+          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact Nepalnews.com</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -6017,42 +6017,42 @@
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>11efb1b5283d4658</t>
+          <t>410a103aaf7c4528</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>269 children lost their parents in the Bhotekoshi flood - Ekantipur</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>269 children lost their parents in the Bhotekoshi flood Ekantipur</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>410a103aaf7c4528</t>
+          <t>b44663cde7bfcda6</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -6084,27 +6084,27 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>b44663cde7bfcda6</t>
+          <t>af991dce59e57aa5</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>af991dce59e57aa5</t>
+          <t>85987c70074e39ad</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6225,42 +6225,42 @@
     <row r="113" ht="48" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>85987c70074e39ad</t>
+          <t>ab6e3de447176b06</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>bbfc4fc9ec971ea7</t>
+          <t>1f6c419cec878e51</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -7441,22 +7441,22 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing - myRepublica</t>
+          <t>201 parents, 38 students missing in Rasuwa flood - myRepublica</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing myRepublica</t>
+          <t>201 parents, 38 students missing in Rasuwa flood myRepublica</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="137" ht="48" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>659e477407972cf2</t>
+          <t>bbfc4fc9ec971ea7</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T04:54:40Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ - Khabarhub</t>
+          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing - myRepublica</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ Khabarhub</t>
+          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing myRepublica</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -7525,7 +7525,7 @@
     <row r="138" ht="48" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>dd5f23720e096ffa</t>
+          <t>659e477407972cf2</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -7535,32 +7535,32 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-25T04:54:40Z</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>The Loss and Damage Collaboration</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count - The Loss and Damage Collaboration</t>
+          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ - Khabarhub</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count The Loss and Damage Collaboration</t>
+          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ Khabarhub</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -7577,7 +7577,7 @@
     <row r="139" ht="48" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>f1e11b960864e93a</t>
+          <t>dd5f23720e096ffa</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for - radionepalonline.com</t>
+          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count - The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for radionepalonline.com</t>
+          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="140" ht="48" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>6e0819f293fe319a</t>
+          <t>f1e11b960864e93a</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -7639,32 +7639,32 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T11:59:03Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact - Nepalnews.com</t>
+          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for - radionepalonline.com</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact Nepalnews.com</t>
+          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for radionepalonline.com</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10T21:41:32Z</t>
+          <t>2026-10-11T05:42:53Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10T21:41:32Z · 833 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-11T05:42:53Z · 833 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8e369d28dac1be4d</t>
+          <t>b44663cde7bfcda6</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>ada55db68109e06e</t>
+          <t>85987c70074e39ad</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3625,17 +3625,17 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>639253c0e6c27bfc</t>
+          <t>eee0dd2411bff598</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-09-22T16:55:33Z</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -3645,22 +3645,22 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>e65a6f7e606852ff</t>
+          <t>639253c0e6c27bfc</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>a074d8d9f7cf953e</t>
+          <t>e65a6f7e606852ff</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T12:44:27Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>The Tourism Times</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>4a93f7eb5178c8ad</t>
+          <t>a074d8d9f7cf953e</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -3791,32 +3791,32 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-09-21T12:44:27Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,42 +3833,42 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>8e672e38aa2a06b2</t>
+          <t>4a93f7eb5178c8ad</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>399c31fb867245f3</t>
+          <t>8e672e38aa2a06b2</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -3895,32 +3895,32 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>7ffe997ac778dbf1</t>
+          <t>399c31fb867245f3</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3947,32 +3947,32 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T22:00:24Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3989,17 +3989,17 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>104cdf9d46c50f0a</t>
+          <t>7ffe997ac778dbf1</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T04:34:59Z</t>
+          <t>2026-10-05T22:00:24Z</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4009,22 +4009,22 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>39ff34f1f426316f</t>
+          <t>104cdf9d46c50f0a</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -4051,32 +4051,32 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T00:32:15Z</t>
+          <t>2026-09-19T04:34:59Z</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>af40c0f4cdd9b4d0</t>
+          <t>39ff34f1f426316f</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
@@ -4103,32 +4103,32 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-01T00:32:15Z</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4145,42 +4145,42 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>c6dcc4398d0f1aa3</t>
+          <t>af40c0f4cdd9b4d0</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>ed3cde30c6d7a272</t>
+          <t>c6dcc4398d0f1aa3</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -4207,32 +4207,32 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T23:56:47Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4249,42 +4249,42 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>5d30da09bcb70fcb</t>
+          <t>ed3cde30c6d7a272</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-10-04T23:56:47Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>339773c2b74968e7</t>
+          <t>5d30da09bcb70fcb</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T11:38:32Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>c16a9e76fde589cb</t>
+          <t>339773c2b74968e7</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>5dee575dde9896b2</t>
+          <t>c16a9e76fde589cb</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-17T11:38:32Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>63e3a3c4068798b8</t>
+          <t>5dee575dde9896b2</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T16:02:57Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -4477,22 +4477,22 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,17 +4509,17 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>1d8ccfd0e472ee8d</t>
+          <t>63e3a3c4068798b8</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-09-20T16:02:57Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -4529,22 +4529,22 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>a0d887b6e71fa24a</t>
+          <t>1d8ccfd0e472ee8d</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T09:46:47Z</t>
+          <t>2026-10-04T12:19:26Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>cc1e404c3c7b5539</t>
+          <t>a0d887b6e71fa24a</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-29T09:46:47Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4665,7 +4665,7 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>40652f6cba568b14</t>
+          <t>cc1e404c3c7b5539</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -4675,32 +4675,32 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T04:29:29Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
+          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
+          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4717,17 +4717,17 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>9740579eff616080</t>
+          <t>40652f6cba568b14</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-04T04:29:29Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -4737,22 +4737,22 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>976a3738cc5bbc8c</t>
+          <t>9740579eff616080</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>3a44f3c3227b20ff</t>
+          <t>976a3738cc5bbc8c</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -4836,27 +4836,27 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>3f5e5c359d3906bd</t>
+          <t>3a44f3c3227b20ff</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>a724087f81f68a0e</t>
+          <t>3f5e5c359d3906bd</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -4935,32 +4935,32 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -4977,7 +4977,7 @@
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>f62c2f3efb4f90da</t>
+          <t>a724087f81f68a0e</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -4987,32 +4987,32 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>509e249c7e4eed4b</t>
+          <t>f62c2f3efb4f90da</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -5039,32 +5039,32 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5081,42 +5081,42 @@
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>2fdda12f5042e371</t>
+          <t>509e249c7e4eed4b</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Nepal plans Bhotekoshi flood resettlement within two years - UA.NEWS</t>
+          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Nepal plans Bhotekoshi flood resettlement within two years UA.NEWS</t>
+          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5133,42 +5133,42 @@
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>0179379ee0bcea80</t>
+          <t>5550c86ea2eb32e9</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T00:59:03Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -5185,42 +5185,42 @@
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>4553867da1cf7f24</t>
+          <t>2fdda12f5042e371</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 7,570 homes across 5 districts - OnlineKhabar English News</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years - UA.NEWS</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 7,570 homes across 5 districts OnlineKhabar English News</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years UA.NEWS</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -5237,42 +5237,42 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>ae42ae903bc8d76f</t>
+          <t>0179379ee0bcea80</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T04:44:23Z</t>
+          <t>2026-09-29T00:59:03Z</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>fbacf2163aebfd9e</t>
+          <t>4553867da1cf7f24</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -5299,32 +5299,32 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance - Ekantipur</t>
+          <t>Bhotekoshi flood damages 7,570 homes across 5 districts - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance Ekantipur</t>
+          <t>Bhotekoshi flood damages 7,570 homes across 5 districts OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxQMFVjbDZlWW9KSWFCNkRUYnFEUlVrdnF1b3czT04yU2ZQSzFlZGxoMGNoaUlrdWs0VFJGYjVZUTEtejVNLXNuQmJXaUJRS3dOZElmT254dElfRHZWM1BacTF1V0VjdjJ4a1hKdnBncWg2X3ctV0l0YU96OTJvNEYxNmNKeGV3d1RkbEZnLWtqbW9ZM1VKa3dj?oc=5</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>ee48897af3fcec08</t>
+          <t>ae42ae903bc8d76f</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -5351,32 +5351,32 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-13T04:44:23Z</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: Over 3,000 DNA samples collected - OnlineKhabar English News</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: Over 3,000 DNA samples collected OnlineKhabar English News</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,386; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdElMcm1iSWxkOGY1RkVSMDZMZ3Q2Nk9YNVdGSDRRZW0yMjNHRC1GZm8wQ05XUUU2RV80dmdsN0VkNUVIbWxjWXNpNEVLNnhEN1pWdXc1aXBVYjR4M3hDbVVsbElkM2dpcHN5RHNwNHJyMkRrRjR5Q2tFZFVvemZGR3FlaEZXN29xNDBHeEF0MDc2ZEdmS3Q2U18xX01wYUR2bFdiRmd6dnY?oc=5</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>36ae5311c55c236f</t>
+          <t>ee48897af3fcec08</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -5403,32 +5403,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T05:15:51Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families - Nepalnews.com</t>
+          <t>Rasuwa flood: Over 3,000 DNA samples collected - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families Nepalnews.com</t>
+          <t>Rasuwa flood: Over 3,000 DNA samples collected OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9xczBsd3VFY0ZUaEhjTnZ0cExZQ1N3b3I2dVBQM3FkRXcwbXY2WHdSRlh4b19Cc1VsOC1ZS0tzckNsaWRJbHhhdjZnTEZiQ2lLQlFZU2Z4ajBkLUV2bFpwNGdPNW4wSEJpV2hN?oc=5</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -5445,42 +5445,42 @@
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>9b19a739b91a113a</t>
+          <t>36ae5311c55c236f</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-27T05:15:51Z</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - Ratopati</t>
+          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families - Nepalnews.com</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage Ratopati</t>
+          <t>Government announces monthly housing allowance for Bhote Koshi flood affected families Nepalnews.com</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzRjWXo1WXdRbXUtZHJJOGRLQ21sd25FNHFNRmJlaXM3ckd1bEdobEZ1TFE0ZmxoNVhiQ0FzX0QycmVJcmIzMExpSDBaNHZVaW9VWXlmbzk0bmw5TTdPTm9PR3FfYmM3ekZJOE4wVWFRZEM1WVBBX24tb3MwdUpaV0pzM2E3YjZORFl5UHRDa2RCU0VLQWV0dU50TGI3TW1MMDNuWnpQREk0UGd0TzNVYVE4Wng3dmprTnZNTHFBd2FxV25USXZj?oc=5</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="99" ht="48" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>599e39e4bd45cec7</t>
+          <t>9b19a739b91a113a</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -5517,22 +5517,22 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood - Ratopati</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - Ratopati</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Ratopati</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage Ratopati</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>895a2cd3bab3daaf</t>
+          <t>599e39e4bd45cec7</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
@@ -5559,32 +5559,32 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T20:31:43Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood - Ratopati</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Ratopati</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="101" ht="48" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>b2f3f0d35363b27e</t>
+          <t>895a2cd3bab3daaf</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -5611,32 +5611,32 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-09-12T20:31:43Z</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>DNA Testing Underway for Bhote Koshi Flood Victims - Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>DNA Testing Underway for Bhote Koshi Flood Victims Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMmJzNjU3UnMwd0VLd01PdWp6RHg0bmhFZ3RpcFAzTE5GQl9CU0RrSUFaVzhzSW9EbW10RVdzLWFXMW5vdDl5cENCNTRjZVZ6cGNhaFdzQ3FvVlVYZ19yaHVCRk8wQk8tZnRxdDhDUHltdUt3bHNjNlhSS1lrYnhkUFRzdE5uVlJhUDFQTGxySHpoQ1JCVDRRZld6aXVaWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxPMmJzNjU3UnMwd0VLd01PdWp6RHg0bmhFZ3RpcFAzTE5GQl9CU0RrSUFaVzhzSW9EbW10RVdzLWFXMW5vdDl5cENCNTRjZVZ6cGNhaFdzQ3FvVlVYZ19yaHVCRk8wQk8tZnRxdDhDUHltdUt3bHNjNlhSS1lrYnhkUFRzdE5uVlJhUDFQTGxySHpoQ1JCVDRRZld6aXVaWGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="102" ht="48" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>b15a4ac14f51f39e</t>
+          <t>b2f3f0d35363b27e</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -5663,32 +5663,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,384 as search and rescue operations continue - Nepalnews.com</t>
+          <t>DNA Testing Underway for Bhote Koshi Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,384 as search and rescue operations continue Nepalnews.com</t>
+          <t>DNA Testing Underway for Bhote Koshi Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPVlhfS1l3NWR0dGtTdjVQN3Y4T1liZ3pDYTI0bS1oOHR1a0xRQldBbFBMdHR2T1VROXhCMEZmeXBCamdvd1gxMnVYTjF6RnkxaG51ZkFZWnVmeW0xU29JMjluWnJDRmtVOXcxS3pXb1NlVUlfRE11dHU3Z0o3OWdnZnJuTnVwbzhNRmZiNm14Vm1PS1FlTnNURThEbFBMN3RBTWp2QUpwaklrN0VSbWMwVlB2Uk04c0xCWjZzN3o3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMmJzNjU3UnMwd0VLd01PdWp6RHg0bmhFZ3RpcFAzTE5GQl9CU0RrSUFaVzhzSW9EbW10RVdzLWFXMW5vdDl5cENCNTRjZVZ6cGNhaFdzQ3FvVlVYZ19yaHVCRk8wQk8tZnRxdDhDUHltdUt3bHNjNlhSS1lrYnhkUFRzdE5uVlJhUDFQTGxySHpoQ1JCVDRRZld6aXVaWGc?oc=5</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPVlhfS1l3NWR0dGtTdjVQN3Y4T1liZ3pDYTI0bS1oOHR1a0xRQldBbFBMdHR2T1VROXhCMEZmeXBCamdvd1gxMnVYTjF6RnkxaG51ZkFZWnVmeW0xU29JMjluWnJDRmtVOXcxS3pXb1NlVUlfRE11dHU3Z0o3OWdnZnJuTnVwbzhNRmZiNm14Vm1PS1FlTnNURThEbFBMN3RBTWp2QUpwaklrN0VSbWMwVlB2Uk04c0xCWjZzN3o3SQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxPMmJzNjU3UnMwd0VLd01PdWp6RHg0bmhFZ3RpcFAzTE5GQl9CU0RrSUFaVzhzSW9EbW10RVdzLWFXMW5vdDl5cENCNTRjZVZ6cGNhaFdzQ3FvVlVYZ19yaHVCRk8wQk8tZnRxdDhDUHltdUt3bHNjNlhSS1lrYnhkUFRzdE5uVlJhUDFQTGxySHpoQ1JCVDRRZld6aXVaWGc?oc=5</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="103" ht="48" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>ff75d7063b59861e</t>
+          <t>b15a4ac14f51f39e</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -5715,32 +5715,32 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,386 Bodies Found - Ekantipur</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,384 as search and rescue operations continue - Nepalnews.com</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,386 Bodies Found Ekantipur</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,384 as search and rescue operations continue Nepalnews.com</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPVlhfS1l3NWR0dGtTdjVQN3Y4T1liZ3pDYTI0bS1oOHR1a0xRQldBbFBMdHR2T1VROXhCMEZmeXBCamdvd1gxMnVYTjF6RnkxaG51ZkFZWnVmeW0xU29JMjluWnJDRmtVOXcxS3pXb1NlVUlfRE11dHU3Z0o3OWdnZnJuTnVwbzhNRmZiNm14Vm1PS1FlTnNURThEbFBMN3RBTWp2QUpwaklrN0VSbWMwVlB2Uk04c0xCWjZzN3o3SQ?oc=5</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPVlhfS1l3NWR0dGtTdjVQN3Y4T1liZ3pDYTI0bS1oOHR1a0xRQldBbFBMdHR2T1VROXhCMEZmeXBCamdvd1gxMnVYTjF6RnkxaG51ZkFZWnVmeW0xU29JMjluWnJDRmtVOXcxS3pXb1NlVUlfRE11dHU3Z0o3OWdnZnJuTnVwbzhNRmZiNm14Vm1PS1FlTnNURThEbFBMN3RBTWp2QUpwaklrN0VSbWMwVlB2Uk04c0xCWjZzN3o3SQ?oc=5</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -5757,42 +5757,42 @@
     <row r="104" ht="48" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>c128671407c846d2</t>
+          <t>ff75d7063b59861e</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: 1,386 Bodies Found - Ekantipur</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify Nepalnews.com</t>
+          <t>Bhotekoshi Flood: 1,386 Bodies Found Ekantipur</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMijwFBVV95cUxNNERqMDhDdDZERHViNTU5emNrMFRWOG9oTHJ2bngxMkNmVEFUZ1dTZUU2SlVIMER2ZjRqbUhZT3V4SjRYYXRtc052bU5FanNyNlQtbldRWTNMTjRDSDdUWnNlaEhLbXNrVkMyLXJISzZjaTJxWFhLb1htLTNRVFB6Tm5jSThOMFQxZXpXSlJ4aw?oc=5</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>410a103aaf7c4528</t>
+          <t>8e369d28dac1be4d</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -6027,32 +6027,32 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>b44663cde7bfcda6</t>
+          <t>ada55db68109e06e</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>af991dce59e57aa5</t>
+          <t>410a103aaf7c4528</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>85987c70074e39ad</t>
+          <t>af991dce59e57aa5</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxObmlPbEI4LUh1NzlRSVR5Y0s4di0wVzlfTEZpMHRrRjF5V25oNjU3NnFNMzV2VEltZHpuNVBQTXJEWVdubUpTU1QxOTNJZmg4X3ZCcHdlRFdtU0RnX1Z3d0ZBUU93QmVYNzY2LVpSNVdVWlJLcFprNzVuNTBETGlwNVVqanNzck50c21UMlVJRVFjMnhkRXBaeFpLeVlraVVlWnNSSmJZbE9uUmJLaXl6MmNFT1ZuVy0xLWtqMVI4ZXJ3RDBidUsw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="145" ht="48" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>eee0dd2411bff598</t>
+          <t>2a300e5247974c0e</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T16:55:33Z</t>
+          <t>2026-09-23T11:32:09Z</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7941,42 +7941,42 @@
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>2a300e5247974c0e</t>
+          <t>c25c8930bdcedd55</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T11:32:09Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -7993,7 +7993,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>c25c8930bdcedd55</t>
+          <t>fd633a6a2a2a1810</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-09-21T04:52:28Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>fd633a6a2a2a1810</t>
+          <t>3d1620d408627250</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T04:52:28Z</t>
+          <t>2026-09-22T00:04:58Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,42 +8097,42 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>3d1620d408627250</t>
+          <t>1a65df9c73c0c5f1</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T00:04:58Z</t>
+          <t>2026-09-27T05:15:51Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>1a65df9c73c0c5f1</t>
+          <t>f91e5ab1620e5293</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T05:15:51Z</t>
+          <t>2026-10-04T18:38:31Z</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
+          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
+          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="151" ht="48" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>f91e5ab1620e5293</t>
+          <t>25275754a5c497fa</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -8211,32 +8211,32 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T18:38:31Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>25275754a5c497fa</t>
+          <t>09825b491361a412</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -8263,32 +8263,32 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8305,7 +8305,7 @@
     <row r="153" ht="48" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>09825b491361a412</t>
+          <t>535fbbf54d3b4684</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-27T16:56:20Z</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Khoj Samachar</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>535fbbf54d3b4684</t>
+          <t>10604521935094cd</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -8367,32 +8367,32 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T16:56:20Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Khoj Samachar</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="155" ht="48" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>10604521935094cd</t>
+          <t>6ec42694b67ab866</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -8419,32 +8419,32 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-09-20T20:47:03Z</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8461,42 +8461,42 @@
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>6ec42694b67ab866</t>
+          <t>bb5552718a993013</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T20:47:03Z</t>
+          <t>2026-09-28T13:50:00Z</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="157" ht="48" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>bb5552718a993013</t>
+          <t>c5054155e8d76e19</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T13:50:00Z</t>
+          <t>2026-09-19T15:51:25Z</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -8533,22 +8533,22 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>c5054155e8d76e19</t>
+          <t>4a782c7db12159fc</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -8575,32 +8575,32 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T15:51:25Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8617,42 +8617,42 @@
     <row r="159" ht="48" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>4a782c7db12159fc</t>
+          <t>cc153ab4c5f0bc02</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>cc153ab4c5f0bc02</t>
+          <t>26e0f34695ac0146</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -8679,32 +8679,32 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>26e0f34695ac0146</t>
+          <t>bf0bd71a8811a3de</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-09-18T16:22:29Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>bf0bd71a8811a3de</t>
+          <t>caa83d5807a4f588</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,32 +8783,32 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T16:22:29Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>caa83d5807a4f588</t>
+          <t>5aeddf14059c9769</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8835,32 +8835,32 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>chinachristiandaily.com</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>5aeddf14059c9769</t>
+          <t>81625d31ed27040d</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>chinachristiandaily.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>81625d31ed27040d</t>
+          <t>382aacee35c12bd2</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -8939,32 +8939,32 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
+          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
+          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>382aacee35c12bd2</t>
+          <t>c953c8abf57268ed</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -8991,32 +8991,32 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepali Patro</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>c953c8abf57268ed</t>
+          <t>11bd9764f90f4f0b</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Nepali Patro</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>11bd9764f90f4f0b</t>
+          <t>718a52966e5afa2e</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>718a52966e5afa2e</t>
+          <t>7c3d1c068a76eb4d</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9152,27 +9152,27 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Setopati</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,42 +9189,42 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>7c3d1c068a76eb4d</t>
+          <t>562a7c16c434d881</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Setopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds - myRepublica</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds myRepublica</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>562a7c16c434d881</t>
+          <t>a098d8aae7af06f0</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,32 +9251,32 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds - myRepublica</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds myRepublica</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>a098d8aae7af06f0</t>
+          <t>4199945559bb4c8e</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,32 +9303,32 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
+          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
+          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>4199945559bb4c8e</t>
+          <t>a3af223902597f26</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -9355,32 +9355,32 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>a3af223902597f26</t>
+          <t>035dc924f46d515d</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,42 +9449,42 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>035dc924f46d515d</t>
+          <t>07c99b7aeae28b29</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-10-04T12:19:26Z</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
+          <t>Rasuwa flood stole happiness: A forgotten festival - Nepalnews.com</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
+          <t>Rasuwa flood stole happiness: A forgotten festival Nepalnews.com</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>07c99b7aeae28b29</t>
+          <t>ddd57575c35c350d</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
@@ -9511,32 +9511,32 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival - Nepalnews.com</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival Nepalnews.com</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>ddd57575c35c350d</t>
+          <t>2c0a3b5d2befbf82</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
+          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
+          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>2c0a3b5d2befbf82</t>
+          <t>f391daeeca51bbbc</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T05:20:23Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -9625,22 +9625,22 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -9657,7 +9657,7 @@
     <row r="179" ht="48" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>f391daeeca51bbbc</t>
+          <t>751a0e165234bde9</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>hariyalinepal.com</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>751a0e165234bde9</t>
+          <t>9ab27519f391ac8a</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -9719,32 +9719,32 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-16T04:46:36Z</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>hariyalinepal.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -9761,42 +9761,42 @@
     <row r="181" ht="48" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>9ab27519f391ac8a</t>
+          <t>355ca1951767eb7e</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T04:46:36Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -9813,7 +9813,7 @@
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>5550c86ea2eb32e9</t>
+          <t>7c8af6b0d120695d</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
@@ -9823,32 +9823,32 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="183" ht="48" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>355ca1951767eb7e</t>
+          <t>2ff03089e15253df</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -9875,32 +9875,32 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>7c8af6b0d120695d</t>
+          <t>b933797459c3a582</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
@@ -9927,32 +9927,32 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="185" ht="48" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>2ff03089e15253df</t>
+          <t>97b6fb8c1bbdde22</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>english.khabarhub.com</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>b933797459c3a582</t>
+          <t>38b94bc7bc5df2f9</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -10031,32 +10031,32 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myRepublica</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
+          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myRepublica</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="187" ht="48" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>97b6fb8c1bbdde22</t>
+          <t>c0bc6670e36c05ca</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -10083,32 +10083,32 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
+          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood - Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
+          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood Ministry Of Foreign Affairs</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
         </is>
       </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>38b94bc7bc5df2f9</t>
+          <t>62d5c38304aa356a</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
@@ -10140,27 +10140,27 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction - myRepublica</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>The Hard Questions of Post-Bhote Koshi Flood Reconstruction myRepublica</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxOZkpOZnVnMlBDZk9MSWtDZlIwTTg2MlZBci1GbTlUTjZwd2VxTzBobnNPS2pZQzc0bnY5ZEp3bHNPeXl2X3BMZE9yamNHTWQ5dDAxUS1vOHMzWm1nNFZvc21CNk5ZTUo4LUE2VnRydV81NVcxRmVNVWg1b2dVbTRsMjBXa3RpWVJTdTIzdzZUb0VnVlM0Ymh3QTBTcWoxMGEwY2RfS2dYOUZUNC1vU2F4T1BrUGU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
     <row r="189" ht="48" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>c0bc6670e36c05ca</t>
+          <t>71f08f0e90525437</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -10192,27 +10192,27 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Ministry Of Foreign Affairs</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood - Ministry Of Foreign Affairs</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Press Briefing Note by Hon. Minister for Foreign Affairs on Bhote Koshi Flood Ministry Of Foreign Affairs</t>
+          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZkFVX3lxTFBEY29TQkhXazlibE5Ed1VYSUdWNVZpOG5TcFltLU5LNXo2UUtVMXFYdWJPb29KWC04VmJZaUxWZzZhSTd2aERRcUZOSDhvSHRaUmFnQzhjWFNkMkxwTEVDUWtXU0l3QQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>62d5c38304aa356a</t>
+          <t>038d44da2885beeb</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
@@ -10239,32 +10239,32 @@
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 - Khabarhub</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,395 Khabarhub</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93cUZBejFEbVNNVzFBUXpHT2FWLTVLSDlaV2U3LXN6a1NtcE5rWXFqOXVPYTBVMFRobWRHX0oxSjREMmtKV2hLLTJXMVdzb0JrYkpxcV9LRmo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -10281,42 +10281,42 @@
     <row r="191" ht="48" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>71f08f0e90525437</t>
+          <t>ca0bdec000f5c2c0</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood - radionepalonline.com</t>
+          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage - Ratopati</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>607 foreign tourists from 34 countries still missing after Bhotekoshi flood radionepalonline.com</t>
+          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage Ratopati</t>
         </is>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
         </is>
       </c>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzSS1zT0t5Y2dGd3o5Q01SMFNUdnJCUGo1S1IwWWFUZ0NhTXRoQnlkR1M2YjhOTERJc3JQMGlFZ21WNElDWVYzczZKSUhQOEFkeVZPYkN4YnZNT2RDc29QY09CQlY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -10333,42 +10333,42 @@
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>038d44da2885beeb</t>
+          <t>7ac46d8fe1e78a5e</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood dampens Teej celebrations - The Rising Nepal</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood dampens Teej celebrations The Rising Nepal</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
         </is>
       </c>
       <c r="H192" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="193" ht="48" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>ca0bdec000f5c2c0</t>
+          <t>167458bbff2621be</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -10395,32 +10395,32 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage - Ratopati</t>
+          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage Ratopati</t>
+          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
         </is>
       </c>
       <c r="H193" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -10437,7 +10437,7 @@
     <row r="194" ht="48" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>7ac46d8fe1e78a5e</t>
+          <t>1db4b46680067f6b</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood dampens Teej celebrations - The Rising Nepal</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - Khabarhub</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood dampens Teej celebrations The Rising Nepal</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses Khabarhub</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
         </is>
       </c>
       <c r="H194" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBXa0ZCdDh6Z0d3a3N6dTRDZWRWTTMwRnNWcElQSEhrUlhRVDhRZW8xVV9UZkdtU1VocVhUME1ZSER4VGhSdWxiUTgxZkUxcFAx?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="195" ht="48" customHeight="1">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>167458bbff2621be</t>
+          <t>7901378bf0efe6dd</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post - UA.NEWS</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,390; over 4,000 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post UA.NEWS</t>
         </is>
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
         </is>
       </c>
       <c r="H195" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRjNyS3FLWXQzbW9vTUVxNmpNd1g3SUUwT2UtVlhYQXNmWE9TY29rWGVXbk9OcVNDMTM4RkNLOUpuRUhjR0xPc3RRLVVobkRtQU5VM0R0TEoyeVBhMHU0bzhPVmZQNGdUczZvX3VnRzF2NlA1ODNXRkVjNFpWTGM1SU00N1gyUTlqUmYwTm9WZGFCdW1jWmtPYmlUS2pMYWlzS0dKZGhYSVo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -10541,7 +10541,7 @@
     <row r="196" ht="48" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>1db4b46680067f6b</t>
+          <t>4f53e036a604bfe8</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
@@ -10551,32 +10551,32 @@
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - Khabarhub</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses Khabarhub</t>
+          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
         </is>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="H196" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFB0S3g3NlctSVNWcHZnQ2RkV3c4TVlqbFNKMERmRHI5dm96TVBWOWFuUlNZcWEwcEF6dzhmRXBrazBOdGVLQm8wdVRXWmZfVV9XTTVEZzZLeVc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -10593,7 +10593,7 @@
     <row r="197" ht="48" customHeight="1">
       <c r="A197" s="8" t="inlineStr">
         <is>
-          <t>7901378bf0efe6dd</t>
+          <t>0df7da2f9815834b</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
@@ -10603,32 +10603,32 @@
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post - UA.NEWS</t>
+          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood in Nepal complicates access to hospitals — Kathmandu Post UA.NEWS</t>
+          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
         </is>
       </c>
       <c r="H197" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxOaVZmblVncHBqZzhld3EwbXA5VVE2RzdqWEdSRDJfZDZvQ0daWnVjaEJxRGpNS3ZxYmRuN0RUZlVGVzRBbGFyRTRzSXhKV2pHdmlQUXdEd05abElYRGtid2Vadk9Zc0dlb2p2NktmaS13dFpJeDZuTVVSY2tLZEd4c041Vk1IcXM2dHJHTE9oVGdtS0pQcUZRZDRhSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -10645,7 +10645,7 @@
     <row r="198" ht="48" customHeight="1">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>4f53e036a604bfe8</t>
+          <t>59b055075d559d93</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
@@ -10655,32 +10655,32 @@
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>myrepublica.nagariknetwork.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses - myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood death toll rises to 1,392 - Khabarhub</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood causes over Rs 1 billion in agricultural losses myrepublica.nagariknetwork.com</t>
+          <t>Bhotekoshi flood death toll rises to 1,392 Khabarhub</t>
         </is>
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
         </is>
       </c>
       <c r="H198" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeHlOTHM0Q3gwMW9DQXZwVFF4V2xGczVFUk9Qb1BvdFNzSVNRMHR2WlZXSlNobnk3Wm94RXhwZnBfd1JmUzVEc0FseGQwX3p5ZGdQSzl5c0dlVHRaTXRod0xpUTBHX1FUUlhldG9PNlpHSFRIcEYyb3UxeVI5clJRNEFGSHNPdUFncEtRZjJEOHNmX1R2V0JvM2dLRG9ZQzloZF9GY0RFQl9MWkk1ZTZ0R3ZoX2FmdHl2aGJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="199" ht="48" customHeight="1">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>0df7da2f9815834b</t>
+          <t>353f4e432ea55d9d</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
@@ -10707,32 +10707,32 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-14T12:42:21Z</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood - myRepublica</t>
+          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly - The Rising Nepal</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Disaster relief fund swells to Rs 13.58 billion after Bhotekoshi flood myRepublica</t>
+          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly The Rising Nepal</t>
         </is>
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
         </is>
       </c>
       <c r="H199" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXVjZVZWTzgwZTNfYnBBMlg2NEl5UzZkNkdzUTVHU2NzNHdMQVpSNkJ5QWNEcU5QR09zVnlib2t2ZVFlQUFVWFpWQ1ZpYUdVZ3FfdXB0TGpETXBDUUtUamtEZlhvZjh5a1VsWFNFSjRQOWdELUUxOFhla2syM0VwcGF4V3AtQVpzZEl4MzVfNWZTTUFhUmp0Szdwbk5DNjVYQXBwYXJtRnJoNmU2bFF4WTVwOVBSUVdWRGoxOTdhT0xOZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -10749,42 +10749,42 @@
     <row r="200" ht="48" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>59b055075d559d93</t>
+          <t>fbacf2163aebfd9e</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll rises to 1,392 - Khabarhub</t>
+          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance - Ekantipur</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll rises to 1,392 Khabarhub</t>
+          <t>Bhotekoshi Flood: US Provides Nepal Police with $1 Million in Forensic Investigation Assistance Ekantipur</t>
         </is>
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
         </is>
       </c>
       <c r="H200" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1kSU5KaTVwbDl2U2s4TnhZc1VvaWpvSjRhaDVPQ01jYnVIZVZVbFdFM3lDSnIzcWNFb2llWU5kWTg1dGl3Ym5BZ3ZxbGZkN3phc2w0bEVZMF8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxQSTY3VjJmRFREcEpDbEd1bGlEUFlWSE1qMlNLVjgxa2FmcWo3blhjTHE5WFVxa25Sek0xS0JkSWtELW1XYldidDFtQkFfbVppYUJYNUU3S0YtbGxDUUM5SGtnRUduLXF6MVZfLVBiM2dROHBfQXdWR3lzTUJxZDc2ZU5mWkxJVGN4Sk9BdGs0VFcyOURPOUxqTG1xaXlNYkZmdks2akxwWldWX3pzNnFBQk9n?oc=5</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -10801,42 +10801,42 @@
     <row r="201" ht="48" customHeight="1">
       <c r="A201" s="8" t="inlineStr">
         <is>
-          <t>353f4e432ea55d9d</t>
+          <t>115ca238296d3ef7</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T12:42:21Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly - The Rising Nepal</t>
+          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million - Khabarhub</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood victim families to receive Rs. 15,000 monthly The Rising Nepal</t>
+          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million Khabarhub</t>
         </is>
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
         </is>
       </c>
       <c r="H201" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9Nc1BFU2xSVWZjYTVPZlF6eEFkeUZvWUJZSTdWMEZNanpCNW44YTRiekxzTFJkWm9pdWFFVXdqSmNHaHQ2UVhKdHM5Wnh4WXRN?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -10853,7 +10853,7 @@
     <row r="202" ht="48" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>115ca238296d3ef7</t>
+          <t>7b8b40468e96ee9a</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
@@ -10863,32 +10863,32 @@
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million - Khabarhub</t>
+          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. - Ekantipur</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood damages seven health institutions worth Rs 236.6 million Khabarhub</t>
+          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. Ekantipur</t>
         </is>
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
         </is>
       </c>
       <c r="H202" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBZOWFHRTRHYjdfU0R5WUtrTmJhMHZrOFZiblhHYUJSdzQtbFFYeVlkbzdrWkJfR2UwWnA1M3llNDJ1TWhxNGp4NzNUV1pUdFdicHNyOUZRaXY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="203" ht="48" customHeight="1">
       <c r="A203" s="8" t="inlineStr">
         <is>
-          <t>7b8b40468e96ee9a</t>
+          <t>11474096db19ba0e</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-10-04T05:49:20Z</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -10925,22 +10925,22 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. - Ekantipur</t>
+          <t>The Bhotekoshi Flood Reminds Us Once Again: Nepal Police and Armed Police Force Still Have No Helicopters - Ekantipur</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Following the Bhotekoshi flood, 77 Kailash pilgrims and three volunteers from the Isha Foundation are still missing. Ekantipur</t>
+          <t>The Bhotekoshi Flood Reminds Us Once Again: Nepal Police and Armed Police Force Still Have No Helicopters Ekantipur</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQZktuNmlaeWxOenZndXR5V0xtdjYyWFJXS0d5RlJVSDJ1QV96bHdDekNSYWZBT2JOMjFaQVJRUEZoV3QxVmN1cm95eUgtdFhmcmpwZzFzSWM2bV8wVjJvNEZseERLUmdKNkpMbjRZUkZXOWFpNjFiTUV1bEpETFNCQVJVcHREd2RBaThZdW9YRWZ4c3YtVTd5Uzk5eXowZWFSQzRNZWs4bXJzTlo5SXlONmtkdVhKcjg1RmxrTmpBY3NYTWZoMEdQWF9oVHBBQQ?oc=5</t>
         </is>
       </c>
       <c r="H203" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi4AFBVV95cUxQeTEwSTdJUVJoRTVZT1VmYmFIaktDcEFPbjNWdFk0aTFRX1NhOV9qaHlkd2lsVEdPX01PSmJrWWltVGIzUHRPWGpoc25rLWxDWUZScW1SeVktVmVWeVBhX1FYUnJLUE8xQXUtcm9PcW5JRHgxX3lBRjBpS0JSalRYR29HRHNVbzJLQTNBR2xLMGkwbmthVU5lMzhUc0JndmFiZGYxYzNPYzVUczdTSXBsUVhuYjR3S1FXUGQ2XzEwVG5JTWZwbXlpd1RHYzlMNlRqaGt3RUR3bTZ4Wmh4djJOWg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxQZktuNmlaeWxOenZndXR5V0xtdjYyWFJXS0d5RlJVSDJ1QV96bHdDekNSYWZBT2JOMjFaQVJRUEZoV3QxVmN1cm95eUgtdFhmcmpwZzFzSWM2bV8wVjJvNEZseERLUmdKNkpMbjRZUkZXOWFpNjFiTUV1bEpETFNCQVJVcHREd2RBaThZdW9YRWZ4c3YtVTd5Uzk5eXowZWFSQzRNZWs4bXJzTlo5SXlONmtkdVhKcjg1RmxrTmpBY3NYTWZoMEdQWF9oVHBBQQ?oc=5</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="204" ht="48" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>11474096db19ba0e</t>
+          <t>d8670c3b0d995ad2</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
@@ -10967,32 +10967,32 @@
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T05:49:20Z</t>
+          <t>2026-09-14T23:52:01Z</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>The Bhotekoshi Flood Reminds Us Once Again: Nepal Police and Armed Police Force Still Have No Helicopters - Ekantipur</t>
+          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing - myRepublica</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>The Bhotekoshi Flood Reminds Us Once Again: Nepal Police and Armed Police Force Still Have No Helicopters Ekantipur</t>
+          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing myRepublica</t>
         </is>
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQZktuNmlaeWxOenZndXR5V0xtdjYyWFJXS0d5RlJVSDJ1QV96bHdDekNSYWZBT2JOMjFaQVJRUEZoV3QxVmN1cm95eUgtdFhmcmpwZzFzSWM2bV8wVjJvNEZseERLUmdKNkpMbjRZUkZXOWFpNjFiTUV1bEpETFNCQVJVcHREd2RBaThZdW9YRWZ4c3YtVTd5Uzk5eXowZWFSQzRNZWs4bXJzTlo5SXlONmtkdVhKcjg1RmxrTmpBY3NYTWZoMEdQWF9oVHBBQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
         </is>
       </c>
       <c r="H204" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxQZktuNmlaeWxOenZndXR5V0xtdjYyWFJXS0d5RlJVSDJ1QV96bHdDekNSYWZBT2JOMjFaQVJRUEZoV3QxVmN1cm95eUgtdFhmcmpwZzFzSWM2bV8wVjJvNEZseERLUmdKNkpMbjRZUkZXOWFpNjFiTUV1bEpETFNCQVJVcHREd2RBaThZdW9YRWZ4c3YtVTd5Uzk5eXowZWFSQzRNZWs4bXJzTlo5SXlONmtkdVhKcjg1RmxrTmpBY3NYTWZoMEdQWF9oVHBBQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="205" ht="48" customHeight="1">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>d8670c3b0d995ad2</t>
+          <t>03019cd0bb2d589e</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T23:52:01Z</t>
+          <t>2026-09-25T17:08:24Z</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -11029,22 +11029,22 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing - myRepublica</t>
+          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,390 bodies recovered, 4,089 still missing myRepublica</t>
+          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
         </is>
       </c>
       <c r="H205" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxPdW9BYXg1dllFNXk4RkxyU3dkMjExdEg5VmF0VHVqT3AzZnRRS1ZtRTFRQTZIcmdPSVN6SDloajNjY2duTEd6OFVpWElYZzEyV2lMNXI3X0lySXNnNnRLUzd3d25YY3pienh5Q1cyNkhRbzJoYXphY2c1SDFLQjFJU1pTazN1b1BzRl9vQzJ6ZXU5UkdhMFA3SV9paERsc2pZOVhPdDBHeDNWRzhYVldTeHZR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="206" ht="48" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>03019cd0bb2d589e</t>
+          <t>67b5a6753c351977</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T17:08:24Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -11081,22 +11081,22 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood - myRepublica</t>
+          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>641 EVs enter Nepal via Korala in two weeks after Bhotekoshi flood myRepublica</t>
+          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
         </is>
       </c>
       <c r="H206" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNU2hBb250dW00Y1kwNUVWZGpxUEZOVGs2cHZDV2dWR2dDOFBfQVhTVlYzZ2FBVjdtc25BNVZoSHZ3U3ozWmFQajVyRllYcTV2OGF5U0c0LS1hd3hJSnNmclkwVXl3TkI2aWxLbVFNTFRaYmhpRndVMThUUDdUck5wYUdXYUtVYlMyS29zZFd6dkFXOHYtd2tpcXU4SnpkZlZXTVdKN015THIzVW9aU2hCbFpFUUx0cDk0bnEtV2JB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="207" ht="48" customHeight="1">
       <c r="A207" s="8" t="inlineStr">
         <is>
-          <t>67b5a6753c351977</t>
+          <t>74b200acb9b39a43</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
@@ -11123,32 +11123,32 @@
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-13T11:48:33Z</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims - myRepublica</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Govt to provide up to Rs 15,000 monthly housing allowance to Bhotekoshi flood victims myRepublica</t>
+          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
         </is>
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="H207" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPelUzLU9fbXM0cnlrQkJXR0w3ZWlrMTdKTWVZY3ZhRVcwZFZpRElmWktwS2dZakVCci1rQXJRQkN2d0gyTmNMcGFPLXNFWWNHUXlnVW92VUczQ0VUaTNrbjNWUTBJd0NVbDJRQWxUYUdteEZkb01TeExWLUhkTWNvVnlZcDFTM3BtSHJOYmE3SS15ZVZnZ194WVhpejVpRnNCT2I1My03MS1uNjE4Q0pVU1hPd2hYWWdEc3BvMlhGcGp6cXl0ZWpOblpR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -11165,42 +11165,42 @@
     <row r="208" ht="48" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>74b200acb9b39a43</t>
+          <t>52872a4049999b34</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>2026-09-13T11:48:33Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts - Khabarhub</t>
+          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked - Ekantipur</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 18 schools across three districts Khabarhub</t>
+          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked Ekantipur</t>
         </is>
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
         </is>
       </c>
       <c r="H208" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBIMHEtSUpXRGRjcGtXVm14ZFYzRGNET1ItV182YjhBYXd4VUhSS3g2RFROWTg5bUw4ZjFGUmNoUTlYeXdzZExfWVlJTnhpT0dVWGg0SFJhaTU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -11217,7 +11217,7 @@
     <row r="209" ht="48" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>52872a4049999b34</t>
+          <t>d8f4f558107297e7</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
@@ -11227,32 +11227,32 @@
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked - Ekantipur</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Main Highway in Rasuwa Still Completely Blocked Ekantipur</t>
+          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
         </is>
       </c>
       <c r="H209" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTFA0ODQ3eEJDOGxiRmVDSVNReC1YY2p3MHFFZ1ByeUZ1OFczLU42NWIwdkc4Tk1PSmhMZWFMZTRGOW0tMHF3c1JWUVRfNHRSOHlFRzhYTU4xU2czeDR1UV9XXzhYVm9BNEZ4ZHJMYVJkR3g?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -11269,7 +11269,7 @@
     <row r="210" ht="48" customHeight="1">
       <c r="A210" s="8" t="inlineStr">
         <is>
-          <t>d8f4f558107297e7</t>
+          <t>b24ad7ca0530ad59</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
@@ -11284,27 +11284,27 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing - myRepublica</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 1,386, over 4,000 remain missing myRepublica</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
         </is>
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="H210" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRFJZZFhNdTNVV3pYWWRTMFctWlRNV3BRQ09wWXBqMW5RRmJSeUdzMU5oc2FOX1o3RmdNcGo1WFdFLXM5YlgzdEtBOFJrdGVpZTFuekhmX3lVblFfWjJxU3dOTlhka0N0Vk1DYmVrdDZ6aFlQbGI4ZllGc3ZBSDA2Z3ViN3NOM01fTHJWd0xNVzVwYjRlaEdMdV9uSFlGa1R0UF9SR1hzNHpSelA3cFdKblJGTjhLdjVJeGpBWnFqemxyVXc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -11321,42 +11321,42 @@
     <row r="211" ht="48" customHeight="1">
       <c r="A211" s="8" t="inlineStr">
         <is>
-          <t>b24ad7ca0530ad59</t>
+          <t>c128671407c846d2</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify - Nepalnews.com</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,385 as rescue operations intensify Nepalnews.com</t>
         </is>
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
         </is>
       </c>
       <c r="H211" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxObTFxaE5vM2Y0dTQ1RTV3aFNfRmRRVjh2QnJfODhGbnl2YUZrNEhpd1NhcFk0TWl0XzFSdEk1ckE0S2IyZE03NS1xVTlSNHJ5NHpYaVZ3ZDdDcFhodlgzWEczWWt2Z2FhRkJlSl9kYzA5bG1iT0pkeGx1Njk0N1RLRHlXVFhlczQ2ZjVVQTJ3enVlRW5ZSERGSzBJRjh3eXd2YUdxLThsQXdncGpkaS1ITHJn?oc=5</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12T21:15:18Z</t>
+          <t>2026-10-13T02:35:01Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-12T21:15:18Z · 847 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-13T02:35:01Z · 847 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ea90ccbaf00b6f3a</t>
+          <t>11efb1b5283d4658</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -728,27 +728,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing - Ratopati</t>
+          <t>269 children lost their parents in the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing Ratopati</t>
+          <t>269 children lost their parents in the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -765,42 +765,42 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>356ab3a0efc73abe</t>
+          <t>ea90ccbaf00b6f3a</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing - Ratopati</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>1,457 Dead in Bhote Koshi Flood, 4,720 Missing Ratopati</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxONXY0S3JsM1RmLUJyb0tRM2dPSzk4REZSYjFaQ3cwS1JHakUyanNyUENvbGFmMlV2SFh5RGtqYnhJSnhydERWei1FUFB0d1ZlWUhIRllrd2pKbWVBdTBoWHBXUUpESW0yeDdZeUtCaUFWQnV3aHNVX1B4Tmo4Vnk5S3hlNEFtMEhobGRtWXhBQ2k?oc=5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>a1c1bf932fb5fd38</t>
+          <t>356ab3a0efc73abe</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -827,32 +827,32 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT0gFcQVVfeXFMTmpOQWJzM3ZLWUtPNWpHTzhXbmFybFF4RGl6WnAxb3dPNFlKMlVlN1RJcUpDVzVYcW1xeHlMWTBha1IyaTdRRXVKTzJ2dHhaYWxldjlwa1JuQTRPeVQ?oc=5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ada55db68109e06e</t>
+          <t>af991dce59e57aa5</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -889,22 +889,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -921,42 +921,42 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>93bc198ad99eb753</t>
+          <t>ada55db68109e06e</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T18:49:52Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction - The Kathmandu Post</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction The Kathmandu Post</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -973,42 +973,42 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>162caaf3e8c44aad</t>
+          <t>93bc198ad99eb753</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T00:58:35Z</t>
+          <t>2026-10-08T18:49:52Z</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>The Climate Watch</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa - The Climate Watch</t>
+          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa The Climate Watch</t>
+          <t>Bagmati province seeks Rs1 billion for Bhotekoshi flood reconstruction The Kathmandu Post</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNcnlxeXRPRFJ3Wm53ZTlveERuZlUtdHYzMGJrZG84cE1YSGpEYkRBMjhZVGxsWU5JWGoyMHpRNjhNdXpUZDBuVUJhclNvcHB0eGcyRWVPdG9lQmI1bFBVZ3pJd0hrdnN2aUJsQ0drMzB6a1dVYllaZ2piTFJrdTlxQ2FJZVRVQ2hMalRlR2l5ZW54SDh4T19ybmwtR2JIdHZXT1o1akxTVVFnZ2c2SElsbXpRaURTVWs?oc=5</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>9bd2494473a30589</t>
+          <t>162caaf3e8c44aad</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T00:31:04Z</t>
+          <t>2026-10-08T00:58:35Z</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Climate Watch</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>NDRRMA seeks proposals to build temporary housings for Bhote Koshi flood-hit families - Nepalnews.com</t>
+          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa - The Climate Watch</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>NDRRMA seeks proposals to build temporary housings for Bhote Koshi flood-hit families Nepalnews.com</t>
+          <t>Relief materials sent to Bhotekoshi flood victims in Rasuwa The Climate Watch</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYkMyNlowRmdBa19TNEJjYXg3bkFjQjFMaTJzdy1RXzVyQmEzMEdzSnlBZEtQLVRZYjdfMHVfSUNFTzNuZE04NzV3Tjgxc3RVN2V4U0JlN0pyUmZFUGl3b0dmQWdtXy12eUx5SG9vUFRIVWlia2UtYzBFaDlZdElBc1p6OFEzMGp0cGRKbVQybS1ZTVVUTUt3STV1OFh3aGdkMEdmTW9BNlBIVnNHeTVVVmZVdFdFUGhUaHRLNHdQZVBUa2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYkMyNlowRmdBa19TNEJjYXg3bkFjQjFMaTJzdy1RXzVyQmEzMEdzSnlBZEtQLVRZYjdfMHVfSUNFTzNuZE04NzV3Tjgxc3RVN2V4U0JlN0pyUmZFUGl3b0dmQWdtXy12eUx5SG9vUFRIVWlia2UtYzBFaDlZdElBc1p6OFEzMGp0cGRKbVQybS1ZTVVUTUt3STV1OFh3aGdkMEdmTW9BNlBIVnNHeTVVVmZVdFdFUGhUaHRLNHdQZVBUa2s?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxOT2dqZUs4ZXdfQWRUSExoTm5iWGdJWEsxS2RLRENuU0w1M3dLNHZsREphdmJwcDN1SmZLWHAtSDZVTWItcGhaY1BhWUg1cG5qcnhEN1pDRDJhVWwzQkdkY0ZRbXJXejh5c2xxZXdOUjByZHJZcWpoZmZNQ0pPRWI3OGJlcHdIZ1ZaQ0hjMzJHaFg5UQ?oc=5</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>8f5026d4b74c2e76</t>
+          <t>9bd2494473a30589</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1087,32 +1087,32 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-12T00:31:04Z</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
+          <t>NDRRMA seeks proposals to build temporary housings for Bhote Koshi flood-hit families - Nepalnews.com</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
+          <t>NDRRMA seeks proposals to build temporary housings for Bhote Koshi flood-hit families Nepalnews.com</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYkMyNlowRmdBa19TNEJjYXg3bkFjQjFMaTJzdy1RXzVyQmEzMEdzSnlBZEtQLVRZYjdfMHVfSUNFTzNuZE04NzV3Tjgxc3RVN2V4U0JlN0pyUmZFUGl3b0dmQWdtXy12eUx5SG9vUFRIVWlia2UtYzBFaDlZdElBc1p6OFEzMGp0cGRKbVQybS1ZTVVUTUt3STV1OFh3aGdkMEdmTW9BNlBIVnNHeTVVVmZVdFdFUGhUaHRLNHdQZVBUa2s?oc=5</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYkMyNlowRmdBa19TNEJjYXg3bkFjQjFMaTJzdy1RXzVyQmEzMEdzSnlBZEtQLVRZYjdfMHVfSUNFTzNuZE04NzV3Tjgxc3RVN2V4U0JlN0pyUmZFUGl3b0dmQWdtXy12eUx5SG9vUFRIVWlia2UtYzBFaDlZdElBc1p6OFEzMGp0cGRKbVQybS1ZTVVUTUt3STV1OFh3aGdkMEdmTW9BNlBIVnNHeTVVVmZVdFdFUGhUaHRLNHdQZVBUa2s?oc=5</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>902d716c8ffa7987</t>
+          <t>8f5026d4b74c2e76</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1139,32 +1139,32 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T18:56:09Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Devdiscourse</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1181,42 +1181,42 @@
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>10084f79d062af80</t>
+          <t>902d716c8ffa7987</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-07T18:56:09Z</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>a5a4dd9e93872116</t>
+          <t>6974acfd82237ba0</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T00:40:33Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Projected to Slow Following Devastating Rasuwa Flood - World Bank Group</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Projected to Slow Following Devastating Rasuwa Flood World Bank Group</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNb0NVeldyV3VHTDBWaGxhWlJ3ei1oZExSejNvZTIzdzZUdEQyTENXeWF3MnpZdEtVVjJ4QVk2andqbGxOQW9IWWJCTS1wLUd3bG44SVh2TmtqTFpqSE1IQXV1OXRoVDVfSDg3Rlc1UnNLaXJnMXFuV29QeDF4dlRRcUtnd2lMNGN3Wm9idWtEb0xxUkRlSzVFUm5mVXlxanVaendFS01pWTFLNUx3clV4V3pFb0sxdGVycEVjVXpJYXZ2S1VV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNb0NVeldyV3VHTDBWaGxhWlJ3ei1oZExSejNvZTIzdzZUdEQyTENXeWF3MnpZdEtVVjJ4QVk2andqbGxOQW9IWWJCTS1wLUd3bG44SVh2TmtqTFpqSE1IQXV1OXRoVDVfSDg3Rlc1UnNLaXJnMXFuV29QeDF4dlRRcUtnd2lMNGN3Wm9idWtEb0xxUkRlSzVFUm5mVXlxanVaendFS01pWTFLNUx3clV4V3pFb0sxdGVycEVjVXpJYXZ2S1VV?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>ead0ab018856c3cb</t>
+          <t>cf90c325291d2551</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1295,32 +1295,32 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T22:00:24Z</t>
+          <t>2026-10-06T20:17:26Z</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Victims Lament Government Neglect 40 Days Later - Ratopati</t>
+          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Victims Lament Government Neglect 40 Days Later Ratopati</t>
+          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood The Kathmandu Post</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNUg1Y2w4NWhuOElYakh0ZDViaGd3V2VEeXJyOXQteE1iejdIdy1XQno3QlVkaTVIUk1ocU1zX3Y2M0RqM1VXSW5wVmhOSW5NQl9xazFWQlctSVpKRDE4ZFJvcHpkUndmUmZEenZIb0Vvdy1OWDN2RDQ0YVpnWVNZVGpyTnI2V1hjZzhTb2E1ZGVCam9RdEcyanlkSEdNX1RhNmptdy1yOG85aHk1TXlVVVNhM0kzeDVQUC14NlRObGZRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNUg1Y2w4NWhuOElYakh0ZDViaGd3V2VEeXJyOXQteE1iejdIdy1XQno3QlVkaTVIUk1ocU1zX3Y2M0RqM1VXSW5wVmhOSW5NQl9xazFWQlctSVpKRDE4ZFJvcHpkUndmUmZEenZIb0Vvdy1OWDN2RDQ0YVpnWVNZVGpyTnI2V1hjZzhTb2E1ZGVCam9RdEcyanlkSEdNX1RhNmptdy1yOG85aHk1TXlVVVNhM0kzeDVQUC14NlRObGZRUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1337,42 +1337,42 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>581be780bb79f3b7</t>
+          <t>10084f79d062af80</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T14:32:40Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Progressive International</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOekZGRHZfTE02d2xwRFBWZU9uQW93RUR5bC1DX2tWTFNsemREdkhGam53cmdBVFg3YzNJbW8tc21VTmJLLUdoYW5WMlVmRWp2bDVRRm9kVTM3NVBGNjNRMmFEWU5GX1NoNE1LZlozQjI0TXBnS3BvODVzZ1VTaEhic1FxZ01FUWtsejdmTm9QVHVyLVMyNHJ0a0lqbVhQakFCa0lnVi1QNkczMDduams0QkJFSlpEMzhqVDRqTHZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOekZGRHZfTE02d2xwRFBWZU9uQW93RUR5bC1DX2tWTFNsemREdkhGam53cmdBVFg3YzNJbW8tc21VTmJLLUdoYW5WMlVmRWp2bDVRRm9kVTM3NVBGNjNRMmFEWU5GX1NoNE1LZlozQjI0TXBnS3BvODVzZ1VTaEhic1FxZ01FUWtsejdmTm9QVHVyLVMyNHJ0a0lqbVhQakFCa0lnVi1QNkczMDduams0QkJFSlpEMzhqVDRqTHZ3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3Y?oc=5</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1389,42 +1389,42 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>e5ce7b893fae78cc</t>
+          <t>a5a4dd9e93872116</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-10-07T00:40:33Z</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
+          <t>Nepal’s Growth Projected to Slow Following Devastating Rasuwa Flood - World Bank Group</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
+          <t>Nepal’s Growth Projected to Slow Following Devastating Rasuwa Flood World Bank Group</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQQ3BoMkNvLUZlcUt5VzBTVFVPWktaazVVaU1fcm5WVDVsOHVnTDlvSzk1bWwyVnZHYXRQcy1EN0VqVlZ3Z2lnM0p0OXFKVVl2OU5oX04xLVVvUUJ2V2d1eEtPbFpRVXhUZGhBaklqeUFsOENnbmtOTHdYY2JGUlJETDdQQVJ4VjdrVG45SUQ0Q0R4cWVDbWxQMk8yVnRtSlN6TUFzVGExdV9PcHlrZUdwNnBmUnJ3Z0JpQXVRZk1LQTVCLWJ6RVBZeklZNDJBRkZjXzRFanRENjN2NWVlUFNSejF6aTlSUzhiOGZUQWpHSk05a3BOWE9B0gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNb0NVeldyV3VHTDBWaGxhWlJ3ei1oZExSejNvZTIzdzZUdEQyTENXeWF3MnpZdEtVVjJ4QVk2andqbGxOQW9IWWJCTS1wLUd3bG44SVh2TmtqTFpqSE1IQXV1OXRoVDVfSDg3Rlc1UnNLaXJnMXFuV29QeDF4dlRRcUtnd2lMNGN3Wm9idWtEb0xxUkRlSzVFUm5mVXlxanVaendFS01pWTFLNUx3clV4V3pFb0sxdGVycEVjVXpJYXZ2S1VV?oc=5</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9wFBVV95cUxQQ3BoMkNvLUZlcUt5VzBTVFVPWktaazVVaU1fcm5WVDVsOHVnTDlvSzk1bWwyVnZHYXRQcy1EN0VqVlZ3Z2lnM0p0OXFKVVl2OU5oX04xLVVvUUJ2V2d1eEtPbFpRVXhUZGhBaklqeUFsOENnbmtOTHdYY2JGUlJETDdQQVJ4VjdrVG45SUQ0Q0R4cWVDbWxQMk8yVnRtSlN6TUFzVGExdV9PcHlrZUdwNnBmUnJ3Z0JpQXVRZk1LQTVCLWJ6RVBZeklZNDJBRkZjXzRFanRENjN2NWVlUFNSejF6aTlSUzhiOGZUQWpHSk05a3BOWE9B0gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNb0NVeldyV3VHTDBWaGxhWlJ3ei1oZExSejNvZTIzdzZUdEQyTENXeWF3MnpZdEtVVjJ4QVk2andqbGxOQW9IWWJCTS1wLUd3bG44SVh2TmtqTFpqSE1IQXV1OXRoVDVfSDg3Rlc1UnNLaXJnMXFuV29QeDF4dlRRcUtnd2lMNGN3Wm9idWtEb0xxUkRlSzVFUm5mVXlxanVaendFS01pWTFLNUx3clV4V3pFb0sxdGVycEVjVXpJYXZ2S1VV?oc=5</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>7670ab80881f6fec</t>
+          <t>ead0ab018856c3cb</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1456,27 +1456,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Congress raises over Rs 27.5 million for Bhotekoshi flood victims - OnlineKhabar English News</t>
+          <t>Bhote Koshi Flood Victims Lament Government Neglect 40 Days Later - Ratopati</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Congress raises over Rs 27.5 million for Bhotekoshi flood victims OnlineKhabar English News</t>
+          <t>Bhote Koshi Flood Victims Lament Government Neglect 40 Days Later Ratopati</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE01dmlPYUFTOXZOTnFFSGNlaG1LenFUQ0hESlRIUU9wVzc3c3hlOGVERzFfcjVlODJ1R2dveW5YclIyVE1qY2hvRmo2aFVSTUU1MFFlRDlxb2pKMnd4cEV3Tkp1czhmSFdmTlJGWTZPQzdVZXNE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNUg1Y2w4NWhuOElYakh0ZDViaGd3V2VEeXJyOXQteE1iejdIdy1XQno3QlVkaTVIUk1ocU1zX3Y2M0RqM1VXSW5wVmhOSW5NQl9xazFWQlctSVpKRDE4ZFJvcHpkUndmUmZEenZIb0Vvdy1OWDN2RDQ0YVpnWVNZVGpyTnI2V1hjZzhTb2E1ZGVCam9RdEcyanlkSEdNX1RhNmptdy1yOG85aHk1TXlVVVNhM0kzeDVQUC14NlRObGZRUQ?oc=5</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE01dmlPYUFTOXZOTnFFSGNlaG1LenFUQ0hESlRIUU9wVzc3c3hlOGVERzFfcjVlODJ1R2dveW5YclIyVE1qY2hvRmo2aFVSTUU1MFFlRDlxb2pKMnd4cEV3Tkp1czhmSFdmTlJGWTZPQzdVZXNE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNUg1Y2w4NWhuOElYakh0ZDViaGd3V2VEeXJyOXQteE1iejdIdy1XQno3QlVkaTVIUk1ocU1zX3Y2M0RqM1VXSW5wVmhOSW5NQl9xazFWQlctSVpKRDE4ZFJvcHpkUndmUmZEenZIb0Vvdy1OWDN2RDQ0YVpnWVNZVGpyTnI2V1hjZzhTb2E1ZGVCam9RdEcyanlkSEdNX1RhNmptdy1yOG85aHk1TXlVVVNhM0kzeDVQUC14NlRObGZRUQ?oc=5</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>f723c486e638fe1b</t>
+          <t>581be780bb79f3b7</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1503,32 +1503,32 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T22:00:24Z</t>
+          <t>2026-10-05T14:32:40Z</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ThePrint</t>
+          <t>Progressive International</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - ThePrint</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction ThePrint</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQY3FQeDBTSGhwTF9oc0MxX2J6WGFZTHRxWTkwVDk4T01XZExSYnJSbUxBNEFpY3dkYWptc2xUeW55VGRrQndjT1Y1Yy1GNlR6Uzc5MTAyaEZSbVFYNXNjQWx1UDl5SVFXT0hWV3RmeEpXRF8xUnpneTdCeEVTWlZ1ek9PX1hDSzVtdVZSVE14ZDRCd09VbVJka1RJcjk4SkcwZVJDZy1hUVBjaGV2elpxa3YybFZqQdIBuwFBVV95cUxOTnpGQ1c4TUdNbGFaUGFMUEI3U1Y4dngyWXViWXFBcm9BcEUtbFlCYUVjUFFVbzBSNEdZdWd4eGQ1WWlFcmhsN1NhaHU0U3g4VTd0SzM3bnJpWTJwa0VYX1hyeVJKaEtkRGJsMUFrUnIwR2NRd1hMdmprTlhnR3FtMkNxYlU4WDlWT0VieUJDd25iSTVaTDBpUGN4bGVkb2trM2VpU3kzbk8td2dJY2NBdTJWWlJnc1E4RW80?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOekZGRHZfTE02d2xwRFBWZU9uQW93RUR5bC1DX2tWTFNsemREdkhGam53cmdBVFg3YzNJbW8tc21VTmJLLUdoYW5WMlVmRWp2bDVRRm9kVTM3NVBGNjNRMmFEWU5GX1NoNE1LZlozQjI0TXBnS3BvODVzZ1VTaEhic1FxZ01FUWtsejdmTm9QVHVyLVMyNHJ0a0lqbVhQakFCa0lnVi1QNkczMDduams0QkJFSlpEMzhqVDRqTHZ3?oc=5</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQY3FQeDBTSGhwTF9oc0MxX2J6WGFZTHRxWTkwVDk4T01XZExSYnJSbUxBNEFpY3dkYWptc2xUeW55VGRrQndjT1Y1Yy1GNlR6Uzc5MTAyaEZSbVFYNXNjQWx1UDl5SVFXT0hWV3RmeEpXRF8xUnpneTdCeEVTWlZ1ek9PX1hDSzVtdVZSVE14ZDRCd09VbVJka1RJcjk4SkcwZVJDZy1hUVBjaGV2elpxa3YybFZqQdIBuwFBVV95cUxOTnpGQ1c4TUdNbGFaUGFMUEI3U1Y4dngyWXViWXFBcm9BcEUtbFlCYUVjUFFVbzBSNEdZdWd4eGQ1WWlFcmhsN1NhaHU0U3g4VTd0SzM3bnJpWTJwa0VYX1hyeVJKaEtkRGJsMUFrUnIwR2NRd1hMdmprTlhnR3FtMkNxYlU4WDlWT0VieUJDd25iSTVaTDBpUGN4bGVkb2trM2VpU3kzbk8td2dJY2NBdTJWWlJnc1E4RW80?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOekZGRHZfTE02d2xwRFBWZU9uQW93RUR5bC1DX2tWTFNsemREdkhGam53cmdBVFg3YzNJbW8tc21VTmJLLUdoYW5WMlVmRWp2bDVRRm9kVTM3NVBGNjNRMmFEWU5GX1NoNE1LZlozQjI0TXBnS3BvODVzZ1VTaEhic1FxZ01FUWtsejdmTm9QVHVyLVMyNHJ0a0lqbVhQakFCa0lnVi1QNkczMDduams0QkJFSlpEMzhqVDRqTHZ3?oc=5</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>23004b4b81bcb74f</t>
+          <t>e5ce7b893fae78cc</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T05:35:23Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Will the civil campaign inspired by the Bhotekoshi flood sustain itself? - myRepublica</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Will the civil campaign inspired by the Bhotekoshi flood sustain itself? myRepublica</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOUUdXVkIwQ1lzZ29VMWE5eU5kbnBDZ01JekdJVVBENzZwR0hadXBSbkk4SmNpRmlKV3U3RXpjQVBtWVZLUEJtMTAwcV96TExYVnU5T19iRmpFblVjRGxhaHFxWGhqZjRZelpWS0prMGROVnNxNmc4TUtBM0E3RFJkVE8xYm5SaFlZVEw4SDdGcHoxalM0QTlkYk0tS1lPMTdkRTJyNGZZaS1QQVpaUk1xaDVmbmI5SF9WU3RwTHRuX3A2WXlO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQQ3BoMkNvLUZlcUt5VzBTVFVPWktaazVVaU1fcm5WVDVsOHVnTDlvSzk1bWwyVnZHYXRQcy1EN0VqVlZ3Z2lnM0p0OXFKVVl2OU5oX04xLVVvUUJ2V2d1eEtPbFpRVXhUZGhBaklqeUFsOENnbmtOTHdYY2JGUlJETDdQQVJ4VjdrVG45SUQ0Q0R4cWVDbWxQMk8yVnRtSlN6TUFzVGExdV9PcHlrZUdwNnBmUnJ3Z0JpQXVRZk1LQTVCLWJ6RVBZeklZNDJBRkZjXzRFanRENjN2NWVlUFNSejF6aTlSUzhiOGZUQWpHSk05a3BOWE9B0gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOUUdXVkIwQ1lzZ29VMWE5eU5kbnBDZ01JekdJVVBENzZwR0hadXBSbkk4SmNpRmlKV3U3RXpjQVBtWVZLUEJtMTAwcV96TExYVnU5T19iRmpFblVjRGxhaHFxWGhqZjRZelpWS0prMGROVnNxNmc4TUtBM0E3RFJkVE8xYm5SaFlZVEw4SDdGcHoxalM0QTlkYk0tS1lPMTdkRTJyNGZZaS1QQVpaUk1xaDVmbmI5SF9WU3RwTHRuX3A2WXlO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9wFBVV95cUxQQ3BoMkNvLUZlcUt5VzBTVFVPWktaazVVaU1fcm5WVDVsOHVnTDlvSzk1bWwyVnZHYXRQcy1EN0VqVlZ3Z2lnM0p0OXFKVVl2OU5oX04xLVVvUUJ2V2d1eEtPbFpRVXhUZGhBaklqeUFsOENnbmtOTHdYY2JGUlJETDdQQVJ4VjdrVG45SUQ0Q0R4cWVDbWxQMk8yVnRtSlN6TUFzVGExdV9PcHlrZUdwNnBmUnJ3Z0JpQXVRZk1LQTVCLWJ6RVBZeklZNDJBRkZjXzRFanRENjN2NWVlUFNSejF6aTlSUzhiOGZUQWpHSk05a3BOWE9B0gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1597,42 +1597,42 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>32fb999ba596439f</t>
+          <t>7670ab80881f6fec</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T23:56:47Z</t>
+          <t>2026-10-05T22:00:24Z</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
+          <t>Congress raises over Rs 27.5 million for Bhotekoshi flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
+          <t>Congress raises over Rs 27.5 million for Bhotekoshi flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE01dmlPYUFTOXZOTnFFSGNlaG1LenFUQ0hESlRIUU9wVzc3c3hlOGVERzFfcjVlODJ1R2dveW5YclIyVE1qY2hvRmo2aFVSTUU1MFFlRDlxb2pKMnd4cEV3Tkp1czhmSFdmTlJGWTZPQzdVZXNE?oc=5</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE01dmlPYUFTOXZOTnFFSGNlaG1LenFUQ0hESlRIUU9wVzc3c3hlOGVERzFfcjVlODJ1R2dveW5YclIyVE1qY2hvRmo2aFVSTUU1MFFlRDlxb2pKMnd4cEV3Tkp1czhmSFdmTlJGWTZPQzdVZXNE?oc=5</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1649,42 +1649,42 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>f72b6aa392f3fd34</t>
+          <t>f723c486e638fe1b</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02T22:11:34Z</t>
+          <t>2026-10-05T22:00:24Z</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>ThePrint</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims - Ratopati</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - ThePrint</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims Ratopati</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction ThePrint</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQeGdaNzhKNk8wVXNEM3FfTHJjdkFMQ2ltRjhJa1NUUUVlUHE1QmFfTXNGdnF0OUhtOFZac0pkM0xDaC0xU0hnempaajVjY09qWXFua3M4MnZsWEtYWHhwYlo3ZUFKcjlMS1ZEdnZ6ay1MNlc4blNRUzBncV85aFlfcEZPN0NvOFdQSEI4SmctYnBqaEZDVTBidnR0U015cm9NMTBaZDk3Qy13RU1uMVRWT1pKeDhCLVB3QU1wdDZDQS1nMDhjOXZWQ1MtbjNHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQY3FQeDBTSGhwTF9oc0MxX2J6WGFZTHRxWTkwVDk4T01XZExSYnJSbUxBNEFpY3dkYWptc2xUeW55VGRrQndjT1Y1Yy1GNlR6Uzc5MTAyaEZSbVFYNXNjQWx1UDl5SVFXT0hWV3RmeEpXRF8xUnpneTdCeEVTWlZ1ek9PX1hDSzVtdVZSVE14ZDRCd09VbVJka1RJcjk4SkcwZVJDZy1hUVBjaGV2elpxa3YybFZqQdIBuwFBVV95cUxOTnpGQ1c4TUdNbGFaUGFMUEI3U1Y4dngyWXViWXFBcm9BcEUtbFlCYUVjUFFVbzBSNEdZdWd4eGQ1WWlFcmhsN1NhaHU0U3g4VTd0SzM3bnJpWTJwa0VYX1hyeVJKaEtkRGJsMUFrUnIwR2NRd1hMdmprTlhnR3FtMkNxYlU4WDlWT0VieUJDd25iSTVaTDBpUGN4bGVkb2trM2VpU3kzbk8td2dJY2NBdTJWWlJnc1E4RW80?oc=5</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxQeGdaNzhKNk8wVXNEM3FfTHJjdkFMQ2ltRjhJa1NUUUVlUHE1QmFfTXNGdnF0OUhtOFZac0pkM0xDaC0xU0hnempaajVjY09qWXFua3M4MnZsWEtYWHhwYlo3ZUFKcjlMS1ZEdnZ6ay1MNlc4blNRUzBncV85aFlfcEZPN0NvOFdQSEI4SmctYnBqaEZDVTBidnR0U015cm9NMTBaZDk3Qy13RU1uMVRWT1pKeDhCLVB3QU1wdDZDQS1nMDhjOXZWQ1MtbjNHdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxQY3FQeDBTSGhwTF9oc0MxX2J6WGFZTHRxWTkwVDk4T01XZExSYnJSbUxBNEFpY3dkYWptc2xUeW55VGRrQndjT1Y1Yy1GNlR6Uzc5MTAyaEZSbVFYNXNjQWx1UDl5SVFXT0hWV3RmeEpXRF8xUnpneTdCeEVTWlZ1ek9PX1hDSzVtdVZSVE14ZDRCd09VbVJka1RJcjk4SkcwZVJDZy1hUVBjaGV2elpxa3YybFZqQdIBuwFBVV95cUxOTnpGQ1c4TUdNbGFaUGFMUEI3U1Y4dngyWXViWXFBcm9BcEUtbFlCYUVjUFFVbzBSNEdZdWd4eGQ1WWlFcmhsN1NhaHU0U3g4VTd0SzM3bnJpWTJwa0VYX1hyeVJKaEtkRGJsMUFrUnIwR2NRd1hMdmprTlhnR3FtMkNxYlU4WDlWT0VieUJDd25iSTVaTDBpUGN4bGVkb2trM2VpU3kzbk8td2dJY2NBdTJWWlJnc1E4RW80?oc=5</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1701,42 +1701,42 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>1f474f3512d0099c</t>
+          <t>af2418e17dcf9378</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T00:40:33Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Press Trust of India</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days - myRepublica</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Press Trust of India</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days myRepublica</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Press Trust of India</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOckIycW1iR0VXRnFlRmlxRU5NUDFSYWVOei1yb1lGSnhIa0V4XzYzcTBFTlk4eE0zMFBBU0VCcE1yN1oxVXQ3N0VvZ2RlWlNhVFVtTjEzZUk2cEF5N0lrNkd3RFhhRFpOV1YtS0JsVmNiSHBGZXB2bEF6QjFhZTRPaTdrN0FsdWFkWXpyLUI3dnBpUmlyV2NLdGgxTFhGUXpVMFphM3l6TXY4NWsydzRvRTd1cXJQaDV0MmgxS2ZTT2VyWFYyMmpnYVdnTm8?oc=5</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOckIycW1iR0VXRnFlRmlxRU5NUDFSYWVOei1yb1lGSnhIa0V4XzYzcTBFTlk4eE0zMFBBU0VCcE1yN1oxVXQ3N0VvZ2RlWlNhVFVtTjEzZUk2cEF5N0lrNkd3RFhhRFpOV1YtS0JsVmNiSHBGZXB2bEF6QjFhZTRPaTdrN0FsdWFkWXpyLUI3dnBpUmlyV2NLdGgxTFhGUXpVMFphM3l6TXY4NWsydzRvRTd1cXJQaDV0MmgxS2ZTT2VyWFYyMmpnYVdnTm8?oc=5</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>4189224770f11312</t>
+          <t>23004b4b81bcb74f</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T00:40:33Z</t>
+          <t>2026-10-05T05:35:23Z</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1773,22 +1773,22 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Wagle assures support to families of missing customs staff - myRepublica</t>
+          <t>Will the civil campaign inspired by the Bhotekoshi flood sustain itself? - myRepublica</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Wagle assures support to families of missing customs staff myRepublica</t>
+          <t>Will the civil campaign inspired by the Bhotekoshi flood sustain itself? myRepublica</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQOEMtSFdGUDdqRjhZREdSRlJ5VjA5aFVZLThzTDltU3JyaHVyMHhDTGwwMkR3VXJic1NmWi1WNnJtYjJqUFl0MGtQT3huWjA0UHVsWmIzODNCWUdKT3kyVzB5enAzYkVuODVnM0tUUXZCUmtGemswRE9pZkxmaWZHYVgwTGpaM25DNEFxMkt1dUtRTmVhX3Z1WFlZUEVublRUZnVyS0k5RWY5LWY5Z2QzcjFMMF82WXdsNzlHa19QQldXSEZucUtOYnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOUUdXVkIwQ1lzZ29VMWE5eU5kbnBDZ01JekdJVVBENzZwR0hadXBSbkk4SmNpRmlKV3U3RXpjQVBtWVZLUEJtMTAwcV96TExYVnU5T19iRmpFblVjRGxhaHFxWGhqZjRZelpWS0prMGROVnNxNmc4TUtBM0E3RFJkVE8xYm5SaFlZVEw4SDdGcHoxalM0QTlkYk0tS1lPMTdkRTJyNGZZaS1QQVpaUk1xaDVmbmI5SF9WU3RwTHRuX3A2WXlO?oc=5</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQOEMtSFdGUDdqRjhZREdSRlJ5VjA5aFVZLThzTDltU3JyaHVyMHhDTGwwMkR3VXJic1NmWi1WNnJtYjJqUFl0MGtQT3huWjA0UHVsWmIzODNCWUdKT3kyVzB5enAzYkVuODVnM0tUUXZCUmtGemswRE9pZkxmaWZHYVgwTGpaM25DNEFxMkt1dUtRTmVhX3Z1WFlZUEVublRUZnVyS0k5RWY5LWY5Z2QzcjFMMF82WXdsNzlHa19QQldXSEZucUtOYnVB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOUUdXVkIwQ1lzZ29VMWE5eU5kbnBDZ01JekdJVVBENzZwR0hadXBSbkk4SmNpRmlKV3U3RXpjQVBtWVZLUEJtMTAwcV96TExYVnU5T19iRmpFblVjRGxhaHFxWGhqZjRZelpWS0prMGROVnNxNmc4TUtBM0E3RFJkVE8xYm5SaFlZVEw4SDdGcHoxalM0QTlkYk0tS1lPMTdkRTJyNGZZaS1QQVpaUk1xaDVmbmI5SF9WU3RwTHRuX3A2WXlO?oc=5</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1805,42 +1805,42 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>adb172dfb88094ff</t>
+          <t>252af02ba0bf3af1</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T18:56:09Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Risky ‘tuins’ make comeback following Bhotekoshi flood - myRepublica</t>
+          <t>Over 800 Bhotekoshi flood displaced receive winter relief in Kathmandu holding centres - The Tourism Times</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Risky ‘tuins’ make comeback following Bhotekoshi flood myRepublica</t>
+          <t>Over 800 Bhotekoshi flood displaced receive winter relief in Kathmandu holding centres The Tourism Times</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWVYzNGtuOTlhbXRIUjhGb1FtbjFLdEIxekhlUm1fRk1iODI0V3ltZ3hBUHhNdm5McXRpSTFSY2hIQ3ZTcHl5V2NtYTRYeVgtRWxXQW5BUVBVWnpXYlAzSVBIanliak5fZTRMNmNaLV9FMDRTajF2dnlKSkJCVG1oR05keWlLeXpSMkdmT1VkRDJ2dGZBYzNKNFZTV3FoUzZnd2pfNlBtNmxjUEFTQWhqUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPZHlWWm5hZk90NVFqdXFGZ1Vud2ZrWDhvbGdZTHJBMS16Qmw1MUNBWDVzT0VXa3JhVDJIQkItREdtTUtoXzFCOUFhU2tfZ0p5akFRN19sNFRQNWw0b09DaXpxQWJUQzRNUGd1d09ycEdBUkR0bmktRG56OVJuVnpITEJ1eE1Jc2JySFBhMnZYZXg1QWN4S2VTUW5SancyTXFUS3ZZUEpkM05DS0lqTm5sdWljTmtwYXc0NGxEem0ydXgyX2NHN2ZNZTJR?oc=5</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPWVYzNGtuOTlhbXRIUjhGb1FtbjFLdEIxekhlUm1fRk1iODI0V3ltZ3hBUHhNdm5McXRpSTFSY2hIQ3ZTcHl5V2NtYTRYeVgtRWxXQW5BUVBVWnpXYlAzSVBIanliak5fZTRMNmNaLV9FMDRTajF2dnlKSkJCVG1oR05keWlLeXpSMkdmT1VkRDJ2dGZBYzNKNFZTV3FoUzZnd2pfNlBtNmxjUEFTQWhqUg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPZHlWWm5hZk90NVFqdXFGZ1Vud2ZrWDhvbGdZTHJBMS16Qmw1MUNBWDVzT0VXa3JhVDJIQkItREdtTUtoXzFCOUFhU2tfZ0p5akFRN19sNFRQNWw0b09DaXpxQWJUQzRNUGd1d09ycEdBUkR0bmktRG56OVJuVnpITEJ1eE1Jc2JySFBhMnZYZXg1QWN4S2VTUW5SancyTXFUS3ZZUEpkM05DS0lqTm5sdWljTmtwYXc0NGxEem0ydXgyX2NHN2ZNZTJR?oc=5</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1857,42 +1857,42 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>5c121de89e21fbf8</t>
+          <t>32fb999ba596439f</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T05:49:20Z</t>
+          <t>2026-10-04T23:56:47Z</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood - Ekantipur</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood Ekantipur</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1909,42 +1909,42 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>05a5afebc7bbc90d</t>
+          <t>f72b6aa392f3fd34</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-10-02T22:11:34Z</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid - Ekantipur</t>
+          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid Ekantipur</t>
+          <t>Collective Deep Lighting in Memory of Bhote Koshi Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNTG9vek41ano0UWFfUzgwbU5KWXEtN0NwOG40OXFIajVtMXZVNXYyckhCTXRDVktUaEk0RmxoZVlLRXBZeDB3T2Jkai1wSWptWjdyM1ZyaVlodFlSQUhUdGVqamh5WHNpWTE5ME4ta2QydzJMX1VUUkRlV3hETWVxYzJyV1FERGJRVkJuLTloaEVLSG9DVlZrNU5NczBCdTFENml3a3ZZWVJNQWEtMnl3Y0lBWHpWQjVFUWVqc1E5X3k1bTJPUm1mSFJscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQeGdaNzhKNk8wVXNEM3FfTHJjdkFMQ2ltRjhJa1NUUUVlUHE1QmFfTXNGdnF0OUhtOFZac0pkM0xDaC0xU0hnempaajVjY09qWXFua3M4MnZsWEtYWHhwYlo3ZUFKcjlMS1ZEdnZ6ay1MNlc4blNRUzBncV85aFlfcEZPN0NvOFdQSEI4SmctYnBqaEZDVTBidnR0U015cm9NMTBaZDk3Qy13RU1uMVRWT1pKeDhCLVB3QU1wdDZDQS1nMDhjOXZWQ1MtbjNHdw?oc=5</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxNTG9vek41ano0UWFfUzgwbU5KWXEtN0NwOG40OXFIajVtMXZVNXYyckhCTXRDVktUaEk0RmxoZVlLRXBZeDB3T2Jkai1wSWptWjdyM1ZyaVlodFlSQUhUdGVqamh5WHNpWTE5ME4ta2QydzJMX1VUUkRlV3hETWVxYzJyV1FERGJRVkJuLTloaEVLSG9DVlZrNU5NczBCdTFENml3a3ZZWVJNQWEtMnl3Y0lBWHpWQjVFUWVqc1E5X3k1bTJPUm1mSFJscw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxQeGdaNzhKNk8wVXNEM3FfTHJjdkFMQ2ltRjhJa1NUUUVlUHE1QmFfTXNGdnF0OUhtOFZac0pkM0xDaC0xU0hnempaajVjY09qWXFua3M4MnZsWEtYWHhwYlo3ZUFKcjlMS1ZEdnZ6ay1MNlc4blNRUzBncV85aFlfcEZPN0NvOFdQSEI4SmctYnBqaEZDVTBidnR0U015cm9NMTBaZDk3Qy13RU1uMVRWT1pKeDhCLVB3QU1wdDZDQS1nMDhjOXZWQ1MtbjNHdw?oc=5</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1961,42 +1961,42 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>3d6c5b299994a4f3</t>
+          <t>1f474f3512d0099c</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-10-07T00:40:33Z</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>One Month Since Bhote Koshi Flood - Ratopati</t>
+          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days - myRepublica</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>One Month Since Bhote Koshi Flood Ratopati</t>
+          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days myRepublica</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPVmRpdHpwOTRTaVFzU204c2RSS3dsWWNkSXM5amNSdlZpY0NzYTh6eFotcVJDTzk3dnBCZFNXRTVwN0hudERYaUw0dldxb25nVi1nN3U2N0dfYmUtWU8tVmhGVmppUGpjU2FYdGhIS19KUUVaNUJ6T1pRWVZTQ0tzNGtUX09iNTJYNVZnV1JWV2pCaVd6WDRSVTRrY3pkdDNZZ2NzT0RjakhydS1MNmtkWGl5Q3BhZzQwNG5NaEpOOEQ3VWNnalAyNndxczdyR0V5bEF5bGcyeVpBZG5zcmRLbE9mRGI5c0lJR2pnQzlhMnU4ZzRMMWNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9wFBVV95cUxPVmRpdHpwOTRTaVFzU204c2RSS3dsWWNkSXM5amNSdlZpY0NzYTh6eFotcVJDTzk3dnBCZFNXRTVwN0hudERYaUw0dldxb25nVi1nN3U2N0dfYmUtWU8tVmhGVmppUGpjU2FYdGhIS19KUUVaNUJ6T1pRWVZTQ0tzNGtUX09iNTJYNVZnV1JWV2pCaVd6WDRSVTRrY3pkdDNZZ2NzT0RjakhydS1MNmtkWGl5Q3BhZzQwNG5NaEpOOEQ3VWNnalAyNndxczdyR0V5bEF5bGcyeVpBZG5zcmRLbE9mRGI5c0lJR2pnQzlhMnU4ZzRMMWNB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2013,42 +2013,42 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>06470ae82fa46649</t>
+          <t>4189224770f11312</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T10:05:07Z</t>
+          <t>2026-10-07T00:40:33Z</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
+          <t>Bhotekoshi flood: Wagle assures support to families of missing customs staff - myRepublica</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
+          <t>Bhotekoshi flood: Wagle assures support to families of missing customs staff myRepublica</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQOEMtSFdGUDdqRjhZREdSRlJ5VjA5aFVZLThzTDltU3JyaHVyMHhDTGwwMkR3VXJic1NmWi1WNnJtYjJqUFl0MGtQT3huWjA0UHVsWmIzODNCWUdKT3kyVzB5enAzYkVuODVnM0tUUXZCUmtGemswRE9pZkxmaWZHYVgwTGpaM25DNEFxMkt1dUtRTmVhX3Z1WFlZUEVublRUZnVyS0k5RWY5LWY5Z2QzcjFMMF82WXdsNzlHa19QQldXSEZucUtOYnVB?oc=5</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQOEMtSFdGUDdqRjhZREdSRlJ5VjA5aFVZLThzTDltU3JyaHVyMHhDTGwwMkR3VXJic1NmWi1WNnJtYjJqUFl0MGtQT3huWjA0UHVsWmIzODNCWUdKT3kyVzB5enAzYkVuODVnM0tUUXZCUmtGemswRE9pZkxmaWZHYVgwTGpaM25DNEFxMkt1dUtRTmVhX3Z1WFlZUEVublRUZnVyS0k5RWY5LWY5Z2QzcjFMMF82WXdsNzlHa19QQldXSEZucUtOYnVB?oc=5</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2065,42 +2065,42 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>738417ce4d61c407</t>
+          <t>adb172dfb88094ff</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T12:31:08Z</t>
+          <t>2026-10-07T18:56:09Z</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing - OnlineKhabar English News</t>
+          <t>Risky ‘tuins’ make comeback following Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing OnlineKhabar English News</t>
+          <t>Risky ‘tuins’ make comeback following Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN29XYk56N3hnTFFmQzhmNzQ0ckZfNmF5UE4tWXlVaXZ2NWg5ODUxV0VFcEo4UFJucUZSRUZoYVNwS2NuZEhheHh6X1dtdkVtVU1fSE9EaGYzUEQ1elJGVFl6NnlObk5qNHp4MmdVUl9WaXVCanhtaWFsRFBfLUJVOTlTM3ZQckR3dmJ1V09UNTVhdk1pdWNSZDNVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWVYzNGtuOTlhbXRIUjhGb1FtbjFLdEIxekhlUm1fRk1iODI0V3ltZ3hBUHhNdm5McXRpSTFSY2hIQ3ZTcHl5V2NtYTRYeVgtRWxXQW5BUVBVWnpXYlAzSVBIanliak5fZTRMNmNaLV9FMDRTajF2dnlKSkJCVG1oR05keWlLeXpSMkdmT1VkRDJ2dGZBYzNKNFZTV3FoUzZnd2pfNlBtNmxjUEFTQWhqUg?oc=5</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxPN29XYk56N3hnTFFmQzhmNzQ0ckZfNmF5UE4tWXlVaXZ2NWg5ODUxV0VFcEo4UFJucUZSRUZoYVNwS2NuZEhheHh6X1dtdkVtVU1fSE9EaGYzUEQ1elJGVFl6NnlObk5qNHp4MmdVUl9WaXVCanhtaWFsRFBfLUJVOTlTM3ZQckR3dmJ1V09UNTVhdk1pdWNSZDNVZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPWVYzNGtuOTlhbXRIUjhGb1FtbjFLdEIxekhlUm1fRk1iODI0V3ltZ3hBUHhNdm5McXRpSTFSY2hIQ3ZTcHl5V2NtYTRYeVgtRWxXQW5BUVBVWnpXYlAzSVBIanliak5fZTRMNmNaLV9FMDRTajF2dnlKSkJCVG1oR05keWlLeXpSMkdmT1VkRDJ2dGZBYzNKNFZTV3FoUzZnd2pfNlBtNmxjUEFTQWhqUg?oc=5</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2117,42 +2117,42 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>628390c58d92cb27</t>
+          <t>5c121de89e21fbf8</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T12:31:08Z</t>
+          <t>2026-10-04T05:49:20Z</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>The drivers swept away by the Bhotekoshi flood - OnlineKhabar English News</t>
+          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood - Ekantipur</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>The drivers swept away by the Bhotekoshi flood OnlineKhabar English News</t>
+          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood Ekantipur</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBmNDRadEh1THMyakl4TEt4UlZXUzAyYm5HTVgwbkNiTFRCa3NLeWFlcGVMVS04RGhzdjI3THRzMHN6dWNVN2pVcFROUnRhVzJWUzE5Rklfd2otcGQwVTdIcDg4NWR4VUQ3dzhQYXYtdVphUXNkS3ZhdVRQbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMie0FVX3lxTFBmNDRadEh1THMyakl4TEt4UlZXUzAyYm5HTVgwbkNiTFRCa3NLeWFlcGVMVS04RGhzdjI3THRzMHN6dWNVN2pVcFROUnRhVzJWUzE5Rklfd2otcGQwVTdIcDg4NWR4VUQ3dzhQYXYtdVphUXNkS3ZhdVRQbw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>d97d72a45c8b8c3a</t>
+          <t>05a5afebc7bbc90d</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -2179,32 +2179,32 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T12:31:08Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Govt seeking alternative after Bhotekoshi flood knocks out 430 MW power - myRepublica</t>
+          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid - Ekantipur</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Govt seeking alternative after Bhotekoshi flood knocks out 430 MW power myRepublica</t>
+          <t>Claims of Rs 21 billion for damage caused by the Bhotekoshi flood, but only Rs 6.7 million paid Ekantipur</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXdqOTNOVmFGUTAxQU9pVFg4MmpDWWVUWjJZOUVDc3lOSkR3SXhzX1lTR3dwWFU4RDNoTi1ybnBvYmZ2Sk9LSkxENWdTRnBnUWJQOEpYM0dXbWRFaldfdEdfU29wMVBzUTdydnFtVXBBQTBuXzRqV3pRem1rX3JEU2xZbUpvZjIzb3B2MnJTX21wMW9ld1FnN09NckNxSHBCZnRNek9JTGRDU2RmeHViQnZ1ZktmNG1pOEhCR1ltcVZDME1p?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNTG9vek41ano0UWFfUzgwbU5KWXEtN0NwOG40OXFIajVtMXZVNXYyckhCTXRDVktUaEk0RmxoZVlLRXBZeDB3T2Jkai1wSWptWjdyM1ZyaVlodFlSQUhUdGVqamh5WHNpWTE5ME4ta2QydzJMX1VUUkRlV3hETWVxYzJyV1FERGJRVkJuLTloaEVLSG9DVlZrNU5NczBCdTFENml3a3ZZWVJNQWEtMnl3Y0lBWHpWQjVFUWVqc1E5X3k1bTJPUm1mSFJscw?oc=5</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXdqOTNOVmFGUTAxQU9pVFg4MmpDWWVUWjJZOUVDc3lOSkR3SXhzX1lTR3dwWFU4RDNoTi1ybnBvYmZ2Sk9LSkxENWdTRnBnUWJQOEpYM0dXbWRFaldfdEdfU29wMVBzUTdydnFtVXBBQTBuXzRqV3pRem1rX3JEU2xZbUpvZjIzb3B2MnJTX21wMW9ld1FnN09NckNxSHBCZnRNek9JTGRDU2RmeHViQnZ1ZktmNG1pOEhCR1ltcVZDME1p?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxNTG9vek41ano0UWFfUzgwbU5KWXEtN0NwOG40OXFIajVtMXZVNXYyckhCTXRDVktUaEk0RmxoZVlLRXBZeDB3T2Jkai1wSWptWjdyM1ZyaVlodFlSQUhUdGVqamh5WHNpWTE5ME4ta2QydzJMX1VUUkRlV3hETWVxYzJyV1FERGJRVkJuLTloaEVLSG9DVlZrNU5NczBCdTFENml3a3ZZWVJNQWEtMnl3Y0lBWHpWQjVFUWVqc1E5X3k1bTJPUm1mSFJscw?oc=5</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>0c3afc561d607c43</t>
+          <t>3d6c5b299994a4f3</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -2231,32 +2231,32 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T12:31:08Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal - OnlineKhabar English News</t>
+          <t>One Month Since Bhote Koshi Flood - Ratopati</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal OnlineKhabar English News</t>
+          <t>One Month Since Bhote Koshi Flood Ratopati</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPVmRpdHpwOTRTaVFzU204c2RSS3dsWWNkSXM5amNSdlZpY0NzYTh6eFotcVJDTzk3dnBCZFNXRTVwN0hudERYaUw0dldxb25nVi1nN3U2N0dfYmUtWU8tVmhGVmppUGpjU2FYdGhIS19KUUVaNUJ6T1pRWVZTQ0tzNGtUX09iNTJYNVZnV1JWV2pCaVd6WDRSVTRrY3pkdDNZZ2NzT0RjakhydS1MNmtkWGl5Q3BhZzQwNG5NaEpOOEQ3VWNnalAyNndxczdyR0V5bEF5bGcyeVpBZG5zcmRLbE9mRGI5c0lJR2pnQzlhMnU4ZzRMMWNB?oc=5</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9wFBVV95cUxPVmRpdHpwOTRTaVFzU204c2RSS3dsWWNkSXM5amNSdlZpY0NzYTh6eFotcVJDTzk3dnBCZFNXRTVwN0hudERYaUw0dldxb25nVi1nN3U2N0dfYmUtWU8tVmhGVmppUGpjU2FYdGhIS19KUUVaNUJ6T1pRWVZTQ0tzNGtUX09iNTJYNVZnV1JWV2pCaVd6WDRSVTRrY3pkdDNZZ2NzT0RjakhydS1MNmtkWGl5Q3BhZzQwNG5NaEpOOEQ3VWNnalAyNndxczdyR0V5bEF5bGcyeVpBZG5zcmRLbE9mRGI5c0lJR2pnQzlhMnU4ZzRMMWNB?oc=5</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2273,42 +2273,42 @@
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>44cfaa1316789a14</t>
+          <t>06470ae82fa46649</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-10-01T10:05:07Z</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing - Ekantipur</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing Ekantipur</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNkxpOUhnRTJ6Vk1FVTU4VUt4YmhEY2NZYWxGd0xNY2hNN0ZXQlhqV2Z6RkN3dU5xYkU0ZjVhQkk0ZnlQVHlfdmh4S1RZdTJJM3lQeGFVOE5LSDF3b3Y2dHF2QzlTNTlFcjhXMzQ1enAxdU9JN1pfYVZ3Wm1Fcmp1U09kSDNuclBlanlVMVoxb0pLd2R6Tk9iYTlTZ1ViOHU4WlNZNHlZY29HQ3ZSQk5hdjZLMGM2aTE3YURUYlRjbEVUZTJpd0ZNT1lmMTVtblN5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNkxpOUhnRTJ6Vk1FVTU4VUt4YmhEY2NZYWxGd0xNY2hNN0ZXQlhqV2Z6RkN3dU5xYkU0ZjVhQkk0ZnlQVHlfdmh4S1RZdTJJM3lQeGFVOE5LSDF3b3Y2dHF2QzlTNTlFcjhXMzQ1enAxdU9JN1pfYVZ3Wm1Fcmp1U09kSDNuclBlanlVMVoxb0pLd2R6Tk9iYTlTZ1ViOHU4WlNZNHlZY29HQ3ZSQk5hdjZLMGM2aTE3YURUYlRjbEVUZTJpd0ZNT1lmMTVtblN5?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2325,42 +2325,42 @@
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>39d829f09e372591</t>
+          <t>738417ce4d61c407</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-30T12:31:08Z</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims - myRepublica</t>
+          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims myRepublica</t>
+          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQakctVVNnbXRfa0RCMHd6aTgwM0xrUmJrUXoxdy1rN3ZwOVRPQkFYU1dyQ3c2NVJycnp1cjBTakppbUxnWHUzZks3TjZqSWZaVG1NRU1FV3UzYy1Ra2xTalJDUGE2bzN2TTZRVjhRZXNiWFU3SjRxR3c3WncxdExVNWE5Y24xUWR4T09abVVxbUhPOFYwa09tYzJOdGdTSWZRanAtRWNGemh1OWYteXlXY3ZhS3lzR1o3eGFlSGtfWVd1LTc5UHNQOE93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN29XYk56N3hnTFFmQzhmNzQ0ckZfNmF5UE4tWXlVaXZ2NWg5ODUxV0VFcEo4UFJucUZSRUZoYVNwS2NuZEhheHh6X1dtdkVtVU1fSE9EaGYzUEQ1elJGVFl6NnlObk5qNHp4MmdVUl9WaXVCanhtaWFsRFBfLUJVOTlTM3ZQckR3dmJ1V09UNTVhdk1pdWNSZDNVZw?oc=5</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQakctVVNnbXRfa0RCMHd6aTgwM0xrUmJrUXoxdy1rN3ZwOVRPQkFYU1dyQ3c2NVJycnp1cjBTakppbUxnWHUzZks3TjZqSWZaVG1NRU1FV3UzYy1Ra2xTalJDUGE2bzN2TTZRVjhRZXNiWFU3SjRxR3c3WncxdExVNWE5Y24xUWR4T09abVVxbUhPOFYwa09tYzJOdGdTSWZRanAtRWNGemh1OWYteXlXY3ZhS3lzR1o3eGFlSGtfWVd1LTc5UHNQOE93?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxPN29XYk56N3hnTFFmQzhmNzQ0ckZfNmF5UE4tWXlVaXZ2NWg5ODUxV0VFcEo4UFJucUZSRUZoYVNwS2NuZEhheHh6X1dtdkVtVU1fSE9EaGYzUEQ1elJGVFl6NnlObk5qNHp4MmdVUl9WaXVCanhtaWFsRFBfLUJVOTlTM3ZQckR3dmJ1V09UNTVhdk1pdWNSZDNVZw?oc=5</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2377,42 +2377,42 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>3f9753b6880aea96</t>
+          <t>628390c58d92cb27</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T18:24:29Z</t>
+          <t>2026-09-30T12:31:08Z</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 10 (As of 29 September 2026) - ReliefWeb</t>
+          <t>The drivers swept away by the Bhotekoshi flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 10 (As of 29 September 2026) ReliefWeb</t>
+          <t>The drivers swept away by the Bhotekoshi flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTGdSelhScERDR1RPSEQ3eWYxQXhyam1sZE5FaU5iaVFTcG1fV3lxQ2RaMS1aS0VTZjVhRHQtU3djR0RMVmY3eWlXZ2p4YXRUZHVfYXlfeTlDNFRLNnBpeGc5b1ZOYjFxeWpxSTVoZGZjLWNhNXFPRm1OcURUNXFoVmotWTVtU1g4YVVCSDJyRUVSNU1NaTQzNWpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBmNDRadEh1THMyakl4TEt4UlZXUzAyYm5HTVgwbkNiTFRCa3NLeWFlcGVMVS04RGhzdjI3THRzMHN6dWNVN2pVcFROUnRhVzJWUzE5Rklfd2otcGQwVTdIcDg4NWR4VUQ3dzhQYXYtdVphUXNkS3ZhdVRQbw?oc=5</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQTGdSelhScERDR1RPSEQ3eWYxQXhyam1sZE5FaU5iaVFTcG1fV3lxQ2RaMS1aS0VTZjVhRHQtU3djR0RMVmY3eWlXZ2p4YXRUZHVfYXlfeTlDNFRLNnBpeGc5b1ZOYjFxeWpxSTVoZGZjLWNhNXFPRm1OcURUNXFoVmotWTVtU1g4YVVCSDJyRUVSNU1NaTQzNWpn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMie0FVX3lxTFBmNDRadEh1THMyakl4TEt4UlZXUzAyYm5HTVgwbkNiTFRCa3NLeWFlcGVMVS04RGhzdjI3THRzMHN6dWNVN2pVcFROUnRhVzJWUzE5Rklfd2otcGQwVTdIcDg4NWR4VUQ3dzhQYXYtdVphUXNkS3ZhdVRQbw?oc=5</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2429,42 +2429,42 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>6269be2526b4a2c1</t>
+          <t>d97d72a45c8b8c3a</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-09-30T12:31:08Z</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Bagmati CM seeks support from six provinces for Bhote Koshi flood reconstruction - Nepalnews.com</t>
+          <t>Govt seeking alternative after Bhotekoshi flood knocks out 430 MW power - myRepublica</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Bagmati CM seeks support from six provinces for Bhote Koshi flood reconstruction Nepalnews.com</t>
+          <t>Govt seeking alternative after Bhotekoshi flood knocks out 430 MW power myRepublica</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTllJYnpWQTN4bm55REItcjJhTEIwelBRdmNBNTVaNjdBR2JWbV9kZjJZME1WdzR4bXpYdHk3MkZqZGlJT3hUcV9NMzB6Y1BwUmo3ZENLOHJXQVlwRVhRdUFORWQwbnZFMXAyZDNETHZSLUtlaHNPYXh6OWJ3cW5seVpaMnBOY2RJekkyZEtVdTQwZlJGcEZROC0xN1ZfeVpYWG9DeHFrQ1oybjNXUUdocFF0bFh4Nk9Mdl9wOUtvaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXdqOTNOVmFGUTAxQU9pVFg4MmpDWWVUWjJZOUVDc3lOSkR3SXhzX1lTR3dwWFU4RDNoTi1ybnBvYmZ2Sk9LSkxENWdTRnBnUWJQOEpYM0dXbWRFaldfdEdfU29wMVBzUTdydnFtVXBBQTBuXzRqV3pRem1rX3JEU2xZbUpvZjIzb3B2MnJTX21wMW9ld1FnN09NckNxSHBCZnRNek9JTGRDU2RmeHViQnZ1ZktmNG1pOEhCR1ltcVZDME1p?oc=5</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOTllJYnpWQTN4bm55REItcjJhTEIwelBRdmNBNTVaNjdBR2JWbV9kZjJZME1WdzR4bXpYdHk3MkZqZGlJT3hUcV9NMzB6Y1BwUmo3ZENLOHJXQVlwRVhRdUFORWQwbnZFMXAyZDNETHZSLUtlaHNPYXh6OWJ3cW5seVpaMnBOY2RJekkyZEtVdTQwZlJGcEZROC0xN1ZfeVpYWG9DeHFrQ1oybjNXUUdocFF0bFh4Nk9Mdl9wOUtvaw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXdqOTNOVmFGUTAxQU9pVFg4MmpDWWVUWjJZOUVDc3lOSkR3SXhzX1lTR3dwWFU4RDNoTi1ybnBvYmZ2Sk9LSkxENWdTRnBnUWJQOEpYM0dXbWRFaldfdEdfU29wMVBzUTdydnFtVXBBQTBuXzRqV3pRem1rX3JEU2xZbUpvZjIzb3B2MnJTX21wMW9ld1FnN09NckNxSHBCZnRNek9JTGRDU2RmeHViQnZ1ZktmNG1pOEhCR1ltcVZDME1p?oc=5</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2481,42 +2481,42 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>75dbec3ba72a6952</t>
+          <t>0c3afc561d607c43</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T16:56:20Z</t>
+          <t>2026-09-30T12:31:08Z</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>‘I survived by sheer luck’: Visually impaired teacher recalls escaping the Bhote Koshi flood - Nepalnews.com</t>
+          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>‘I survived by sheer luck’: Visually impaired teacher recalls escaping the Bhote Koshi flood Nepalnews.com</t>
+          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQU3d5cmcwSUJxamt1M2tlNXdIdi10RnV1NGN0bXV2QjN5amxGLTBjc1JRYy1saF9Yc2hLdURqUHRCM0luZXVIdjBjZS1pSW5KQlZ5a3JIUDdlZlh5RWlfbGNwV1ppb2gwX1JvTi1HeTZmdUdaOFU3bkQxTjZVTzRUTW1jYmR1bklBangydl9UcWxsakRrQkpOdGQtY3h3U25BRFBnbDhEeDN0UXF5UWVDeVo4Z2xLaklrSDh1Sk52WFhkTG16TFFlQWhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQU3d5cmcwSUJxamt1M2tlNXdIdi10RnV1NGN0bXV2QjN5amxGLTBjc1JRYy1saF9Yc2hLdURqUHRCM0luZXVIdjBjZS1pSW5KQlZ5a3JIUDdlZlh5RWlfbGNwV1ppb2gwX1JvTi1HeTZmdUdaOFU3bkQxTjZVTzRUTW1jYmR1bklBangydl9UcWxsakRrQkpOdGQtY3h3U25BRFBnbDhEeDN0UXF5UWVDeVo4Z2xLaklrSDh1Sk52WFhkTG16TFFlQWhB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2533,12 +2533,12 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>62a2f75222fd5241</t>
+          <t>44cfaa1316789a14</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2548,27 +2548,27 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 5,285 people remain unaccounted for - Khabarhub</t>
+          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing - Ekantipur</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 5,285 people remain unaccounted for Khabarhub</t>
+          <t>Two Brothers Missing in the Bhotekoshi Flood, Another Brother Dies in an Avalanche, Nephew Missing Ekantipur</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE41M1RIbktTMWUzdGdiSldXdWphay00QjFUUERVamxlaTBkRU1tUmwzQWZDdlkycWpib1lJVWJQTzlKQ3JEUjhfUVpxMC1aQ2VIcWxSb1A5bHU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNkxpOUhnRTJ6Vk1FVTU4VUt4YmhEY2NZYWxGd0xNY2hNN0ZXQlhqV2Z6RkN3dU5xYkU0ZjVhQkk0ZnlQVHlfdmh4S1RZdTJJM3lQeGFVOE5LSDF3b3Y2dHF2QzlTNTlFcjhXMzQ1enAxdU9JN1pfYVZ3Wm1Fcmp1U09kSDNuclBlanlVMVoxb0pLd2R6Tk9iYTlTZ1ViOHU4WlNZNHlZY29HQ3ZSQk5hdjZLMGM2aTE3YURUYlRjbEVUZTJpd0ZNT1lmMTVtblN5?oc=5</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE41M1RIbktTMWUzdGdiSldXdWphay00QjFUUERVamxlaTBkRU1tUmwzQWZDdlkycWpib1lJVWJQTzlKQ3JEUjhfUVpxMC1aQ2VIcWxSb1A5bHU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNkxpOUhnRTJ6Vk1FVTU4VUt4YmhEY2NZYWxGd0xNY2hNN0ZXQlhqV2Z6RkN3dU5xYkU0ZjVhQkk0ZnlQVHlfdmh4S1RZdTJJM3lQeGFVOE5LSDF3b3Y2dHF2QzlTNTlFcjhXMzQ1enAxdU9JN1pfYVZ3Wm1Fcmp1U09kSDNuclBlanlVMVoxb0pLd2R6Tk9iYTlTZ1ViOHU4WlNZNHlZY29HQ3ZSQk5hdjZLMGM2aTE3YURUYlRjbEVUZTJpd0ZNT1lmMTVtblN5?oc=5</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -2585,42 +2585,42 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>42068b0abc4eceb0</t>
+          <t>39d829f09e372591</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction - Ekantipur</t>
+          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims - myRepublica</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction Ekantipur</t>
+          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims myRepublica</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQTmw1TUxmRmR1NGJ4c3JwaWdYaW1PWm5JX2xxUVo4WjBGUzJ3SXNyZ0liZFNLdFZyQ1I5TktzS2cwUWdxb0NGNUhJOFhLZVIwUG1iT3Fycy1pMmtEekx0SmJDSjFvOUE4TGtWSlZ6LTBua044NVFfVV9qRnVSNEY5S0dtcTFRUy1mOFAyQ25MbnlnaFRzUVZHN3lrbDVHM1F1ekE3eGFPSlhrQVp0WkJUWlpfUE1tV25JZzluYVIyY0ZZZE9RdUtmTTJxSFFTdl9LU3pPWkY0bWpDSlZZZXQ1b1ZSRmk0YktVTkx2NGtQYnJrVUx3VFJiV0hfMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQakctVVNnbXRfa0RCMHd6aTgwM0xrUmJrUXoxdy1rN3ZwOVRPQkFYU1dyQ3c2NVJycnp1cjBTakppbUxnWHUzZks3TjZqSWZaVG1NRU1FV3UzYy1Ra2xTalJDUGE2bzN2TTZRVjhRZXNiWFU3SjRxR3c3WncxdExVNWE5Y24xUWR4T09abVVxbUhPOFYwa09tYzJOdGdTSWZRanAtRWNGemh1OWYteXlXY3ZhS3lzR1o3eGFlSGtfWVd1LTc5UHNQOE93?oc=5</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi-wFBVV95cUxQTmw1TUxmRmR1NGJ4c3JwaWdYaW1PWm5JX2xxUVo4WjBGUzJ3SXNyZ0liZFNLdFZyQ1I5TktzS2cwUWdxb0NGNUhJOFhLZVIwUG1iT3Fycy1pMmtEekx0SmJDSjFvOUE4TGtWSlZ6LTBua044NVFfVV9qRnVSNEY5S0dtcTFRUy1mOFAyQ25MbnlnaFRzUVZHN3lrbDVHM1F1ekE3eGFPSlhrQVp0WkJUWlpfUE1tV25JZzluYVIyY0ZZZE9RdUtmTTJxSFFTdl9LU3pPWkY0bWpDSlZZZXQ1b1ZSRmk0YktVTkx2NGtQYnJrVUx3VFJiV0hfMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQakctVVNnbXRfa0RCMHd6aTgwM0xrUmJrUXoxdy1rN3ZwOVRPQkFYU1dyQ3c2NVJycnp1cjBTakppbUxnWHUzZks3TjZqSWZaVG1NRU1FV3UzYy1Ra2xTalJDUGE2bzN2TTZRVjhRZXNiWFU3SjRxR3c3WncxdExVNWE5Y24xUWR4T09abVVxbUhPOFYwa09tYzJOdGdTSWZRanAtRWNGemh1OWYteXlXY3ZhS3lzR1o3eGFlSGtfWVd1LTc5UHNQOE93?oc=5</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2637,42 +2637,42 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>00d345c544c7756b</t>
+          <t>3f9753b6880aea96</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T05:20:23Z</t>
+          <t>2026-10-01T18:24:29Z</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>UAE pledges additional $25 million for Bhotekoshi flood victims - myRepublica</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 10 (As of 29 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>UAE pledges additional $25 million for Bhotekoshi flood victims myRepublica</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 10 (As of 29 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVHRJTFBpTmhMLUVfM2F1SUxIQTFyVFNKY0UxN0VGVE9xTGZCSEUyX2w1VTFIR3dXNHFDbGxNZlE4ZXNzeThzMTFid21TbkpITDRoTWE5V2swZGxYOFRqaF9OeFFUV2dfTFE3Zy1kSlVCR1RzanNubkVVNW94dk1ra0dnTUVrNkhKU2Z3VFVMbHdjZ09wYjZHS2Vjbjg1RTJxQjhsaGp0RDkxUWxUM3BTeC1QdGhBWWhf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTGdSelhScERDR1RPSEQ3eWYxQXhyam1sZE5FaU5iaVFTcG1fV3lxQ2RaMS1aS0VTZjVhRHQtU3djR0RMVmY3eWlXZ2p4YXRUZHVfYXlfeTlDNFRLNnBpeGc5b1ZOYjFxeWpxSTVoZGZjLWNhNXFPRm1OcURUNXFoVmotWTVtU1g4YVVCSDJyRUVSNU1NaTQzNWpn?oc=5</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVHRJTFBpTmhMLUVfM2F1SUxIQTFyVFNKY0UxN0VGVE9xTGZCSEUyX2w1VTFIR3dXNHFDbGxNZlE4ZXNzeThzMTFid21TbkpITDRoTWE5V2swZGxYOFRqaF9OeFFUV2dfTFE3Zy1kSlVCR1RzanNubkVVNW94dk1ra0dnTUVrNkhKU2Z3VFVMbHdjZ09wYjZHS2Vjbjg1RTJxQjhsaGp0RDkxUWxUM3BTeC1QdGhBWWhf?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQTGdSelhScERDR1RPSEQ3eWYxQXhyam1sZE5FaU5iaVFTcG1fV3lxQ2RaMS1aS0VTZjVhRHQtU3djR0RMVmY3eWlXZ2p4YXRUZHVfYXlfeTlDNFRLNnBpeGc5b1ZOYjFxeWpxSTVoZGZjLWNhNXFPRm1OcURUNXFoVmotWTVtU1g4YVVCSDJyRUVSNU1NaTQzNWpn?oc=5</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2689,42 +2689,42 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>a5dbcf34da1934e3</t>
+          <t>75dbec3ba72a6952</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-09-27T16:56:20Z</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Deshsanchar</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 5,285 missing; 1,451 bodies recovered so far - Deshsanchar</t>
+          <t>‘I survived by sheer luck’: Visually impaired teacher recalls escaping the Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 5,285 missing; 1,451 bodies recovered so far Deshsanchar</t>
+          <t>‘I survived by sheer luck’: Visually impaired teacher recalls escaping the Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPNHBxOUNBRXJhYVRJeEEwQk9HY25HaXIwV0NFYUNqamhoR1hhWHYwTUtoOGd5VnF6dXVmVHRhYjN6X0FpVEFlTXBoZ1hXNjZseWRKRXVJSU9oeTAtT01OUEVJOHZRQ3l4QUUxb29ybU1vRGszOE11Y1o3bk8zUGlkQV9pa1Vrc21yaFp3Y2pNakUtcTZtQTBEUzBpYzludzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQU3d5cmcwSUJxamt1M2tlNXdIdi10RnV1NGN0bXV2QjN5amxGLTBjc1JRYy1saF9Yc2hLdURqUHRCM0luZXVIdjBjZS1pSW5KQlZ5a3JIUDdlZlh5RWlfbGNwV1ppb2gwX1JvTi1HeTZmdUdaOFU3bkQxTjZVTzRUTW1jYmR1bklBangydl9UcWxsakRrQkpOdGQtY3h3U25BRFBnbDhEeDN0UXF5UWVDeVo4Z2xLaklrSDh1Sk52WFhkTG16TFFlQWhB?oc=5</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxPNHBxOUNBRXJhYVRJeEEwQk9HY25HaXIwV0NFYUNqamhoR1hhWHYwTUtoOGd5VnF6dXVmVHRhYjN6X0FpVEFlTXBoZ1hXNjZseWRKRXVJSU9oeTAtT01OUEVJOHZRQ3l4QUUxb29ybU1vRGszOE11Y1o3bk8zUGlkQV9pa1Vrc21yaFp3Y2pNakUtcTZtQTBEUzBpYzludzA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQU3d5cmcwSUJxamt1M2tlNXdIdi10RnV1NGN0bXV2QjN5amxGLTBjc1JRYy1saF9Yc2hLdURqUHRCM0luZXVIdjBjZS1pSW5KQlZ5a3JIUDdlZlh5RWlfbGNwV1ppb2gwX1JvTi1HeTZmdUdaOFU3bkQxTjZVTzRUTW1jYmR1bklBangydl9UcWxsakRrQkpOdGQtY3h3U25BRFBnbDhEeDN0UXF5UWVDeVo4Z2xLaklrSDh1Sk52WFhkTG16TFFlQWhB?oc=5</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2741,42 +2741,42 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>3ab08920b47a6a0e</t>
+          <t>62a2f75222fd5241</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T18:49:52Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
+          <t>Bhotekoshi flood: 5,285 people remain unaccounted for - Khabarhub</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
+          <t>Bhotekoshi flood: 5,285 people remain unaccounted for Khabarhub</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE41M1RIbktTMWUzdGdiSldXdWphay00QjFUUERVamxlaTBkRU1tUmwzQWZDdlkycWpib1lJVWJQTzlKQ3JEUjhfUVpxMC1aQ2VIcWxSb1A5bHU?oc=5</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE41M1RIbktTMWUzdGdiSldXdWphay00QjFUUERVamxlaTBkRU1tUmwzQWZDdlkycWpib1lJVWJQTzlKQ3JEUjhfUVpxMC1aQ2VIcWxSb1A5bHU?oc=5</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -2793,42 +2793,42 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>6e0819f293fe319a</t>
+          <t>42068b0abc4eceb0</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T11:59:03Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact - Nepalnews.com</t>
+          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction - Ekantipur</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact Nepalnews.com</t>
+          <t>One Month Since the Bhotekoshi Flood Disaster: Search and Relief Distribution Ongoing, Challenges in Reconstruction Ekantipur</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQTmw1TUxmRmR1NGJ4c3JwaWdYaW1PWm5JX2xxUVo4WjBGUzJ3SXNyZ0liZFNLdFZyQ1I5TktzS2cwUWdxb0NGNUhJOFhLZVIwUG1iT3Fycy1pMmtEekx0SmJDSjFvOUE4TGtWSlZ6LTBua044NVFfVV9qRnVSNEY5S0dtcTFRUy1mOFAyQ25MbnlnaFRzUVZHN3lrbDVHM1F1ekE3eGFPSlhrQVp0WkJUWlpfUE1tV25JZzluYVIyY0ZZZE9RdUtmTTJxSFFTdl9LU3pPWkY0bWpDSlZZZXQ1b1ZSRmk0YktVTkx2NGtQYnJrVUx3VFJiV0hfMA?oc=5</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi-wFBVV95cUxQTmw1TUxmRmR1NGJ4c3JwaWdYaW1PWm5JX2xxUVo4WjBGUzJ3SXNyZ0liZFNLdFZyQ1I5TktzS2cwUWdxb0NGNUhJOFhLZVIwUG1iT3Fycy1pMmtEekx0SmJDSjFvOUE4TGtWSlZ6LTBua044NVFfVV9qRnVSNEY5S0dtcTFRUy1mOFAyQ25MbnlnaFRzUVZHN3lrbDVHM1F1ekE3eGFPSlhrQVp0WkJUWlpfUE1tV25JZzluYVIyY0ZZZE9RdUtmTTJxSFFTdl9LU3pPWkY0bWpDSlZZZXQ1b1ZSRmk0YktVTkx2NGtQYnJrVUx3VFJiV0hfMA?oc=5</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2845,42 +2845,42 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>0f89b14bbff908dd</t>
+          <t>00d345c544c7756b</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T17:08:24Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>We did not cause the Bhotekoshi flood: Prime Minister - Ekantipur</t>
+          <t>UAE pledges additional $25 million for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>We did not cause the Bhotekoshi flood: Prime Minister Ekantipur</t>
+          <t>UAE pledges additional $25 million for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPTHkxSzRncEk2Mlo2bHFuVWhUSU5tV1VoRktZV3h1RlRUVTQ5NHNUVm1SUWpSNFpEaHBucGtBS3lUeWRqc0ZJdnY5MDNidFdiYndBcmppQWRzdUhNOGxkVEhmZk9HN0Q5Y184X3Y0UVpzaDVxT3E0cGhYNXVRZFhlR09rcjhpV1BuQkI3bjlhWTdWMmhjZUYxbG54UXZPZjBQSlJDOU0tUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVHRJTFBpTmhMLUVfM2F1SUxIQTFyVFNKY0UxN0VGVE9xTGZCSEUyX2w1VTFIR3dXNHFDbGxNZlE4ZXNzeThzMTFid21TbkpITDRoTWE5V2swZGxYOFRqaF9OeFFUV2dfTFE3Zy1kSlVCR1RzanNubkVVNW94dk1ra0dnTUVrNkhKU2Z3VFVMbHdjZ09wYjZHS2Vjbjg1RTJxQjhsaGp0RDkxUWxUM3BTeC1QdGhBWWhf?oc=5</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipwFBVV95cUxPTHkxSzRncEk2Mlo2bHFuVWhUSU5tV1VoRktZV3h1RlRUVTQ5NHNUVm1SUWpSNFpEaHBucGtBS3lUeWRqc0ZJdnY5MDNidFdiYndBcmppQWRzdUhNOGxkVEhmZk9HN0Q5Y184X3Y0UVpzaDVxT3E0cGhYNXVRZFhlR09rcjhpV1BuQkI3bjlhWTdWMmhjZUYxbG54UXZPZjBQSlJDOU0tUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVHRJTFBpTmhMLUVfM2F1SUxIQTFyVFNKY0UxN0VGVE9xTGZCSEUyX2w1VTFIR3dXNHFDbGxNZlE4ZXNzeThzMTFid21TbkpITDRoTWE5V2swZGxYOFRqaF9OeFFUV2dfTFE3Zy1kSlVCR1RzanNubkVVNW94dk1ra0dnTUVrNkhKU2Z3VFVMbHdjZ09wYjZHS2Vjbjg1RTJxQjhsaGp0RDkxUWxUM3BTeC1QdGhBWWhf?oc=5</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -2897,42 +2897,42 @@
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>653af4c6fa9525c4</t>
+          <t>a5dbcf34da1934e3</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Deshsanchar</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa - Bhotekoshi flood: Urgent call for assistance - ReliefWeb</t>
+          <t>Bhotekoshi flood leaves 5,285 missing; 1,451 bodies recovered so far - Deshsanchar</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa - Bhotekoshi flood: Urgent call for assistance ReliefWeb</t>
+          <t>Bhotekoshi flood leaves 5,285 missing; 1,451 bodies recovered so far Deshsanchar</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbTBubVpRWE5Ram5wd3BrcWU2TlJKa3ZLOXpmWEZ0NWZIQ0d1QW41ZTZBeUZMN0ltUHQ0dkZrMzV0dUNzbDFnQ3EtNXBVamJTTG1BM0hyRk1JcmZsREVYUVNxMkNXWGd0elFHa2JOZG44c0pSOTM3eklqa0QtQTdkVlllbWg3ejZVQ05HU3JqaG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPNHBxOUNBRXJhYVRJeEEwQk9HY25HaXIwV0NFYUNqamhoR1hhWHYwTUtoOGd5VnF6dXVmVHRhYjN6X0FpVEFlTXBoZ1hXNjZseWRKRXVJSU9oeTAtT01OUEVJOHZRQ3l4QUUxb29ybU1vRGszOE11Y1o3bk8zUGlkQV9pa1Vrc21yaFp3Y2pNakUtcTZtQTBEUzBpYzludzA?oc=5</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxPbTBubVpRWE5Ram5wd3BrcWU2TlJKa3ZLOXpmWEZ0NWZIQ0d1QW41ZTZBeUZMN0ltUHQ0dkZrMzV0dUNzbDFnQ3EtNXBVamJTTG1BM0hyRk1JcmZsREVYUVNxMkNXWGd0elFHa2JOZG44c0pSOTM3eklqa0QtQTdkVlllbWg3ejZVQ05HU3JqaG4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinwFBVV95cUxPNHBxOUNBRXJhYVRJeEEwQk9HY25HaXIwV0NFYUNqamhoR1hhWHYwTUtoOGd5VnF6dXVmVHRhYjN6X0FpVEFlTXBoZ1hXNjZseWRKRXVJSU9oeTAtT01OUEVJOHZRQ3l4QUUxb29ybU1vRGszOE11Y1o3bk8zUGlkQV9pa1Vrc21yaFp3Y2pNakUtcTZtQTBEUzBpYzludzA?oc=5</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2949,42 +2949,42 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>77b3c93490f3e8fb</t>
+          <t>3ab08920b47a6a0e</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T04:54:40Z</t>
+          <t>2026-10-08T18:49:52Z</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure - Nepalnews.com</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure Nepalnews.com</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxNbUhMRlRUT3VDVldsVEYtQzdObXpCV0g4UjFDRi1jUjBoQU5TZUVERlluUGpUZmZ1TVhsN3MwTWZfUVJKclhQYjlPUTBQaGFyWW1kMUVxM3FoTUFpRERaa2gzRWotUEpQVDZGeVBPTnU0dURGMXJSd3RCVFB3anA2OGFlXzJlenNsdG0xTTlMYjB0eThPcWowYTFDRkRxc1dQelBtUFhPaU1oMmV1ektoS2lWblVPMWRTcFdvNTdfSFNtTWlEb25aM2NTWC1lc1U?oc=5</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3001,42 +3001,42 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>0dfaf4eea6b1deea</t>
+          <t>6e0819f293fe319a</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T23:37:00Z</t>
+          <t>2026-09-27T11:59:03Z</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation - Ekantipur</t>
+          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact - Nepalnews.com</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation Ekantipur</t>
+          <t>Bhote Koshi flood leaves 38 students missing in Rasuwa, 201 parents out of contact Nepalnews.com</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxQM0J0SnBjZUJZa2RNTGxmZHM5TjZfdjF3WjZYRS1XZnBlTWotN1VsN0NJN2pGUGhBWF9aRkt2eHVSZmtjOGNWTkw2d000Mk1EREtMb2hpUVlSaFNOYnlkeEhpNnB4NlB1NDdtNjZQVjBmVHQ4VVJremFtSmJzekwwX3VQMEFod2NwR3pZeUxMQlFuRTBqOERMUUluRGRjbnk4OXhrbWhoQ2U1WWgtUHhPdzB3aDNjdm4wMUZfVHFB?oc=5</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3053,42 +3053,42 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>af8788f535313ce1</t>
+          <t>0f89b14bbff908dd</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-09-25T17:08:24Z</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims - Ratopati</t>
+          <t>We did not cause the Bhotekoshi flood: Prime Minister - Ekantipur</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims Ratopati</t>
+          <t>We did not cause the Bhotekoshi flood: Prime Minister Ekantipur</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPTHkxSzRncEk2Mlo2bHFuVWhUSU5tV1VoRktZV3h1RlRUVTQ5NHNUVm1SUWpSNFpEaHBucGtBS3lUeWRqc0ZJdnY5MDNidFdiYndBcmppQWRzdUhNOGxkVEhmZk9HN0Q5Y184X3Y0UVpzaDVxT3E0cGhYNXVRZFhlR09rcjhpV1BuQkI3bjlhWTdWMmhjZUYxbG54UXZPZjBQSlJDOU0tUQ?oc=5</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipwFBVV95cUxPTHkxSzRncEk2Mlo2bHFuVWhUSU5tV1VoRktZV3h1RlRUVTQ5NHNUVm1SUWpSNFpEaHBucGtBS3lUeWRqc0ZJdnY5MDNidFdiYndBcmppQWRzdUhNOGxkVEhmZk9HN0Q5Y184X3Y0UVpzaDVxT3E0cGhYNXVRZFhlR09rcjhpV1BuQkI3bjlhWTdWMmhjZUYxbG54UXZPZjBQSlJDOU0tUQ?oc=5</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3105,42 +3105,42 @@
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>fbe6c9c66c0161f8</t>
+          <t>653af4c6fa9525c4</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T21:28:28Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? - OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa - Bhotekoshi flood: Urgent call for assistance - ReliefWeb</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa - Bhotekoshi flood: Urgent call for assistance ReliefWeb</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbTBubVpRWE5Ram5wd3BrcWU2TlJKa3ZLOXpmWEZ0NWZIQ0d1QW41ZTZBeUZMN0ltUHQ0dkZrMzV0dUNzbDFnQ3EtNXBVamJTTG1BM0hyRk1JcmZsREVYUVNxMkNXWGd0elFHa2JOZG44c0pSOTM3eklqa0QtQTdkVlllbWg3ejZVQ05HU3JqaG4?oc=5</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikAFBVV95cUxPbTBubVpRWE5Ram5wd3BrcWU2TlJKa3ZLOXpmWEZ0NWZIQ0d1QW41ZTZBeUZMN0ltUHQ0dkZrMzV0dUNzbDFnQ3EtNXBVamJTTG1BM0hyRk1JcmZsREVYUVNxMkNXWGd0elFHa2JOZG44c0pSOTM3eklqa0QtQTdkVlllbWg3ejZVQ05HU3JqaG4?oc=5</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3157,42 +3157,42 @@
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>70d0ca9c487a12e0</t>
+          <t>77b3c93490f3e8fb</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-09-25T04:54:40Z</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Families Await News of Relatives Lost in Bhote Koshi Flood - Ratopati</t>
+          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure - Nepalnews.com</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Families Await News of Relatives Lost in Bhote Koshi Flood Ratopati</t>
+          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure Nepalnews.com</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>e48b76688aaa7e3a</t>
+          <t>0dfaf4eea6b1deea</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -3219,32 +3219,32 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T18:38:31Z</t>
+          <t>2026-09-26T23:37:00Z</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing - Nepalnews.com</t>
+          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation - Ekantipur</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing Nepalnews.com</t>
+          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation Ekantipur</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>2855e2b2deb2042f</t>
+          <t>af8788f535313ce1</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -3271,32 +3271,32 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T19:32:35Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas - myRepublica</t>
+          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas myRepublica</t>
+          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>45f3087f0684f6b2</t>
+          <t>fbe6c9c66c0161f8</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -3323,32 +3323,32 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-09-23T21:28:28Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>For Bhotekoshi flood survivors, the tuin is an ordeal - The Kathmandu Post</t>
+          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>For Bhotekoshi flood survivors, the tuin is an ordeal The Kathmandu Post</t>
+          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3365,42 +3365,42 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>ba6c9c85501c553e</t>
+          <t>70d0ca9c487a12e0</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T04:52:16Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system - The Kathmandu Post</t>
+          <t>Families Await News of Relatives Lost in Bhote Koshi Flood - Ratopati</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system The Kathmandu Post</t>
+          <t>Families Await News of Relatives Lost in Bhote Koshi Flood Ratopati</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3417,42 +3417,42 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>6c8c666c29d070bc</t>
+          <t>e48b76688aaa7e3a</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-10-04T18:38:31Z</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) - ReliefWeb</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) ReliefWeb</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3469,42 +3469,42 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>42158f49795b8ff7</t>
+          <t>2855e2b2deb2042f</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T21:16:33Z</t>
+          <t>2026-10-11T19:32:35Z</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation - Ratopati</t>
+          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas - myRepublica</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation Ratopati</t>
+          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas myRepublica</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3521,42 +3521,42 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>f8be93f473f94b1f</t>
+          <t>45f3087f0684f6b2</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims - OnlineKhabar English News</t>
+          <t>For Bhotekoshi flood survivors, the tuin is an ordeal - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims OnlineKhabar English News</t>
+          <t>For Bhotekoshi flood survivors, the tuin is an ordeal The Kathmandu Post</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>eee0dd2411bff598</t>
+          <t>ba6c9c85501c553e</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -3583,32 +3583,32 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T16:55:33Z</t>
+          <t>2026-09-22T04:52:16Z</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
+          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
+          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system The Kathmandu Post</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2e6f49d4ffa969b3</t>
+          <t>6c8c666c29d070bc</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3635,32 +3635,32 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T10:44:33Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood - Nepalnews.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood Nepalnews.com</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>406ae4eb0f113f1e</t>
+          <t>42158f49795b8ff7</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:15:18Z</t>
+          <t>2026-09-22T21:16:33Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts - Nepalnews.com</t>
+          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation - Ratopati</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts Nepalnews.com</t>
+          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation Ratopati</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,42 +3729,42 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>639253c0e6c27bfc</t>
+          <t>f8be93f473f94b1f</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
+          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
+          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,17 +3781,17 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>e65a6f7e606852ff</t>
+          <t>eee0dd2411bff598</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-22T16:55:33Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -3801,22 +3801,22 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,42 +3833,42 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>a074d8d9f7cf953e</t>
+          <t>2e6f49d4ffa969b3</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T12:44:27Z</t>
+          <t>2026-10-12T10:44:33Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>The Tourism Times</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
+          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
+          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3885,12 +3885,12 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>8e672e38aa2a06b2</t>
+          <t>639253c0e6c27bfc</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,42 +3937,42 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>7ffe997ac778dbf1</t>
+          <t>e65a6f7e606852ff</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T22:00:24Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>f91e5ab1620e5293</t>
+          <t>8e672e38aa2a06b2</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T18:38:31Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4009,22 +4009,22 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>12225c63e0d58b53</t>
+          <t>7ffe997ac778dbf1</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -4051,32 +4051,32 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-10-05T22:00:24Z</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>104cdf9d46c50f0a</t>
+          <t>f91e5ab1620e5293</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T04:34:59Z</t>
+          <t>2026-10-04T18:38:31Z</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -4113,22 +4113,22 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4145,42 +4145,42 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>39ff34f1f426316f</t>
+          <t>12225c63e0d58b53</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T00:32:15Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4197,42 +4197,42 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>c6dcc4398d0f1aa3</t>
+          <t>104cdf9d46c50f0a</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-19T04:34:59Z</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>ed3cde30c6d7a272</t>
+          <t>c6dcc4398d0f1aa3</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -4259,32 +4259,32 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T23:56:47Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,42 +4301,42 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>5d30da09bcb70fcb</t>
+          <t>ed3cde30c6d7a272</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-10-04T23:56:47Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>339773c2b74968e7</t>
+          <t>5d30da09bcb70fcb</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T11:38:32Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>c16a9e76fde589cb</t>
+          <t>339773c2b74968e7</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4425,22 +4425,22 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>5dee575dde9896b2</t>
+          <t>c16a9e76fde589cb</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-17T11:38:32Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>63e3a3c4068798b8</t>
+          <t>5dee575dde9896b2</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T16:02:57Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -4529,22 +4529,22 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>5e6f3bf951c84b5e</t>
+          <t>63e3a3c4068798b8</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:15:18Z</t>
+          <t>2026-09-20T16:02:57Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -4581,22 +4581,22 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood - Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5809,42 +5809,42 @@
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>11efb1b5283d4658</t>
+          <t>a1c1bf932fb5fd38</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>269 children lost their parents in the Bhotekoshi flood - Ekantipur</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>269 children lost their parents in the Bhotekoshi flood Ekantipur</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXpXRGdraUZhbkd3VDh0Q09iODltSkdfcnJfaUlWbWE4eGQtZlpZTUdyX3phdEpuMXF6dXZtWUlQV1hvcU1UQUZ3ZE9pa1JqTFdmUmhYaTAtYWNpTDYzTFBtRVprbTNXak1QbmxlbnUyVVk5WHgtVEZ1Y201MFYzcVdzNHZWTW5PMzdTMERIYk1md2IzX0ZfMG13cEthaFVlX1ZxQ2h4a0E4cUk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>af991dce59e57aa5</t>
+          <t>8e369d28dac1be4d</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>8e369d28dac1be4d</t>
+          <t>410a103aaf7c4528</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6121,42 +6121,42 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>410a103aaf7c4528</t>
+          <t>b514eaf62f9a2f3a</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-09T01:12:32Z</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6173,17 +6173,17 @@
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>b514eaf62f9a2f3a</t>
+          <t>ab6e3de447176b06</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T01:12:32Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6225,7 +6225,7 @@
     <row r="113" ht="48" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>6974acfd82237ba0</t>
+          <t>37af945cd9bf0faa</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="114" ht="48" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>cf90c325291d2551</t>
+          <t>f032fc73f67f980a</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -6287,32 +6287,32 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T20:17:26Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood - The Kathmandu Post</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s growth to slow to 3.7 percent after devastating Rasuwa flood The Kathmandu Post</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQWVd5QllDdWhELVh5OHRvalZ6ejdxcnRQMFl4LUllaVVGRWFKaG52eUxRaEVfQlZUVkFMbDFFM01pR0ZFNmd5SGp4ZWNvWXNmWXJpVXZuczF4bldwSWJrOUZlWnpCTnRrUk1vV2tGcjNjWW1qTkliVWhWZHd3b1d5eE5QSmNXcS1CQjRUeVAwS1MydzRJb2NHRTlmZW9NWk9fY213Qy1EVXJ5QWJRVVBndw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -6329,42 +6329,42 @@
     <row r="115" ht="48" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>ab6e3de447176b06</t>
+          <t>8839b87cd0c93852</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
+          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact - Khabarhub</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
+          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact Khabarhub</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -6381,42 +6381,42 @@
     <row r="116" ht="48" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>37af945cd9bf0faa</t>
+          <t>e6fd7d2a17031541</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-05T14:32:40Z</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -6433,12 +6433,12 @@
     <row r="117" ht="48" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>f032fc73f67f980a</t>
+          <t>e8b8e3296cd3eb52</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -6448,27 +6448,27 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Greater Kashmir</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Greater Kashmir</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Greater Kashmir</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -6485,7 +6485,7 @@
     <row r="118" ht="48" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>af2418e17dcf9378</t>
+          <t>f6fd73d2d1d043d1</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -6495,32 +6495,32 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Press Trust of India</t>
+          <t>Progressive International</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Press Trust of India</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Press Trust of India</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOckIycW1iR0VXRnFlRmlxRU5NUDFSYWVOei1yb1lGSnhIa0V4XzYzcTBFTlk4eE0zMFBBU0VCcE1yN1oxVXQ3N0VvZ2RlWlNhVFVtTjEzZUk2cEF5N0lrNkd3RFhhRFpOV1YtS0JsVmNiSHBGZXB2bEF6QjFhZTRPaTdrN0FsdWFkWXpyLUI3dnBpUmlyV2NLdGgxTFhGUXpVMFphM3l6TXY4NWsydzRvRTd1cXJQaDV0MmgxS2ZTT2VyWFYyMmpnYVdnTm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOckIycW1iR0VXRnFlRmlxRU5NUDFSYWVOei1yb1lGSnhIa0V4XzYzcTBFTlk4eE0zMFBBU0VCcE1yN1oxVXQ3N0VvZ2RlWlNhVFVtTjEzZUk2cEF5N0lrNkd3RFhhRFpOV1YtS0JsVmNiSHBGZXB2bEF6QjFhZTRPaTdrN0FsdWFkWXpyLUI3dnBpUmlyV2NLdGgxTFhGUXpVMFphM3l6TXY4NWsydzRvRTd1cXJQaDV0MmgxS2ZTT2VyWFYyMmpnYVdnTm8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -6537,42 +6537,42 @@
     <row r="119" ht="48" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>8839b87cd0c93852</t>
+          <t>d424f9e7bb14efa4</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-02T17:51:36Z</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact - Khabarhub</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact Khabarhub</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -6589,42 +6589,42 @@
     <row r="120" ht="48" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>e6fd7d2a17031541</t>
+          <t>8c7cdae88307e58c</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T14:32:40Z</t>
+          <t>2026-10-01T18:24:29Z</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
+          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
+          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ200UDhDd0FoWmJ3dC0wakU4cEU4NE9heThMVzBhVkxUUl9YbTJuUHFkclVYUXN1RzlNMll3aXdWQm9DTkctMUdUdkl4SXFzUW9JdG1ZdkFUZU5IQWluRkh5V1VzUEFiWTRJQ0lsbUUtY3poaVJqaC1FWU9WaU5DUms5b3E0X3JzT2pNOFhvNWE0N0U5UTNwc1JJeGRBbnVvZzF6dHdEdFJySU1FVjdPUHJvaFlnVFBza2FLNmRhZk0zajlrNEVFbmNMSGxabldz?oc=5</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ200UDhDd0FoWmJ3dC0wakU4cEU4NE9heThMVzBhVkxUUl9YbTJuUHFkclVYUXN1RzlNMll3aXdWQm9DTkctMUdUdkl4SXFzUW9JdG1ZdkFUZU5IQWluRkh5V1VzUEFiWTRJQ0lsbUUtY3poaVJqaC1FWU9WaU5DUms5b3E0X3JzT2pNOFhvNWE0N0U5UTNwc1JJeGRBbnVvZzF6dHdEdFJySU1FVjdPUHJvaFlnVFBza2FLNmRhZk0zajlrNEVFbmNMSGxabldz?oc=5</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -6641,42 +6641,42 @@
     <row r="121" ht="48" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>e8b8e3296cd3eb52</t>
+          <t>879d526402f9918a</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Greater Kashmir</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Greater Kashmir</t>
+          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal - Khabarhub</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Greater Kashmir</t>
+          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal Khabarhub</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -6693,42 +6693,42 @@
     <row r="122" ht="48" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>f6fd73d2d1d043d1</t>
+          <t>e3676773315ce41e</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-03T23:46:07Z</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Progressive International</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -6745,42 +6745,42 @@
     <row r="123" ht="48" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>252af02ba0bf3af1</t>
+          <t>926f5cba9fb60a4e</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>The Tourism Times</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Over 800 Bhotekoshi flood displaced receive winter relief in Kathmandu holding centres - The Tourism Times</t>
+          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Over 800 Bhotekoshi flood displaced receive winter relief in Kathmandu holding centres The Tourism Times</t>
+          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal radionepalonline.com</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPZHlWWm5hZk90NVFqdXFGZ1Vud2ZrWDhvbGdZTHJBMS16Qmw1MUNBWDVzT0VXa3JhVDJIQkItREdtTUtoXzFCOUFhU2tfZ0p5akFRN19sNFRQNWw0b09DaXpxQWJUQzRNUGd1d09ycEdBUkR0bmktRG56OVJuVnpITEJ1eE1Jc2JySFBhMnZYZXg1QWN4S2VTUW5SancyTXFUS3ZZUEpkM05DS0lqTm5sdWljTmtwYXc0NGxEem0ydXgyX2NHN2ZNZTJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPZHlWWm5hZk90NVFqdXFGZ1Vud2ZrWDhvbGdZTHJBMS16Qmw1MUNBWDVzT0VXa3JhVDJIQkItREdtTUtoXzFCOUFhU2tfZ0p5akFRN19sNFRQNWw0b09DaXpxQWJUQzRNUGd1d09ycEdBUkR0bmktRG56OVJuVnpITEJ1eE1Jc2JySFBhMnZYZXg1QWN4S2VTUW5SancyTXFUS3ZZUEpkM05DS0lqTm5sdWljTmtwYXc0NGxEem0ydXgyX2NHN2ZNZTJR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -6797,42 +6797,42 @@
     <row r="124" ht="48" customHeight="1">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>d424f9e7bb14efa4</t>
+          <t>686c8f3418d0f4d9</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02T17:51:36Z</t>
+          <t>2026-09-30T20:00:18Z</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
+          <t>Government seeks alternative power supply after Bhotekoshi flood damages several hydropower projects - radionepalonline.com</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
+          <t>Government seeks alternative power supply after Bhotekoshi flood damages several hydropower projects radionepalonline.com</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9tbWoyZlJKVTNNdUZFaVhOVVIwVnJEV2R2cnRIN0FMYUlRRE0taUZNS1VhQWNqU29OZ1ljZXYxcnpuclFMaTY0Nmh3UWVpU09mWjVIcGlZb2FKVnZ2LWwyYm5YUEw?oc=5</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9tbWoyZlJKVTNNdUZFaVhOVVIwVnJEV2R2cnRIN0FMYUlRRE0taUZNS1VhQWNqU29OZ1ljZXYxcnpuclFMaTY0Nmh3UWVpU09mWjVIcGlZb2FKVnZ2LWwyYm5YUEw?oc=5</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -6849,42 +6849,42 @@
     <row r="125" ht="48" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>8c7cdae88307e58c</t>
+          <t>b676abbf2614ca1b</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T18:24:29Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing - Khabarhub</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Aims of Surkhet Entrepreneurial Couple Donate Rs 1.111 Million for Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing Khabarhub</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ200UDhDd0FoWmJ3dC0wakU4cEU4NE9heThMVzBhVkxUUl9YbTJuUHFkclVYUXN1RzlNMll3aXdWQm9DTkctMUdUdkl4SXFzUW9JdG1ZdkFUZU5IQWluRkh5V1VzUEFiWTRJQ0lsbUUtY3poaVJqaC1FWU9WaU5DUms5b3E0X3JzT2pNOFhvNWE0N0U5UTNwc1JJeGRBbnVvZzF6dHdEdFJySU1FVjdPUHJvaFlnVFBza2FLNmRhZk0zajlrNEVFbmNMSGxabldz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5uZ3RNRmdCdk1GcGprU2NmWndRcnhHVFBncElxeWJEdnlhSV83aGVfalRmWXBHNG83YWl3b0QtTTVTRUxJNG0xNGdXZlhpd1N4VUdvNVo5Sm4?oc=5</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ200UDhDd0FoWmJ3dC0wakU4cEU4NE9heThMVzBhVkxUUl9YbTJuUHFkclVYUXN1RzlNMll3aXdWQm9DTkctMUdUdkl4SXFzUW9JdG1ZdkFUZU5IQWluRkh5V1VzUEFiWTRJQ0lsbUUtY3poaVJqaC1FWU9WaU5DUms5b3E0X3JzT2pNOFhvNWE0N0U5UTNwc1JJeGRBbnVvZzF6dHdEdFJySU1FVjdPUHJvaFlnVFBza2FLNmRhZk0zajlrNEVFbmNMSGxabldz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5uZ3RNRmdCdk1GcGprU2NmWndRcnhHVFBncElxeWJEdnlhSV83aGVfalRmWXBHNG83YWl3b0QtTTVTRUxJNG0xNGdXZlhpd1N4VUdvNVo5Sm4?oc=5</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -6901,42 +6901,42 @@
     <row r="126" ht="48" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>879d526402f9918a</t>
+          <t>6269be2526b4a2c1</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal - Khabarhub</t>
+          <t>Bagmati CM seeks support from six provinces for Bhote Koshi flood reconstruction - Nepalnews.com</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal Khabarhub</t>
+          <t>Bagmati CM seeks support from six provinces for Bhote Koshi flood reconstruction Nepalnews.com</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTllJYnpWQTN4bm55REItcjJhTEIwelBRdmNBNTVaNjdBR2JWbV9kZjJZME1WdzR4bXpYdHk3MkZqZGlJT3hUcV9NMzB6Y1BwUmo3ZENLOHJXQVlwRVhRdUFORWQwbnZFMXAyZDNETHZSLUtlaHNPYXh6OWJ3cW5seVpaMnBOY2RJekkyZEtVdTQwZlJGcEZROC0xN1ZfeVpYWG9DeHFrQ1oybjNXUUdocFF0bFh4Nk9Mdl9wOUtvaw?oc=5</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOTllJYnpWQTN4bm55REItcjJhTEIwelBRdmNBNTVaNjdBR2JWbV9kZjJZME1WdzR4bXpYdHk3MkZqZGlJT3hUcV9NMzB6Y1BwUmo3ZENLOHJXQVlwRVhRdUFORWQwbnZFMXAyZDNETHZSLUtlaHNPYXh6OWJ3cW5seVpaMnBOY2RJekkyZEtVdTQwZlJGcEZROC0xN1ZfeVpYWG9DeHFrQ1oybjNXUUdocFF0bFh4Nk9Mdl9wOUtvaw?oc=5</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -6953,42 +6953,42 @@
     <row r="127" ht="48" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>e3676773315ce41e</t>
+          <t>6157c6160d3d8585</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03T23:46:07Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
+          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims - myRepublica</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
+          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims myRepublica</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOSU1MdElCTFh3VjhEN3BPNHJkaEpEOEtPbTV4VUJqZ0I0aWE5RnFQa0Y4eXZZR0NDejEzWkhxUm4tZ1RKaXVsWlZhcEdSSDBTQ25ZT2tJNmowa3M5MzJ0N0kzWEhlcFJ0c3E1QjQ5YVpwNXBDaHlWd0R4UWdodGZVU2p0OVlkYmhaWFc4ME9NZnQ4eVZlZHMtbG9Fak5LTXRnQ1NUQURlOWtuWjJaVEJFd2I0M190WV9neldoMHRmczkzNWxyV2ExdkxhSFQ5R2c?oc=5</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxOSU1MdElCTFh3VjhEN3BPNHJkaEpEOEtPbTV4VUJqZ0I0aWE5RnFQa0Y4eXZZR0NDejEzWkhxUm4tZ1RKaXVsWlZhcEdSSDBTQ25ZT2tJNmowa3M5MzJ0N0kzWEhlcFJ0c3E1QjQ5YVpwNXBDaHlWd0R4UWdodGZVU2p0OVlkYmhaWFc4ME9NZnQ4eVZlZHMtbG9Fak5LTXRnQ1NUQURlOWtuWjJaVEJFd2I0M190WV9neldoMHRmczkzNWxyV2ExdkxhSFQ5R2c?oc=5</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -7005,42 +7005,42 @@
     <row r="128" ht="48" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>926f5cba9fb60a4e</t>
+          <t>0b216c4d71927f79</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-27T16:56:20Z</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal - radionepalonline.com</t>
+          <t>Nepali diaspora donates $226,000 to Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal radionepalonline.com</t>
+          <t>Nepali diaspora donates $226,000 to Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93Ry0tSU9VcjFxQ0ZsWktraThGWkdLcFM4RW1udkxnQTFmNmF2Q1I1Y09DNWNzUm9DVnlWRW9vQWg4ZzkzZ3FLVkRETWlHUmlyaGRnOHNMQjk?oc=5</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93Ry0tSU9VcjFxQ0ZsWktraThGWkdLcFM4RW1udkxnQTFmNmF2Q1I1Y09DNWNzUm9DVnlWRW9vQWg4ZzkzZ3FLVkRETWlHUmlyaGRnOHNMQjk?oc=5</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -7057,42 +7057,42 @@
     <row r="129" ht="48" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>686c8f3418d0f4d9</t>
+          <t>a7a755478dffa44c</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Government seeks alternative power supply after Bhotekoshi flood damages several hydropower projects - radionepalonline.com</t>
+          <t>Hilsa deserted after the Bhotekoshi flood; 4,000 Indians cancel Kailash–Mansarovar pilgrimage - Ekantipur</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Government seeks alternative power supply after Bhotekoshi flood damages several hydropower projects radionepalonline.com</t>
+          <t>Hilsa deserted after the Bhotekoshi flood; 4,000 Indians cancel Kailash–Mansarovar pilgrimage Ekantipur</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9tbWoyZlJKVTNNdUZFaVhOVVIwVnJEV2R2cnRIN0FMYUlRRE0taUZNS1VhQWNqU29OZ1ljZXYxcnpuclFMaTY0Nmh3UWVpU09mWjVIcGlZb2FKVnZ2LWwyYm5YUEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1uc3JTYk1UVlMzUmJMeWMzLUwwX1Y5RGwyeW1NUzBueldMVXFncFMwa1NmN1lNS0wzTVRiWEc4Mzh1TTRJbWd6LTRMcHltNERuZGZhZ0hEelp5OERqaF9IX0JTSGNFaElwZWlQSHkzNWVOQTZLd3E4?oc=5</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE9tbWoyZlJKVTNNdUZFaVhOVVIwVnJEV2R2cnRIN0FMYUlRRE0taUZNS1VhQWNqU29OZ1ljZXYxcnpuclFMaTY0Nmh3UWVpU09mWjVIcGlZb2FKVnZ2LWwyYm5YUEw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMid0FVX3lxTE1uc3JTYk1UVlMzUmJMeWMzLUwwX1Y5RGwyeW1NUzBueldMVXFncFMwa1NmN1lNS0wzTVRiWEc4Mzh1TTRJbWd6LTRMcHltNERuZGZhZ0hEelp5OERqaF9IX0JTSGNFaElwZWlQSHkzNWVOQTZLd3E4?oc=5</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -7109,42 +7109,42 @@
     <row r="130" ht="48" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>b676abbf2614ca1b</t>
+          <t>f05e738f35008de0</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing - Khabarhub</t>
+          <t>Nepal Red Cross steps up relief efforts for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,454 bodies recovered, 4,718 still missing Khabarhub</t>
+          <t>Nepal Red Cross steps up relief efforts for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5uZ3RNRmdCdk1GcGprU2NmWndRcnhHVFBncElxeWJEdnlhSV83aGVfalRmWXBHNG83YWl3b0QtTTVTRUxJNG0xNGdXZlhpd1N4VUdvNVo5Sm4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNQlZOcnVDek84ck9IYTF1aWNpeVQ4VS1kMGxjbUJuT0RvN0lrUl9lckdYaW40T2Y1NDBXR21YLXpVREl5cmdaX3loMGo3dm95UU1GdXYyNEYwZlQzdWozX1JjUTVwRGNkRmI5X2psMUJNN1FpWDJhTHdERkdFNzU0TzRxSGZNby1uWE9ydUZHZ0RiTjljRTV6UW1yUEdTekhhSlBNUXJ6SFVEOGUyUkotUzZB?oc=5</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5uZ3RNRmdCdk1GcGprU2NmWndRcnhHVFBncElxeWJEdnlhSV83aGVfalRmWXBHNG83YWl3b0QtTTVTRUxJNG0xNGdXZlhpd1N4VUdvNVo5Sm4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNQlZOcnVDek84ck9IYTF1aWNpeVQ4VS1kMGxjbUJuT0RvN0lrUl9lckdYaW40T2Y1NDBXR21YLXpVREl5cmdaX3loMGo3dm95UU1GdXYyNEYwZlQzdWozX1JjUTVwRGNkRmI5X2psMUJNN1FpWDJhTHdERkdFNzU0TzRxSGZNby1uWE9ydUZHZ0RiTjljRTV6UW1yUEdTekhhSlBNUXJ6SFVEOGUyUkotUzZB?oc=5</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -7161,42 +7161,42 @@
     <row r="131" ht="48" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>6157c6160d3d8585</t>
+          <t>eb98e5c97842eaab</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims - myRepublica</t>
+          <t>One month on, Bhotekoshi flood’s scars still run deep - Khabarhub</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>NIA waives reporting deadline, eases documentation for Bhotekoshi flood claims myRepublica</t>
+          <t>One month on, Bhotekoshi flood’s scars still run deep Khabarhub</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOSU1MdElCTFh3VjhEN3BPNHJkaEpEOEtPbTV4VUJqZ0I0aWE5RnFQa0Y4eXZZR0NDejEzWkhxUm4tZ1RKaXVsWlZhcEdSSDBTQ25ZT2tJNmowa3M5MzJ0N0kzWEhlcFJ0c3E1QjQ5YVpwNXBDaHlWd0R4UWdodGZVU2p0OVlkYmhaWFc4ME9NZnQ4eVZlZHMtbG9Fak5LTXRnQ1NUQURlOWtuWjJaVEJFd2I0M190WV9neldoMHRmczkzNWxyV2ExdkxhSFQ5R2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE54dkdwdEo5Q2pONUJlUTRxcjhnVEVLQ0RNQTIwcV80RS1Ga25FVzYtVnFYWmQ1X2NpSi1vcXBHOFhZanljNlhNSGR2LXVkaktnMzdmbm56Vnk?oc=5</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxOSU1MdElCTFh3VjhEN3BPNHJkaEpEOEtPbTV4VUJqZ0I0aWE5RnFQa0Y4eXZZR0NDejEzWkhxUm4tZ1RKaXVsWlZhcEdSSDBTQ25ZT2tJNmowa3M5MzJ0N0kzWEhlcFJ0c3E1QjQ5YVpwNXBDaHlWd0R4UWdodGZVU2p0OVlkYmhaWFc4ME9NZnQ4eVZlZHMtbG9Fak5LTXRnQ1NUQURlOWtuWjJaVEJFd2I0M190WV9neldoMHRmczkzNWxyV2ExdkxhSFQ5R2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE54dkdwdEo5Q2pONUJlUTRxcjhnVEVLQ0RNQTIwcV80RS1Ga25FVzYtVnFYWmQ1X2NpSi1vcXBHOFhZanljNlhNSGR2LXVkaktnMzdmbm56Vnk?oc=5</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -7213,42 +7213,42 @@
     <row r="132" ht="48" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>0b216c4d71927f79</t>
+          <t>f7d089300b57fd94</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T16:56:20Z</t>
+          <t>2026-09-27T11:59:03Z</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Nepali diaspora donates $226,000 to Bhotekoshi flood victims - Khabarhub</t>
+          <t>UAE pledges additional $25 million for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Nepali diaspora donates $226,000 to Bhotekoshi flood victims Khabarhub</t>
+          <t>UAE pledges additional $25 million for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE93Ry0tSU9VcjFxQ0ZsWktraThGWkdLcFM4RW1udkxnQTFmNmF2Q1I1Y09DNWNzUm9DVnlWRW9vQWg4ZzkzZ3FLVkRETWlHUmlyaGRnOHNMQjk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZEVXZWlaYWNCY1MwVVRheHdDcDNHdHRvbzNqQUVvSWpURFpkR3pwY1A2YlBjU2FWWjlyeUtaTjNsS3RfaUYxMTdya08zMGNpWGNUZXdSTm1MZ3FQallKcGN0a3VkV18tYnF0SDg5Y3B5RXJYYmkta3ZMZG0wanFsejA4dEtuQV9tZk5uMFBQX1FNV3NoNEViT0d1R3VvLXF4X3EzbENQcGVSZVNtakJrWjdWTUltZDIzV2w0YlN3?oc=5</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE93Ry0tSU9VcjFxQ0ZsWktraThGWkdLcFM4RW1udkxnQTFmNmF2Q1I1Y09DNWNzUm9DVnlWRW9vQWg4ZzkzZ3FLVkRETWlHUmlyaGRnOHNMQjk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNZEVXZWlaYWNCY1MwVVRheHdDcDNHdHRvbzNqQUVvSWpURFpkR3pwY1A2YlBjU2FWWjlyeUtaTjNsS3RfaUYxMTdya08zMGNpWGNUZXdSTm1MZ3FQallKcGN0a3VkV18tYnF0SDg5Y3B5RXJYYmkta3ZMZG0wanFsejA4dEtuQV9tZk5uMFBQX1FNV3NoNEViT0d1R3VvLXF4X3EzbENQcGVSZVNtakJrWjdWTUltZDIzV2w0YlN3?oc=5</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -7265,42 +7265,42 @@
     <row r="133" ht="48" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>a7a755478dffa44c</t>
+          <t>cfdfc7443211b106</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-10-06T06:17:07Z</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Hilsa deserted after the Bhotekoshi flood; 4,000 Indians cancel Kailash–Mansarovar pilgrimage - Ekantipur</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Hilsa deserted after the Bhotekoshi flood; 4,000 Indians cancel Kailash–Mansarovar pilgrimage Ekantipur</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1uc3JTYk1UVlMzUmJMeWMzLUwwX1Y5RGwyeW1NUzBueldMVXFncFMwa1NmN1lNS0wzTVRiWEc4Mzh1TTRJbWd6LTRMcHltNERuZGZhZ0hEelp5OERqaF9IX0JTSGNFaElwZWlQSHkzNWVOQTZLd3E4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxONWNFM1Mzejc1OUJwSWxmZktOMVJJemo0djl1QmJjR3RXVVJHZGMwcFZaczRLQzlkQ0RoZU54aUwzVXIwWVBybzB2R1RKeFEtTlB0d3gyVUhSaV96N0tia2JzcWc1RzFSMWhFdGFEVDd4RVJOUU90dUpsV1B4Qmo3ZzBrbDFyMmpuX2FRdDJQekpNdjlmY0c2QW9HaTRmaDZuMUZHVVNjZEt2djZRYmRCdm5rN09IejdfYmJLTVpXcXgwT0dnTGYzVzNrakRqUnc?oc=5</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMid0FVX3lxTE1uc3JTYk1UVlMzUmJMeWMzLUwwX1Y5RGwyeW1NUzBueldMVXFncFMwa1NmN1lNS0wzTVRiWEc4Mzh1TTRJbWd6LTRMcHltNERuZGZhZ0hEelp5OERqaF9IX0JTSGNFaElwZWlQSHkzNWVOQTZLd3E4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxONWNFM1Mzejc1OUJwSWxmZktOMVJJemo0djl1QmJjR3RXVVJHZGMwcFZaczRLQzlkQ0RoZU54aUwzVXIwWVBybzB2R1RKeFEtTlB0d3gyVUhSaV96N0tia2JzcWc1RzFSMWhFdGFEVDd4RVJOUU90dUpsV1B4Qmo3ZzBrbDFyMmpuX2FRdDJQekpNdjlmY0c2QW9HaTRmaDZuMUZHVVNjZEt2djZRYmRCdm5rN09IejdfYmJLTVpXcXgwT0dnTGYzVzNrakRqUnc?oc=5</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="134" ht="48" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>f05e738f35008de0</t>
+          <t>696cf77b77cec8a9</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T05:20:23Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -7337,22 +7337,22 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Nepal Red Cross steps up relief efforts for Bhotekoshi flood victims - myRepublica</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Nepal Red Cross steps up relief efforts for Bhotekoshi flood victims myRepublica</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNQlZOcnVDek84ck9IYTF1aWNpeVQ4VS1kMGxjbUJuT0RvN0lrUl9lckdYaW40T2Y1NDBXR21YLXpVREl5cmdaX3loMGo3dm95UU1GdXYyNEYwZlQzdWozX1JjUTVwRGNkRmI5X2psMUJNN1FpWDJhTHdERkdFNzU0TzRxSGZNby1uWE9ydUZHZ0RiTjljRTV6UW1yUEdTekhhSlBNUXJ6SFVEOGUyUkotUzZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOOGd0ZHVsQ1lvS2dGblhEX1pPdDZ2NEpmTEROUHRTSGpFcXduWm5fZDAtRTk4VDZGRUxseXo2Mk8wUVdIcEFDaU9Gby1rRy1URE9lOVRLSjR1YWRtQ2pIdkpOSTMzLVY1U1B2YW9qUnNOV1ZyVldFdTAxMFloZFBwRlZ4Vjc5QnZzMHdXLW5DN0JJM0szQVA3N195cFd6UFhFLVVuSjQtVXR2OU9vZ1k2ZlhKbHV6cjhmU1g0cGZfN2hEMTJUSlZ2YVJ3?oc=5</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNQlZOcnVDek84ck9IYTF1aWNpeVQ4VS1kMGxjbUJuT0RvN0lrUl9lckdYaW40T2Y1NDBXR21YLXpVREl5cmdaX3loMGo3dm95UU1GdXYyNEYwZlQzdWozX1JjUTVwRGNkRmI5X2psMUJNN1FpWDJhTHdERkdFNzU0TzRxSGZNby1uWE9ydUZHZ0RiTjljRTV6UW1yUEdTekhhSlBNUXJ6SFVEOGUyUkotUzZB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOOGd0ZHVsQ1lvS2dGblhEX1pPdDZ2NEpmTEROUHRTSGpFcXduWm5fZDAtRTk4VDZGRUxseXo2Mk8wUVdIcEFDaU9Gby1rRy1URE9lOVRLSjR1YWRtQ2pIdkpOSTMzLVY1U1B2YW9qUnNOV1ZyVldFdTAxMFloZFBwRlZ4Vjc5QnZzMHdXLW5DN0JJM0szQVA3N195cFd6UFhFLVVuSjQtVXR2OU9vZ1k2ZlhKbHV6cjhmU1g0cGZfN2hEMTJUSlZ2YVJ3?oc=5</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -7369,7 +7369,7 @@
     <row r="135" ht="48" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>eb98e5c97842eaab</t>
+          <t>0f3a9f8fb87a2c7f</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -7379,32 +7379,32 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>One month on, Bhotekoshi flood’s scars still run deep - Khabarhub</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>One month on, Bhotekoshi flood’s scars still run deep Khabarhub</t>
+          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE54dkdwdEo5Q2pONUJlUTRxcjhnVEVLQ0RNQTIwcV80RS1Ga25FVzYtVnFYWmQ1X2NpSi1vcXBHOFhZanljNlhNSGR2LXVkaktnMzdmbm56Vnk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOZXhob3U2RkZaTzVzck5uWldrNVJjeHZYcE00ME5TYVpSdE95a2g5ZHJudktjTnBsdHdQSWIzdjZ2X0NzSjhTQWFCeF8weXMyMTEyN3pVWkVQV29pTDY4QTZRamRwdDdBQ01JbE5YeDF3dUhPa1NMR0VXZDd3M2VfeXpTaG9LX2pkb2NqdmR5QWJIUWFKRXZOeDAyWkZUelBfV2hKdUpTRmJxaU1QVWJSdW53SW9kZmRjRjhzYkVpNkFUc1pfR0otcE1OQmpCM1NpalpGVkhreE5SN2p1?oc=5</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE54dkdwdEo5Q2pONUJlUTRxcjhnVEVLQ0RNQTIwcV80RS1Ga25FVzYtVnFYWmQ1X2NpSi1vcXBHOFhZanljNlhNSGR2LXVkaktnMzdmbm56Vnk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxOZXhob3U2RkZaTzVzck5uWldrNVJjeHZYcE00ME5TYVpSdE95a2g5ZHJudktjTnBsdHdQSWIzdjZ2X0NzSjhTQWFCeF8weXMyMTEyN3pVWkVQV29pTDY4QTZRamRwdDdBQ01JbE5YeDF3dUhPa1NMR0VXZDd3M2VfeXpTaG9LX2pkb2NqdmR5QWJIUWFKRXZOeDAyWkZUelBfV2hKdUpTRmJxaU1QVWJSdW53SW9kZmRjRjhzYkVpNkFUc1pfR0otcE1OQmpCM1NpalpGVkhreE5SN2p1?oc=5</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -7421,17 +7421,17 @@
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>f7d089300b57fd94</t>
+          <t>1f6c419cec878e51</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T11:59:03Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -7441,22 +7441,22 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>UAE pledges additional $25 million for Bhotekoshi flood victims - myRepublica</t>
+          <t>201 parents, 38 students missing in Rasuwa flood - myRepublica</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>UAE pledges additional $25 million for Bhotekoshi flood victims myRepublica</t>
+          <t>201 parents, 38 students missing in Rasuwa flood myRepublica</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZEVXZWlaYWNCY1MwVVRheHdDcDNHdHRvbzNqQUVvSWpURFpkR3pwY1A2YlBjU2FWWjlyeUtaTjNsS3RfaUYxMTdya08zMGNpWGNUZXdSTm1MZ3FQallKcGN0a3VkV18tYnF0SDg5Y3B5RXJYYmkta3ZMZG0wanFsejA4dEtuQV9tZk5uMFBQX1FNV3NoNEViT0d1R3VvLXF4X3EzbENQcGVSZVNtakJrWjdWTUltZDIzV2w0YlN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNZEVXZWlaYWNCY1MwVVRheHdDcDNHdHRvbzNqQUVvSWpURFpkR3pwY1A2YlBjU2FWWjlyeUtaTjNsS3RfaUYxMTdya08zMGNpWGNUZXdSTm1MZ3FQallKcGN0a3VkV18tYnF0SDg5Y3B5RXJYYmkta3ZMZG0wanFsejA4dEtuQV9tZk5uMFBQX1FNV3NoNEViT0d1R3VvLXF4X3EzbENQcGVSZVNtakJrWjdWTUltZDIzV2w0YlN3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="137" ht="48" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>cfdfc7443211b106</t>
+          <t>bbfc4fc9ec971ea7</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T06:17:07Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -7493,22 +7493,22 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
+          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing - myRepublica</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
+          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing myRepublica</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxONWNFM1Mzejc1OUJwSWxmZktOMVJJemo0djl1QmJjR3RXVVJHZGMwcFZaczRLQzlkQ0RoZU54aUwzVXIwWVBybzB2R1RKeFEtTlB0d3gyVUhSaV96N0tia2JzcWc1RzFSMWhFdGFEVDd4RVJOUU90dUpsV1B4Qmo3ZzBrbDFyMmpuX2FRdDJQekpNdjlmY0c2QW9HaTRmaDZuMUZHVVNjZEt2djZRYmRCdm5rN09IejdfYmJLTVpXcXgwT0dnTGYzVzNrakRqUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxONWNFM1Mzejc1OUJwSWxmZktOMVJJemo0djl1QmJjR3RXVVJHZGMwcFZaczRLQzlkQ0RoZU54aUwzVXIwWVBybzB2R1RKeFEtTlB0d3gyVUhSaV96N0tia2JzcWc1RzFSMWhFdGFEVDd4RVJOUU90dUpsV1B4Qmo3ZzBrbDFyMmpuX2FRdDJQekpNdjlmY0c2QW9HaTRmaDZuMUZHVVNjZEt2djZRYmRCdm5rN09IejdfYmJLTVpXcXgwT0dnTGYzVzNrakRqUnc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -7525,42 +7525,42 @@
     <row r="138" ht="48" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>696cf77b77cec8a9</t>
+          <t>659e477407972cf2</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-25T04:54:40Z</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
+          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ - Khabarhub</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
+          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ Khabarhub</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOOGd0ZHVsQ1lvS2dGblhEX1pPdDZ2NEpmTEROUHRTSGpFcXduWm5fZDAtRTk4VDZGRUxseXo2Mk8wUVdIcEFDaU9Gby1rRy1URE9lOVRLSjR1YWRtQ2pIdkpOSTMzLVY1U1B2YW9qUnNOV1ZyVldFdTAxMFloZFBwRlZ4Vjc5QnZzMHdXLW5DN0JJM0szQVA3N195cFd6UFhFLVVuSjQtVXR2OU9vZ1k2ZlhKbHV6cjhmU1g0cGZfN2hEMTJUSlZ2YVJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOOGd0ZHVsQ1lvS2dGblhEX1pPdDZ2NEpmTEROUHRTSGpFcXduWm5fZDAtRTk4VDZGRUxseXo2Mk8wUVdIcEFDaU9Gby1rRy1URE9lOVRLSjR1YWRtQ2pIdkpOSTMzLVY1U1B2YW9qUnNOV1ZyVldFdTAxMFloZFBwRlZ4Vjc5QnZzMHdXLW5DN0JJM0szQVA3N195cFd6UFhFLVVuSjQtVXR2OU9vZ1k2ZlhKbHV6cjhmU1g0cGZfN2hEMTJUSlZ2YVJ3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -7577,42 +7577,42 @@
     <row r="139" ht="48" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>0f3a9f8fb87a2c7f</t>
+          <t>dd5f23720e096ffa</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world - myRepublica</t>
+          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count - The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>PM Shah makes passionate appeal for climate action, calls Bhotekoshi flood a warning to world myRepublica</t>
+          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count The Loss and Damage Collaboration</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOZXhob3U2RkZaTzVzck5uWldrNVJjeHZYcE00ME5TYVpSdE95a2g5ZHJudktjTnBsdHdQSWIzdjZ2X0NzSjhTQWFCeF8weXMyMTEyN3pVWkVQV29pTDY4QTZRamRwdDdBQ01JbE5YeDF3dUhPa1NMR0VXZDd3M2VfeXpTaG9LX2pkb2NqdmR5QWJIUWFKRXZOeDAyWkZUelBfV2hKdUpTRmJxaU1QVWJSdW53SW9kZmRjRjhzYkVpNkFUc1pfR0otcE1OQmpCM1NpalpGVkhreE5SN2p1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxOZXhob3U2RkZaTzVzck5uWldrNVJjeHZYcE00ME5TYVpSdE95a2g5ZHJudktjTnBsdHdQSWIzdjZ2X0NzSjhTQWFCeF8weXMyMTEyN3pVWkVQV29pTDY4QTZRamRwdDdBQ01JbE5YeDF3dUhPa1NMR0VXZDd3M2VfeXpTaG9LX2pkb2NqdmR5QWJIUWFKRXZOeDAyWkZUelBfV2hKdUpTRmJxaU1QVWJSdW53SW9kZmRjRjhzYkVpNkFUc1pfR0otcE1OQmpCM1NpalpGVkhreE5SN2p1?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="140" ht="48" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>1f6c419cec878e51</t>
+          <t>f1e11b960864e93a</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -7639,32 +7639,32 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>201 parents, 38 students missing in Rasuwa flood - myRepublica</t>
+          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for - radionepalonline.com</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>201 parents, 38 students missing in Rasuwa flood myRepublica</t>
+          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for radionepalonline.com</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipAFBVV95cUxQNThRUExNd3V6QUx4aElCVVRrWHlyYXRrbEx4Z2J5c2NPSVdhNGdLR0RPbkpDVG1oWnVEcnhtSzBMWm5kZVJTN0xkb2dZQXJoM2p2cU9odktELVdlSmNUVmp2Smh1YkU2eVRYano1RkszbHZqcTMxQUJKX0ZaUGNlMk9yNy1QMVVoTm84V1FyQmNrRV9aRHFweFQ2NHhFclFmN2daaA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -7681,17 +7681,17 @@
     <row r="141" ht="48" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>bbfc4fc9ec971ea7</t>
+          <t>c2a5c1a2976b2e2c</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-23T21:28:28Z</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -7701,22 +7701,22 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing - myRepublica</t>
+          <t>Bhotekoshi flood: US to provide additional $31 million in aid - myRepublica</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves 338 trucks, 440 drivers, helpers missing myRepublica</t>
+          <t>Bhotekoshi flood: US to provide additional $31 million in aid myRepublica</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxOTVozTHdUYjVBVi1mTkNaSTRscENSTzF6bWlta2hJeHNOMnhOZUNRMjhadXJub0lpQl9JMTdOWS1zSTIwWEFLekxWdzFLakVmSER5dmQzZTZOWEFDZWtUYjdOQW9iak9jX2V2bGVxZkVUV2ZrNTFvb01ueUU1bXFnRGNRLWRQd21HaW1GOEd0d2RJWkYwbGN5bnRKZzBXNjIxbW1YbjVTYjVwdGw0bFN4cTNEU2puT2Zy?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -7733,42 +7733,42 @@
     <row r="142" ht="48" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>659e477407972cf2</t>
+          <t>8d1bfbbdb90796c5</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T04:54:40Z</t>
+          <t>2026-09-25T17:08:24Z</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Setopati</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ - Khabarhub</t>
+          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya - Setopati</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>PM Balen asks at UNGA: ‘The Bhotekoshi flood was a warning to the world—did you hear it?’ Khabarhub</t>
+          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya Setopati</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBXeF9hWUVWWEpxTDNzRmdxbS13WEdkUjVzeS1VUG83UDFFZGZqMmFXeklmbjhGTXNSWFhMREUxSndHWk52STJJTFlSQUlibWNSdnNCT0xKRE8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -7785,42 +7785,42 @@
     <row r="143" ht="48" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>dd5f23720e096ffa</t>
+          <t>b5cefde113f20b10</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>The Loss and Damage Collaboration</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count - The Loss and Damage Collaboration</t>
+          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood - The Annapurna Express</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Invisible Erosion: What the Bhotekoshi flood took that we cannot count The Loss and Damage Collaboration</t>
+          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood The Annapurna Express</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNVERJSUhZVTVhYklCWG9nbk5leWhsbFFXYThHZmdzaXJsTm1EdDJvdmduUEpzd1J0SWM2YjRESjBvdHZHQ3ZyN00zVEdWd3Z1azdkV2VTT25jdW1tcHFJaHpQSFdBbmRWc1pPOHR3LWdDSlBlM3N3ZG5ULVp0enFYVGNZeGp5NkVfZms3X1FfQVM5NUh1UlFFTndtT0NrNjRRLTRXSmxqaEpNU1IwV09TeWJDdEhNMkxFQ25COUFrQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -7837,42 +7837,42 @@
     <row r="144" ht="48" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>f1e11b960864e93a</t>
+          <t>406ae4eb0f113f1e</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-10-12T21:15:18Z</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for - radionepalonline.com</t>
+          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts - Nepalnews.com</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Three representatives from Rasuwa still unaccounted for radionepalonline.com</t>
+          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts Nepalnews.com</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5UU2JQVWFTeFZTWmFnRmotaVRBWE13QktUWHk1V1UyQUFjWGswblZQbmpsR0xOLXlGem9Td3YtLWd5S256S3pacVBVdVZNRjJ1aWpmbXg3a0lJd1pEMFBHdklzTjY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -7889,42 +7889,42 @@
     <row r="145" ht="48" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>c2a5c1a2976b2e2c</t>
+          <t>2a300e5247974c0e</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T21:28:28Z</t>
+          <t>2026-09-23T11:32:09Z</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: US to provide additional $31 million in aid - myRepublica</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: US to provide additional $31 million in aid myRepublica</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7941,42 +7941,42 @@
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>8d1bfbbdb90796c5</t>
+          <t>a074d8d9f7cf953e</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T17:08:24Z</t>
+          <t>2026-09-21T12:44:27Z</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Setopati</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya - Setopati</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya Setopati</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -7993,42 +7993,42 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>b5cefde113f20b10</t>
+          <t>f60efed8fd40992a</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-10-11T19:32:35Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood - The Annapurna Express</t>
+          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary - The Rising Nepal</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood The Annapurna Express</t>
+          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary The Rising Nepal</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,42 +8045,42 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>2a300e5247974c0e</t>
+          <t>4a93f7eb5178c8ad</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T11:32:09Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>f60efed8fd40992a</t>
+          <t>c25c8930bdcedd55</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -8107,32 +8107,32 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T19:32:35Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary - The Rising Nepal</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary The Rising Nepal</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>4a93f7eb5178c8ad</t>
+          <t>fd633a6a2a2a1810</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-09-21T04:52:28Z</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="151" ht="48" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>c25c8930bdcedd55</t>
+          <t>3d1620d408627250</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -8211,32 +8211,32 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-09-22T00:04:58Z</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -8253,42 +8253,42 @@
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>fd633a6a2a2a1810</t>
+          <t>399c31fb867245f3</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T04:52:28Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8305,42 +8305,42 @@
     <row r="153" ht="48" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>3d1620d408627250</t>
+          <t>1a65df9c73c0c5f1</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T00:04:58Z</t>
+          <t>2026-09-27T05:15:51Z</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>399c31fb867245f3</t>
+          <t>25275754a5c497fa</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -8367,32 +8367,32 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="155" ht="48" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>1a65df9c73c0c5f1</t>
+          <t>09825b491361a412</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -8419,32 +8419,32 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T05:15:51Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>25275754a5c497fa</t>
+          <t>535fbbf54d3b4684</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -8471,32 +8471,32 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-27T16:56:20Z</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Khoj Samachar</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="157" ht="48" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>09825b491361a412</t>
+          <t>10604521935094cd</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -8523,32 +8523,32 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>535fbbf54d3b4684</t>
+          <t>6ec42694b67ab866</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -8575,32 +8575,32 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T16:56:20Z</t>
+          <t>2026-09-20T20:47:03Z</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Khoj Samachar</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8617,42 +8617,42 @@
     <row r="159" ht="48" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>10604521935094cd</t>
+          <t>39ff34f1f426316f</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-10-01T00:32:15Z</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8669,42 +8669,42 @@
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>6ec42694b67ab866</t>
+          <t>af40c0f4cdd9b4d0</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T20:47:03Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>af40c0f4cdd9b4d0</t>
+          <t>bb5552718a993013</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-09-28T13:50:00Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>bb5552718a993013</t>
+          <t>c5054155e8d76e19</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T13:50:00Z</t>
+          <t>2026-09-19T15:51:25Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -8793,22 +8793,22 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>c5054155e8d76e19</t>
+          <t>4a782c7db12159fc</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8835,32 +8835,32 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T15:51:25Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,42 +8877,42 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>4a782c7db12159fc</t>
+          <t>cc153ab4c5f0bc02</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>cc153ab4c5f0bc02</t>
+          <t>26e0f34695ac0146</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -8939,32 +8939,32 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>26e0f34695ac0146</t>
+          <t>bf0bd71a8811a3de</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -8991,32 +8991,32 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-09-18T16:22:29Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>bf0bd71a8811a3de</t>
+          <t>caa83d5807a4f588</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T16:22:29Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>caa83d5807a4f588</t>
+          <t>5aeddf14059c9769</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>chinachristiandaily.com</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>5aeddf14059c9769</t>
+          <t>81625d31ed27040d</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>chinachristiandaily.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>81625d31ed27040d</t>
+          <t>382aacee35c12bd2</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -9199,32 +9199,32 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
+          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
+          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>382aacee35c12bd2</t>
+          <t>c953c8abf57268ed</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,32 +9251,32 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepali Patro</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>c953c8abf57268ed</t>
+          <t>11bd9764f90f4f0b</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,32 +9303,32 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Nepali Patro</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>11bd9764f90f4f0b</t>
+          <t>718a52966e5afa2e</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -9355,32 +9355,32 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>718a52966e5afa2e</t>
+          <t>7c3d1c068a76eb4d</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -9412,27 +9412,27 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Setopati</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,42 +9449,42 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>7c3d1c068a76eb4d</t>
+          <t>5e6f3bf951c84b5e</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-10-12T21:15:18Z</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Setopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
+          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
+          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13T19:14:49Z</t>
+          <t>2026-10-14T00:16:32Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13T19:14:49Z · 854 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-14T00:16:32Z · 854 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>8f5026d4b74c2e76</t>
+          <t>902d716c8ffa7987</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-07T18:56:09Z</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
+          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1285,42 +1285,42 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>902d716c8ffa7987</t>
+          <t>6974acfd82237ba0</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T18:56:09Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Devdiscourse</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk - Devdiscourse</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Growth Slows After Rasuwa Flood as Rebuilding Tests Its Readiness for Risk Devdiscourse</t>
+          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdTRnMWlzTG9qZTctOFFjUUlPSnFDb2hPa3hTa3dWZHQxUUt6MWFreUpPUTQtN0EwVjVaa2NwaFRJbTAxOFUtM3RuQ3M4bGdvLU0wYzdHdS1HZkt6YnI2UVhRaTVDRWlxQjBmZU9qZ3Z0a3pHNVZiamp4WnRtYjNyRklaQkdnUkdvWGhMSkZLM1huZ2JSSERsYVp6YWJZOEY4a1AwN095VWJGRTdYMFc3VmFHQU5uOG0wTkZpNFFZUjBmTDJST1dFelZIM0xnQ2Y10gHWAUFVX3lxTE94WDVpby1YYjlUNEJiaFJPSEZ0T0J0R19nZUxoaHJkZldKWUZES2o2aHJ3RjRJSHM2YkVfbDRqanhDNDJHem5ZRUhyd2ZPR2tfWEJrQkpIdlZkRURQUEVxSDJROUVaVUszbzlFWTFEQThLZVVwVTJ5RGZuaDVDSjV0dWFiYU1sa01TSHhVdmtRVV93dVU2VmhocDZRVjM5LUdQeUJMN0NkZlNVc1FmREhrcm1nT0xuTWFCTFlvdElPaHpoVDFDWmhONzhFOE9lMmJDU0cxN1E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3105,42 +3105,42 @@
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>77b3c93490f3e8fb</t>
+          <t>0dfaf4eea6b1deea</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T04:54:40Z</t>
+          <t>2026-09-26T23:37:00Z</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure - Nepalnews.com</t>
+          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation - Ekantipur</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure Nepalnews.com</t>
+          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation Ekantipur</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>0dfaf4eea6b1deea</t>
+          <t>af8788f535313ce1</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T23:37:00Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation - Ekantipur</t>
+          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>JCB India Honors Those Deployed in the Bhote Koshi Flood Rescue Operation Ekantipur</t>
+          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNYS12ZmxfeGZ4TlZ0WTFZNWdwUHZZUnBFRmNIZW1yQmo2dG53b28xeTFlQ2hpVGdkQkVDSDlfS3hQRl9GaXZGRU53NEd1T0tpdnZ2OWRRM283ckhWSlVVQkNuRXV0QUk2Vlc1c1NaUTM4QlEySFhhalJSc2dvRkJUWW9sNEJQQzVnWVN4NE00NmpBWlZUdlFnVkxtWDlIWThydWZXbkZIcFAxRkVIZjhSdkxB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>af8788f535313ce1</t>
+          <t>fbe6c9c66c0161f8</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -3219,32 +3219,32 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-09-23T21:28:28Z</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims - Ratopati</t>
+          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>ECAN Jhapa Donates NPR 1 Million for Rasuwa Flood Victims Ratopati</t>
+          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxQQUw5emN1dzhKS08tNGJkc3FVdjVLNkVYeGRteXVRdHVvOVUweldOMTFONThFaWd2R3NMbVdrU3FLV3JxbUpKbmtkQkNHd2JoMGhDME55SFNESlhHWExoTUw1b243ZXJLUjJLRTB3bm1zM2dUanIwamsyczBJanFZaVowMU1IdEJsYjRpVU0tLWVBRllQazBmd1pseUY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>fbe6c9c66c0161f8</t>
+          <t>70d0ca9c487a12e0</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -3271,32 +3271,32 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T21:28:28Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? - OnlineKhabar English News</t>
+          <t>Families Await News of Relatives Lost in Bhote Koshi Flood - Ratopati</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>After Nepal’s Bhotekoshi flood, who pays for the damage? OnlineKhabar English News</t>
+          <t>Families Await News of Relatives Lost in Bhote Koshi Flood Ratopati</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE8tTE9jY1FvOTJTZGo4TWkydmtiNi1WdlJBcnNZV3MwSzBWN3ZyNHZjRndEeFVBVHR3WWYtUGlrNzhXQXpwTU9CczNEcWdybE9MeDNKYXpEM3ItTTY1VFJWM2hxWmtENWxSSVlSdW1kOTlxYVpRUDhnZFln?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>70d0ca9c487a12e0</t>
+          <t>e48b76688aaa7e3a</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -3323,32 +3323,32 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-10-04T18:38:31Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Families Await News of Relatives Lost in Bhote Koshi Flood - Ratopati</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Families Await News of Relatives Lost in Bhote Koshi Flood Ratopati</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPYko4UFRnSk4xZHg1REFsR3RETEQxUnpkUzJBSlp6bHNBUTU3cDRiSnFZM1l5cURSY0pWMTA1ODRKWjNfSUNWVXl3UEJFRzBTRG14QTBtX25IdVlSNnBYdjFEX29fbFhPVHFNOWh3Q1RLcU41WElWMFljSy02cWtYU2U0VkUxcUhibkJhdkxvNkpFaUpkZWJTM2piZ1JXeGhwVHFLY01tRm1OclUxOEpZeGZ1cWJkLVJOOXBqRHRFN29WV0NjMThNMUJNSlRtdXlMZXVmT1pWUDhUbkJx?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>e48b76688aaa7e3a</t>
+          <t>2855e2b2deb2042f</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T18:38:31Z</t>
+          <t>2026-10-11T19:32:35Z</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas - myRepublica</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,452; over 4,700 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas myRepublica</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaFAydmtEY1hXX3dTdGRfMUFqMU1wcTJQV3dmWUNmYVdjV25oM1E3MjdBLXlzWkxYb3NqRlJWOWNvZWh1SlhzMUZmMXRSSzBXb0RzTEpQNWxrUERRWVdHNlMwOTlOTlIyMS1SQW1qQzZGSVpTWkJDTnk4VXBmNUQtZ2J2NmQzclpsQ1lyckhjZjBYR1VTYTJKS0FiSUZXUGkzdHUxQTIwbFFNdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2855e2b2deb2042f</t>
+          <t>45f3087f0684f6b2</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T19:32:35Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas - myRepublica</t>
+          <t>For Bhotekoshi flood survivors, the tuin is an ordeal - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt to restrict building permanent homes in flood-hit areas myRepublica</t>
+          <t>For Bhotekoshi flood survivors, the tuin is an ordeal The Kathmandu Post</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizwFBVV95cUxPS2tQSFhkeWN0MHQyMVk1OF9FV1ZFTnRDVloyTmdIbjMxd3RlUExKYWtPRkt1bnRXSmltU3dEanRRZlZnQUFhUTBzb2tXU252ZVVWLWhhc05zUGVQYk14VGFDNFhNd29QUzhwd0JZbUlZNnlBVk5YUnZQRERKN1FoOURXdlBPdXBLVlBXMWFSM0RzTTlsSkc1eXVnd0VyTHhlZGE1cGpqek52QmVhZTdjMC1HMjBvdzJ2WUpBMGk5ZndvUlBFdjBvR1AtbV8yTmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>45f3087f0684f6b2</t>
+          <t>65de24a358e93196</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -3479,32 +3479,32 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-10-13T10:31:33Z</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>For Bhotekoshi flood survivors, the tuin is an ordeal - The Kathmandu Post</t>
+          <t>China provides equipment and technology for DNA testing of Rasuwa flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>For Bhotekoshi flood survivors, the tuin is an ordeal The Kathmandu Post</t>
+          <t>China provides equipment and technology for DNA testing of Rasuwa flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOF9iekRvalRrUlJtc29aRzJITHhoV1JybTNMdUc1YnM1RVEydl91SldWdTZHOTIxQW0tSjM2cjhHTjQzTUpBNTBiZ2pZNWZVVUQxRW0xU0dwUXZPbWNxSHFaWFZQQWRFMW1tc2dBZFNaYkx6YlJyZEo0NmF6NG5nQWlrbW1pSkQ0VUZkTGhkeHVZMF9YT3pZMV9sT2FwU1ZEdFVINzh6b3M3SUF4RE1HQlQxcElfTk4y?oc=5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxObnVTNi0xWDJIb2J2Z0dFRWZoRjcySmRmd0JWQmVtYmFwU3FzVENLb0EyY1l0akt4MVhMSzZua3FZMXBCbVprTEFjenRtMHBmaTdwc1Mwck43VjMxQmJUU3g3c3hLcktXeDBpX2NmSm0wUWVRWUZNMkFRNE9Gck1MLUVqVlhidDY4NHE5SjBVeUpVeDNkcmtBYkZrX1NVUGJ6Tl94VWtB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOF9iekRvalRrUlJtc29aRzJITHhoV1JybTNMdUc1YnM1RVEydl91SldWdTZHOTIxQW0tSjM2cjhHTjQzTUpBNTBiZ2pZNWZVVUQxRW0xU0dwUXZPbWNxSHFaWFZQQWRFMW1tc2dBZFNaYkx6YlJyZEo0NmF6NG5nQWlrbW1pSkQ0VUZkTGhkeHVZMF9YT3pZMV9sT2FwU1ZEdFVINzh6b3M3SUF4RE1HQlQxcElfTk4y?oc=5</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>65de24a358e93196</t>
+          <t>40d913556db308cb</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13T10:31:33Z</t>
+          <t>2026-10-13T19:14:49Z</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>China provides equipment and technology for DNA testing of Rasuwa flood victims - OnlineKhabar English News</t>
+          <t>MP Bharat Parajuli Draws Attention to BhoteKoshi Flood Victims' Relief - Ratopati</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>China provides equipment and technology for DNA testing of Rasuwa flood victims OnlineKhabar English News</t>
+          <t>MP Bharat Parajuli Draws Attention to BhoteKoshi Flood Victims' Relief Ratopati</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOF9iekRvalRrUlJtc29aRzJITHhoV1JybTNMdUc1YnM1RVEydl91SldWdTZHOTIxQW0tSjM2cjhHTjQzTUpBNTBiZ2pZNWZVVUQxRW0xU0dwUXZPbWNxSHFaWFZQQWRFMW1tc2dBZFNaYkx6YlJyZEo0NmF6NG5nQWlrbW1pSkQ0VUZkTGhkeHVZMF9YT3pZMV9sT2FwU1ZEdFVINzh6b3M3SUF4RE1HQlQxcElfTk4y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNWk1ieXh6cTRpZDZOOGJMWU92TWFjMS1qWUNvbXVoQU4zcWRxQXBPTzNsajM2Q1RYekdxV3BlakNURU5CZWtlVWJTREl0c3lUczBMZUtfclVoTDdwd0dBc1RVajQyVDBIMWFPV3czeFVaS0JXbE5HXzFoZ2tPd1dEZVFZVlJpeFl5TXBSNkRQZ3MwS0paSDBLdFhSaFRGOHYzNU0xY2gtc1VsR0pRWXpWa3djbEg3by1OcWQ4TjFoT1UxNkxMSHpNbUNzYU1GdHdjQjQySzZETkVtTDdXeDEyeXA5YVI5b3BpWkZxTG1PTQ?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOF9iekRvalRrUlJtc29aRzJITHhoV1JybTNMdUc1YnM1RVEydl91SldWdTZHOTIxQW0tSjM2cjhHTjQzTUpBNTBiZ2pZNWZVVUQxRW0xU0dwUXZPbWNxSHFaWFZQQWRFMW1tc2dBZFNaYkx6YlJyZEo0NmF6NG5nQWlrbW1pSkQ0VUZkTGhkeHVZMF9YT3pZMV9sT2FwU1ZEdFVINzh6b3M3SUF4RE1HQlQxcElfTk4y?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi7wFBVV95cUxNWk1ieXh6cTRpZDZOOGJMWU92TWFjMS1qWUNvbXVoQU4zcWRxQXBPTzNsajM2Q1RYekdxV3BlakNURU5CZWtlVWJTREl0c3lUczBMZUtfclVoTDdwd0dBc1RVajQyVDBIMWFPV3czeFVaS0JXbE5HXzFoZ2tPd1dEZVFZVlJpeFl5TXBSNkRQZ3MwS0paSDBLdFhSaFRGOHYzNU0xY2gtc1VsR0pRWXpWa3djbEg3by1OcWQ4TjFoT1UxNkxMSHpNbUNzYU1GdHdjQjQySzZETkVtTDdXeDEyeXA5YVI5b3BpWkZxTG1PTQ?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,42 +3573,42 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>40d913556db308cb</t>
+          <t>ba6c9c85501c553e</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13T19:14:49Z</t>
+          <t>2026-09-22T04:52:16Z</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>MP Bharat Parajuli Draws Attention to BhoteKoshi Flood Victims' Relief - Ratopati</t>
+          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>MP Bharat Parajuli Draws Attention to BhoteKoshi Flood Victims' Relief Ratopati</t>
+          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system The Kathmandu Post</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNWk1ieXh6cTRpZDZOOGJMWU92TWFjMS1qWUNvbXVoQU4zcWRxQXBPTzNsajM2Q1RYekdxV3BlakNURU5CZWtlVWJTREl0c3lUczBMZUtfclVoTDdwd0dBc1RVajQyVDBIMWFPV3czeFVaS0JXbE5HXzFoZ2tPd1dEZVFZVlJpeFl5TXBSNkRQZ3MwS0paSDBLdFhSaFRGOHYzNU0xY2gtc1VsR0pRWXpWa3djbEg3by1OcWQ4TjFoT1UxNkxMSHpNbUNzYU1GdHdjQjQySzZETkVtTDdXeDEyeXA5YVI5b3BpWkZxTG1PTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi7wFBVV95cUxNWk1ieXh6cTRpZDZOOGJMWU92TWFjMS1qWUNvbXVoQU4zcWRxQXBPTzNsajM2Q1RYekdxV3BlakNURU5CZWtlVWJTREl0c3lUczBMZUtfclVoTDdwd0dBc1RVajQyVDBIMWFPV3czeFVaS0JXbE5HXzFoZ2tPd1dEZVFZVlJpeFl5TXBSNkRQZ3MwS0paSDBLdFhSaFRGOHYzNU0xY2gtc1VsR0pRWXpWa3djbEg3by1OcWQ4TjFoT1UxNkxMSHpNbUNzYU1GdHdjQjQySzZETkVtTDdXeDEyeXA5YVI5b3BpWkZxTG1PTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>ba6c9c85501c553e</t>
+          <t>6c8c666c29d070bc</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3635,32 +3635,32 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T04:52:16Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system - The Kathmandu Post</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Opinion | What the Bhotekoshi flood revealed about Nepal’s health system The Kathmandu Post</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxNU1RQS2VCSDhNalYyTHA2Wkh4WEJBRGdDR0xaaFpoZ1g4elZ3azZ3RVRQVUFMd3RsYjg0eEVFWFQ4ZmM3X1NrUWU0dk9OZVRhX1JpZkZVTHNtYmpkTUMwamR2amhtSy1udlpvQjhPcUl5dXdUR0lHLXRKaVVjYlpfNDh4ZlQ1dnA1OGxQY1VqdGdCZDBBU1VrdmhNZ243SzlXLWp3TC1NWnczaXM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>6c8c666c29d070bc</t>
+          <t>42158f49795b8ff7</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-09-22T21:16:33Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) - ReliefWeb</t>
+          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation - Ratopati</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 9 (As of 22 September 2026) ReliefWeb</t>
+          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation Ratopati</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOZUg3S1d0VE1YZWVpbG4waHUzODRIbmtNRFY0ZEhhRE50U0ZGYzRXTzQ2eE95MnBoR0MtNW90akpvRFlpVzNOSTAySDRDcWRiVlgtVW1BdE5Ha3M2OHlLR1FQeG9ISVhRYWw4a3BPX3llYmJkWEpLcGtpQ3MyZDRDVEx2YklvSDZFeXpFT0tkMk15RzVyNks4VA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>42158f49795b8ff7</t>
+          <t>f8be93f473f94b1f</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T21:16:33Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation - Ratopati</t>
+          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Nature's Rebellion Against Human Exploitation Ratopati</t>
+          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMingFBVV95cUxOS2haX3M0eHRlNVlUQVpJOEFfUWxaVHJXY0diSXgwVUx0djZQOUE1dDEzSE03MWVjU2t4UWw5QkVHMkhNUk5RaEhlall1Sy00NlJIRmoxR1RGVEFNaEVPeDlEUTdQa3FQSVlMRk13UlhuM2ZvVjF6a2U5ZU1QcFM1TFBMcV9PYUxkSzFtcnVyd2Rkcm1ic2RPV2VoSVdNZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>f8be93f473f94b1f</t>
+          <t>eee0dd2411bff598</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -3791,32 +3791,32 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-09-22T16:55:33Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims - OnlineKhabar English News</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to tour four European countries; proceeds to go to Bhotekoshi flood victims OnlineKhabar English News</t>
+          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMic0FVX3lxTFBhYzREc0NXRjhlYl9OUGRUSm5RRkVVaFJTODBjQ3N6cENsQW95ZlB6ZzhldW9iTUptMXh2OVdrYnB5LUFuNGg5WHpuUi1haVlTU1JhXzRodVVSLW93X3NtSEhXZmRrbXNldjRsWlp0bHdhaTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>eee0dd2411bff598</t>
+          <t>2e6f49d4ffa969b3</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T16:55:33Z</t>
+          <t>2026-10-12T10:44:33Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion - Nepalnews.com</t>
+          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Financial assistance continues for Bhote Koshi flood victims as PM Relief Fund surpasses Rs 15 billion Nepalnews.com</t>
+          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX2xtRlZjenQ1b1puQ2VIeEt6VnNTazc4RWFjbXpZNDhRbGRxNEM2T0JrMDAwMnRfbFFSVnhlT1lxX1F1NE5EN2dZdWlmVzJnRngwY19ocnp3MXBOUlFvZFpnME1FYkZJVXVMb3Q5Z1k0NDV1dklhZGcxeU5qaF83cHBSNUh4WHBadk5iR20zU1duRVRuUmcxZXB6Y255LVhZNzI0alVzeE1XX1pMcjJHQmwtZzNrS0JfZG9WQWNpRW50UFM5UkdHak81UzdHdWU2cU1HOUl2RVZxZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3885,17 +3885,17 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>2e6f49d4ffa969b3</t>
+          <t>639253c0e6c27bfc</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T10:44:33Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood - Nepalnews.com</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers call for focus on rehabilitation and reconstruction after Bhote Koshi flood Nepalnews.com</t>
+          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQYTZtU21zdHhHR1REdDRoNnhxRTVHOEhldC11cFM2YWtoT2lXWDZCS3NudFNHR1FCMmdVMUdUUFRVR3NBeElZaDBjaG1CT3NmcTY2UHVYMDA0Y2VZSTNSRldpcDZHTzRVTVZTYXBDdkhsbmVxeVNmMThlSVF1NzJJVnk2cUxvZGdJbFE5eDBtUVZ0WFExMGt3RnFOT05yWXNwZWRqako0TnJhWHJEbm5TdWtYNFBpWkQ1Y1FDZlBvS3BFS21Sb3c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>639253c0e6c27bfc</t>
+          <t>e65a6f7e606852ff</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood - Nepalnews.com</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>China provides Rs 11 million to support children affected by Bhote Koshi flood Nepalnews.com</t>
+          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNWVdKY1Q5MnBqaVhnTFg1SGNPcEFkbjd1dnItOUowSjJNUGZLN25fVXJFZ2FvTERWUGVxQVlHZ0otYzhXSlhUNFBpOGh3T09Na01xMXFZb3FpVmdzRDV4T2I3Y1B1UG1KcjBsbUh3UThoOTQ0am15cHM1RzFuLUNNdkhud005MTZhMy1rcjBBTlJ6X0lvdFBDVERNNktzTjFIbHJ1dG5xbHVfcjZVcVo0d3IwMTVJTV9nRzZva0l3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3989,42 +3989,42 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>e65a6f7e606852ff</t>
+          <t>8e672e38aa2a06b2</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood - Nepalnews.com</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Authorities begin verification of missing persons data from Bhote Koshi flood Nepalnews.com</t>
+          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxNa096R000MXNBazNXYTFEM3ppRTFyVzdZem91YUZDVm4zbzdxSzVXOWNjaDhnMDdqdEZFcVNYMXNsMVExLUtTZEZYTTU0U2tBcHVvaUtJYy1DLXczYWZ1eHowTG5Ha3dhY3NwR2x4d3B1RklUZ3VfbkpDM2NrMTZYRGVvUHdEOG5ndW5Sc2lzRkQzR1c1ZzNYVGs1Y2JRQlg2SDFPaEtyRDlzSDE3amVVbXV0UmNTWWtm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>8e672e38aa2a06b2</t>
+          <t>7ffe997ac778dbf1</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-10-05T22:00:24Z</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -4061,22 +4061,22 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood - OnlineKhabar English News</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>K-pop’s Bang Chan donates to help rebuild after Bhotekoshi flood OnlineKhabar English News</t>
+          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTE4yLV9JZ3R0OUlnSVp6T2UwYXpLekg2TjhpaXQ4MmowekdOZENURGF1M2JXbFdzR3NLU3l6dHVMWlZPQTZNLVhMOWZVRVRVUEJIT1VreXZMVG93NWFCRVI0M2ZhUkV1c1BENkpaS1FsNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>7ffe997ac778dbf1</t>
+          <t>f91e5ab1620e5293</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T22:00:24Z</t>
+          <t>2026-10-04T18:38:31Z</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -4113,22 +4113,22 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption - OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>NCP rethinks convention schedule after Rasuwa flood disruption OnlineKhabar English News</t>
+          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE5ZSGJ4aVpkVUVhT1dPNjJwekphbGZPYXBOZWh5VzZ5VEJRNHBqa0xTWFZQc0k2TUd3Q05RNGlZUk5CcDJHZXpjWXlDejhCWUpNVE9NMjRiemJEUnpRcXVTWjFuUlh2TnUycVZRMjNJdm15cVN1TjRvXzdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>f91e5ab1620e5293</t>
+          <t>399c31fb867245f3</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -4155,32 +4155,32 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T18:38:31Z</t>
+          <t>2026-09-25T11:48:07Z</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found - OnlineKhabar English News</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,436 bodies found OnlineKhabar English News</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTE5QLWFxeHluNWxVQnZHSkhmNkVOYjlWZkRlWVlqWmFkQnpYOVFFandUT0ZaRnNYRUdHLUVvRzV4LUpqQWI5ZTA4VWJuWTl4Tjl4b1ZMcUlTNE5pM1d4TGlTcmU2WW5qdE4xcElZT0U2aDVyNWtT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4197,42 +4197,42 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>399c31fb867245f3</t>
+          <t>104cdf9d46c50f0a</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T11:48:07Z</t>
+          <t>2026-09-19T04:34:59Z</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
+          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZ9IB0wFBVV95cUxOMS1QblYyWVppalRadm5zS3ZPVnpJb0NNZDBUUW5NeHZYSFcySjh0OGxnR3hMQzl1dHNxNlR0cXBLUzJtOXNiWm5HdlFLU3VIeWQ2WENraUhNWFBnNGlHTUtydDc4NXRjOVNVb1NucnZVNWdWdGh5Y2dDMWFnd0pETWVxQmlxUFdHbVdjRlR0S2V2RXhhLUtFcUpGSlRNX0V3amQxakxNSGwwQ2xLV1JMWGdTWk5PTFQ0ZkgtLVhCVXoxNEtsZGNqWUFDakE2SW1Wd2dR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>104cdf9d46c50f0a</t>
+          <t>af40c0f4cdd9b4d0</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T04:34:59Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -4269,22 +4269,22 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards - OnlineKhabar English News</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood reveals the growing danger of Himalayan cascading hazards OnlineKhabar English News</t>
+          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTE1nV2NzVWFYZFY1WEZmbmhtNVJJODBwVW5QSjlNYXQ5U0NfSWRTZF82ZVJfVm5pZTgybndKWmJEMHhNcVFzRUhVbEQ5NXVjOF9pQ25ncU5qekxyWnVSWTlMRDI2NjMtRkR1OEwtM1BZTTlLbVV5QXB4bnd3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4301,42 +4301,42 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>af40c0f4cdd9b4d0</t>
+          <t>c6dcc4398d0f1aa3</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas - OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Infectious disease risks rise in Rasuwa flood-hit areas OnlineKhabar English News</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifkFVX3lxTFByNDJQOS0tOE5ZUHlYeEdmbmV0NDhXZjRsY0pvc3Y0aXRUa2k1aWZrc1pwMC1ERkpqdVVKYUtlOHlrMU1xdUkzcjdGdE43bUliWlFUUnlDU2ZDbmR6aHBRMndrbjFEdGwtdHQ4d3VSZGFIUGx2bjZFaW9sM3FFQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>c6dcc4398d0f1aa3</t>
+          <t>ed3cde30c6d7a272</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-10-04T23:56:47Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) - ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 8 (As of 15 September 2026) ReliefWeb</t>
+          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxQcTdYb3pxVFRlT3lQOU5BSnFpVlZydnVqckxIdlVHcHlZZElSV192ZGxjMXhITm1Jc2NmR3VmUlhZTTlsR2ZuSW03LXc3NDM5dzJ5aFJSbER2Qnl3Zl9jdU00ZDMzUzh6bnhwN1daVjZpNTAwdWJtMlMyX3I2dTdSMVdjRl92anBBQ1o1Q3pQaUJSdFQxN1NBbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,42 +4405,42 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>ed3cde30c6d7a272</t>
+          <t>5d30da09bcb70fcb</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T23:56:47Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims - OnlineKhabar English News</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Inside the DNA and fingerprint effort to identify Rasuwa flood victims OnlineKhabar English News</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiaEFVX3lxTE16di1uYU9GWE83SWNzcm9jY1EtQWtIcG1oUGRVU2NYOWhLS2xoaGxrM280OGt0elQtMmdVbHFLaXdtOExDd0ZRMndrSWxVaHlDdHVZQjROOXFXTE51VkVrMjZUMjBQWmVt?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>5d30da09bcb70fcb</t>
+          <t>339773c2b74968e7</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -4467,32 +4467,32 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-09-17T11:38:32Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 - ReliefWeb</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 17 September 2026 ReliefWeb</t>
+          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxQRGk1X3VtWVhlVnh5TzZiUnhpWWEwUEVua3VCNDhxczBlQ1RscERRTnd5c1p1ak5KWmJTOXh4TEJxcjhTa21wcTk3SFBFMlF0WjhHNUdRZTNqUEx5YzVid2dqT0NrZXh1MDhyNGZHVUFyQnpEeW9jWUxBWnRxMlBia292Z1BLVVZyVVQ5YjN5T1F6MzZwWHkyOXd6Q0ppSGlValJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>339773c2b74968e7</t>
+          <t>c16a9e76fde589cb</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -4529,22 +4529,22 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 - Khabarhub</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll rises to 1,409 Khabarhub</t>
+          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9UbWg4Y2R3U0MzZTZoRnEwZDRGVWdjRlVrRExidDkxNWpKaG90YjdxNGdqYVhPMzFpbDNZWDZKc3pSTms2aF9aQ2NwaDE1X0hkc1pzN3RQWVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>c16a9e76fde589cb</t>
+          <t>5dee575dde9896b2</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T11:38:32Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief - Khabarhub</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Kathmandu University contributes Rs 8.5 million to Bhotekoshi flood relief Khabarhub</t>
+          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9Kbjg0aDZjVXNxNHA0REdGSXZKYVdKNmUxUTNDc0JuVldPblY5WEVSX29ubmU1ZkQ2aXVuLTVUa0p1ZENtTVhqQzUzX0g3U05qbHBudEVLWDU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>5dee575dde9896b2</t>
+          <t>63e3a3c4068798b8</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-20T16:02:57Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -4633,22 +4633,22 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM - Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood death toll reaches 1,410 as of 7 PM Nepalnews.com</t>
+          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPUFFxZ1JoTjBwcmVvRnkwS3RfTWcyeTBMTHRfMjJzeEZYOGdoWmYtUlVwMWI4WHdNVG1jbUxQNHVLSVc3eElUbkhweFJORVFPWFF5NFJvMXl3alBkRmQxYlpUeXZNazIyWWxDeW5FeFFyc2wxYUlXb0gwZU5NUlhka2tPY2RvUy1XMGNRY3dEQzVRTkFZRXVZ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4665,7 +4665,7 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>63e3a3c4068798b8</t>
+          <t>5623728116740765</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -4675,32 +4675,32 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T16:02:57Z</t>
+          <t>2026-10-13T10:31:33Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 63 people from Jumla still missing - Khabarhub</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>30-day extension granted for asset declarations after Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhotekoshi flood: 63 people from Jumla still missing Khabarhub</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE10ZTJUQ3ppc1VNS3NjSFdDMFhPQmU4eEpEclRFaVpfbFF0ZWlScHk1SURURllSN0stQW0ySFBIbEQtMV9xaHhDT2Y1N2dIUUEyMk5YeVdMeGY?oc=5</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxPZDZzRWdXNU1wVEI0VmNRZk94TXNvSmRNMXJiSW9VUTNLRnM3TmNadWZxU2lSV1YwWXBXOWRSaUhWc0wtNmFJWGVQemlnSVBzUEZkRGRzU3ZDMFBHWHo5TjJMM1RDU05VZG10cHRLSVZoNHVwVU5rSjY3TkJRWWQ1NTlLNEVSenM5UkY3ZTBPQm43bFY2X1o4Vkh4X2Y3QThqX0I3R0IwYmtlUHdaajA2MA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE10ZTJUQ3ppc1VNS3NjSFdDMFhPQmU4eEpEclRFaVpfbFF0ZWlScHk1SURURllSN0stQW0ySFBIbEQtMV9xaHhDT2Y1N2dIUUEyMk5YeVdMeGY?oc=5</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4717,42 +4717,42 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>5623728116740765</t>
+          <t>1d8ccfd0e472ee8d</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13T10:31:33Z</t>
+          <t>2026-10-04T12:19:26Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 63 people from Jumla still missing - Khabarhub</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 63 people from Jumla still missing Khabarhub</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE10ZTJUQ3ppc1VNS3NjSFdDMFhPQmU4eEpEclRFaVpfbFF0ZWlScHk1SURURllSN0stQW0ySFBIbEQtMV9xaHhDT2Y1N2dIUUEyMk5YeVdMeGY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE10ZTJUQ3ppc1VNS3NjSFdDMFhPQmU4eEpEclRFaVpfbFF0ZWlScHk1SURURllSN0stQW0ySFBIbEQtMV9xaHhDT2Y1N2dIUUEyMk5YeVdMeGY?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>1d8ccfd0e472ee8d</t>
+          <t>a0d887b6e71fa24a</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-09-29T09:46:47Z</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>a0d887b6e71fa24a</t>
+          <t>cc1e404c3c7b5539</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T09:46:47Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
+          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
+          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>cc1e404c3c7b5539</t>
+          <t>07c99b7aeae28b29</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-10-04T12:19:26Z</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
+          <t>Rasuwa flood stole happiness: A forgotten festival - Nepalnews.com</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
+          <t>Rasuwa flood stole happiness: A forgotten festival Nepalnews.com</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>07c99b7aeae28b29</t>
+          <t>acae95309b3026f7</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -4935,32 +4935,32 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: Parliamentary Special Committee to Be Formed to Monitor Government’s Work - Ekantipur</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival Nepalnews.com</t>
+          <t>Bhotekoshi Flood: Parliamentary Special Committee to Be Formed to Monitor Government’s Work Ekantipur</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPXzRpSFgyVHhjSHQzWGlFckVwYzkyWmlCVWx0OUpwS1JocU1OcHZ3SU0zT3ZnSUdkdGxhR0g5eG4zeTV6MkNmTUJTSVluNWhnNU5ub0xjUjVMZDV4TGVIa2tSUk85T1BMYjlWVk9Uc0hUai1fRzBlZ2wyaGd3bFk1VU9NRm05emx6emV1aGw0UWpzNUR6NFZhdDdjUThDU2NGbXJCWlN5SEpUeWN1QTlNQ1dmai1EaENfaEF3Z2xHMVNHUDRqR05fYUY0M29MTTBMaWJ3cDBmdGhyakVS?oc=5</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPXzRpSFgyVHhjSHQzWGlFckVwYzkyWmlCVWx0OUpwS1JocU1OcHZ3SU0zT3ZnSUdkdGxhR0g5eG4zeTV6MkNmTUJTSVluNWhnNU5ub0xjUjVMZDV4TGVIa2tSUk85T1BMYjlWVk9Uc0hUai1fRzBlZ2wyaGd3bFk1VU9NRm05emx6emV1aGw0UWpzNUR6NFZhdDdjUThDU2NGbXJCWlN5SEpUeWN1QTlNQ1dmai1EaENfaEF3Z2xHMVNHUDRqR05fYUY0M29MTTBMaWJ3cDBmdGhyakVS?oc=5</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -4977,7 +4977,7 @@
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>acae95309b3026f7</t>
+          <t>c3b951bc012f9fdc</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -4987,32 +4987,32 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-10-13T10:31:33Z</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Parliamentary Special Committee to Be Formed to Monitor Government’s Work - Ekantipur</t>
+          <t>Legal gap leaves Rasuwa flood families unable to register deaths of missing relatives - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Parliamentary Special Committee to Be Formed to Monitor Government’s Work Ekantipur</t>
+          <t>Legal gap leaves Rasuwa flood families unable to register deaths of missing relatives OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPXzRpSFgyVHhjSHQzWGlFckVwYzkyWmlCVWx0OUpwS1JocU1OcHZ3SU0zT3ZnSUdkdGxhR0g5eG4zeTV6MkNmTUJTSVluNWhnNU5ub0xjUjVMZDV4TGVIa2tSUk85T1BMYjlWVk9Uc0hUai1fRzBlZ2wyaGd3bFk1VU9NRm05emx6emV1aGw0UWpzNUR6NFZhdDdjUThDU2NGbXJCWlN5SEpUeWN1QTlNQ1dmai1EaENfaEF3Z2xHMVNHUDRqR05fYUY0M29MTTBMaWJ3cDBmdGhyakVS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9kZklGT3VEMk5EY09DZjNwVTE1SmZIb2RRcVB2MElGbHZmNllJbG1XTXh6NEdkbjkwM29Lb2FVN3RhX0RZNzNMTDY1SXo0QUdUY2l4SUNwcDQwZVVqTFNqTm0xMUxRNHZBNkI3a0tMbE1FeVFRLXVDdlRRWWI2dUk?oc=5</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi3AFBVV95cUxPXzRpSFgyVHhjSHQzWGlFckVwYzkyWmlCVWx0OUpwS1JocU1OcHZ3SU0zT3ZnSUdkdGxhR0g5eG4zeTV6MkNmTUJTSVluNWhnNU5ub0xjUjVMZDV4TGVIa2tSUk85T1BMYjlWVk9Uc0hUai1fRzBlZ2wyaGd3bFk1VU9NRm05emx6emV1aGw0UWpzNUR6NFZhdDdjUThDU2NGbXJCWlN5SEpUeWN1QTlNQ1dmai1EaENfaEF3Z2xHMVNHUDRqR05fYUY0M29MTTBMaWJ3cDBmdGhyakVS?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMif0FVX3lxTE9kZklGT3VEMk5EY09DZjNwVTE1SmZIb2RRcVB2MElGbHZmNllJbG1XTXh6NEdkbjkwM29Lb2FVN3RhX0RZNzNMTDY1SXo0QUdUY2l4SUNwcDQwZVVqTFNqTm0xMUxRNHZBNkI3a0tMbE1FeVFRLXVDdlRRWWI2dUk?oc=5</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>c3b951bc012f9fdc</t>
+          <t>9ab27519f391ac8a</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -5039,32 +5039,32 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13T10:31:33Z</t>
+          <t>2026-09-16T04:46:36Z</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Legal gap leaves Rasuwa flood families unable to register deaths of missing relatives - OnlineKhabar English News</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Legal gap leaves Rasuwa flood families unable to register deaths of missing relatives OnlineKhabar English News</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9kZklGT3VEMk5EY09DZjNwVTE1SmZIb2RRcVB2MElGbHZmNllJbG1XTXh6NEdkbjkwM29Lb2FVN3RhX0RZNzNMTDY1SXo0QUdUY2l4SUNwcDQwZVVqTFNqTm0xMUxRNHZBNkI3a0tMbE1FeVFRLXVDdlRRWWI2dUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMif0FVX3lxTE9kZklGT3VEMk5EY09DZjNwVTE1SmZIb2RRcVB2MElGbHZmNllJbG1XTXh6NEdkbjkwM29Lb2FVN3RhX0RZNzNMTDY1SXo0QUdUY2l4SUNwcDQwZVVqTFNqTm0xMUxRNHZBNkI3a0tMbE1FeVFRLXVDdlRRWWI2dUk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5081,17 +5081,17 @@
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>9ab27519f391ac8a</t>
+          <t>9740579eff616080</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T04:46:36Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -5101,22 +5101,22 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>9740579eff616080</t>
+          <t>976a3738cc5bbc8c</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -5143,32 +5143,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>976a3738cc5bbc8c</t>
+          <t>3a44f3c3227b20ff</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -5200,27 +5200,27 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>3a44f3c3227b20ff</t>
+          <t>3f5e5c359d3906bd</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -5247,32 +5247,32 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>3f5e5c359d3906bd</t>
+          <t>a724087f81f68a0e</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -5299,32 +5299,32 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>a724087f81f68a0e</t>
+          <t>f62c2f3efb4f90da</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -5351,32 +5351,32 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>f62c2f3efb4f90da</t>
+          <t>509e249c7e4eed4b</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -5403,32 +5403,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
+          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
+          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>509e249c7e4eed4b</t>
+          <t>5550c86ea2eb32e9</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="99" ht="48" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>5550c86ea2eb32e9</t>
+          <t>97b6fb8c1bbdde22</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -5507,32 +5507,32 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - Khabarhub</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing Khabarhub</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6121,42 +6121,42 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>6974acfd82237ba0</t>
+          <t>8f5026d4b74c2e76</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies - Ratopati</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Ambulance Drivers Honored for Role in Managing Bhote Koshi Flood Victims' Bodies Ratopati</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxNUmtrVFc0NFcxQVdCNFh1UkV1TWQ4eWZha2VHT2ktY09wemE5a1pJMEQ5eEpWSUxBVkFfaGZmU0ZJdGd6dlgtWklZRHR0dGVDeUt4YmExREVJckhlQ3VxY0FOUUtfc01CVExXVlZyOVZFT0FQRDF5ZlhGdU5kd2hQZVo2aTVTUUNidFhUTm5uWFZvQTJGczdOQjZuNGdHMk5UZFJyRTdiQVhpSkR3a2RHQWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -7785,42 +7785,42 @@
     <row r="143" ht="48" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>c2a5c1a2976b2e2c</t>
+          <t>77b3c93490f3e8fb</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T21:28:28Z</t>
+          <t>2026-09-25T04:54:40Z</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: US to provide additional $31 million in aid - myRepublica</t>
+          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure - Nepalnews.com</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: US to provide additional $31 million in aid myRepublica</t>
+          <t>ADB offers technical support for Bhote Koshi flood assessment, climate-resilient power infrastructure Nepalnews.com</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbG44NlhORExnTUNKeDd3VlByNUozRm5EaWh0ZmdJUjl0b19oTFRvRE9OVHRYeXlaaGlkR2VlRWJjR3U3dHVLaThZYU41QmJ4YkhtVlhzWGRneGNRb1ZpaWxwOXV2ZUJGMVJKV2lsbXJlVW5FMlNaZFREMHI1dW0zMzJ3Z2h3Nl9qTnVOZ3d6Z1h5MHkzVVVnNDZUcWxyQUFKQm1ncnZvT3JNOE51NVFFek9rS2pxUHFCUUVfZnM4Wmt6UUdzTWY2LWtDNTFjWTB4eUljcmtpU2ZkUQ?oc=5</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -7837,7 +7837,7 @@
     <row r="144" ht="48" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>8d1bfbbdb90796c5</t>
+          <t>c2a5c1a2976b2e2c</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -7847,32 +7847,32 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T17:08:24Z</t>
+          <t>2026-09-23T21:28:28Z</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Setopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya - Setopati</t>
+          <t>Bhotekoshi flood: US to provide additional $31 million in aid - myRepublica</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya Setopati</t>
+          <t>Bhotekoshi flood: US to provide additional $31 million in aid myRepublica</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxQR2VaQkhHeTlrMUphQzlWOURxc0N6akdNbkN6QkFFQmlpbWxCS1dmNWJReWY5bkw3R2dQVTNJNG1qRlV4eTF4TFAydl9vY2FHUlJRY3JieTB0ZFMxWmFsTmcwTGt0U2I4Ym02a0NxQlJjRHpvYnllOWc4V0tfTWpvRFY5eVpFb1Q0b1I2RjRMWXJEUWowOWNpVnFhQ1lsdDNMcHJDdERSUlkwRzVTQjREY0ZUMEI?oc=5</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="145" ht="48" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>b5cefde113f20b10</t>
+          <t>8d1bfbbdb90796c5</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-25T17:08:24Z</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>Setopati</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood - The Annapurna Express</t>
+          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya - Setopati</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood The Annapurna Express</t>
+          <t>Nepal’s pathway to reconstruction and rehabilitation after the Rasuwa-Bhotekoshi disaster :: Bijay Karmacharya Setopati</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiS0FVX3lxTE9rdmFRSE43VnkxN2pKLURybUNHYXEyR1o4Y0NSc0ttTGJjZlBkckhWMGZTNVV2S254Rkd5UXRTQzg1MmJFNGE0aUJWMA?oc=5</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7941,42 +7941,42 @@
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>406ae4eb0f113f1e</t>
+          <t>b5cefde113f20b10</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:15:18Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts - Nepalnews.com</t>
+          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood - The Annapurna Express</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts Nepalnews.com</t>
+          <t>Victims by global emitters: Demanding climate justice for Bhotekoshi flood The Annapurna Express</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE0xRUdaWTlNYXlJZF8tN1Y2RXNGU1g5YkQ4NXlDbTE3RXQzNm81eXhkc1lxN2J6bjhxczVsNklBRl9lSzA4NlVuSHhGMUszYkdxSXpZYzZlUQ?oc=5</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -7993,7 +7993,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>2a300e5247974c0e</t>
+          <t>406ae4eb0f113f1e</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T11:32:09Z</t>
+          <t>2026-10-12T21:15:18Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
+          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts - Nepalnews.com</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
+          <t>Um Hong Gil foundation to expand Bhote Koshi flood relief in four districts Nepalnews.com</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxPbVpDTnpFZENoaFd6RU1vUmR6VF90aGd5QjVCRGMtd3BWanJVWTVhcG1Ta1dRUkdlbDlvMUVaSktESVJ0ZnViYWtFZzZmZThYU0xKRDNyXzJJUGVKQWJPTFVwdUxXRlhhY1dNUWRQN1R5bzZzTm9zcWpySTE2Zi1BLTJYLXA1NndBU1BubHM3bTd1TncwMllNYkxrOERTY0h2V3kwejdaSEJubENVMVdoN0hRYm02XzBjX0E?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,42 +8045,42 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>a074d8d9f7cf953e</t>
+          <t>2a300e5247974c0e</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T12:44:27Z</t>
+          <t>2026-09-23T11:32:09Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>The Tourism Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims - Ekantipur</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
+          <t>Mongolian Heart to Donate European Tour Proceeds to Bhotekoshi Flood Victims Ekantipur</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxOalJDNnFhSTdZc2NoSzFTRDhWTklKSmg4NXE1THpzZE5jdXBCUlVwdGYzMldzaV9XcFR0NC1OTFZTU3l5c0VwN0g0bnRid1A4VmozMy12ZVlGcXRYMUxKNGVGMnF2MVlDVVNaUVBNaFJQLWNZWk1WV3FQbFFtZERMUVVLTThrM1N3SC1YcUs3UTlxRTJWalZFWmZkSGJicGY1V1Bid1ozdHQyNHFVZmExd1B6RjNqbWJWMXB2M3U2MmZ3eFQ3Tk9vcFc4cmZIOE9VOC1LUFpjM1JuUQ?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>f60efed8fd40992a</t>
+          <t>a074d8d9f7cf953e</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -8107,32 +8107,32 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T19:32:35Z</t>
+          <t>2026-09-21T12:44:27Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary - The Rising Nepal</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy - The Tourism Times</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary The Rising Nepal</t>
+          <t>NNMGA provides relief to families hit by Bhotekoshi flood tragedy The Tourism Times</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQclhISW1aXzFsS0RYdTM1NkI4Wlp6SmJ1NUk2UTV1V1BETFNCb0U3RU9nRVJBenpWbFU5MkpfeVJNTEh4b1hpVTFJNS1xWWFrUWhaSG5KdlVFN3JsanRnaEJNQkJCRzExeHBVWUYtejVvWm9yQV9kSXBSblJnMFk2Q3VFMGJRejl3bjVrS3paTUlCSEkzOVFaWmFXSDNPcF9GcWNnUDJWYklyRGc?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>4a93f7eb5178c8ad</t>
+          <t>f60efed8fd40992a</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-11T19:32:35Z</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
+          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary - The Rising Nepal</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
+          <t>Rescue and relief operations continue in Bhotekoshi flood-hit area: Home Secretary The Rising Nepal</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1NY2RJM3VMUnVMOWhWaUlQY1BGVmxqUndYWE5pdEJoeG1rWDBndXR2dTJPTVlxUWQ4cGZUMlA0QWNkSmNhcHFhLWxZRER0c2h1?oc=5</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="151" ht="48" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>c25c8930bdcedd55</t>
+          <t>4a93f7eb5178c8ad</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -8211,32 +8211,32 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24T11:42:26Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
+          <t>Special parliamentary committee formed to study Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxONUluZWVkWlZ6ZnlPNGV1WXpkSFhSQkJuM05rbE1XRkdjTkRoVFBzcE5oX0hTV05LWEFhbE4waG1HM3oxQXZZcm9welRFa3dSRXEyZks2SGE4M0pXRFFMc055YVB5em82LXlnQU03VGVObzJfZEdqQ1ItM0JPYlJoRFZidlBDMC0tNnlMbThXcFdRSDh5d0NQVDJkaEMwTGlFMmpTQnFuS0h5ODg?oc=5</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>fd633a6a2a2a1810</t>
+          <t>c25c8930bdcedd55</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -8263,32 +8263,32 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T04:52:28Z</t>
+          <t>2026-09-24T11:42:26Z</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital - myRepublica</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
+          <t>Don’t leave Bhotekoshi flood victims stuck in paperwork: RSP Whip Dhital myRepublica</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcklZUDJ0NGRSdF80SHM4d3R0NFFnU244S0JUeWxkQU1HdkFrWGp1YUMxTmkxWFUySU1kckdMaGVhdTlpUGJyTXRhV0dpdnhpNW5JZHQ5bXBRcWhnellrOGpEcmdoX3IwSHlSQ1JtakZFbG9kVmE1QS0yZTZNMFd3aUV1cmFPSUp1TS01Um5LdjNNYzRNZlpZMnhNUUhPU0VtZ0l6TTlVblJxVjNDNnRkRXR2TXJtLWpoNUxwR29UYjltdkU?oc=5</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8305,7 +8305,7 @@
     <row r="153" ht="48" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>3d1620d408627250</t>
+          <t>fd633a6a2a2a1810</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T00:04:58Z</t>
+          <t>2026-09-21T04:52:28Z</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
+          <t>RSP: Expedite DNA testing of Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE40RzVsN3g0TjNwMEVuNFBWalNMU0tOWVBYT1Vra21aMVQzT3BFYW1HTmRYV2RaVHhYaVNWQUpzUFZFUTJPN3dnYl9KQjJWOW5z?oc=5</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -8357,42 +8357,42 @@
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>12225c63e0d58b53</t>
+          <t>3d1620d408627250</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-09-22T00:04:58Z</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>WION</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas - radionepalonline.com</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
+          <t>Government to relocate and rebuild Bhotekoshi flood-affected settlements in safer areas radionepalonline.com</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE84M2FSR05feVY0UE5nMGpxOTJNNUFJTlBZSHNxMnpxWUszSGZKX3h6MHlydDk5RWJEN2RwMXpwd09MTUFUQ1p3eVFuVXMzOGVESHVJd3FEZ3JuV09vTVV2VFpwb1M?oc=5</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="155" ht="48" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>1a65df9c73c0c5f1</t>
+          <t>12225c63e0d58b53</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -8419,32 +8419,32 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T05:15:51Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>WION</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream - WION</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
+          <t>Nepal forms 7-member panel to probe August 26 Bhotekoshi flood from source to downstream WION</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizgFBVV95cUxOSkpBOEZpMmlwU0MzbmFiQW5FeUZZMXJ4OVd0YjlnVVlITm5KWldFMTh5MkdncGd1Q0cxQUZiVXVCRnM2SW8yMkU1Qm1VVUhqWEFmRENaQy0zNGdPVzdmb0ZsUC0wbW92QjdFUVlkb2FGM0xWYmRYRVJKd3JPNHhpQTFORXoyRDBiQjdsU1pRU0FMQTZabnhfNWRlMWhSY09CQ0F3dk90Nk1ydDhTeU1ldzJfaVJSVXhsSE8zb2lDYjJkaTJhb2VBR1l1eVZvZw?oc=5</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>25275754a5c497fa</t>
+          <t>1a65df9c73c0c5f1</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-27T05:15:51Z</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
+          <t>Chinese organization provides assistance to Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9pRUtINVpPR1VUVUduQTVFSlhpWjlKQ3lybUx5QTBKbDZKWVZHWE1qRmFKRjkwT1JkOWtuTnB5YS1yVjUxeVRQVXV5Z0FfLVZmRWViU1JtdGw?oc=5</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="157" ht="48" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>09825b491361a412</t>
+          <t>25275754a5c497fa</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -8523,32 +8523,32 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 - Khabarhub</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,436 Khabarhub</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5kc0xJZmliM0JlREh2OEdWUTJqOFY3eUVKTjctWUxScERDdjROUzdYN3U5WGRHaXIzT1dJUnItbXRxYllzNEZiNDBuYnFUemIwaEpLR2FzQlc?oc=5</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>535fbbf54d3b4684</t>
+          <t>09825b491361a412</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
@@ -8575,32 +8575,32 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27T16:56:20Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Khoj Samachar</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations - Ratopati</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
+          <t>Rupak Sapkota Discusses Bhote Koshi Flood, Nepal-China Relations Ratopati</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxNTHZpeXdFcWpXU0lub3BDZ1ZqdE9GQl9kT29RSmlpR1llNlRHNjdEbUViMUkzTjFueEtaalNHMVFEclFrNVpjWkk0a3ZxUlFvaFB5dmcxNTlvZmpma01PVDlaNHR0UEprMWJXTGR6YUhKNTd3YkxPQnZocHFCY3pQWlZKQWU0N2YxMThxbXpqd3FmdWRhNmU3SU9rZ01hOVNRbnVUNXVn?oc=5</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8617,7 +8617,7 @@
     <row r="159" ht="48" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>10604521935094cd</t>
+          <t>535fbbf54d3b4684</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
@@ -8627,32 +8627,32 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-09-27T16:56:20Z</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khoj Samachar</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood - Khoj Samachar</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
+          <t>RSP Urges Faster Relief and Recovery After Bhotekoshi Flood Khoj Samachar</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMib0FVX3lxTFBmekI3NjByRXo0Vks1bUpNd0gyRFR4R1BBYURLV1ZocVJ5LTdfclRsaW1VOElQbXhPVGtZczZJQzNLN1dsbmxVTjkyRlZxWTRsUG5DbjVxal9PWkNpb0dMdzNaemVQbE81N2tLOEVaNA?oc=5</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>6ec42694b67ab866</t>
+          <t>10604521935094cd</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -8679,32 +8679,32 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T20:47:03Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly - myRepublica</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
+          <t>Bhotekoshi flood: Study finds 23 Uttarakhand glaciers retreating rapidly myRepublica</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOem1pdXRPWGlHM3lydjVRNDRncWlYc25vdkQ4dlZxXzE0X0ltcGtLUU9ZTVdhQXdsQ0x0YVhJWkRYbnl2cmRoUXItNC1ZQjBHS3NmdkNPSmVvekRSaHJVckJad3dXNWJEOF9lMmNQM3ZOXzlCNlNubW0zb3RCQUt4UndERUh0T1FwbGdqTm9UY1pxZ0xYRHRmdktRdUV4WVpTVjNVZTJfR1RtSzRWNkx5TVJPaUNvRHNIVE9WZVBfWjFYT1Y2?oc=5</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8721,42 +8721,42 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>39ff34f1f426316f</t>
+          <t>6ec42694b67ab866</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T00:32:15Z</t>
+          <t>2026-09-20T20:47:03Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies - radionepalonline.com</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
+          <t>Bhotekoshi flood: Families hold mass funeral for 10 missing people from Jumla using sacred Kusha’s effigies radionepalonline.com</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE11NExqWkx6Y1FOdEdDTUFhQ0wwMVE1SWxSQXQ3eHVraUlmaWtYcExyM0JKQUZIYmNWdWFSekdURm43RWY4UWVrTDA2WnFvRGFfTGF5akd2dWZTZUtTa3gzemVHWTc?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>bb5552718a993013</t>
+          <t>39ff34f1f426316f</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,32 +8783,32 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T13:50:00Z</t>
+          <t>2026-10-01T00:32:15Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
+          <t>NCRC, MITGF plan long-term support for children affected by Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxQdENOay1uQzh3bWQtal80T2FXRlgtdU9UQjJYMlZJd2JoUnBLajdGZml2V2NqYnVBZGozN3BmYThEVFBUWFVSUEpCYmNNaEZtVWNkXzNubEdxMDBlYVdia09iZkh5Q2FmTXE0VnJZOWFueGQ1VDJBSEVHX1BVdnlUb3U2cW9odG9tbTFhTFJqRXVQR2VHbF9ta0Y3MTZWdUhzNHBpMV85SDJhZDlvbE12Sg?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>c5054155e8d76e19</t>
+          <t>bb5552718a993013</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19T15:51:25Z</t>
+          <t>2026-09-28T13:50:00Z</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -8845,22 +8845,22 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing - myRepublica</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
+          <t>Bhotekoshi flood damages 11 hydropower projects, 837 people missing myRepublica</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxOY0M5RXJfdEVMcWcybWZQX0ZLWF9JR0dMTzFQSEJzNmZPdE8waDVsZ2k2bXViY1p0UWdPbG0tVktaM0FSQnpycVR3V3l0SG9DZE1qdkRrV29obmxlVjhhUnUzc3NnLWJhdEIxSExLWmhBa3ZpelA1c1BQYktiWkxjdExLNUVVekVPbGluMHRVd3NNTEswUjl6bGthT1RiMllIZnZMMFlMaVRMWEtIc2trTDZJZEs4M3VDbTh0cmxn?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>4a782c7db12159fc</t>
+          <t>c5054155e8d76e19</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-20T11:20:07Z</t>
+          <t>2026-09-19T15:51:25Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills - myRepublica</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
+          <t>Bhotekoshi Flood: Building Resilience With Green Skills myRepublica</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPUE5Kd3NDcUpEWUJqSy1OaVVONmN3bUlOT3VRTTlGOFhVSF9oTUpaQVBQcnFidzY2OUhhbTNSalFkVXcweUhSVnlfU0xhdnliZno0ZGhydFJKdmRZQWZpN3hIeHp5RjBycGllZjJSN1VjNE1FNlhjSEcySjJ3U3JNRXJkazlLdVcwMmhKNnF1Z19uVm04V0RXREtEY2NCcEF0T05EbDA3TnM2cWxtWVE?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,42 +8929,42 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>cc153ab4c5f0bc02</t>
+          <t>4a782c7db12159fc</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-20T11:20:07Z</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days - Ekantipur</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
+          <t>Bhotekoshi Flood: Collective Cremation Held for 10 Patarasi Residents After They Remained Missing for 24 Days Ekantipur</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNmhwUFFIZFFVZW9ZTFR2R01UbHlrWXc2Z0VkX3ZjdXFGZVVtSmc5ZGNqQTlWcnBlUmZ4cnYyN2NpTzRMM1RSOFlia1p1WWRzZXRINGlqN3ZrTndSWjJOOFVPcnItdmlQWDhROFJsa05DWEpoUElsckdKVDF0dGF4NDc5Vm9Wbmt0OHZaWmtnbkZkZkNEOWNMQW9Cel85VGV0WFg0cTBQbmVlLXdlNHVFR19OcTQtbnBqMEk1X3FFbHN3TFZKdkRlbEVxTWJLaWxvaGc?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>26e0f34695ac0146</t>
+          <t>cc153ab4c5f0bc02</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -8991,32 +8991,32 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25T21:32:55Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors - Nepalnews.com</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
+          <t>NRNs in Texas contribute 21.5 million rupees for Bhote Koshi flood survivors Nepalnews.com</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxNQlBidkkwdFdkU1BidmNZdklRQkZDVVd2clowbGhESFkyaEk2U2tSZzRnd1NwYmJ3eXN4eFduMEZaU3BydGZrSzhIeUdGbEplaUZUWDFLSjd6TExrZkJPYmpyaDRaYWdIcVJjeE45TzFUdWlHUFplSkpLLTVIMzRrdXp4d0ZOREluX29ETEZjd1RKZnJGMFRKaVN0aUV1dktWVUYwUWwxNk9WSUdZWGhFcFpKRWRaeFE?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>bf0bd71a8811a3de</t>
+          <t>26e0f34695ac0146</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T16:22:29Z</t>
+          <t>2026-09-25T21:32:55Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies - Ekantipur</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>Bhotekoshi Flood: DNA Testing Underway on 837 Bodies Ekantipur</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMipgFBVV95cUxONlBydHR3ZWw3eW9nanFXVnlSYWZTR095NGZ3ZkRJWXIybG5ZQ3hjQXBtT0VkLVIzRXFiTlB5bXVuMzdDZkdEcmZselhXRkFiMThwY3FOS3Q0d1JiczBMUzBUYTBISTVXbnhwTThNY3lLTUgyS014UWdYTWg1TF94eEI1aU1hSGI1aUUxOFpiTVhMbjI3NDBqcEQ2TnlPNW05NEtrd0dB?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>caa83d5807a4f588</t>
+          <t>bf0bd71a8811a3de</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-18T16:22:29Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOaXRQMDdhVElYNmpxa2kxaXo4VUFtYkQ4TDlmTkRkOHI1VTg5emo5NlpNOWhyVGwwSjRQR1JtbWJFQW54SXBrNUpkN2pRdVhzeXNPOGduQlRDMHFnTHpkQTZva01MRHpLWkJudDdJTWdBVm1xSjJuVVNSb0NZcEpiV2UxRFpadjFZUC1jdkNMc2V4ZHI0UThieGVOeWFIN0sxUkY4SGVHOHM1ZTVRbEF0VXJkWFlGcTdIV3JKTTR5cVdxdVU?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>5aeddf14059c9769</t>
+          <t>caa83d5807a4f588</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>chinachristiandaily.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] - Ekantipur</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
+          <t>This Is How Displaced Children Are Continuing Their Education After the Bhotekoshi Flood [Video] Ekantipur</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzRUNEwzbmxUVXFiZGZYLW16dEtnVFBBQzZtTl9OLVh0RUdvM29iZm9Va1dSMVJjWTdaVkZSNS00RWRkSFFJU0ZPajlrMnhSamRqTG9LWVRtTk9sOGo0U2RkSXpDWmJvOUlSOUlWQzhkVTNJMWN1Zm5VNWxrdVZPcTJwWGpMT3M1ckNmWklLbDR4T0k?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>81625d31ed27040d</t>
+          <t>5aeddf14059c9769</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -9199,32 +9199,32 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>chinachristiandaily.com</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings - chinachristiandaily.com</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
+          <t>Bhote Koshi Flood Leaves More Than 200 Church Members Missing, Damages Nine Church Buildings chinachristiandaily.com</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ0JnZDBzZGxLRHFBb0hyam1heDhPa205eVBnQTFyeUFBcng1UmVlUERkRnBwWnNXYlVOaGctZS0tYVA0cklSSE03TVY2N3Rxd2ZST2ZhOXZPV2lPa2VyeWdfZDVyRE1XejlVT2xENktEQlRuSXRuaGMxTnhVdG1scjN1TjR1cm4yQ2xDRC16dmRWU0k1c0h6aDAxcm5jcUgzUHdqakxKRzlYMjRRdEh2cWVGaUMwcDMtRUNsaVU0NVhLLWlkVDZVbmxlVWFTaUtoenNDVU5Yak54c2haSVZmajZzT2hHZ2dDcVBhOTZpZDBPZDVr?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>382aacee35c12bd2</t>
+          <t>81625d31ed27040d</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,32 +9251,32 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors - Khabarhub</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhote Koshi flood survivors Khabarhub</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5FdVpUWXMtLU9ndWxnQWNJVG5lakQ0R1VkNVhueU1NYTJiLVBoWWFZT1lqU0hqc2kxTTBJWlJqU2dlX1ZfNUk4ck14MXlxaWtWbHB3dW9NcVI?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>c953c8abf57268ed</t>
+          <t>382aacee35c12bd2</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,32 +9303,32 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21T19:58:53Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Nepali Patro</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
+          <t>In The Aftermath Of Bhotekoshi Flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
+          <t>In The Aftermath Of Bhotekoshi Flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1rbXVBem44Y1pWX0ZvaWZFVjM5SFdBZm1UQTlCbmFFaXpHS1pzb05KSGZsQjBFTjFyb29LYlA0OVJRX0tRZzFPa0VlY1dwM0hs?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>11bd9764f90f4f0b</t>
+          <t>c953c8abf57268ed</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -9355,32 +9355,32 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-09-21T19:58:53Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepali Patro</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief - Nepali Patro</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
+          <t>Texas Nepali Community Donates Rs 21.5 Million for Bhotekoshi Flood Relief Nepali Patro</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWkFVX3lxTE1lN2Ztc3BrMXA1VGlYTXFEd05BeXNVSkdybnN4dDQySC1nZThlR0pVdFdESm9VcW00YUpsVkxqeVd3ZTZrekNLTFYyUWdJOVB0eDBIeWRrMElLUQ?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>718a52966e5afa2e</t>
+          <t>11bd9764f90f4f0b</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T20:52:41Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
+          <t>Texans Donate Over NPR 2 Crore for Bhote Koshi Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVnRkNmFHRlp0ck9WSDdGM1JYek9hMkpqM0REZ2p3OG4xbWtzOWhDM2ZOSnVfN093Vy04Q2FuZE5IYnBMTUJjR0ZRMVJ5WXVRZEhrbXBtV3p3cTMtSjMyNTdSMFdnUldrbnhTcC1CWi1fUXp1SkFSQ2d4ZzF6TDN4RTd6V0ZBV3JGMUxON0lfdkU3a19BbENWcjRHdnB6SUctWXBEaXVNOWVCNVU?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>7c3d1c068a76eb4d</t>
+          <t>718a52966e5afa2e</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
@@ -9464,27 +9464,27 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Setopati</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors - myRepublica</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
+          <t>NRNs in Texas contribute Rs 21.5 million for Bhotekoshi flood survivors myRepublica</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeENrTU5HZ0JQcW4tV3drY3RWdlA5SzN0YjlwVm4zTWx3MURQalFkMWJZY1MxSll3NV80eVNKUGYzTTJzM1U3cUhzR1Q3aW9IOUpjMTlYYXluckJibzUzTWdWVUczNC1ZYmxIVG9nQkQ5TEZ5R1NQUFFGUm9lRVQ0MnBqMXg2c1EzalotNUhvTnhOa3pvTWxNZU5Nb2dSUGJ5OFRpTFJzdTRBa19tQkVPYlg2YzBILW53dWNjRFBOeDFwdDJJRHYxOA?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -9501,42 +9501,42 @@
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>5e6f3bf951c84b5e</t>
+          <t>7c3d1c068a76eb4d</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12T21:15:18Z</t>
+          <t>2026-09-18T20:52:41Z</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Setopati</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing - Setopati</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood Nepalnews.com</t>
+          <t>Bhotekoshi flood: 1,410 bodies recovered, 5,145 people still missing Setopati</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiTkFVX3lxTE12emVsNDhpeURjQVhFcjVMZzRRcFQwVFpKeWdiQ1p5S3dqWlU1TGFZZUNvcXlVSDZneEd4QnBfVTRXN182QmxTRW9hQWltQQ?oc=5</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>562a7c16c434d881</t>
+          <t>5e6f3bf951c84b5e</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T04:40:24Z</t>
+          <t>2026-10-12T21:15:18Z</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds - myRepublica</t>
+          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Climate change contributed to Bhotekoshi flood, international study finds myRepublica</t>
+          <t>606 foreign tourists from 36 countries still missing in Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
         </is>
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxQVnktWS1CclNjMlRLWG5KSDRoaVo1eTA2T1Vqek9tWU96blpmT19BWFVRQjV2bkpYejRQNEx4RUdoQmtSS2ljNDFBeDJ4SzJpRHQ0YU5UN0dBZk51Y0JJWlR4T3VyX1hqM3U1VGlHS0xPUmVoVGxHZzVaYlFibVdPcS1xQlJGUGpiQ1RxWVBTOUxPck81WV8yZE5xQWRjaDNyVUU4OWctNjd6SjFVS19QeWlYdw?oc=5</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>a098d8aae7af06f0</t>
+          <t>562a7c16c434d881</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:59Z</t>
+          <t>2026-09-18T04:40:24Z</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds - myRepublica</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
+          <t>Climate change contributed to Bhotekoshi flood, international study finds myRepublica</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxQUjFUVkhUWTY1TTFXVFNDUy1JNkpncC1lYWpDWjN3RW9TWUF1STdvS1JMY2g4LWVCdGpPNzRhWTVPNDhGcmdWck1XU21QM0xDV0RGdmtyeHZEdmFrZ0I4elF4LUtpb0pILVZLQVUycDBvdWU3WXh0UTJLV1Zkd0EyV1Ryb294bldCOU9UcEd2a21FYXIxZTZhSnRhLThkMGNYUjdCdko2dW5YMFgyQ0VtdnpLdy1kejA1anNGVmZ5eEl6Rk1kRWc?oc=5</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -9657,7 +9657,7 @@
     <row r="179" ht="48" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>4199945559bb4c8e</t>
+          <t>a098d8aae7af06f0</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T04:50:01Z</t>
+          <t>2026-09-18T11:10:59Z</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing - Ekantipur</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
+          <t>Bhotekoshi Flood: 1,410 Bodies Recovered, 6,145 Still Missing Ekantipur</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTFBQMklpZG55Qm1pdkdyM29kOF9CZ1ZiSjhLMlZ3Ri01amVCN000Yk13SXE3UW9PVlQ5RVhtOUNwMTJpMW9DallBcWdMSzVURnhwUmJsQjlfbC1VS3dZN1pUVWRCZ2JMbEF3SnRVTUE4M0RHQQ?oc=5</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>a3af223902597f26</t>
+          <t>4199945559bb4c8e</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -9719,32 +9719,32 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T04:54:51Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
+          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
+          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="181" ht="48" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>035dc924f46d515d</t>
+          <t>a3af223902597f26</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
@@ -9771,32 +9771,32 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17T16:58:05Z</t>
+          <t>2026-09-26T04:54:51Z</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
+          <t>606 foreign nationals from 36 countries still missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNTFAzUmtyM2x5SGxwWWhGQS1GZDRBNTFaMFhwSDdXS3hrN1UxVW5pcTFyUHMwNGh5MTdjZnl0bl9rSlhaeVNJR3FZZFBXU0xHQ29EQnVuYUgxdzdSVlN6VDdjQlRzcVdfNEctWmtESEc4WFUtS19UcERPVl8xZmJqaWs3cEh3MC1xTTZzZjc0ZzlMMDQ3ZktKUlVVa1BNMnBJMFRMWV95QU9nUi1PamdSUEJ2b1R0aFdnS05sakRXdk5DY2dfbEJv?oc=5</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -9813,42 +9813,42 @@
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>2c0a3b5d2befbf82</t>
+          <t>035dc924f46d515d</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28T05:20:23Z</t>
+          <t>2026-09-17T16:58:05Z</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing - Khabarhub</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
+          <t>Bhotekoshi flood: 191 vehicles damaged, 344 people missing Khabarhub</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5MQWRhREpxS195UG5EczJTc09fR05Ra1prRHNSX1hnRkZrRVJZRXJYRnBaWlNyYjk4d2FDUGJxMWVzUVc0LURsd2NQY2NJUG54SXAxZzhnZ2U?oc=5</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="183" ht="48" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>40652f6cba568b14</t>
+          <t>2c0a3b5d2befbf82</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -9875,32 +9875,32 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T04:29:29Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
+          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
+          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>3341c2c6bed379e9</t>
+          <t>40652f6cba568b14</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
@@ -9927,32 +9927,32 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>2026-10-11T12:45:44Z</t>
+          <t>2026-09-04T04:29:29Z</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Samples Collected from 33 Relatives in Jumla - Ekantipur</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: DNA Samples Collected from 33 Relatives in Jumla Ekantipur</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQV3VCcURXekt4VU45d0oydGpxbnVyMWY4TjNzc0M5bW1OTC1JYlZ5WFRtOVhnR1NqQ2xLSDdiellJT0hTbFJjeEg0YlhxZjl0cEVIc3BSVTZEc2I1OFhZNkZfMnpyNlFwS3VjcXYxdkZHLVFneWNKOURyT3A0emRHbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQV3VCcURXekt4VU45d0oydGpxbnVyMWY4TjNzc0M5bW1OTC1JYlZ5WFRtOVhnR1NqQ2xLSDdiellJT0hTbFJjeEg0YlhxZjl0cEVIc3BSVTZEc2I1OFhZNkZfMnpyNlFwS3VjcXYxdkZHLVFneWNKOURyT3A0emRHbQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="185" ht="48" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>ddd57575c35c350d</t>
+          <t>3341c2c6bed379e9</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-10-11T12:45:44Z</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
+          <t>Bhotekoshi Flood: DNA Samples Collected from 33 Relatives in Jumla - Ekantipur</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
+          <t>Bhotekoshi Flood: DNA Samples Collected from 33 Relatives in Jumla Ekantipur</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQV3VCcURXekt4VU45d0oydGpxbnVyMWY4TjNzc0M5bW1OTC1JYlZ5WFRtOVhnR1NqQ2xLSDdiellJT0hTbFJjeEg0YlhxZjl0cEVIc3BSVTZEc2I1OFhZNkZfMnpyNlFwS3VjcXYxdkZHLVFneWNKOURyT3A0emRHbQ?oc=5</t>
         </is>
       </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQV3VCcURXekt4VU45d0oydGpxbnVyMWY4TjNzc0M5bW1OTC1JYlZ5WFRtOVhnR1NqQ2xLSDdiellJT0hTbFJjeEg0YlhxZjl0cEVIc3BSVTZEc2I1OFhZNkZfMnpyNlFwS3VjcXYxdkZHLVFneWNKOURyT3A0emRHbQ?oc=5</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>f391daeeca51bbbc</t>
+          <t>ddd57575c35c350d</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -10031,32 +10031,32 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island - myRepublica</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>Bhotekoshi flood a wake-up call for vulnerable communities of Nepal’s Srilanka Island myRepublica</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTmJrTkFIbzJ0XzRhQXJxaUt4dEdSMElsYktFNWNBTk9Qdmc5RGlKc3FEX1hfN2JFZXI2bC1PMEhUZEtkV1V0WVNhc25La2hxWlc1ZWs4d2xMMVFnazY3b0dSMnNnN0lpYVp2aFI3WTdHSEVtTmVfNV9CR2k1cEpWSE90MHltMmdUUlRSZjZ1TnU5WldwNmNkRm8wN3BuZmNHeU5IckhHTW9sWXZUX3hhRlRURWxUbVltbm9mNzNNS1hMQQ?oc=5</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="187" ht="48" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>751a0e165234bde9</t>
+          <t>f391daeeca51bbbc</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -10083,32 +10083,32 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T19:50:19Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>hariyalinepal.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxNd3c5OVhteGo1Wng4TURLV2dDUVFPdFVsN05HcVFIc2lhM1dsc3l3Q3pDVkt4YnI1ZV9ORF9uM2IzQUNfdVlndThEQUEzWEV3dXZFdG9TSHNHamtiTmFfeHNfOUFCdEZSelowUE0xLWU5VTh1U29YbFVXUTY5TlBUUHdEeXZ5N2M4YXdaWk4xWjF4eDRwQUhVaExIbGV1TWMwUXRYTFZ2bzRPSEtBYjR2LWpJSVhfSnp6TElVV3lfcw?oc=5</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -10125,42 +10125,42 @@
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>038d44da2885beeb</t>
+          <t>751a0e165234bde9</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-14T19:50:19Z</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>hariyalinepal.com</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain - hariyalinepal.com</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
+          <t>Bhotekoshi flood is a structural humanitarian crisis, says IFRC Secretary General Chapagain hariyalinepal.com</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiSEFVX3lxTFBxVHptMjFPQkphTk15REpPdG0yR1E0ckxiSWIyc1lLVlcwTndBVFQyMGV1ajM0VnRVQ2d2WlBwbGR3b0RHRTQxTQ?oc=5</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
     <row r="189" ht="48" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>355ca1951767eb7e</t>
+          <t>038d44da2885beeb</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
+          <t>Bhote Koshi flood: 1,399 bodies recovered so far; 4,089 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRlRPX0Q3TTdRMFdkMHlrZjRiNDRObmREUDh6a3Z2RlI3UHFfUmVDOGladU9FYlZWUWxqX2tNdW11dndZRk9qQk9kOWRLR1MxcERyVl9YSU5OaXBJSFB5NE1IRVdOdmo5V0cwWXFnNXk5WlY1SHRrZDhPSXo3Uk1scnprekhXaDdDcmU2d1czMGFmWUF3ZHUxZGswYWQ4MGFHQXJaX3luSVI?oc=5</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>7c8af6b0d120695d</t>
+          <t>355ca1951767eb7e</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
@@ -10239,32 +10239,32 @@
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T16:21:28Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
+          <t>Nearly Rs 3 trillion in private-sector losses from the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxOSUdyV3RJYzFIVzBEdFd2NTZ4emVCTk80dS1GVzlJeVdCNHpZS0taYlJOOGlvaFFZaFJzaHZLS0ZMcnhVaDM5VWdZdGdOVHJWcHA3N0VuTWloQ1pJdUduYzFZc1UwTDlUOU5xZFdaUnZLaFpMcnVjRkZUNDduTURMR3Y0ZzNzQjJpUjBFWlVTc21QXzlta05WVzkyTHRQTDU2VmdrVHZaN2s5YXc5YVRHTGJibTFuOU9sbG5KV3Rldw?oc=5</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -10281,7 +10281,7 @@
     <row r="191" ht="48" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>2ff03089e15253df</t>
+          <t>7c8af6b0d120695d</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -10291,32 +10291,32 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T16:52:14Z</t>
+          <t>2026-09-26T16:21:28Z</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
+          <t>HoR session: Lawmakers demand expedited DNA test results for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxQRmVfdHQ4WTFCQk5HcVZkMmxTUUFGM3lXWWlpNVgzS0JFWm9BN1lHRzVBU0M3eURGTS1WaFA1b3R2NVk5X1haMGlxUnNRSnRZajUzSXZmbV9jVTR2SUU1cXdxU1FGMDFyOGZHdi0taXZXYmJsZ3h0M2RLNzlaaEN2VDl5Nnl1Vkl5c2tydGh3elM3NlEzLVQ1ZFlTd3V2Ym5Pam1JSXc4QUZtTi16TTNQbTJWc092NWdkanNfV0YxdkVyM3hJUXBqWDBR?oc=5</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>b933797459c3a582</t>
+          <t>2ff03089e15253df</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
@@ -10343,32 +10343,32 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-16T16:52:14Z</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
+          <t>Who defines reconstruction after the Bhotekoshi flood? OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="H192" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiekFVX3lxTFBEWkRHamZud3Izay1nT0hZRjJLcUtoTnZlbzh3aW5ZTm1YaE1xQVdXRnBNOHdGNldKVmNnZjBneW1FNUdCWW9sMVNKbVZMWmxpSEFYNm5vRnF1ZGJKd01jbTRyOW9KeWpDZ1VRNmNXd2VhN01LQy13dmZn?oc=5</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="193" ht="48" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>97b6fb8c1bbdde22</t>
+          <t>b933797459c3a582</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -10395,32 +10395,32 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - english.khabarhub.com</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing english.khabarhub.com</t>
+          <t>HoR MPs seek faster DNA tests and search for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="H193" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5PX211aWdKakZfUFVRSERhRzlaY1NSV29GUk15Ti1QZ09tVlVoSzVqQjVCNWRFMmFiWTRfZ0ZydG9pR3NVZF9sT2xaWnp6cFJ5SzJqZGdTXzg?oc=5</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14T00:16:32Z</t>
+          <t>2026-10-14T04:58:11Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14T00:16:32Z · 854 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-10-14T04:58:11Z · 854 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>a1c1bf932fb5fd38</t>
+          <t>af991dce59e57aa5</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T00:48:04Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -4717,42 +4717,42 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>1d8ccfd0e472ee8d</t>
+          <t>4199945559bb4c8e</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-09-17T04:50:01Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
+          <t>Agenda For Rasuwagadhi Flood At UN - The Rising Nepal</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
+          <t>Agenda For Rasuwagadhi Flood At UN The Rising Nepal</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1CRDM5ZUwzVy0zcjdmR3NobDIwSERxTFJiSjhrVHphdXRveTZnVWpBbl9hZTY0eFpoYV9LeGZxaFlidTk3LU1YV0dDWndJaUhX?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>a0d887b6e71fa24a</t>
+          <t>1d8ccfd0e472ee8d</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T09:46:47Z</t>
+          <t>2026-10-04T12:19:26Z</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath - Nepalnews.com</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
+          <t>Timeline: How the Bhote Koshi flood unfolded hour by hour and its 3-week aftermath Nepalnews.com</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYjg1Q3IyelVhdFIxcEtTQnU0a0lEM28wa0JNOU5YSy1kX2hTSm5jekFNV2ZycVFQTEY0dS1TRzgxdGY1cWEtU1VmZ2dJLVVWZlkxWE9nM2NnNDFIYnM3NGV5eWtiTThuZDZ0dlUxXzkyVnZyaDB1MGxDY0x3Z3VydEVDZndnSVNpYkwxVU1OWktKeFhNRkNnOGs5YlhJWVhMb1R6U1psajdXM2JxTkMwN0JTbGFhUE9EZ0RIejJYUy1NZmc?oc=5</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>cc1e404c3c7b5539</t>
+          <t>a0d887b6e71fa24a</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T11:28:55Z</t>
+          <t>2026-09-29T09:46:47Z</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
+          <t>Expert panel formed to scientifically study Rasuwa Flood OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxPckZIUkhBNmJ6c0FIN0ltZ1Y3VWxGSzdJNzhUbndaTWJpODdkSFFFVk1WRmhvMVpfNVNTYkJpZzU4TWxxZ2Z3bTQ5NGFUNmQwb2xjMWFSRjNKUjBuaWVJSm5sV1h4bjZRLTZId2xEZ3ljTUhwVlBtLXR4UXdLSmtMQmtlX1JoNDZYMlRIS3RDQmJLdndQQm5HdTBn?oc=5</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>07c99b7aeae28b29</t>
+          <t>cc1e404c3c7b5539</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T12:19:26Z</t>
+          <t>2026-09-16T11:28:55Z</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival - Nepalnews.com</t>
+          <t>Government forms expert panel to study Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood stole happiness: A forgotten festival Nepalnews.com</t>
+          <t>Government forms expert panel to study Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikwFBVV95cUxQZVRMN1lDOGI5aWxzSGp1ZVc1R1hIX0k4d25hbk41RjRobmItTE1KeTA4aXg5TEVoMlUxbTVRdGoxSGgxdHppcVAtalpLSjh4ckhlUndOZ0U1dDNVVWZFeXY1c0oxVUdRTFBTalFvbjlJSGpHTXp1UDBNMmJQVXpYRDdBbWZNcndDR1l0OUFWU2JYWVE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE56SjJoS29NSnlfRUR0LWp4X0hOdlAwNUxwRHM4ZmttQUZUVUNHTXJ1Zjd2Nm9PQzRGUmtya0syeGE0V3ppQjhzdFU0VUhPb2JfYkR0bmRZYWU?oc=5</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>9ab27519f391ac8a</t>
+          <t>2c0a3b5d2befbf82</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -5039,32 +5039,32 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16T04:46:36Z</t>
+          <t>2026-09-28T05:20:23Z</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
+          <t>Bhote Koshi flood: Committee formed to collect details - Nepalnews.com</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
+          <t>Bhote Koshi flood: Committee formed to collect details Nepalnews.com</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxNNlFBTmFzR3NpUUdFVlM5aF9sR2JYMnFhZUI1RFBPb1p3UFFkcS1LQmxfNWQwbi1nN1AzZ3U3eDB3bXl5cXlILUdCSjlydkctbGdZYXFYem9aZmdEVXpFTkZOVTVvSlh5dXNRMExyemQ5TUhBS3RwWjlqeHlmZFZBSmx5bklQakthZ1VxNC1oZjhBZGczSjJsaw?oc=5</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5081,17 +5081,17 @@
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>9740579eff616080</t>
+          <t>9ab27519f391ac8a</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-16T04:46:36Z</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -5101,22 +5101,22 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
+          <t>Over 400 containers swept away by Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9OTTFTZVhCR05jS1ExWTE2Y1JRVnBBTWNHbG5TRnZ5VXFqVUVqOHdxQVp3dDB6a2lUd1lvQjRPYUwwNXdVc1pDQ3NTdnIxRUJO?oc=5</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>976a3738cc5bbc8c</t>
+          <t>9740579eff616080</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -5143,32 +5143,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T04:51:32Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
+          <t>'Bhotekoshi flood is a structural humanitarian crisis' The Rising Nepal</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE0zeTRrU2dxRmdjSU9faVFRb3hoaUw3ai1Eem9BTm1ZY3k3eGZPRVlJNmlXZXlWNl9KdE5iZS0zVXVZS0JsTTk5QmZaR3oxT1pG?oc=5</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>3a44f3c3227b20ff</t>
+          <t>976a3738cc5bbc8c</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -5200,27 +5200,27 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>The Kathmandu Post</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses - The Kathmandu Post</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
+          <t>Private sector bears bulk of Bhotekoshi flood losses The Kathmandu Post</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNcnU5NkhndUJhTDV3LTJ1MDRlOFFKSGJUZlRidE5VbXlaU2g3eDFycnVlRTdkMFRvanpEQzA4Zm45M2JCMjFFSkVXNFo1TDVCQ0h1WHJFVXB1Vlk5SzFneEZvYThiWEoxOTVmNS1oaTVva1FyaGVETHh0cTA4UDEwdGhNODdReTJUMXRsYjhUckp6Q3BsN0hqMzJoMA?oc=5</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>3f5e5c359d3906bd</t>
+          <t>3a44f3c3227b20ff</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -5247,32 +5247,32 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T22:13:04Z</t>
+          <t>2026-09-15T04:51:32Z</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims - Ratopati</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
+          <t>New York Program Collects Over $1,500 for Rasuwa Flood Victims Ratopati</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirAFBVV95cUxPWnkxVDA2TVg5YVZOQmEwY0RIWXhFOTF6aHRsNUgySFFmSWtwS0NsMExUeW1vX1E5N3V2M3lJVmhaZTRzeE1pdWJjOUlvRXJkdHFkdU5tZ3VraUtnUlNmbDE2VXFsMmFQVTJKaC04eS1Ic3dlUlc0aFV0QlowTHd1U0JlaWVVbFI1MFU5OWgyWlNfRnMxd25fdGRlWUZUWDlPaFFYR2p5Mjkzd0Zu?oc=5</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>a724087f81f68a0e</t>
+          <t>3f5e5c359d3906bd</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -5299,32 +5299,32 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-09-29T22:13:04Z</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
+          <t>Inside Rasuwa’s flood zone, a forensic doctor’s hardest case OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMia0FVX3lxTE9wNkVpMlo1dm50cDUwUTM5cFp4VHI1bjdiZUR1b2xEZjM4ZVV0TElvZmdzNmRnRE1nakpGOHJ3SlhwbGgxaG15Wko3M2x2SzhBbEFaODJYLTFnQ2k1WHRZcVlqTVd3NWJpZ2Mw?oc=5</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>f62c2f3efb4f90da</t>
+          <t>a724087f81f68a0e</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -5351,32 +5351,32 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T16:57:06Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing - Ratopati</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
+          <t>Bhote Koshi Flood: 1,395 Bodies Recovered, 5,130 Missing Ratopati</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxQTTNhQnF2UVdMWVNZZ1JFcWZ1OUd0T19md3Ytbk43a2c0ZnNGcHpHcG5oNTVQck9uemVCTTk5MnJHb25kTnpJdy1veVJKQjZIME1aREJnenNtczk2cVgxYXhaNFZRTDVpSkQ4VU12VnlqYXVTRC1BYWtvbFYwSjhubw?oc=5</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>509e249c7e4eed4b</t>
+          <t>f62c2f3efb4f90da</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -5403,32 +5403,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26T11:21:48Z</t>
+          <t>2026-09-15T16:57:06Z</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
+          <t>MPs demand swift release of DNA reports for Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxOakRGck1HTXdsR1g5VTJsT21Ja1ZCYVBWMkV4QUU1ZTlxVE5tMFZwVERpcFFxUjFDRWNzNl9mLTJSblRJR2stRTBMcFcwMVFveGRHX3kzTXdRU2ZCa19ndXhidGpvcDYxdGJuSUNURmZQSE1UTEVWbzVqWkNxcklrRkVWcmZhTFBScXllVHlBeGp5b3ZackhzeHMzNktqOUhmN2toVTJES0hETU11UG9MTw?oc=5</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>5550c86ea2eb32e9</t>
+          <t>509e249c7e4eed4b</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08T10:31:40Z</t>
+          <t>2026-09-26T11:21:48Z</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
+          <t>Private schools support Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
+          <t>Private schools support Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBQVEJJQjBrX0d0X2pVSjNLNWg4d1Z4OTNISUJRMk5zakZIbHNkVUxjbnFHWDRaeWE4WUpBZlg1TU5sTVBWQXJJVUFOU3BGdVptbGl2OUwzb3o?oc=5</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="99" ht="48" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>97b6fb8c1bbdde22</t>
+          <t>5550c86ea2eb32e9</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -5507,32 +5507,32 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15T11:41:34Z</t>
+          <t>2026-10-08T10:31:40Z</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - Khabarhub</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing Khabarhub</t>
+          <t>Disaster platform discusses recovery and reconstruction after Rasuwa-Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxOVTJkX1JEWmFxZzBHX0lEYlFQbzBiZDRpdk0wRENYbkIzSUJVT2Jfa3dEV2NEeHA0el9rbUE5OVhqMlVWQV9ma3JRLXJxTUZ0N1BhYWtxNzRpRnZtLWF2RXVQV0xVWDV2OWVnc1UzYmF1ZkhONE91NEFhZ3I3ZGJxVWFGQW1lU01UampPVTl1LVBSaEhtbzBQdDRpYWk1aHdhUWdfck9VbnFzLTd6VXd6QlE5aUtla3NJOHJzZWlYTjZ4OVVM?oc=5</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -5549,42 +5549,42 @@
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>2fdda12f5042e371</t>
+          <t>97b6fb8c1bbdde22</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14T04:52:51Z</t>
+          <t>2026-09-15T11:41:34Z</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Nepal plans Bhotekoshi flood resettlement within two years - UA.NEWS</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing - Khabarhub</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Nepal plans Bhotekoshi flood resettlement within two years UA.NEWS</t>
+          <t>Bhotekoshi flood: 607 foreign tourists from 34 countries missing Khabarhub</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE5xbXU4RGVLZXZzUWlldzV6RndEaVpDRkJEbFRrS0YxamJMQ1c3UV9ib2U4ckd0Y2JoUnZ1bzhQT25TZVM3OG5OLXVkLUtYbEI0YUpoSXpwYXo?oc=5</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="101" ht="48" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>0179379ee0bcea80</t>
+          <t>2fdda12f5042e371</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -5611,32 +5611,32 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29T00:59:03Z</t>
+          <t>2026-09-14T04:52:51Z</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years - UA.NEWS</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
+          <t>Nepal plans Bhotekoshi flood resettlement within two years UA.NEWS</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxPazRTc2l3U0hMY3hYOURDb0JBZHBQb1d1VllqZkhRSUxtbnlLeDh1RGxZWmRhZExPSlFtaURqdmo3bi1mZ0RUcWNEMlREV0ZlOUhvWVh0VXdiYWlKQkJNNkhna0RhY2xPdGloalc5QTgzOEtfaEdReEp4YWlzWDFENnVleGFkVkpYWWhYV3JFb2NRaElMUHJNWC1oZkZBSEdQNDVrMGNtOVJNOXcwUUFYcEgxZWc?oc=5</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="102" ht="48" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>ca0bdec000f5c2c0</t>
+          <t>0179379ee0bcea80</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -5663,32 +5663,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-09-29T00:59:03Z</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage - Ratopati</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage Ratopati</t>
+          <t>Ignored study reports led to higher Rasuwa flood toll, experts say OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMidEFVX3lxTFBjRW9UN0xxNWdtZC1Ud1BSbWtoUWx3OElYTGplbHc2UXBrcmttc0FaMkY4Yk8yV3lpNXRldzAwc3hnT0tfMFc1VlMyRGtLV2MtbTNseUFZbU90ZHlBSjdPdXlsUW9FZFFyMWc2bDZLajY3ejFr?oc=5</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="103" ht="48" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>f4275fa3453686f2</t>
+          <t>ca0bdec000f5c2c0</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -5715,32 +5715,32 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13T19:14:49Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood washed away 2,792 meters of bridges, report finds - OnlineKhabar English News</t>
+          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage - Ratopati</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood washed away 2,792 meters of bridges, report finds OnlineKhabar English News</t>
+          <t>Bhotekoshi Flood Causes Over NPR 400 Billion in Infrastructure Damage Ratopati</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE4taUswb1drd19FMGFlSkZUQjZSQWNpZjY3bThYT1RlN3ZDdFduZ25YWGtYX3c4RHZ5NF9yY2tuYllfdUxzNEpRZlpTcklmODBtOFVNa2JDNDlZckVKNC1KblZUeVg3NEEtY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiakFVX3lxTE4taUswb1drd19FMGFlSkZUQjZSQWNpZjY3bThYT1RlN3ZDdFduZ25YWGtYX3c4RHZ5NF9yY2tuYllfdUxzNEpRZlpTcklmODBtOFVNa2JDNDlZckVKNC1KblZUeVg3NEEtY2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi0wFBVV95cUxQOEl0VjFhSzVGQjFFeTAtdl9qby1UX3JzSE9lbld6UjNicnhEMVEtdFpqRkpEMEM4Z1ItdXdDd1lMWTFoaloxQ0J3d3lQNE1GZHQ5eWpUZmNoQnV3cnltWTd2bjVOcEQySjFLenVjZVoyQlVlck1uakhZVWdvT2tMWV90Qy1xQVNoZmxLN1ZNM2pXT0E5d0FzcEtNYTctWXhydS1GS25PMExyRmx6dzZfYmhJMEU2bVJaYTlkbEU2elFGeHFMQ2JJRXRqTGFTRGExNUhj?oc=5</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -5757,42 +5757,42 @@
     <row r="104" ht="48" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>af991dce59e57aa5</t>
+          <t>f4275fa3453686f2</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-13T19:14:49Z</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
+          <t>Rasuwa flood washed away 2,792 meters of bridges, report finds - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
+          <t>Rasuwa flood washed away 2,792 meters of bridges, report finds OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE4taUswb1drd19FMGFlSkZUQjZSQWNpZjY3bThYT1RlN3ZDdFduZ25YWGtYX3c4RHZ5NF9yY2tuYllfdUxzNEpRZlpTcklmODBtOFVNa2JDNDlZckVKNC1KblZUeVg3NEEtY2c?oc=5</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixgFBVV95cUxPdVd4aS1qdGpYbGtQZlpzQ01qYklhQlhweTNIaWhfMjd6VldoRTRlVy1aTFRodUVkVWxra056LWNaMTQ0QnozcjJkcVpXazRsT1FwLVhQeWFkNU10VTl6c2RXSUQ3T1NsUU1xeWs1Rm1NME9Tb2ZUZjN1V2pXU2tRM3M3VC1lU3dVbzhlTVFxUU5iVGJvdU9KZmg1XzBhUThsU2RDajRSMEQwZUdEUVgtaHczd05jcnd0LVVZbmhKdDBMSE5YM2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiakFVX3lxTE4taUswb1drd19FMGFlSkZUQjZSQWNpZjY3bThYT1RlN3ZDdFduZ25YWGtYX3c4RHZ5NF9yY2tuYllfdUxzNEpRZlpTcklmODBtOFVNa2JDNDlZckVKNC1KblZUeVg3NEEtY2c?oc=5</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>ada55db68109e06e</t>
+          <t>a1c1bf932fb5fd38</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -5829,22 +5829,22 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
+          <t>Nepali community in Washington raises $20,000 for Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiywFBVV95cUxOelRBS1RKZlNKOTNCcUNNMERUbk1YUlAzcUNRc1M4Sm1HbjRhYUJsMllzWFBVdkVxWUoyZ0ZVMmoxUDZ3ZjdIODYxY0lJNkZqSTNVVHBGVm1jaXp5aWdQZHhCeG9adTdzcnhzOEZRXzdQOUoteFlFMnY1bklLMV9UXzZLRGF6TWdDNktFRGVoQUxZY3N5cXF5XzlwM1FTelJ3UlZtS2ROUlR0d01Nb2xsWWJDZldKMGtKS2ZFbEFCZVpkTnNkMlAxeWZ0QQ?oc=5</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="106" ht="48" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>6c6838329cdfbfc3</t>
+          <t>ada55db68109e06e</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -5871,32 +5871,32 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T20:17:26Z</t>
+          <t>2026-10-10T00:48:04Z</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood - The Rising Nepal</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain - myRepublica</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood The Rising Nepal</t>
+          <t>Govt to build 50 model houses for Bhotekoshi flood victims before Dashain myRepublica</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMi2gFBVV95cUxQLWpGSElnM3BJM0NUS3VIRUdiZzBENTJFOUZ5VlR4WGNWT3FDVlZOUmhRV2JsdmZIS2hTMXV2UDYxOE9pLTFXbDk2R0ZXaEpseWxpMjlQdFB2S3NURzdMSm5RQWpoYVpJVE5IMEFVRlhkcEZ0NHZnSFAyZExYSG8zaGRScE1ZazBHNVFEUnFWZFdzNDBlNXloeVV6ZGtMRVphcEw5WE0wU2ZCMHgtWVQ2YXVORmNvcVcwMUtSNDR0bXp6ekFyQlRuOFF2NXJjMlFneXdESXNkaXM5dw?oc=5</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="107" ht="48" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>b44663cde7bfcda6</t>
+          <t>6c6838329cdfbfc3</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-06T20:17:26Z</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -5933,22 +5933,22 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
+          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
+          <t>WB projects Nepal’s growth to slow following devastating Rasuwa flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5IbjljV0lEUmtkV0J1a3hFSXRwYWdXM2lkNmRnZF9hOUJsTVpXSnhqTHFSQU1ydXo0OFN2YmxXR3RKR1Z5dlBnQ2doUjIzbmhm?oc=5</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="108" ht="48" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>8e369d28dac1be4d</t>
+          <t>b44663cde7bfcda6</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiVkFVX3lxTE5fNGhMSEtkZG0yWGt2SXRwQWw4RkpWNU1rajR4WXlCUmJEa1lCVjJ1V1ZRUTRlZW5hOXNZRWlWRjhGa3hsMWZOTUJvZGc4MkRCZ2RCVXFn?oc=5</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>410a103aaf7c4528</t>
+          <t>8e369d28dac1be4d</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -6027,32 +6027,32 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T18:20:23Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted - The Rising Nepal</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
+          <t>Report on flood damage in Rasuwa submitted The Rising Nepal</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1Za1hKYVg5V2M4MEJhQ3FEeDRITEt5QklLQkhwQzR2eTlTNmhWbldlOEpKNEtwRVJ1WXVPUG9BV2kwZXpjdzc0LXU4NTVkY0x3?oc=5</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6069,42 +6069,42 @@
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>b514eaf62f9a2f3a</t>
+          <t>410a103aaf7c4528</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T01:12:32Z</t>
+          <t>2026-10-09T18:20:23Z</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
+          <t>Japan provides DNA kits to identify victims of Rasuwa flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxOYXBYUnE1U3I2MWdxYThodjgxVTZCRzc3Sy12aEtqd1JvR0Y1ekJkek5KWEh0MUdNZzJiMjhDSTVMLVh3QVJYV0NZLWhCcmdMWlN3RE5SZ2xMam9Md1V4Q2xUam1VclVaSEVqVmNlSTVzTlBEc1FoU0d4TG5WSE1NOFYtUTJ1N3J6X3dxYUpfQlN0ZXpJRnQ5cnVqWTk1bzZT?oc=5</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6121,42 +6121,42 @@
     <row r="111" ht="48" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>8f5026d4b74c2e76</t>
+          <t>b514eaf62f9a2f3a</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T17:19:50Z</t>
+          <t>2026-10-09T01:12:32Z</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing - Ekantipur</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
+          <t>Bagmati government’s preliminary report on damage caused by the Bhotekoshi flood: 1,455 dead, 5,285 missing Ekantipur</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMickFVX3lxTE9HamJZbFhNVFNMZ1duZlFwZ09pY2V4TFBhTnl4S3ZFT0ZoRUJXUmZ6VW8wWU1yVktrWWNVdHdSSGEtdGJQZ1ExcGlCMjRWY2VzSDA5OE1WUmVEZHNJbUdxYkhUaExfRHI1MjRoWlFXZ1pYUQ?oc=5</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6173,42 +6173,42 @@
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>ab6e3de447176b06</t>
+          <t>8f5026d4b74c2e76</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-10T17:19:50Z</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families - Khabarhub</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
+          <t>Red Cross to provide Rs 100,000 cash aid to Bhotekoshi flood-hit families Khabarhub</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE8teWxZLVNadmpDQ2Y4Z0JmNnk1cnZuaURhTHFzLXFJZkJLNUxuNXU3b2FkV1U3X3dIbXJ2OUFpUkVzankwVkR3UC1fN3RjZm8xTXY3TFFPTjA?oc=5</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6225,7 +6225,7 @@
     <row r="113" ht="48" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>37af945cd9bf0faa</t>
+          <t>ab6e3de447176b06</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09T10:29:46Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident - Ekantipur</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
+          <t>Bhotekoshi Flood: Study Team Stuck on Naming the Incident Ekantipur</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiogFBVV95cUxNUHZCR3JmVkxmTExJcFRRd3RXeExEdWFCZ3hiMks1aWs3SW15dXMtaUVlZXhHcXRxa0k3UnFFazVLd2F6QjBZeEcxeV9fbTdFLXlpZTRtZzBvU0FiYmc2QWlCUVBlOUVrcnBxWl8xSlUtTTBsUXJCWlJ2NnRtd080NlZhWWJkZkFJUzJRSVNTUXQ5aUZfRUItZGxWR2NIQ2k0OHc?oc=5</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="114" ht="48" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>f032fc73f67f980a</t>
+          <t>37af945cd9bf0faa</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-09T10:29:46Z</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUGhxS2NPUm1xQ1l6T2t2UkhnREV5cGZTUExoZDR1V0lVTlF6N1ZFcExMQ1RqYjB2NTJnVEcyOUYyNzVjQUd2VkhXQ2RybmwyUUpMSEJOZUIxWV9RZ3NrREg1V04zc0pQWFp1Y1RhSjdqeWNYZE5SNWkwSmZNOWN5UmJobDRSZk9rS1BWTm9fSzVSOV9XZm00NmQxeVBCWjZtTjhKYmp5Q3bSAVxBVV95cUxQcEhGMmNhMTRiYjRqbWNPbk1RRHY2STBRZVJuRUltY1ZoVGZxXzV4dWVFYU1PVUc3ZUdtYkQ4UEVMdGxCNjFGa196N0RUS3pRcnJhRG8yeG1wLVZnZA?oc=5</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -6329,42 +6329,42 @@
     <row r="115" ht="48" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>8839b87cd0c93852</t>
+          <t>f032fc73f67f980a</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10T09:47:10Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact - Khabarhub</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank - The Himalayan Times</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact Khabarhub</t>
+          <t>Nepal growth projected to slow to 3.7% after Rasuwa flood: World Bank The Himalayan Times</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTFBwSEYyY2ExNGJiNGptY09uTVFEdjZJMFFlUm5FSW1jVmhUZnFfNXh1ZUVhTU9VRzdlR21iRDhQRUx0bEI2MUZrX3o3RFRLelFycmFEbzJ4bXAtVmdk0gFcQVVfeXFMUHBIRjJjYTE0YmI0am1jT25NUUR2NkkwUWVSbkVJbWNWaFRmcV81eHVlRWFNT1VHN2VHbWJEOFBFTHRsQjYxRmtfejdEVEt6UXJyYURvMnhtcC1WZ2Q?oc=5</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -6381,7 +6381,7 @@
     <row r="116" ht="48" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>e6fd7d2a17031541</t>
+          <t>8839b87cd0c93852</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05T14:32:40Z</t>
+          <t>2026-10-10T09:47:10Z</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
+          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact - Khabarhub</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
+          <t>Bhotekoshi flood: 45 students from Rasuwa still out of contact Khabarhub</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBBWm9VUTZ1bUlFbFVlTFdPb1BFWThSbGtmUFg4eHhXazdJeEVkMDl6TUQ3X0s2eEJLQ0ZXanlGTEs5bWdyWlMyNFVrcmxfRzV2Y0hmYkp4Y0I?oc=5</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="117" ht="48" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>e8b8e3296cd3eb52</t>
+          <t>e6fd7d2a17031541</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -6443,32 +6443,32 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06T13:22:59Z</t>
+          <t>2026-10-05T14:32:40Z</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Greater Kashmir</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Greater Kashmir</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - The Economic Times</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Greater Kashmir</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction The Economic Times</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigwJBVV95cUxNZEN5ZGVBbzJTcGtrV2lHVWE0aVpEY0FOZV9NZ3RFSEd4dUR0dTQwX210UnVUUWdSeHI5enNZOTNEYV9hZ2xfTzEtUF9BNG1TdWdMelVzckhlaE1yQVJ3RnB1eWZFMU8zOGpvQVRSaWhIVkk1NjFINDk3TDlRUmlrYnVTeW5CNHh0UHMwZHNzbElmVjNxaW51bDk2MFVKYU5YNElHYy16RGk2cmRkbEhqT2c0WUhXYV9nMTNBS0lfU1lGMkJqNmQ2a1NvZzFiZ3ZybWs5eEpQVlpMcHV1WURtdlFsZDd0WmlRc05FZFBYcU10WTZiT0o3RzA4R1YzTGpLdHV30gH8AUFVX3lxTE8tMU9vYjRWZk9uMlRwdEVjNUpNVlpxb0NWRV9jRGpmdGVRMkUyY3l3cWwyeEF1V0VYNl9CNEpOVURub19OMEpXU1FDdm45Nk5SYVFsQkZXN052WGxuazBZUTBLSU9MYnZ5X2RJSUR3cFF0bUNCMmdjeGlDSUNnR3dZcTRhZTdER3RPbWJvWDVoYmNIN1EyaTd1NVNYQUMwZTNlM29iaGtuQ1hjM042d3NNZ3UtXy1hRUgyS19xSFI2Q0MxLXZuaExuWFNMdmNPbnA3LUNwdjhtOTI5SWFtWVBrSEpBU0hhWi15aWdkZF9ueXVGWUFOV1dGS25KbA?oc=5</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -6485,7 +6485,7 @@
     <row r="118" ht="48" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>f6fd73d2d1d043d1</t>
+          <t>e8b8e3296cd3eb52</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -6500,27 +6500,27 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Progressive International</t>
+          <t>Greater Kashmir</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction - Greater Kashmir</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
+          <t>Nepal wraps up Rasuwa flood search; shifts focus to rehabilitation, reconstruction Greater Kashmir</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixAFBVV95cUxNcFEwaW1ITWNPRHRza09NVXRZYUlsVlliSEYxckpwOVVzYUFKd0IwMENMTVc3UGxBN0QxYzl1a2M5MEVsb1JXb2JlYllnTDl0ZTl2TU9INnU4QnQ2NTB1UUhDdUxPdk1CS0Ixb3h3UW1teXRnQXJ6OHJ5NFR5bGduRmExRlJGOGlRTmFBRjIwanNwRl9TN0dIbmJtWGdyWFE2OGdBYVRUNVNLWGFzM2JHTjFROWNpY1JwUjlxVHdnUUxscXdw0gHKAUFVX3lxTFBfU2NKNjhFQUpvYnpQejVGRmxCU0lHTkVVSnBWbVpVejZWU1Y1bFI2U19xLUJzeGRYeHl1YWt6YkdfOXg5RjZDOFBJZnNNeEN0WG5hV2ZnNDZHSGZFRHZfZVV6dHN3TGFHQ283ekFWZml2MDRQQmtaZnYtNG9kbWw1eG9URzFwVzVtNURjcVF6UE5HcmZhTzE5dzViOGV1OUt3M2l0NVJyYVF0S25DYkJ1aXhaUjVQZlVZUmk5eENPTFZka05tRVhkR3c?oc=5</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -6537,42 +6537,42 @@
     <row r="119" ht="48" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>32fb999ba596439f</t>
+          <t>f6fd73d2d1d043d1</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T23:56:47Z</t>
+          <t>2026-10-06T13:22:59Z</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Progressive International</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world - Progressive International</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
+          <t>Nepal’s Rasuwa flood disaster is an alert to Southasia and the world Progressive International</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxOVWNuWksxS1IzeVhDZTJnbWlrSkY5WjQ4eXUtMUItbFprSmExQUlfMEdwSUxFNXgxdmFWcGNCeEU2VGFKRXFXZGdKNFZxRmVpc3FBemtaTm9vME5LNWtsQnVmWElJczFHbUEwLVRWNktrOW9VeThxQ0ZfT0MyeHRTblVGbVc2WjVKak5namdhWUdmcGVqVjF6Wlc4dW5UUENvczl6ZndPOFA4YlIzM3RlRzVHLV9wWnBKUFE?oc=5</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -6589,7 +6589,7 @@
     <row r="120" ht="48" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>1f474f3512d0099c</t>
+          <t>32fb999ba596439f</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
@@ -6599,32 +6599,32 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07T00:40:33Z</t>
+          <t>2026-10-04T23:56:47Z</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days - myRepublica</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days myRepublica</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitgFBVV95cUxNSmVhcFN6TDV2OWlRY0dDZEFFM3ptWmJ3eG5WOGo0M2pEYTV3VnBJc1hEd1JUMDR6eXA0V3pLN0RyYVF1WmhZYlkxczlYMm5MRkRJamptc1d4OHBjVDc5S0Z2c21QeW1HcDJzeDdHNWZTcjV0MFVudGRYVUozY0tQY0hwM2dOM0pQUTdaWUtzV203RzRtb0pPVWc3ZnFxd0xua1laY0dMcDc5MFNvT2xXU3VLTmpaUQ?oc=5</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -6641,7 +6641,7 @@
     <row r="121" ht="48" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>d424f9e7bb14efa4</t>
+          <t>1f474f3512d0099c</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -6651,32 +6651,32 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02T17:51:36Z</t>
+          <t>2026-10-07T00:40:33Z</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
+          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days - myRepublica</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
+          <t>Malaysian national missing after Bhotekoshi flood found safe after 37 days myRepublica</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSllEOWFub0tCcHhiRWotREZXbkltMHE2eDdjemxpY2R1Mjlvb0Z5NnphWEtIckg2NUFfajlBdUE0QkMweXN3emVUTHBELWxQMWVEdlUxQ1FiXzdmU3BhcEhsdlc1MUx2N0dPNjlEcUhaSnFqbEM3WmhjY0U0ZHl2VFFnVG94SDItd1NBcUFGSXJyMkFEYWY4dGQ1elZrbXpPS0RBaEVZTkwzemZXT2JyVGoxUHJtZ00xMmRrajFMVjBYaXc4OHZoaA?oc=5</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -6693,42 +6693,42 @@
     <row r="122" ht="48" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>5c121de89e21fbf8</t>
+          <t>d424f9e7bb14efa4</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>2026-10-04T05:49:20Z</t>
+          <t>2026-10-02T17:51:36Z</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood - Ekantipur</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims - The Himalayan Times</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood Ekantipur</t>
+          <t>Tenzing Norgay and Um Hong Gil foundations support Bhotekoshi flood victims The Himalayan Times</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiXEFVX3lxTE1qR1Z4WEdRLUU1Vlg2QTVITDJKWEowbjRSV2sxYzYxM241Sy1FZXh6dzNrbVRCWjBqNEZNd2VPWVowNWFTQUVxQVlkaktIUldKQnRTWG5GMEtiUXdn?oc=5</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -6745,42 +6745,42 @@
     <row r="123" ht="48" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>06470ae82fa46649</t>
+          <t>5c121de89e21fbf8</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T10:05:07Z</t>
+          <t>2026-10-04T05:49:20Z</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
+          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood - Ekantipur</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
+          <t>विचार | Social Vulnerability Exposed by the Bhotekoshi Flood Ekantipur</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMinAFBVV95cUxPanhFVW5iZGc2RjJDUjdOdlJUdTRaLWF1dklHRmtYNnUtYWwtTHRyckVCY3I0YXlnZ0FTX0dKZ0RNTVFpX1ZxcjF1UFlaMDBNWXBhSngwOXhYUXRwVVZFcW5RbGNYSDd3QjhZX2d5Qnc3bGprX084aTVHdllqSHhQZEpMQ1dXNTBBT2h5VG9UOWpzeWR6eUVoQ2pXSC0?oc=5</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -6797,7 +6797,7 @@
     <row r="124" ht="48" customHeight="1">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>0c3afc561d607c43</t>
+          <t>06470ae82fa46649</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T12:31:08Z</t>
+          <t>2026-10-01T10:05:07Z</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>OnlineKhabar English News</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal - OnlineKhabar English News</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal OnlineKhabar English News</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn?oc=5</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="125" ht="48" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>879d526402f9918a</t>
+          <t>0c3afc561d607c43</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
@@ -6859,32 +6859,32 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T05:29:36Z</t>
+          <t>2026-09-30T12:31:08Z</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>OnlineKhabar English News</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal - Khabarhub</t>
+          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal - OnlineKhabar English News</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal Khabarhub</t>
+          <t>International community keen to support Nepal after Bhotekoshi flood: Foreign Minister Khanal OnlineKhabar English News</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMifEFVX3lxTE1ib1NEZHlSSDhNTjFzTGdFVExNRm1WMUhKOEhqdzBqMGM4bjVUNnVYVlVEQVU1TUdjdUZPSVNsaER6clpqR0xuQm5iRmZ1RG5Tc2cyZmhFNDRYLUNIUFYweUpMQlY3Y1U1Vkh5RnZQNkk3M2tNVEg5dDBfUEU?oc=5</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -6901,7 +6901,7 @@
     <row r="126" ht="48" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>e3676773315ce41e</t>
+          <t>879d526402f9918a</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
@@ -6911,32 +6911,32 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03T23:46:07Z</t>
+          <t>2026-09-30T05:29:36Z</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
+          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal - Khabarhub</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
+          <t>Int’l community keen to help with post-Bhotekoshi flood reconstruction: Foreign Minister Khanal Khabarhub</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE11RHRmQVUxTEhzX3dKd05SeTc3b01QRzBMcHE5eXpwb3pLMFBrUWo3SFNRU09IYm1FMDF1MDVKSzZQZFdQbkhzc0RjNWlHdUxMR01UdVFBSjE?oc=5</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="127" ht="48" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>926f5cba9fb60a4e</t>
+          <t>e3676773315ce41e</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30T20:00:18Z</t>
+          <t>2026-10-03T23:46:07Z</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal - radionepalonline.com</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood - The Himalayan Times</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Nepal strongly raised climate justice and Bhotekoshi flood issues at UNGA: Foreign Affairs Minister Khanal radionepalonline.com</t>
+          <t>Govt plans alternative power supply after Bhotekoshi flood The Himalayan Times</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdGxSRDNleFZIOU9iaHAtTE94ZGhIRmVkVm5DMm1tQlJ5NzY5c2stQnpyc2VLZW5Sb2xtZ0pFQ0ZWY0Y2akFjTzZRQjFoRFlrU2dncldvY1lneVZYWk5hakNPZ01XNm5pX0RtWXNlOGJFaHNjN3VOUk1vTmFiOXlUb0wydTBuWlN2c1ZLclZZOURJTjY0dXhJVkxn0gFcQVVfeXFMUEdnTlJ1eTM2eEV0dkc0SnFQN2l4MkM3RWNjbzJGd3UzaVZWODhPVmVnX1N0czJrVDN1WGtuV0lXYTFFNVZuM3BieTVVQ1ZHTDFBVmtTd3NETjlDZ08?oc=5</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1KanVZUGJEZjVUZkJaQlNBbW52VDMtcUxNTi00eWRXOC1nMnJqcE5fbWNFTkUtUVNPVlR0eEg2Ym1VVDBBWkVrQmw3TzlDZnNhWjc1WTBPNlFpLXlFTmw1QURWWVc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimgFBVV95c